--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs - VENTAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_6B7902D85257D20E62355476585DCE3A87478B38" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71F84C49-F48B-473E-AD58-AB95E1727F94}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_6E3DB7AA5043420F62355476585DCE3A87460B3A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4377BBA1-22CF-440E-AB3E-73169438365E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="74">
   <si>
     <t>Producto</t>
   </si>
@@ -56,6 +56,192 @@
   </si>
   <si>
     <t>% Cumplimiento Puntos</t>
+  </si>
+  <si>
+    <t>POSTPAGO</t>
+  </si>
+  <si>
+    <t>LIDER</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>Sin pago (0%)</t>
+  </si>
+  <si>
+    <t>HOGAR</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>TERMINALES</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t>CVS PLUS</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>27%</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t>Maria Camila Arango VÃ©lez</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>Lider Frontino Cely Ruiz</t>
+  </si>
+  <si>
+    <t>FRONTINO</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>17%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Moreno Durango</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>42%</t>
+  </si>
+  <si>
+    <t>28%</t>
+  </si>
+  <si>
+    <t>Le finalizaron contraro el 11 de junio</t>
+  </si>
+  <si>
+    <t>49%</t>
+  </si>
+  <si>
+    <t>67%</t>
+  </si>
+  <si>
+    <t>Vacaciones del  18 al 06 de julio - se realiza reajuste de meta al CVS</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
+    <t>12%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>Elabora 11 días x vac -  meta puntos 497.3                    meta postp 12</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>meta 3</t>
+  </si>
+  <si>
+    <t>meta 11</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>meta 40</t>
+  </si>
+  <si>
+    <t>meta 286.9</t>
+  </si>
+  <si>
+    <t>32%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>Lider Natalie Bolivar Restrepo</t>
+  </si>
+  <si>
+    <t>CIUDAD BOLIVAR</t>
+  </si>
+  <si>
+    <t>9 Días apoya vacaciones de cajera</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>Leidy Yaneth Galeano Ortiz</t>
+  </si>
+  <si>
+    <t>41%</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>Lider Don Matias Diana Ruiz</t>
+  </si>
+  <si>
+    <t>DON MATIAS</t>
+  </si>
+  <si>
+    <t>Cubre vacaciones de cajera 7 días</t>
+  </si>
+  <si>
+    <t>250%</t>
+  </si>
+  <si>
+    <t>22%</t>
+  </si>
+  <si>
+    <t>38%</t>
+  </si>
+  <si>
+    <t>Evelyn Daniela Lopera Lopera</t>
+  </si>
+  <si>
+    <t>37%</t>
   </si>
 </sst>
 </file>
@@ -74,7 +260,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -419,14 +604,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="59" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,6 +647,1958 @@
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+      <c r="L2">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3">
+        <v>100</v>
+      </c>
+      <c r="L3">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+      <c r="L4">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>69</v>
+      </c>
+      <c r="C5">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+      <c r="L5">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>473</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+      <c r="L6">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+      <c r="L7">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8">
+        <v>100</v>
+      </c>
+      <c r="L8">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>26</v>
+      </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9">
+        <v>100</v>
+      </c>
+      <c r="L9">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>47</v>
+      </c>
+      <c r="C10">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10">
+        <v>100</v>
+      </c>
+      <c r="L10">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>318</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+      <c r="L11">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>59</v>
+      </c>
+      <c r="C14">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14">
+        <v>100</v>
+      </c>
+      <c r="L14">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>104</v>
+      </c>
+      <c r="C15">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>709</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16">
+        <v>100</v>
+      </c>
+      <c r="L16">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>25</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18">
+        <v>100</v>
+      </c>
+      <c r="L18">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>84</v>
+      </c>
+      <c r="C20">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>47</v>
+      </c>
+      <c r="H20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>53</v>
+      </c>
+      <c r="K20">
+        <v>100</v>
+      </c>
+      <c r="L20">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>600</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>54</v>
+      </c>
+      <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22">
+        <v>37</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23">
+        <v>100</v>
+      </c>
+      <c r="L23">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24">
+        <v>36</v>
+      </c>
+      <c r="C24">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24">
+        <v>100</v>
+      </c>
+      <c r="L24">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25">
+        <v>126</v>
+      </c>
+      <c r="C25">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25">
+        <v>100</v>
+      </c>
+      <c r="L25">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26">
+        <v>900</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>56</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+      <c r="L26">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K27">
+        <v>100</v>
+      </c>
+      <c r="L27">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28">
+        <v>100</v>
+      </c>
+      <c r="L28">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>20</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29">
+        <v>100</v>
+      </c>
+      <c r="L29">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30">
+        <v>54</v>
+      </c>
+      <c r="C30">
+        <v>18</v>
+      </c>
+      <c r="D30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31">
+        <v>320</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s">
+        <v>60</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31">
+        <v>100</v>
+      </c>
+      <c r="L31">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E32" t="s">
+        <v>63</v>
+      </c>
+      <c r="F32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" t="s">
+        <v>60</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
+      </c>
+      <c r="L32">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" t="s">
+        <v>60</v>
+      </c>
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+      <c r="L33">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34">
+        <v>30</v>
+      </c>
+      <c r="C34">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" t="s">
+        <v>60</v>
+      </c>
+      <c r="H34" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34">
+        <v>100</v>
+      </c>
+      <c r="L34">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35">
+        <v>81</v>
+      </c>
+      <c r="C35">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
+      <c r="L35">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36">
+        <v>480</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
+      <c r="D37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" t="s">
+        <v>66</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s">
+        <v>67</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>68</v>
+      </c>
+      <c r="K37">
+        <v>100</v>
+      </c>
+      <c r="L37">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s">
+        <v>67</v>
+      </c>
+      <c r="H38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39">
+        <v>18</v>
+      </c>
+      <c r="C39">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40">
+        <v>32</v>
+      </c>
+      <c r="C40">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" t="s">
+        <v>66</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s">
+        <v>67</v>
+      </c>
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40">
+        <v>100</v>
+      </c>
+      <c r="L40">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41">
+        <v>480</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41">
+        <v>100</v>
+      </c>
+      <c r="L41">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42">
+        <v>22</v>
+      </c>
+      <c r="C42">
+        <v>6</v>
+      </c>
+      <c r="D42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" t="s">
+        <v>72</v>
+      </c>
+      <c r="F42" t="s">
+        <v>21</v>
+      </c>
+      <c r="G42" t="s">
+        <v>67</v>
+      </c>
+      <c r="H42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42">
+        <v>100</v>
+      </c>
+      <c r="L42">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+      <c r="K43">
+        <v>100</v>
+      </c>
+      <c r="L43">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44">
+        <v>27</v>
+      </c>
+      <c r="C44">
+        <v>10</v>
+      </c>
+      <c r="D44" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" t="s">
+        <v>72</v>
+      </c>
+      <c r="F44" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" t="s">
+        <v>67</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44">
+        <v>100</v>
+      </c>
+      <c r="L44">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45">
+        <v>48</v>
+      </c>
+      <c r="C45">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+      <c r="L45">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46">
+        <v>720</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" t="s">
+        <v>21</v>
+      </c>
+      <c r="G46" t="s">
+        <v>67</v>
+      </c>
+      <c r="H46" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46">
+        <v>100</v>
+      </c>
+      <c r="L46">
+        <v>29.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47">
+        <v>12</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47" t="s">
+        <v>34</v>
+      </c>
+      <c r="E47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47">
+        <v>100</v>
+      </c>
+      <c r="L47">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48">
+        <v>100</v>
+      </c>
+      <c r="L48">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49">
+        <v>55</v>
+      </c>
+      <c r="C49">
+        <v>23</v>
+      </c>
+      <c r="D49" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49">
+        <v>100</v>
+      </c>
+      <c r="L49">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50">
+        <v>40</v>
+      </c>
+      <c r="C50">
+        <v>11</v>
+      </c>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50">
+        <v>100</v>
+      </c>
+      <c r="L50">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51">
+        <v>750</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" t="s">
+        <v>32</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51">
+        <v>100</v>
+      </c>
+      <c r="L51">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52">
+        <v>12</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>34</v>
+      </c>
+      <c r="E52" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H52" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" t="s">
+        <v>39</v>
+      </c>
+      <c r="K52">
+        <v>100</v>
+      </c>
+      <c r="L52">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" t="s">
+        <v>35</v>
+      </c>
+      <c r="F53" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" t="s">
+        <v>32</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53">
+        <v>100</v>
+      </c>
+      <c r="L53">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54">
+        <v>55</v>
+      </c>
+      <c r="C54">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" t="s">
+        <v>35</v>
+      </c>
+      <c r="F54" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54" t="s">
+        <v>32</v>
+      </c>
+      <c r="H54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54">
+        <v>100</v>
+      </c>
+      <c r="L54">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55">
+        <v>40</v>
+      </c>
+      <c r="C55">
+        <v>20</v>
+      </c>
+      <c r="D55" t="s">
+        <v>36</v>
+      </c>
+      <c r="E55" t="s">
+        <v>35</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" t="s">
+        <v>32</v>
+      </c>
+      <c r="H55" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55">
+        <v>100</v>
+      </c>
+      <c r="L55">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56">
+        <v>750</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" t="s">
+        <v>35</v>
+      </c>
+      <c r="F56" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56">
+        <v>100</v>
+      </c>
+      <c r="L56">
+        <v>27.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs - VENTAS/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs - VENTAS - CONDICIONAL SABA/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_6E3DB7AA5043420F62355476585DCE3A87460B3A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4377BBA1-22CF-440E-AB3E-73169438365E}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_6E3DB7AA5043420F62355476585DCE3A87460B3A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8AF350B-7FAF-4A3A-BBC2-010A2FEAE852}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="84">
   <si>
     <t>Producto</t>
   </si>
@@ -242,24 +242,49 @@
   </si>
   <si>
     <t>37%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>106%</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>Evelis Mary Ojeda Baldovino</t>
+  </si>
+  <si>
+    <t>Se le tiene en cuenta los días que estuvo en Girardota, por en de el total general  no debe de contar esas cantidades para el cumplimiento general</t>
+  </si>
+  <si>
+    <t>114%</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t>96%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -270,7 +295,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -278,30 +303,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -612,40 +619,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2599,6 +2606,534 @@
       </c>
       <c r="L56">
         <v>27.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57">
+        <v>8</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57" t="s">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57">
+        <v>100</v>
+      </c>
+      <c r="L57">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s">
+        <v>75</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58">
+        <v>100</v>
+      </c>
+      <c r="L58">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59">
+        <v>18</v>
+      </c>
+      <c r="C59">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" t="s">
+        <v>75</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59">
+        <v>100</v>
+      </c>
+      <c r="L59">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60">
+        <v>24</v>
+      </c>
+      <c r="C60">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" t="s">
+        <v>74</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" t="s">
+        <v>75</v>
+      </c>
+      <c r="H60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60">
+        <v>100</v>
+      </c>
+      <c r="L60">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61">
+        <v>375</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" t="s">
+        <v>74</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61">
+        <v>100</v>
+      </c>
+      <c r="L61">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62">
+        <v>11</v>
+      </c>
+      <c r="C62">
+        <v>7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>33</v>
+      </c>
+      <c r="E62" t="s">
+        <v>78</v>
+      </c>
+      <c r="F62" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" t="s">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" t="s">
+        <v>79</v>
+      </c>
+      <c r="K62">
+        <v>100</v>
+      </c>
+      <c r="L62">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>36</v>
+      </c>
+      <c r="E63" t="s">
+        <v>78</v>
+      </c>
+      <c r="F63" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" t="s">
+        <v>75</v>
+      </c>
+      <c r="H63" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" t="s">
+        <v>15</v>
+      </c>
+      <c r="K63">
+        <v>100</v>
+      </c>
+      <c r="L63">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64">
+        <v>27</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
+      </c>
+      <c r="D64" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" t="s">
+        <v>78</v>
+      </c>
+      <c r="F64" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" t="s">
+        <v>75</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64">
+        <v>100</v>
+      </c>
+      <c r="L64">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65">
+        <v>36</v>
+      </c>
+      <c r="C65">
+        <v>41</v>
+      </c>
+      <c r="D65" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65" t="s">
+        <v>78</v>
+      </c>
+      <c r="F65" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" t="s">
+        <v>75</v>
+      </c>
+      <c r="H65" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65">
+        <v>100</v>
+      </c>
+      <c r="L65">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66">
+        <v>563</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" t="s">
+        <v>78</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" t="s">
+        <v>75</v>
+      </c>
+      <c r="H66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66">
+        <v>100</v>
+      </c>
+      <c r="L66">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67">
+        <v>11</v>
+      </c>
+      <c r="C67">
+        <v>8</v>
+      </c>
+      <c r="D67" t="s">
+        <v>81</v>
+      </c>
+      <c r="E67" t="s">
+        <v>82</v>
+      </c>
+      <c r="F67" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" t="s">
+        <v>75</v>
+      </c>
+      <c r="H67" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67">
+        <v>100</v>
+      </c>
+      <c r="L67">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" t="s">
+        <v>82</v>
+      </c>
+      <c r="F68" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68" t="s">
+        <v>75</v>
+      </c>
+      <c r="H68" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" t="s">
+        <v>15</v>
+      </c>
+      <c r="K68">
+        <v>100</v>
+      </c>
+      <c r="L68">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>27</v>
+      </c>
+      <c r="C69">
+        <v>26</v>
+      </c>
+      <c r="D69" t="s">
+        <v>83</v>
+      </c>
+      <c r="E69" t="s">
+        <v>82</v>
+      </c>
+      <c r="F69" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" t="s">
+        <v>75</v>
+      </c>
+      <c r="H69" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" t="s">
+        <v>15</v>
+      </c>
+      <c r="K69">
+        <v>100</v>
+      </c>
+      <c r="L69">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70">
+        <v>36</v>
+      </c>
+      <c r="C70">
+        <v>34</v>
+      </c>
+      <c r="D70" t="s">
+        <v>43</v>
+      </c>
+      <c r="E70" t="s">
+        <v>82</v>
+      </c>
+      <c r="F70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70">
+        <v>100</v>
+      </c>
+      <c r="L70">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71">
+        <v>563</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" t="s">
+        <v>82</v>
+      </c>
+      <c r="F71" t="s">
+        <v>21</v>
+      </c>
+      <c r="G71" t="s">
+        <v>75</v>
+      </c>
+      <c r="H71" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71">
+        <v>100</v>
+      </c>
+      <c r="L71">
+        <v>78.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs - VENTAS - CONDICIONAL SABA/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_6E3DB7AA5043420F62355476585DCE3A87460B3A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8AF350B-7FAF-4A3A-BBC2-010A2FEAE852}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_77DDB655914D040E62355476585DCE3A87458B1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="199">
   <si>
     <t>Producto</t>
   </si>
@@ -61,15 +61,27 @@
     <t>POSTPAGO</t>
   </si>
   <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>Lider Natalie Bolivar Restrepo</t>
+  </si>
+  <si>
     <t>LIDER</t>
   </si>
   <si>
+    <t>CIUDAD BOLIVAR</t>
+  </si>
+  <si>
     <t>2026-06</t>
   </si>
   <si>
     <t>Sin pago (0%)</t>
   </si>
   <si>
+    <t>9 Días apoya vacaciones de cajera</t>
+  </si>
+  <si>
     <t>HOGAR</t>
   </si>
   <si>
@@ -79,19 +91,499 @@
     <t>TERMINALES</t>
   </si>
   <si>
+    <t>15%</t>
+  </si>
+  <si>
     <t>OTROS</t>
   </si>
   <si>
+    <t>33%</t>
+  </si>
+  <si>
     <t>CVS PLUS</t>
   </si>
   <si>
+    <t>Leidy Yaneth Galeano Ortiz</t>
+  </si>
+  <si>
     <t>ASESOR</t>
   </si>
   <si>
     <t>27%</t>
   </si>
   <si>
-    <t>71%</t>
+    <t>41%</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>Lider Don Matias Diana Ruiz</t>
+  </si>
+  <si>
+    <t>DON MATIAS</t>
+  </si>
+  <si>
+    <t>Cubre vacaciones de cajera 7 días</t>
+  </si>
+  <si>
+    <t>250%</t>
+  </si>
+  <si>
+    <t>22%</t>
+  </si>
+  <si>
+    <t>38%</t>
+  </si>
+  <si>
+    <t>Evelyn Daniela Lopera Lopera</t>
+  </si>
+  <si>
+    <t>37%</t>
+  </si>
+  <si>
+    <t>146%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>159%</t>
+  </si>
+  <si>
+    <t>43%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Taborda Ruiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elabora 7 días x VAC  - meta puntos  630.7     meta post 13 </t>
+  </si>
+  <si>
+    <t>Meta hogar 2</t>
+  </si>
+  <si>
+    <t>Meta terminales 20</t>
+  </si>
+  <si>
+    <t>Meta otros 42</t>
+  </si>
+  <si>
+    <t>CVS 139</t>
+  </si>
+  <si>
+    <t>116%</t>
+  </si>
+  <si>
+    <t>Jessica Catherine Gutierrez Garcia</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>85%</t>
+  </si>
+  <si>
+    <t>108%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>110%</t>
+  </si>
+  <si>
+    <t>93%</t>
+  </si>
+  <si>
+    <t>3%</t>
+  </si>
+  <si>
+    <t>Johan Daniel Herrera Mazo</t>
+  </si>
+  <si>
+    <t>SUPERNUMERARIO</t>
+  </si>
+  <si>
+    <t>1 día Líder meta puntos 591.3   meta post 1</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>meta 3</t>
+  </si>
+  <si>
+    <t>meta 5</t>
+  </si>
+  <si>
+    <t>57%</t>
+  </si>
+  <si>
+    <t>Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>15 días, asesora meta puntos 1.182,5   meta post 24</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>Meta Hogar  3</t>
+  </si>
+  <si>
+    <t>69%</t>
+  </si>
+  <si>
+    <t>Meta Terminales 38</t>
+  </si>
+  <si>
+    <t>46%</t>
+  </si>
+  <si>
+    <t>Meta Otros 78</t>
+  </si>
+  <si>
+    <t>cvs plus 261</t>
+  </si>
+  <si>
+    <t>113%</t>
+  </si>
+  <si>
+    <t>Lider Paula Andrea Cano Monsalve</t>
+  </si>
+  <si>
+    <t>SAN CRISTOBAL</t>
+  </si>
+  <si>
+    <t>87%</t>
+  </si>
+  <si>
+    <t>83%</t>
+  </si>
+  <si>
+    <t>1 día, entrega el punto</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>Lider Girardota Paulina Andrea Zapata Jimenez</t>
+  </si>
+  <si>
+    <t>GIRARDOTA</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>95%</t>
+  </si>
+  <si>
+    <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>Apoyo 1 día</t>
+  </si>
+  <si>
+    <t>1 día líder</t>
+  </si>
+  <si>
+    <t>217%</t>
+  </si>
+  <si>
+    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
+  </si>
+  <si>
+    <t>DABEIBA</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>221%</t>
+  </si>
+  <si>
+    <t>Estelli Alejandra Ramirez Florez</t>
+  </si>
+  <si>
+    <t>12 días x vac meta puntos 453.9       meta post  5</t>
+  </si>
+  <si>
+    <t>meta terminales 16</t>
+  </si>
+  <si>
+    <t>meta otros 19</t>
+  </si>
+  <si>
+    <t>117%</t>
+  </si>
+  <si>
+    <t>Lider Frontino Cely Ruiz</t>
+  </si>
+  <si>
+    <t>FRONTINO</t>
+  </si>
+  <si>
+    <t>122%</t>
+  </si>
+  <si>
+    <t>17%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Moreno Durango</t>
+  </si>
+  <si>
+    <t>Le finalizaron contraro el 11 de junio</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>Yeilisa Fernanda Higuita David</t>
+  </si>
+  <si>
+    <t>mes de gracia</t>
+  </si>
+  <si>
+    <t>45%</t>
+  </si>
+  <si>
+    <t>169%</t>
+  </si>
+  <si>
+    <t>Lider Marcela Valencia Tabares</t>
+  </si>
+  <si>
+    <t>ITAGUI</t>
+  </si>
+  <si>
+    <t>67%</t>
+  </si>
+  <si>
+    <t>105%</t>
+  </si>
+  <si>
+    <t>147%</t>
+  </si>
+  <si>
+    <t>Dailyn Del Valle Alvarez Rueda</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>142%</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Posada Galeano</t>
+  </si>
+  <si>
+    <t>Mes de gracia hasta el 15 de junio</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>133%</t>
+  </si>
+  <si>
+    <t>Evelis Mary Ojeda Baldovino</t>
+  </si>
+  <si>
+    <t>Se le tiene en cuenta los días que estuvo en Girardota, por en de el total general  no debe de contar esas cantidades para el cumplimiento general</t>
+  </si>
+  <si>
+    <t>Mes de gracia</t>
+  </si>
+  <si>
+    <t>189%</t>
+  </si>
+  <si>
+    <t>136%</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t>153%</t>
+  </si>
+  <si>
+    <t>Lider Jhon Alejandro Cardona Quintero</t>
+  </si>
+  <si>
+    <t>LA ESTRELLA</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>107%</t>
+  </si>
+  <si>
+    <t>11%</t>
+  </si>
+  <si>
+    <t>1 día lider   meta puntos 26  meta postp 1</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>meta 1</t>
+  </si>
+  <si>
+    <t>16%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>Elabora 11 días x vac -  meta puntos 497.3                    meta postp 12</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>meta 11</t>
+  </si>
+  <si>
+    <t>meta 40</t>
+  </si>
+  <si>
+    <t>meta 286.9</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>125%</t>
+  </si>
+  <si>
+    <t>106%</t>
+  </si>
+  <si>
+    <t>104%</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>14 días líder   meta puntos 633   meta postp  15</t>
+  </si>
+  <si>
+    <t>Meta hogar 5</t>
+  </si>
+  <si>
+    <t>14%</t>
+  </si>
+  <si>
+    <t>Meta terminales  15</t>
+  </si>
+  <si>
+    <t>Meta otros 51</t>
+  </si>
+  <si>
+    <t>Meta 366</t>
+  </si>
+  <si>
+    <t>Tatiana  Guerra Gonzalez</t>
+  </si>
+  <si>
+    <t>CAUCASIA</t>
+  </si>
+  <si>
+    <t>72%</t>
+  </si>
+  <si>
+    <t>12%</t>
+  </si>
+  <si>
+    <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>1 día líder  meta puntos 43</t>
+  </si>
+  <si>
+    <t>157%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 días x vac Meta puntos 921.7   meta postpago </t>
+  </si>
+  <si>
+    <t>meta Hogar 1</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>Meta terminales  24</t>
+  </si>
+  <si>
+    <t>Meta otros 19</t>
+  </si>
+  <si>
+    <t>114%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
+    <t>1 día asesor  meta puntos 69</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>3 días líder meta puntos 345.6        meta postpago  2</t>
+  </si>
+  <si>
+    <t>Meta terminales 4</t>
+  </si>
+  <si>
+    <t>Meta otros 7</t>
   </si>
   <si>
     <t>Lider Yolima Mesa Zapata</t>
@@ -100,191 +592,50 @@
     <t>CALDAS</t>
   </si>
   <si>
-    <t>63%</t>
+    <t>267%</t>
+  </si>
+  <si>
+    <t>168%</t>
   </si>
   <si>
     <t>Johnson AndrÃ©s Gutierrez Escobar</t>
   </si>
   <si>
+    <t>Vacaciones del  18 al 06 de julio - se realiza reajuste de meta al CVS</t>
+  </si>
+  <si>
+    <t>300%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>70%</t>
+  </si>
+  <si>
     <t>Maria Camila Arango VÃ©lez</t>
   </si>
   <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>Lider Frontino Cely Ruiz</t>
-  </si>
-  <si>
-    <t>FRONTINO</t>
-  </si>
-  <si>
-    <t>64%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>Diana Marcela Moreno Durango</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>42%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>Le finalizaron contraro el 11 de junio</t>
-  </si>
-  <si>
-    <t>49%</t>
-  </si>
-  <si>
-    <t>67%</t>
-  </si>
-  <si>
-    <t>Vacaciones del  18 al 06 de julio - se realiza reajuste de meta al CVS</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Arbelaez</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>Elabora 11 días x vac -  meta puntos 497.3                    meta postp 12</t>
-  </si>
-  <si>
-    <t>36%</t>
-  </si>
-  <si>
-    <t>meta 3</t>
-  </si>
-  <si>
-    <t>meta 11</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>meta 40</t>
-  </si>
-  <si>
-    <t>meta 286.9</t>
-  </si>
-  <si>
-    <t>32%</t>
-  </si>
-  <si>
-    <t>Andrea  Arenas Hurtado</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>44%</t>
-  </si>
-  <si>
-    <t>Lider Natalie Bolivar Restrepo</t>
-  </si>
-  <si>
-    <t>CIUDAD BOLIVAR</t>
-  </si>
-  <si>
-    <t>9 Días apoya vacaciones de cajera</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>Leidy Yaneth Galeano Ortiz</t>
-  </si>
-  <si>
-    <t>41%</t>
-  </si>
-  <si>
-    <t>61%</t>
-  </si>
-  <si>
-    <t>Lider Don Matias Diana Ruiz</t>
-  </si>
-  <si>
-    <t>DON MATIAS</t>
-  </si>
-  <si>
-    <t>Cubre vacaciones de cajera 7 días</t>
-  </si>
-  <si>
-    <t>250%</t>
-  </si>
-  <si>
-    <t>22%</t>
-  </si>
-  <si>
-    <t>38%</t>
-  </si>
-  <si>
-    <t>Evelyn Daniela Lopera Lopera</t>
-  </si>
-  <si>
-    <t>37%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
-  </si>
-  <si>
-    <t>BARBOSA</t>
-  </si>
-  <si>
-    <t>106%</t>
-  </si>
-  <si>
     <t>79%</t>
-  </si>
-  <si>
-    <t>Evelis Mary Ojeda Baldovino</t>
-  </si>
-  <si>
-    <t>Se le tiene en cuenta los días que estuvo en Girardota, por en de el total general  no debe de contar esas cantidades para el cumplimiento general</t>
-  </si>
-  <si>
-    <t>114%</t>
-  </si>
-  <si>
-    <t>73%</t>
-  </si>
-  <si>
-    <t>Sene Del Socorro Suarez Torres</t>
-  </si>
-  <si>
-    <t>96%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -295,7 +646,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -303,12 +654,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,48 +980,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L216"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="59" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -661,174 +1026,177 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
       </c>
       <c r="K2">
         <v>100</v>
       </c>
       <c r="L2">
-        <v>26.8</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K3">
         <v>100</v>
       </c>
       <c r="L3">
-        <v>26.8</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B4">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K4">
         <v>100</v>
       </c>
       <c r="L4">
-        <v>26.8</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C5">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K5">
         <v>100</v>
       </c>
       <c r="L5">
-        <v>26.8</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B6">
-        <v>473</v>
+        <v>320</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>26.8</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -839,174 +1207,171 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K7">
         <v>100</v>
       </c>
       <c r="L7">
-        <v>72.3</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>72.3</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>72.3</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>72.3</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>318</v>
+        <v>480</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
         <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>72.3</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1014,174 +1379,177 @@
         <v>12</v>
       </c>
       <c r="B12">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s">
         <v>33</v>
       </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>34</v>
       </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>17.100000000000001</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>17.100000000000001</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B14">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>17.100000000000001</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B15">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="C15">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>17.100000000000001</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B16">
-        <v>709</v>
+        <v>480</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>17.100000000000001</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1189,189 +1557,174 @@
         <v>12</v>
       </c>
       <c r="B17">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>23.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G18" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>23.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>23.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B20">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C20">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G20" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>23.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B21">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="K21">
         <v>100</v>
       </c>
       <c r="L21">
-        <v>23.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1379,174 +1732,174 @@
         <v>12</v>
       </c>
       <c r="B22">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
-        <v>38.4</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>38.4</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C24">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>38.4</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C25">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E25" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>38.4</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B26">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>38.4</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1554,177 +1907,189 @@
         <v>12</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>16.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
+        <v>49</v>
       </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>16.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B29">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H29" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J29" t="s">
+        <v>50</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>16.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B30">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="C30">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J30" t="s">
+        <v>51</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>16.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B31">
-        <v>320</v>
+        <v>399</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H31" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J31" t="s">
+        <v>52</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>16.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -1732,174 +2097,174 @@
         <v>12</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F32" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>28.3</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F33" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H33" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>28.3</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B34">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G34" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H34" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K34">
         <v>100</v>
       </c>
       <c r="L34">
-        <v>28.3</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B35">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C35">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E35" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F35" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H35" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>28.3</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B36">
-        <v>480</v>
+        <v>399</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F36" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H36" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K36">
         <v>100</v>
       </c>
       <c r="L36">
-        <v>28.3</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -1907,177 +2272,174 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C37">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G37" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H37" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>15</v>
-      </c>
-      <c r="J37" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>34.1</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G38" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H38" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K38">
         <v>100</v>
       </c>
       <c r="L38">
-        <v>34.1</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B39">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G39" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H39" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K39">
         <v>100</v>
       </c>
       <c r="L39">
-        <v>34.1</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B40">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G40" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H40" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K40">
         <v>100</v>
       </c>
       <c r="L40">
-        <v>34.1</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B41">
-        <v>480</v>
+        <v>399</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G41" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H41" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K41">
         <v>100</v>
       </c>
       <c r="L41">
-        <v>34.1</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2085,174 +2447,183 @@
         <v>12</v>
       </c>
       <c r="B42">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G42" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H42" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J42" t="s">
+        <v>64</v>
       </c>
       <c r="K42">
         <v>100</v>
       </c>
       <c r="L42">
-        <v>29.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F43" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G43" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H43" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K43">
         <v>100</v>
       </c>
       <c r="L43">
-        <v>29.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B44">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C44">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E44" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F44" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G44" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H44" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J44" t="s">
+        <v>66</v>
       </c>
       <c r="K44">
         <v>100</v>
       </c>
       <c r="L44">
-        <v>29.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B45">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="C45">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D45" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" t="s">
         <v>62</v>
       </c>
-      <c r="E45" t="s">
-        <v>72</v>
-      </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G45" t="s">
+        <v>42</v>
+      </c>
+      <c r="H45" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" t="s">
         <v>67</v>
       </c>
-      <c r="H45" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" t="s">
-        <v>15</v>
-      </c>
       <c r="K45">
         <v>100</v>
       </c>
       <c r="L45">
-        <v>29.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B46">
-        <v>720</v>
+        <v>399</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F46" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G46" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="H46" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K46">
         <v>100</v>
       </c>
       <c r="L46">
-        <v>29.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2260,174 +2631,189 @@
         <v>12</v>
       </c>
       <c r="B47">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E47" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G47" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H47" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J47" t="s">
+        <v>70</v>
       </c>
       <c r="K47">
         <v>100</v>
       </c>
       <c r="L47">
-        <v>40</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H48" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J48" t="s">
+        <v>72</v>
       </c>
       <c r="K48">
         <v>100</v>
       </c>
       <c r="L48">
-        <v>40</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B49">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C49">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D49" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G49" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H49" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J49" t="s">
+        <v>74</v>
       </c>
       <c r="K49">
         <v>100</v>
       </c>
       <c r="L49">
-        <v>40</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B50">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="C50">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G50" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H50" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I50" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J50" t="s">
+        <v>76</v>
       </c>
       <c r="K50">
         <v>100</v>
       </c>
       <c r="L50">
-        <v>40</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B51">
-        <v>750</v>
+        <v>399</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G51" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H51" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J51" t="s">
+        <v>77</v>
       </c>
       <c r="K51">
         <v>100</v>
       </c>
       <c r="L51">
-        <v>40</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2435,177 +2821,174 @@
         <v>12</v>
       </c>
       <c r="B52">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I52" t="s">
-        <v>15</v>
-      </c>
-      <c r="J52" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="K52">
         <v>100</v>
       </c>
       <c r="L52">
-        <v>27.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K53">
         <v>100</v>
       </c>
       <c r="L53">
-        <v>27.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B54">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C54">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F54" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K54">
         <v>100</v>
       </c>
       <c r="L54">
-        <v>27.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B55">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C55">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K55">
         <v>100</v>
       </c>
       <c r="L55">
-        <v>27.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B56">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F56" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I56" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K56">
         <v>100</v>
       </c>
       <c r="L56">
-        <v>27.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -2613,174 +2996,177 @@
         <v>12</v>
       </c>
       <c r="B57">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="E57" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G57" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J57" t="s">
+        <v>83</v>
       </c>
       <c r="K57">
         <v>100</v>
       </c>
       <c r="L57">
-        <v>87.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G58" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K58">
         <v>100</v>
       </c>
       <c r="L58">
-        <v>87.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B59">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C59">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E59" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G59" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I59" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K59">
         <v>100</v>
       </c>
       <c r="L59">
-        <v>87.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B60">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="C60">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="E60" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G60" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K60">
         <v>100</v>
       </c>
       <c r="L60">
-        <v>87.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B61">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E61" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G61" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K61">
         <v>100</v>
       </c>
       <c r="L61">
-        <v>87.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2788,177 +3174,174 @@
         <v>12</v>
       </c>
       <c r="B62">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="E62" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F62" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>15</v>
-      </c>
-      <c r="J62" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="K62">
         <v>100</v>
       </c>
       <c r="L62">
-        <v>48.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E63" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F63" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H63" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I63" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K63">
         <v>100</v>
       </c>
       <c r="L63">
-        <v>48.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B64">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E64" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F64" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I64" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K64">
         <v>100</v>
       </c>
       <c r="L64">
-        <v>48.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B65">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C65">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="E65" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F65" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H65" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K65">
         <v>100</v>
       </c>
       <c r="L65">
-        <v>48.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B66">
-        <v>563</v>
+        <v>480</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F66" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K66">
         <v>100</v>
       </c>
       <c r="L66">
-        <v>48.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -2966,174 +3349,5351 @@
         <v>12</v>
       </c>
       <c r="B67">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F67" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G67" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K67">
         <v>100</v>
       </c>
       <c r="L67">
-        <v>78.8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="E68" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F68" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G68" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K68">
         <v>100</v>
       </c>
       <c r="L68">
-        <v>78.8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B69">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C69">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D69" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E69" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F69" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G69" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K69">
         <v>100</v>
       </c>
       <c r="L69">
-        <v>78.8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B70">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C70">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E70" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F70" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G70" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="H70" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K70">
         <v>100</v>
       </c>
       <c r="L70">
-        <v>78.8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>26</v>
+      </c>
+      <c r="B71">
+        <v>720</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" t="s">
+        <v>89</v>
+      </c>
+      <c r="F71" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" t="s">
+        <v>86</v>
+      </c>
+      <c r="H71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" t="s">
+        <v>18</v>
+      </c>
+      <c r="K71">
+        <v>100</v>
+      </c>
+      <c r="L71">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72">
+        <v>21</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" t="s">
+        <v>62</v>
+      </c>
+      <c r="F72" t="s">
+        <v>63</v>
+      </c>
+      <c r="G72" t="s">
+        <v>86</v>
+      </c>
+      <c r="H72" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J72" t="s">
+        <v>92</v>
+      </c>
+      <c r="K72">
+        <v>100</v>
+      </c>
+      <c r="L72">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>20</v>
       </c>
-      <c r="B71">
+      <c r="B73">
+        <v>5</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" t="s">
+        <v>62</v>
+      </c>
+      <c r="F73" t="s">
+        <v>63</v>
+      </c>
+      <c r="G73" t="s">
+        <v>86</v>
+      </c>
+      <c r="H73" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" t="s">
+        <v>18</v>
+      </c>
+      <c r="K73">
+        <v>100</v>
+      </c>
+      <c r="L73">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74">
+        <v>30</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" t="s">
+        <v>62</v>
+      </c>
+      <c r="F74" t="s">
+        <v>63</v>
+      </c>
+      <c r="G74" t="s">
+        <v>86</v>
+      </c>
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" t="s">
+        <v>18</v>
+      </c>
+      <c r="K74">
+        <v>100</v>
+      </c>
+      <c r="L74">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75">
+        <v>78</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" t="s">
+        <v>62</v>
+      </c>
+      <c r="F75" t="s">
+        <v>63</v>
+      </c>
+      <c r="G75" t="s">
+        <v>86</v>
+      </c>
+      <c r="H75" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" t="s">
+        <v>18</v>
+      </c>
+      <c r="K75">
+        <v>100</v>
+      </c>
+      <c r="L75">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>26</v>
+      </c>
+      <c r="B76">
+        <v>720</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" t="s">
+        <v>62</v>
+      </c>
+      <c r="F76" t="s">
+        <v>63</v>
+      </c>
+      <c r="G76" t="s">
+        <v>86</v>
+      </c>
+      <c r="H76" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" t="s">
+        <v>18</v>
+      </c>
+      <c r="K76">
+        <v>100</v>
+      </c>
+      <c r="L76">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77">
+        <v>21</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77" t="s">
+        <v>69</v>
+      </c>
+      <c r="F77" t="s">
+        <v>63</v>
+      </c>
+      <c r="G77" t="s">
+        <v>86</v>
+      </c>
+      <c r="H77" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" t="s">
+        <v>18</v>
+      </c>
+      <c r="J77" t="s">
+        <v>93</v>
+      </c>
+      <c r="K77">
+        <v>100</v>
+      </c>
+      <c r="L77">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78" t="s">
+        <v>21</v>
+      </c>
+      <c r="E78" t="s">
+        <v>69</v>
+      </c>
+      <c r="F78" t="s">
+        <v>63</v>
+      </c>
+      <c r="G78" t="s">
+        <v>86</v>
+      </c>
+      <c r="H78" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" t="s">
+        <v>18</v>
+      </c>
+      <c r="K78">
+        <v>100</v>
+      </c>
+      <c r="L78">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79">
+        <v>30</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79" t="s">
+        <v>21</v>
+      </c>
+      <c r="E79" t="s">
+        <v>69</v>
+      </c>
+      <c r="F79" t="s">
+        <v>63</v>
+      </c>
+      <c r="G79" t="s">
+        <v>86</v>
+      </c>
+      <c r="H79" t="s">
+        <v>17</v>
+      </c>
+      <c r="I79" t="s">
+        <v>18</v>
+      </c>
+      <c r="K79">
+        <v>100</v>
+      </c>
+      <c r="L79">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80">
+        <v>78</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80" t="s">
+        <v>21</v>
+      </c>
+      <c r="E80" t="s">
+        <v>69</v>
+      </c>
+      <c r="F80" t="s">
+        <v>63</v>
+      </c>
+      <c r="G80" t="s">
+        <v>86</v>
+      </c>
+      <c r="H80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80" t="s">
+        <v>18</v>
+      </c>
+      <c r="K80">
+        <v>100</v>
+      </c>
+      <c r="L80">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>26</v>
+      </c>
+      <c r="B81">
+        <v>720</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81" t="s">
+        <v>21</v>
+      </c>
+      <c r="E81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F81" t="s">
+        <v>63</v>
+      </c>
+      <c r="G81" t="s">
+        <v>86</v>
+      </c>
+      <c r="H81" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" t="s">
+        <v>18</v>
+      </c>
+      <c r="K81">
+        <v>100</v>
+      </c>
+      <c r="L81">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82">
+        <v>6</v>
+      </c>
+      <c r="C82">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>94</v>
+      </c>
+      <c r="E82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F82" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" t="s">
+        <v>96</v>
+      </c>
+      <c r="H82" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82" t="s">
+        <v>18</v>
+      </c>
+      <c r="K82">
+        <v>100</v>
+      </c>
+      <c r="L82">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>20</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83" t="s">
+        <v>21</v>
+      </c>
+      <c r="E83" t="s">
+        <v>95</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s">
+        <v>96</v>
+      </c>
+      <c r="H83" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" t="s">
+        <v>18</v>
+      </c>
+      <c r="K83">
+        <v>100</v>
+      </c>
+      <c r="L83">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84">
+        <v>20</v>
+      </c>
+      <c r="C84">
+        <v>24</v>
+      </c>
+      <c r="D84" t="s">
+        <v>97</v>
+      </c>
+      <c r="E84" t="s">
+        <v>95</v>
+      </c>
+      <c r="F84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" t="s">
+        <v>96</v>
+      </c>
+      <c r="H84" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84" t="s">
+        <v>18</v>
+      </c>
+      <c r="K84">
+        <v>100</v>
+      </c>
+      <c r="L84">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>24</v>
+      </c>
+      <c r="B85">
+        <v>24</v>
+      </c>
+      <c r="C85">
+        <v>53</v>
+      </c>
+      <c r="D85" t="s">
+        <v>98</v>
+      </c>
+      <c r="E85" t="s">
+        <v>95</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
+        <v>96</v>
+      </c>
+      <c r="H85" t="s">
+        <v>17</v>
+      </c>
+      <c r="I85" t="s">
+        <v>18</v>
+      </c>
+      <c r="K85">
+        <v>100</v>
+      </c>
+      <c r="L85">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>26</v>
+      </c>
+      <c r="B86">
+        <v>480</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86" t="s">
+        <v>21</v>
+      </c>
+      <c r="E86" t="s">
+        <v>95</v>
+      </c>
+      <c r="F86" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" t="s">
+        <v>96</v>
+      </c>
+      <c r="H86" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86" t="s">
+        <v>18</v>
+      </c>
+      <c r="K86">
+        <v>100</v>
+      </c>
+      <c r="L86">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B87">
+        <v>9</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87" t="s">
+        <v>36</v>
+      </c>
+      <c r="E87" t="s">
+        <v>99</v>
+      </c>
+      <c r="F87" t="s">
+        <v>28</v>
+      </c>
+      <c r="G87" t="s">
+        <v>96</v>
+      </c>
+      <c r="H87" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" t="s">
+        <v>100</v>
+      </c>
+      <c r="K87">
+        <v>100</v>
+      </c>
+      <c r="L87">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>20</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88" t="s">
+        <v>21</v>
+      </c>
+      <c r="E88" t="s">
+        <v>99</v>
+      </c>
+      <c r="F88" t="s">
+        <v>28</v>
+      </c>
+      <c r="G88" t="s">
+        <v>96</v>
+      </c>
+      <c r="H88" t="s">
+        <v>17</v>
+      </c>
+      <c r="I88" t="s">
+        <v>18</v>
+      </c>
+      <c r="K88">
+        <v>100</v>
+      </c>
+      <c r="L88">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89">
+        <v>30</v>
+      </c>
+      <c r="C89">
+        <v>13</v>
+      </c>
+      <c r="D89" t="s">
+        <v>46</v>
+      </c>
+      <c r="E89" t="s">
+        <v>99</v>
+      </c>
+      <c r="F89" t="s">
+        <v>28</v>
+      </c>
+      <c r="G89" t="s">
+        <v>96</v>
+      </c>
+      <c r="H89" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" t="s">
+        <v>101</v>
+      </c>
+      <c r="K89">
+        <v>100</v>
+      </c>
+      <c r="L89">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>24</v>
+      </c>
+      <c r="B90">
+        <v>36</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90" t="s">
+        <v>21</v>
+      </c>
+      <c r="E90" t="s">
+        <v>99</v>
+      </c>
+      <c r="F90" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" t="s">
+        <v>96</v>
+      </c>
+      <c r="H90" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" t="s">
+        <v>102</v>
+      </c>
+      <c r="K90">
+        <v>100</v>
+      </c>
+      <c r="L90">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>26</v>
+      </c>
+      <c r="B91">
+        <v>720</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91" t="s">
+        <v>21</v>
+      </c>
+      <c r="E91" t="s">
+        <v>99</v>
+      </c>
+      <c r="F91" t="s">
+        <v>28</v>
+      </c>
+      <c r="G91" t="s">
+        <v>96</v>
+      </c>
+      <c r="H91" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" t="s">
+        <v>18</v>
+      </c>
+      <c r="K91">
+        <v>100</v>
+      </c>
+      <c r="L91">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92">
+        <v>12</v>
+      </c>
+      <c r="C92">
+        <v>14</v>
+      </c>
+      <c r="D92" t="s">
+        <v>103</v>
+      </c>
+      <c r="E92" t="s">
+        <v>104</v>
+      </c>
+      <c r="F92" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" t="s">
+        <v>105</v>
+      </c>
+      <c r="H92" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92" t="s">
+        <v>18</v>
+      </c>
+      <c r="K92">
+        <v>100</v>
+      </c>
+      <c r="L92">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>20</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93" t="s">
+        <v>21</v>
+      </c>
+      <c r="E93" t="s">
+        <v>104</v>
+      </c>
+      <c r="F93" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" t="s">
+        <v>105</v>
+      </c>
+      <c r="H93" t="s">
+        <v>17</v>
+      </c>
+      <c r="I93" t="s">
+        <v>18</v>
+      </c>
+      <c r="K93">
+        <v>100</v>
+      </c>
+      <c r="L93">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94">
+        <v>55</v>
+      </c>
+      <c r="C94">
+        <v>67</v>
+      </c>
+      <c r="D94" t="s">
+        <v>106</v>
+      </c>
+      <c r="E94" t="s">
+        <v>104</v>
+      </c>
+      <c r="F94" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" t="s">
+        <v>105</v>
+      </c>
+      <c r="H94" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" t="s">
+        <v>18</v>
+      </c>
+      <c r="K94">
+        <v>100</v>
+      </c>
+      <c r="L94">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95">
+        <v>40</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95" t="s">
+        <v>21</v>
+      </c>
+      <c r="E95" t="s">
+        <v>104</v>
+      </c>
+      <c r="F95" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95" t="s">
+        <v>105</v>
+      </c>
+      <c r="H95" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95">
+        <v>100</v>
+      </c>
+      <c r="L95">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>26</v>
+      </c>
+      <c r="B96">
+        <v>750</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" t="s">
+        <v>104</v>
+      </c>
+      <c r="F96" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" t="s">
+        <v>105</v>
+      </c>
+      <c r="H96" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96">
+        <v>100</v>
+      </c>
+      <c r="L96">
+        <v>125.8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97">
+        <v>12</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97" t="s">
+        <v>107</v>
+      </c>
+      <c r="E97" t="s">
+        <v>108</v>
+      </c>
+      <c r="F97" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" t="s">
+        <v>105</v>
+      </c>
+      <c r="H97" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97" t="s">
+        <v>18</v>
+      </c>
+      <c r="J97" t="s">
+        <v>109</v>
+      </c>
+      <c r="K97">
+        <v>100</v>
+      </c>
+      <c r="L97">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>20</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98" t="s">
+        <v>21</v>
+      </c>
+      <c r="E98" t="s">
+        <v>108</v>
+      </c>
+      <c r="F98" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" t="s">
+        <v>105</v>
+      </c>
+      <c r="H98" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" t="s">
+        <v>18</v>
+      </c>
+      <c r="K98">
+        <v>100</v>
+      </c>
+      <c r="L98">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99">
+        <v>55</v>
+      </c>
+      <c r="C99">
+        <v>13</v>
+      </c>
+      <c r="D99" t="s">
+        <v>110</v>
+      </c>
+      <c r="E99" t="s">
+        <v>108</v>
+      </c>
+      <c r="F99" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" t="s">
+        <v>105</v>
+      </c>
+      <c r="H99" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" t="s">
+        <v>18</v>
+      </c>
+      <c r="K99">
+        <v>100</v>
+      </c>
+      <c r="L99">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100">
+        <v>40</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100" t="s">
+        <v>21</v>
+      </c>
+      <c r="E100" t="s">
+        <v>108</v>
+      </c>
+      <c r="F100" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" t="s">
+        <v>105</v>
+      </c>
+      <c r="H100" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100">
+        <v>100</v>
+      </c>
+      <c r="L100">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>26</v>
+      </c>
+      <c r="B101">
+        <v>750</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" t="s">
+        <v>108</v>
+      </c>
+      <c r="F101" t="s">
+        <v>28</v>
+      </c>
+      <c r="G101" t="s">
+        <v>105</v>
+      </c>
+      <c r="H101" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" t="s">
+        <v>18</v>
+      </c>
+      <c r="K101">
+        <v>100</v>
+      </c>
+      <c r="L101">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102">
+        <v>12</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102" t="s">
+        <v>21</v>
+      </c>
+      <c r="E102" t="s">
+        <v>111</v>
+      </c>
+      <c r="F102" t="s">
+        <v>28</v>
+      </c>
+      <c r="G102" t="s">
+        <v>105</v>
+      </c>
+      <c r="H102" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" t="s">
+        <v>112</v>
+      </c>
+      <c r="K102">
+        <v>100</v>
+      </c>
+      <c r="L102">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>20</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103" t="s">
+        <v>21</v>
+      </c>
+      <c r="E103" t="s">
+        <v>111</v>
+      </c>
+      <c r="F103" t="s">
+        <v>28</v>
+      </c>
+      <c r="G103" t="s">
+        <v>105</v>
+      </c>
+      <c r="H103" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" t="s">
+        <v>18</v>
+      </c>
+      <c r="K103">
+        <v>100</v>
+      </c>
+      <c r="L103">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104">
+        <v>55</v>
+      </c>
+      <c r="C104">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>113</v>
+      </c>
+      <c r="E104" t="s">
+        <v>111</v>
+      </c>
+      <c r="F104" t="s">
+        <v>28</v>
+      </c>
+      <c r="G104" t="s">
+        <v>105</v>
+      </c>
+      <c r="H104" t="s">
+        <v>17</v>
+      </c>
+      <c r="I104" t="s">
+        <v>18</v>
+      </c>
+      <c r="K104">
+        <v>100</v>
+      </c>
+      <c r="L104">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>24</v>
+      </c>
+      <c r="B105">
+        <v>40</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105" t="s">
+        <v>21</v>
+      </c>
+      <c r="E105" t="s">
+        <v>111</v>
+      </c>
+      <c r="F105" t="s">
+        <v>28</v>
+      </c>
+      <c r="G105" t="s">
+        <v>105</v>
+      </c>
+      <c r="H105" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" t="s">
+        <v>18</v>
+      </c>
+      <c r="K105">
+        <v>100</v>
+      </c>
+      <c r="L105">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>26</v>
+      </c>
+      <c r="B106">
+        <v>750</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106" t="s">
+        <v>111</v>
+      </c>
+      <c r="F106" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" t="s">
+        <v>105</v>
+      </c>
+      <c r="H106" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" t="s">
+        <v>18</v>
+      </c>
+      <c r="K106">
+        <v>100</v>
+      </c>
+      <c r="L106">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107">
+        <v>13</v>
+      </c>
+      <c r="C107">
+        <v>22</v>
+      </c>
+      <c r="D107" t="s">
+        <v>114</v>
+      </c>
+      <c r="E107" t="s">
+        <v>115</v>
+      </c>
+      <c r="F107" t="s">
+        <v>15</v>
+      </c>
+      <c r="G107" t="s">
+        <v>116</v>
+      </c>
+      <c r="H107" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" t="s">
+        <v>18</v>
+      </c>
+      <c r="K107">
+        <v>100</v>
+      </c>
+      <c r="L107">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>20</v>
+      </c>
+      <c r="B108">
+        <v>3</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
+        <v>117</v>
+      </c>
+      <c r="E108" t="s">
+        <v>115</v>
+      </c>
+      <c r="F108" t="s">
+        <v>15</v>
+      </c>
+      <c r="G108" t="s">
+        <v>116</v>
+      </c>
+      <c r="H108" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" t="s">
+        <v>18</v>
+      </c>
+      <c r="K108">
+        <v>100</v>
+      </c>
+      <c r="L108">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109">
+        <v>19</v>
+      </c>
+      <c r="C109">
+        <v>20</v>
+      </c>
+      <c r="D109" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" t="s">
+        <v>115</v>
+      </c>
+      <c r="F109" t="s">
+        <v>15</v>
+      </c>
+      <c r="G109" t="s">
+        <v>116</v>
+      </c>
+      <c r="H109" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109">
+        <v>100</v>
+      </c>
+      <c r="L109">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>24</v>
+      </c>
+      <c r="B110">
+        <v>45</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" t="s">
+        <v>115</v>
+      </c>
+      <c r="F110" t="s">
+        <v>15</v>
+      </c>
+      <c r="G110" t="s">
+        <v>116</v>
+      </c>
+      <c r="H110" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110">
+        <v>100</v>
+      </c>
+      <c r="L110">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>26</v>
+      </c>
+      <c r="B111">
+        <v>375</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111" t="s">
+        <v>21</v>
+      </c>
+      <c r="E111" t="s">
+        <v>115</v>
+      </c>
+      <c r="F111" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" t="s">
+        <v>116</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111">
+        <v>100</v>
+      </c>
+      <c r="L111">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112">
+        <v>19</v>
+      </c>
+      <c r="C112">
+        <v>28</v>
+      </c>
+      <c r="D112" t="s">
+        <v>119</v>
+      </c>
+      <c r="E112" t="s">
+        <v>120</v>
+      </c>
+      <c r="F112" t="s">
+        <v>28</v>
+      </c>
+      <c r="G112" t="s">
+        <v>116</v>
+      </c>
+      <c r="H112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" t="s">
+        <v>18</v>
+      </c>
+      <c r="K112">
+        <v>100</v>
+      </c>
+      <c r="L112">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>20</v>
+      </c>
+      <c r="B113">
+        <v>5</v>
+      </c>
+      <c r="C113">
+        <v>5</v>
+      </c>
+      <c r="D113" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" t="s">
+        <v>120</v>
+      </c>
+      <c r="F113" t="s">
+        <v>28</v>
+      </c>
+      <c r="G113" t="s">
+        <v>116</v>
+      </c>
+      <c r="H113" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" t="s">
+        <v>18</v>
+      </c>
+      <c r="K113">
+        <v>100</v>
+      </c>
+      <c r="L113">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114">
+        <v>28</v>
+      </c>
+      <c r="C114">
+        <v>25</v>
+      </c>
+      <c r="D114" t="s">
+        <v>121</v>
+      </c>
+      <c r="E114" t="s">
+        <v>120</v>
+      </c>
+      <c r="F114" t="s">
+        <v>28</v>
+      </c>
+      <c r="G114" t="s">
+        <v>116</v>
+      </c>
+      <c r="H114" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" t="s">
+        <v>18</v>
+      </c>
+      <c r="K114">
+        <v>100</v>
+      </c>
+      <c r="L114">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>24</v>
+      </c>
+      <c r="B115">
+        <v>68</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115" t="s">
+        <v>120</v>
+      </c>
+      <c r="F115" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115" t="s">
+        <v>116</v>
+      </c>
+      <c r="H115" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" t="s">
+        <v>18</v>
+      </c>
+      <c r="K115">
+        <v>100</v>
+      </c>
+      <c r="L115">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>26</v>
+      </c>
+      <c r="B116">
         <v>563</v>
       </c>
-      <c r="C71">
-        <v>0</v>
-      </c>
-      <c r="D71" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116" t="s">
+        <v>21</v>
+      </c>
+      <c r="E116" t="s">
+        <v>120</v>
+      </c>
+      <c r="F116" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" t="s">
+        <v>116</v>
+      </c>
+      <c r="H116" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116" t="s">
+        <v>18</v>
+      </c>
+      <c r="K116">
+        <v>100</v>
+      </c>
+      <c r="L116">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>12</v>
+      </c>
+      <c r="B117">
+        <v>19</v>
+      </c>
+      <c r="C117">
+        <v>27</v>
+      </c>
+      <c r="D117" t="s">
+        <v>122</v>
+      </c>
+      <c r="E117" t="s">
+        <v>123</v>
+      </c>
+      <c r="F117" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" t="s">
+        <v>116</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" t="s">
+        <v>124</v>
+      </c>
+      <c r="K117">
+        <v>100</v>
+      </c>
+      <c r="L117">
+        <v>100.2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>20</v>
+      </c>
+      <c r="B118">
+        <v>5</v>
+      </c>
+      <c r="C118">
+        <v>3</v>
+      </c>
+      <c r="D118" t="s">
+        <v>125</v>
+      </c>
+      <c r="E118" t="s">
+        <v>123</v>
+      </c>
+      <c r="F118" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" t="s">
+        <v>116</v>
+      </c>
+      <c r="H118" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118">
+        <v>100</v>
+      </c>
+      <c r="L118">
+        <v>100.2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119">
+        <v>28</v>
+      </c>
+      <c r="C119">
+        <v>25</v>
+      </c>
+      <c r="D119" t="s">
+        <v>121</v>
+      </c>
+      <c r="E119" t="s">
+        <v>123</v>
+      </c>
+      <c r="F119" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" t="s">
+        <v>116</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119">
+        <v>100</v>
+      </c>
+      <c r="L119">
+        <v>100.2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>24</v>
+      </c>
+      <c r="B120">
+        <v>68</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120" t="s">
+        <v>21</v>
+      </c>
+      <c r="E120" t="s">
+        <v>123</v>
+      </c>
+      <c r="F120" t="s">
+        <v>28</v>
+      </c>
+      <c r="G120" t="s">
+        <v>116</v>
+      </c>
+      <c r="H120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120">
+        <v>100</v>
+      </c>
+      <c r="L120">
+        <v>100.2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>26</v>
+      </c>
+      <c r="B121">
+        <v>563</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>21</v>
+      </c>
+      <c r="E121" t="s">
+        <v>123</v>
+      </c>
+      <c r="F121" t="s">
+        <v>28</v>
+      </c>
+      <c r="G121" t="s">
+        <v>116</v>
+      </c>
+      <c r="H121" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121">
+        <v>100</v>
+      </c>
+      <c r="L121">
+        <v>100.2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122">
+        <v>8</v>
+      </c>
+      <c r="C122">
+        <v>7</v>
+      </c>
+      <c r="D122" t="s">
+        <v>126</v>
+      </c>
+      <c r="E122" t="s">
+        <v>127</v>
+      </c>
+      <c r="F122" t="s">
+        <v>15</v>
+      </c>
+      <c r="G122" t="s">
+        <v>128</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122">
+        <v>100</v>
+      </c>
+      <c r="L122">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>20</v>
+      </c>
+      <c r="B123">
+        <v>3</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123" t="s">
+        <v>21</v>
+      </c>
+      <c r="E123" t="s">
+        <v>127</v>
+      </c>
+      <c r="F123" t="s">
+        <v>15</v>
+      </c>
+      <c r="G123" t="s">
+        <v>128</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123">
+        <v>100</v>
+      </c>
+      <c r="L123">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>22</v>
+      </c>
+      <c r="B124">
+        <v>18</v>
+      </c>
+      <c r="C124">
+        <v>24</v>
+      </c>
+      <c r="D124" t="s">
+        <v>129</v>
+      </c>
+      <c r="E124" t="s">
+        <v>127</v>
+      </c>
+      <c r="F124" t="s">
+        <v>15</v>
+      </c>
+      <c r="G124" t="s">
+        <v>128</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124">
+        <v>100</v>
+      </c>
+      <c r="L124">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>24</v>
+      </c>
+      <c r="B125">
+        <v>24</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125" t="s">
+        <v>21</v>
+      </c>
+      <c r="E125" t="s">
+        <v>127</v>
+      </c>
+      <c r="F125" t="s">
+        <v>15</v>
+      </c>
+      <c r="G125" t="s">
+        <v>128</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125">
+        <v>100</v>
+      </c>
+      <c r="L125">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>26</v>
+      </c>
+      <c r="B126">
+        <v>375</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>21</v>
+      </c>
+      <c r="E126" t="s">
+        <v>127</v>
+      </c>
+      <c r="F126" t="s">
+        <v>15</v>
+      </c>
+      <c r="G126" t="s">
+        <v>128</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126">
+        <v>100</v>
+      </c>
+      <c r="L126">
+        <v>115.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127">
+        <v>11</v>
+      </c>
+      <c r="C127">
+        <v>11</v>
+      </c>
+      <c r="D127" t="s">
+        <v>44</v>
+      </c>
+      <c r="E127" t="s">
+        <v>130</v>
+      </c>
+      <c r="F127" t="s">
+        <v>28</v>
+      </c>
+      <c r="G127" t="s">
+        <v>128</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" t="s">
+        <v>131</v>
+      </c>
+      <c r="K127">
+        <v>100</v>
+      </c>
+      <c r="L127">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>20</v>
+      </c>
+      <c r="B128">
+        <v>4</v>
+      </c>
+      <c r="C128">
+        <v>3</v>
+      </c>
+      <c r="D128" t="s">
+        <v>87</v>
+      </c>
+      <c r="E128" t="s">
+        <v>130</v>
+      </c>
+      <c r="F128" t="s">
+        <v>28</v>
+      </c>
+      <c r="G128" t="s">
+        <v>128</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" t="s">
+        <v>132</v>
+      </c>
+      <c r="K128">
+        <v>100</v>
+      </c>
+      <c r="L128">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129">
+        <v>27</v>
+      </c>
+      <c r="C129">
+        <v>27</v>
+      </c>
+      <c r="D129" t="s">
+        <v>44</v>
+      </c>
+      <c r="E129" t="s">
+        <v>130</v>
+      </c>
+      <c r="F129" t="s">
+        <v>28</v>
+      </c>
+      <c r="G129" t="s">
+        <v>128</v>
+      </c>
+      <c r="H129" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" t="s">
+        <v>18</v>
+      </c>
+      <c r="K129">
+        <v>100</v>
+      </c>
+      <c r="L129">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>24</v>
+      </c>
+      <c r="B130">
+        <v>36</v>
+      </c>
+      <c r="C130">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>133</v>
+      </c>
+      <c r="E130" t="s">
+        <v>130</v>
+      </c>
+      <c r="F130" t="s">
+        <v>28</v>
+      </c>
+      <c r="G130" t="s">
+        <v>128</v>
+      </c>
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130">
+        <v>100</v>
+      </c>
+      <c r="L130">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>26</v>
+      </c>
+      <c r="B131">
+        <v>563</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131" t="s">
+        <v>21</v>
+      </c>
+      <c r="E131" t="s">
+        <v>130</v>
+      </c>
+      <c r="F131" t="s">
+        <v>28</v>
+      </c>
+      <c r="G131" t="s">
+        <v>128</v>
+      </c>
+      <c r="H131" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" t="s">
+        <v>18</v>
+      </c>
+      <c r="K131">
+        <v>100</v>
+      </c>
+      <c r="L131">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132">
+        <v>11</v>
+      </c>
+      <c r="C132">
+        <v>15</v>
+      </c>
+      <c r="D132" t="s">
+        <v>134</v>
+      </c>
+      <c r="E132" t="s">
+        <v>135</v>
+      </c>
+      <c r="F132" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132" t="s">
+        <v>128</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" t="s">
+        <v>18</v>
+      </c>
+      <c r="K132">
+        <v>100</v>
+      </c>
+      <c r="L132">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>20</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133">
+        <v>4</v>
+      </c>
+      <c r="D133" t="s">
+        <v>44</v>
+      </c>
+      <c r="E133" t="s">
+        <v>135</v>
+      </c>
+      <c r="F133" t="s">
+        <v>28</v>
+      </c>
+      <c r="G133" t="s">
+        <v>128</v>
+      </c>
+      <c r="H133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" t="s">
+        <v>18</v>
+      </c>
+      <c r="K133">
+        <v>100</v>
+      </c>
+      <c r="L133">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>22</v>
+      </c>
+      <c r="B134">
+        <v>27</v>
+      </c>
+      <c r="C134">
+        <v>36</v>
+      </c>
+      <c r="D134" t="s">
+        <v>129</v>
+      </c>
+      <c r="E134" t="s">
+        <v>135</v>
+      </c>
+      <c r="F134" t="s">
+        <v>28</v>
+      </c>
+      <c r="G134" t="s">
+        <v>128</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" t="s">
+        <v>18</v>
+      </c>
+      <c r="K134">
+        <v>100</v>
+      </c>
+      <c r="L134">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>24</v>
+      </c>
+      <c r="B135">
+        <v>36</v>
+      </c>
+      <c r="C135">
+        <v>55</v>
+      </c>
+      <c r="D135" t="s">
+        <v>136</v>
+      </c>
+      <c r="E135" t="s">
+        <v>135</v>
+      </c>
+      <c r="F135" t="s">
+        <v>28</v>
+      </c>
+      <c r="G135" t="s">
+        <v>128</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" t="s">
+        <v>18</v>
+      </c>
+      <c r="K135">
+        <v>100</v>
+      </c>
+      <c r="L135">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>26</v>
+      </c>
+      <c r="B136">
+        <v>563</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136" t="s">
+        <v>21</v>
+      </c>
+      <c r="E136" t="s">
+        <v>135</v>
+      </c>
+      <c r="F136" t="s">
+        <v>28</v>
+      </c>
+      <c r="G136" t="s">
+        <v>128</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+      <c r="K136">
+        <v>100</v>
+      </c>
+      <c r="L136">
+        <v>125.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137">
+        <v>6</v>
+      </c>
+      <c r="C137">
+        <v>6</v>
+      </c>
+      <c r="D137" t="s">
+        <v>44</v>
+      </c>
+      <c r="E137" t="s">
+        <v>137</v>
+      </c>
+      <c r="F137" t="s">
+        <v>15</v>
+      </c>
+      <c r="G137" t="s">
+        <v>138</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" t="s">
+        <v>18</v>
+      </c>
+      <c r="K137">
+        <v>100</v>
+      </c>
+      <c r="L137">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>20</v>
+      </c>
+      <c r="B138">
+        <v>3</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138" t="s">
+        <v>25</v>
+      </c>
+      <c r="E138" t="s">
+        <v>137</v>
+      </c>
+      <c r="F138" t="s">
+        <v>15</v>
+      </c>
+      <c r="G138" t="s">
+        <v>138</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138">
+        <v>100</v>
+      </c>
+      <c r="L138">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>22</v>
+      </c>
+      <c r="B139">
+        <v>12</v>
+      </c>
+      <c r="C139">
+        <v>9</v>
+      </c>
+      <c r="D139" t="s">
+        <v>87</v>
+      </c>
+      <c r="E139" t="s">
+        <v>137</v>
+      </c>
+      <c r="F139" t="s">
+        <v>15</v>
+      </c>
+      <c r="G139" t="s">
+        <v>138</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139">
+        <v>100</v>
+      </c>
+      <c r="L139">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>24</v>
+      </c>
+      <c r="B140">
+        <v>28</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140" t="s">
+        <v>21</v>
+      </c>
+      <c r="E140" t="s">
+        <v>137</v>
+      </c>
+      <c r="F140" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" t="s">
+        <v>138</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" t="s">
+        <v>18</v>
+      </c>
+      <c r="K140">
+        <v>100</v>
+      </c>
+      <c r="L140">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>26</v>
+      </c>
+      <c r="B141">
+        <v>480</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141" t="s">
+        <v>21</v>
+      </c>
+      <c r="E141" t="s">
+        <v>137</v>
+      </c>
+      <c r="F141" t="s">
+        <v>15</v>
+      </c>
+      <c r="G141" t="s">
+        <v>138</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141">
+        <v>100</v>
+      </c>
+      <c r="L141">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B142">
+        <v>9</v>
+      </c>
+      <c r="C142">
+        <v>11</v>
+      </c>
+      <c r="D142" t="s">
+        <v>106</v>
+      </c>
+      <c r="E142" t="s">
+        <v>139</v>
+      </c>
+      <c r="F142" t="s">
+        <v>28</v>
+      </c>
+      <c r="G142" t="s">
+        <v>138</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142">
+        <v>100</v>
+      </c>
+      <c r="L142">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>20</v>
+      </c>
+      <c r="B143">
+        <v>5</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+      <c r="D143" t="s">
+        <v>90</v>
+      </c>
+      <c r="E143" t="s">
+        <v>139</v>
+      </c>
+      <c r="F143" t="s">
+        <v>28</v>
+      </c>
+      <c r="G143" t="s">
+        <v>138</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143">
+        <v>100</v>
+      </c>
+      <c r="L143">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>22</v>
+      </c>
+      <c r="B144">
+        <v>18</v>
+      </c>
+      <c r="C144">
+        <v>14</v>
+      </c>
+      <c r="D144" t="s">
+        <v>140</v>
+      </c>
+      <c r="E144" t="s">
+        <v>139</v>
+      </c>
+      <c r="F144" t="s">
+        <v>28</v>
+      </c>
+      <c r="G144" t="s">
+        <v>138</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" t="s">
+        <v>18</v>
+      </c>
+      <c r="K144">
+        <v>100</v>
+      </c>
+      <c r="L144">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>24</v>
+      </c>
+      <c r="B145">
+        <v>42</v>
+      </c>
+      <c r="C145">
+        <v>45</v>
+      </c>
+      <c r="D145" t="s">
+        <v>141</v>
+      </c>
+      <c r="E145" t="s">
+        <v>139</v>
+      </c>
+      <c r="F145" t="s">
+        <v>28</v>
+      </c>
+      <c r="G145" t="s">
+        <v>138</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145">
+        <v>100</v>
+      </c>
+      <c r="L145">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>26</v>
+      </c>
+      <c r="B146">
+        <v>720</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146" t="s">
+        <v>21</v>
+      </c>
+      <c r="E146" t="s">
+        <v>139</v>
+      </c>
+      <c r="F146" t="s">
+        <v>28</v>
+      </c>
+      <c r="G146" t="s">
+        <v>138</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146">
+        <v>100</v>
+      </c>
+      <c r="L146">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>12</v>
+      </c>
+      <c r="B147">
+        <v>9</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147" t="s">
+        <v>142</v>
+      </c>
+      <c r="E147" t="s">
+        <v>62</v>
+      </c>
+      <c r="F147" t="s">
+        <v>63</v>
+      </c>
+      <c r="G147" t="s">
+        <v>138</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" t="s">
+        <v>18</v>
+      </c>
+      <c r="J147" t="s">
+        <v>143</v>
+      </c>
+      <c r="K147">
+        <v>100</v>
+      </c>
+      <c r="L147">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>20</v>
+      </c>
+      <c r="B148">
+        <v>5</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148" t="s">
+        <v>21</v>
+      </c>
+      <c r="E148" t="s">
+        <v>62</v>
+      </c>
+      <c r="F148" t="s">
+        <v>63</v>
+      </c>
+      <c r="G148" t="s">
+        <v>138</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" t="s">
+        <v>18</v>
+      </c>
+      <c r="K148">
+        <v>100</v>
+      </c>
+      <c r="L148">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>22</v>
+      </c>
+      <c r="B149">
+        <v>18</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149" t="s">
+        <v>144</v>
+      </c>
+      <c r="E149" t="s">
+        <v>62</v>
+      </c>
+      <c r="F149" t="s">
+        <v>63</v>
+      </c>
+      <c r="G149" t="s">
+        <v>138</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" t="s">
+        <v>18</v>
+      </c>
+      <c r="J149" t="s">
+        <v>145</v>
+      </c>
+      <c r="K149">
+        <v>100</v>
+      </c>
+      <c r="L149">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>24</v>
+      </c>
+      <c r="B150">
+        <v>42</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150" t="s">
+        <v>21</v>
+      </c>
+      <c r="E150" t="s">
+        <v>62</v>
+      </c>
+      <c r="F150" t="s">
+        <v>63</v>
+      </c>
+      <c r="G150" t="s">
+        <v>138</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" t="s">
+        <v>18</v>
+      </c>
+      <c r="J150" t="s">
+        <v>145</v>
+      </c>
+      <c r="K150">
+        <v>100</v>
+      </c>
+      <c r="L150">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>26</v>
+      </c>
+      <c r="B151">
+        <v>720</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151" t="s">
+        <v>21</v>
+      </c>
+      <c r="E151" t="s">
+        <v>62</v>
+      </c>
+      <c r="F151" t="s">
+        <v>63</v>
+      </c>
+      <c r="G151" t="s">
+        <v>138</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151">
+        <v>100</v>
+      </c>
+      <c r="L151">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>12</v>
+      </c>
+      <c r="B152">
+        <v>25</v>
+      </c>
+      <c r="C152">
+        <v>4</v>
+      </c>
+      <c r="D152" t="s">
+        <v>146</v>
+      </c>
+      <c r="E152" t="s">
+        <v>147</v>
+      </c>
+      <c r="F152" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" t="s">
+        <v>148</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" t="s">
+        <v>18</v>
+      </c>
+      <c r="J152" t="s">
+        <v>149</v>
+      </c>
+      <c r="K152">
+        <v>100</v>
+      </c>
+      <c r="L152">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>20</v>
+      </c>
+      <c r="B153">
+        <v>6</v>
+      </c>
+      <c r="C153">
+        <v>3</v>
+      </c>
+      <c r="D153" t="s">
+        <v>150</v>
+      </c>
+      <c r="E153" t="s">
+        <v>147</v>
+      </c>
+      <c r="F153" t="s">
+        <v>15</v>
+      </c>
+      <c r="G153" t="s">
+        <v>148</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153" t="s">
+        <v>18</v>
+      </c>
+      <c r="J153" t="s">
+        <v>66</v>
+      </c>
+      <c r="K153">
+        <v>100</v>
+      </c>
+      <c r="L153">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>22</v>
+      </c>
+      <c r="B154">
+        <v>24</v>
+      </c>
+      <c r="C154">
+        <v>7</v>
+      </c>
+      <c r="D154" t="s">
+        <v>151</v>
+      </c>
+      <c r="E154" t="s">
+        <v>147</v>
+      </c>
+      <c r="F154" t="s">
+        <v>15</v>
+      </c>
+      <c r="G154" t="s">
+        <v>148</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" t="s">
+        <v>18</v>
+      </c>
+      <c r="J154" t="s">
+        <v>152</v>
+      </c>
+      <c r="K154">
+        <v>100</v>
+      </c>
+      <c r="L154">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>24</v>
+      </c>
+      <c r="B155">
+        <v>84</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155" t="s">
+        <v>21</v>
+      </c>
+      <c r="E155" t="s">
+        <v>147</v>
+      </c>
+      <c r="F155" t="s">
+        <v>15</v>
+      </c>
+      <c r="G155" t="s">
+        <v>148</v>
+      </c>
+      <c r="H155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" t="s">
+        <v>18</v>
+      </c>
+      <c r="J155" t="s">
+        <v>153</v>
+      </c>
+      <c r="K155">
+        <v>100</v>
+      </c>
+      <c r="L155">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>26</v>
+      </c>
+      <c r="B156">
+        <v>600</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>21</v>
+      </c>
+      <c r="E156" t="s">
+        <v>147</v>
+      </c>
+      <c r="F156" t="s">
+        <v>15</v>
+      </c>
+      <c r="G156" t="s">
+        <v>148</v>
+      </c>
+      <c r="H156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" t="s">
+        <v>18</v>
+      </c>
+      <c r="J156" t="s">
+        <v>154</v>
+      </c>
+      <c r="K156">
+        <v>100</v>
+      </c>
+      <c r="L156">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B157">
+        <v>37</v>
+      </c>
+      <c r="C157">
+        <v>37</v>
+      </c>
+      <c r="D157" t="s">
+        <v>44</v>
+      </c>
+      <c r="E157" t="s">
+        <v>155</v>
+      </c>
+      <c r="F157" t="s">
+        <v>28</v>
+      </c>
+      <c r="G157" t="s">
+        <v>148</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157">
+        <v>100</v>
+      </c>
+      <c r="L157">
+        <v>95.9</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>20</v>
+      </c>
+      <c r="B158">
+        <v>8</v>
+      </c>
+      <c r="C158">
+        <v>10</v>
+      </c>
+      <c r="D158" t="s">
+        <v>156</v>
+      </c>
+      <c r="E158" t="s">
+        <v>155</v>
+      </c>
+      <c r="F158" t="s">
+        <v>28</v>
+      </c>
+      <c r="G158" t="s">
+        <v>148</v>
+      </c>
+      <c r="H158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158">
+        <v>100</v>
+      </c>
+      <c r="L158">
+        <v>95.9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>22</v>
+      </c>
+      <c r="B159">
+        <v>36</v>
+      </c>
+      <c r="C159">
+        <v>38</v>
+      </c>
+      <c r="D159" t="s">
+        <v>157</v>
+      </c>
+      <c r="E159" t="s">
+        <v>155</v>
+      </c>
+      <c r="F159" t="s">
+        <v>28</v>
+      </c>
+      <c r="G159" t="s">
+        <v>148</v>
+      </c>
+      <c r="H159" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159">
+        <v>100</v>
+      </c>
+      <c r="L159">
+        <v>95.9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>24</v>
+      </c>
+      <c r="B160">
+        <v>126</v>
+      </c>
+      <c r="C160">
+        <v>131</v>
+      </c>
+      <c r="D160" t="s">
+        <v>158</v>
+      </c>
+      <c r="E160" t="s">
+        <v>155</v>
+      </c>
+      <c r="F160" t="s">
+        <v>28</v>
+      </c>
+      <c r="G160" t="s">
+        <v>148</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160">
+        <v>100</v>
+      </c>
+      <c r="L160">
+        <v>95.9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>26</v>
+      </c>
+      <c r="B161">
+        <v>900</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161" t="s">
+        <v>21</v>
+      </c>
+      <c r="E161" t="s">
+        <v>155</v>
+      </c>
+      <c r="F161" t="s">
+        <v>28</v>
+      </c>
+      <c r="G161" t="s">
+        <v>148</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161">
+        <v>100</v>
+      </c>
+      <c r="L161">
+        <v>95.9</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>12</v>
+      </c>
+      <c r="B162">
+        <v>37</v>
+      </c>
+      <c r="C162">
+        <v>13</v>
+      </c>
+      <c r="D162" t="s">
+        <v>159</v>
+      </c>
+      <c r="E162" t="s">
+        <v>62</v>
+      </c>
+      <c r="F162" t="s">
+        <v>63</v>
+      </c>
+      <c r="G162" t="s">
+        <v>148</v>
+      </c>
+      <c r="H162" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162" t="s">
+        <v>18</v>
+      </c>
+      <c r="J162" t="s">
+        <v>160</v>
+      </c>
+      <c r="K162">
+        <v>100</v>
+      </c>
+      <c r="L162">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>20</v>
+      </c>
+      <c r="B163">
+        <v>8</v>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+      <c r="D163" t="s">
+        <v>71</v>
+      </c>
+      <c r="E163" t="s">
+        <v>62</v>
+      </c>
+      <c r="F163" t="s">
+        <v>63</v>
+      </c>
+      <c r="G163" t="s">
+        <v>148</v>
+      </c>
+      <c r="H163" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" t="s">
+        <v>18</v>
+      </c>
+      <c r="J163" t="s">
+        <v>161</v>
+      </c>
+      <c r="K163">
+        <v>100</v>
+      </c>
+      <c r="L163">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>22</v>
+      </c>
+      <c r="B164">
+        <v>36</v>
+      </c>
+      <c r="C164">
+        <v>5</v>
+      </c>
+      <c r="D164" t="s">
+        <v>162</v>
+      </c>
+      <c r="E164" t="s">
+        <v>62</v>
+      </c>
+      <c r="F164" t="s">
+        <v>63</v>
+      </c>
+      <c r="G164" t="s">
+        <v>148</v>
+      </c>
+      <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" t="s">
+        <v>163</v>
+      </c>
+      <c r="K164">
+        <v>100</v>
+      </c>
+      <c r="L164">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>24</v>
+      </c>
+      <c r="B165">
+        <v>126</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165" t="s">
+        <v>21</v>
+      </c>
+      <c r="E165" t="s">
+        <v>62</v>
+      </c>
+      <c r="F165" t="s">
+        <v>63</v>
+      </c>
+      <c r="G165" t="s">
+        <v>148</v>
+      </c>
+      <c r="H165" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165" t="s">
+        <v>18</v>
+      </c>
+      <c r="J165" t="s">
+        <v>164</v>
+      </c>
+      <c r="K165">
+        <v>100</v>
+      </c>
+      <c r="L165">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>26</v>
+      </c>
+      <c r="B166">
+        <v>900</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166" t="s">
+        <v>21</v>
+      </c>
+      <c r="E166" t="s">
+        <v>62</v>
+      </c>
+      <c r="F166" t="s">
+        <v>63</v>
+      </c>
+      <c r="G166" t="s">
+        <v>148</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" t="s">
+        <v>18</v>
+      </c>
+      <c r="J166" t="s">
+        <v>165</v>
+      </c>
+      <c r="K166">
+        <v>100</v>
+      </c>
+      <c r="L166">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>12</v>
+      </c>
+      <c r="B167">
+        <v>37</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167" t="s">
+        <v>61</v>
+      </c>
+      <c r="E167" t="s">
+        <v>69</v>
+      </c>
+      <c r="F167" t="s">
+        <v>63</v>
+      </c>
+      <c r="G167" t="s">
+        <v>148</v>
+      </c>
+      <c r="H167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167" t="s">
+        <v>18</v>
+      </c>
+      <c r="J167" t="s">
+        <v>92</v>
+      </c>
+      <c r="K167">
+        <v>100</v>
+      </c>
+      <c r="L167">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>20</v>
+      </c>
+      <c r="B168">
+        <v>8</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168" t="s">
+        <v>21</v>
+      </c>
+      <c r="E168" t="s">
+        <v>69</v>
+      </c>
+      <c r="F168" t="s">
+        <v>63</v>
+      </c>
+      <c r="G168" t="s">
+        <v>148</v>
+      </c>
+      <c r="H168" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168" t="s">
+        <v>18</v>
+      </c>
+      <c r="K168">
+        <v>100</v>
+      </c>
+      <c r="L168">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>22</v>
+      </c>
+      <c r="B169">
+        <v>36</v>
+      </c>
+      <c r="C169">
+        <v>2</v>
+      </c>
+      <c r="D169" t="s">
+        <v>144</v>
+      </c>
+      <c r="E169" t="s">
+        <v>69</v>
+      </c>
+      <c r="F169" t="s">
+        <v>63</v>
+      </c>
+      <c r="G169" t="s">
+        <v>148</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" t="s">
+        <v>18</v>
+      </c>
+      <c r="K169">
+        <v>100</v>
+      </c>
+      <c r="L169">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>24</v>
+      </c>
+      <c r="B170">
+        <v>126</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170" t="s">
+        <v>21</v>
+      </c>
+      <c r="E170" t="s">
+        <v>69</v>
+      </c>
+      <c r="F170" t="s">
+        <v>63</v>
+      </c>
+      <c r="G170" t="s">
+        <v>148</v>
+      </c>
+      <c r="H170" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" t="s">
+        <v>18</v>
+      </c>
+      <c r="K170">
+        <v>100</v>
+      </c>
+      <c r="L170">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>26</v>
+      </c>
+      <c r="B171">
+        <v>900</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171" t="s">
+        <v>21</v>
+      </c>
+      <c r="E171" t="s">
+        <v>69</v>
+      </c>
+      <c r="F171" t="s">
+        <v>63</v>
+      </c>
+      <c r="G171" t="s">
+        <v>148</v>
+      </c>
+      <c r="H171" t="s">
+        <v>17</v>
+      </c>
+      <c r="I171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171">
+        <v>100</v>
+      </c>
+      <c r="L171">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>12</v>
+      </c>
+      <c r="B172">
+        <v>8</v>
+      </c>
+      <c r="C172">
+        <v>7</v>
+      </c>
+      <c r="D172" t="s">
+        <v>126</v>
+      </c>
+      <c r="E172" t="s">
+        <v>166</v>
+      </c>
+      <c r="F172" t="s">
+        <v>15</v>
+      </c>
+      <c r="G172" t="s">
+        <v>167</v>
+      </c>
+      <c r="H172" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172" t="s">
+        <v>18</v>
+      </c>
+      <c r="K172">
+        <v>100</v>
+      </c>
+      <c r="L172">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>20</v>
+      </c>
+      <c r="B173">
+        <v>2</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173" t="s">
+        <v>150</v>
+      </c>
+      <c r="E173" t="s">
+        <v>166</v>
+      </c>
+      <c r="F173" t="s">
+        <v>15</v>
+      </c>
+      <c r="G173" t="s">
+        <v>167</v>
+      </c>
+      <c r="H173" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" t="s">
+        <v>18</v>
+      </c>
+      <c r="K173">
+        <v>100</v>
+      </c>
+      <c r="L173">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>22</v>
+      </c>
+      <c r="B174">
+        <v>40</v>
+      </c>
+      <c r="C174">
+        <v>29</v>
+      </c>
+      <c r="D174" t="s">
+        <v>168</v>
+      </c>
+      <c r="E174" t="s">
+        <v>166</v>
+      </c>
+      <c r="F174" t="s">
+        <v>15</v>
+      </c>
+      <c r="G174" t="s">
+        <v>167</v>
+      </c>
+      <c r="H174" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174" t="s">
+        <v>18</v>
+      </c>
+      <c r="K174">
+        <v>100</v>
+      </c>
+      <c r="L174">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>24</v>
+      </c>
+      <c r="B175">
+        <v>25</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+      <c r="D175" t="s">
+        <v>21</v>
+      </c>
+      <c r="E175" t="s">
+        <v>166</v>
+      </c>
+      <c r="F175" t="s">
+        <v>15</v>
+      </c>
+      <c r="G175" t="s">
+        <v>167</v>
+      </c>
+      <c r="H175" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" t="s">
+        <v>18</v>
+      </c>
+      <c r="K175">
+        <v>100</v>
+      </c>
+      <c r="L175">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>26</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176" t="s">
+        <v>21</v>
+      </c>
+      <c r="E176" t="s">
+        <v>166</v>
+      </c>
+      <c r="F176" t="s">
+        <v>15</v>
+      </c>
+      <c r="G176" t="s">
+        <v>167</v>
+      </c>
+      <c r="H176" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176" t="s">
+        <v>18</v>
+      </c>
+      <c r="K176">
+        <v>100</v>
+      </c>
+      <c r="L176">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>12</v>
+      </c>
+      <c r="B177">
+        <v>8</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="D177" t="s">
+        <v>169</v>
+      </c>
+      <c r="E177" t="s">
+        <v>170</v>
+      </c>
+      <c r="F177" t="s">
+        <v>63</v>
+      </c>
+      <c r="G177" t="s">
+        <v>167</v>
+      </c>
+      <c r="H177" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177" t="s">
+        <v>18</v>
+      </c>
+      <c r="J177" t="s">
+        <v>171</v>
+      </c>
+      <c r="K177">
+        <v>100</v>
+      </c>
+      <c r="L177">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>20</v>
+      </c>
+      <c r="B178">
+        <v>2</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+      <c r="D178" t="s">
+        <v>21</v>
+      </c>
+      <c r="E178" t="s">
+        <v>170</v>
+      </c>
+      <c r="F178" t="s">
+        <v>63</v>
+      </c>
+      <c r="G178" t="s">
+        <v>167</v>
+      </c>
+      <c r="H178" t="s">
+        <v>17</v>
+      </c>
+      <c r="I178" t="s">
+        <v>18</v>
+      </c>
+      <c r="K178">
+        <v>100</v>
+      </c>
+      <c r="L178">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>22</v>
+      </c>
+      <c r="B179">
+        <v>40</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179" t="s">
+        <v>65</v>
+      </c>
+      <c r="E179" t="s">
+        <v>170</v>
+      </c>
+      <c r="F179" t="s">
+        <v>63</v>
+      </c>
+      <c r="G179" t="s">
+        <v>167</v>
+      </c>
+      <c r="H179" t="s">
+        <v>17</v>
+      </c>
+      <c r="I179" t="s">
+        <v>18</v>
+      </c>
+      <c r="K179">
+        <v>100</v>
+      </c>
+      <c r="L179">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>24</v>
+      </c>
+      <c r="B180">
+        <v>25</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+      <c r="D180" t="s">
+        <v>21</v>
+      </c>
+      <c r="E180" t="s">
+        <v>170</v>
+      </c>
+      <c r="F180" t="s">
+        <v>63</v>
+      </c>
+      <c r="G180" t="s">
+        <v>167</v>
+      </c>
+      <c r="H180" t="s">
+        <v>17</v>
+      </c>
+      <c r="I180" t="s">
+        <v>18</v>
+      </c>
+      <c r="K180">
+        <v>100</v>
+      </c>
+      <c r="L180">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>26</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181" t="s">
+        <v>21</v>
+      </c>
+      <c r="E181" t="s">
+        <v>170</v>
+      </c>
+      <c r="F181" t="s">
+        <v>63</v>
+      </c>
+      <c r="G181" t="s">
+        <v>167</v>
+      </c>
+      <c r="H181" t="s">
+        <v>17</v>
+      </c>
+      <c r="I181" t="s">
+        <v>18</v>
+      </c>
+      <c r="K181">
+        <v>100</v>
+      </c>
+      <c r="L181">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182">
+        <v>14</v>
+      </c>
+      <c r="C182">
+        <v>22</v>
+      </c>
+      <c r="D182" t="s">
+        <v>172</v>
+      </c>
+      <c r="E182" t="s">
+        <v>173</v>
+      </c>
+      <c r="F182" t="s">
+        <v>15</v>
+      </c>
+      <c r="G182" t="s">
+        <v>174</v>
+      </c>
+      <c r="H182" t="s">
+        <v>17</v>
+      </c>
+      <c r="I182" t="s">
+        <v>18</v>
+      </c>
+      <c r="J182" t="s">
+        <v>175</v>
+      </c>
+      <c r="K182">
+        <v>100</v>
+      </c>
+      <c r="L182">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>20</v>
+      </c>
+      <c r="B183">
+        <v>1</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183" t="s">
+        <v>21</v>
+      </c>
+      <c r="E183" t="s">
+        <v>173</v>
+      </c>
+      <c r="F183" t="s">
+        <v>15</v>
+      </c>
+      <c r="G183" t="s">
+        <v>174</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183" t="s">
+        <v>18</v>
+      </c>
+      <c r="J183" t="s">
+        <v>176</v>
+      </c>
+      <c r="K183">
+        <v>100</v>
+      </c>
+      <c r="L183">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>22</v>
+      </c>
+      <c r="B184">
+        <v>28</v>
+      </c>
+      <c r="C184">
+        <v>33</v>
+      </c>
+      <c r="D184" t="s">
+        <v>177</v>
+      </c>
+      <c r="E184" t="s">
+        <v>173</v>
+      </c>
+      <c r="F184" t="s">
+        <v>15</v>
+      </c>
+      <c r="G184" t="s">
+        <v>174</v>
+      </c>
+      <c r="H184" t="s">
+        <v>17</v>
+      </c>
+      <c r="I184" t="s">
+        <v>18</v>
+      </c>
+      <c r="J184" t="s">
+        <v>178</v>
+      </c>
+      <c r="K184">
+        <v>100</v>
+      </c>
+      <c r="L184">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>24</v>
+      </c>
+      <c r="B185">
+        <v>56</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185" t="s">
+        <v>21</v>
+      </c>
+      <c r="E185" t="s">
+        <v>173</v>
+      </c>
+      <c r="F185" t="s">
+        <v>15</v>
+      </c>
+      <c r="G185" t="s">
+        <v>174</v>
+      </c>
+      <c r="H185" t="s">
+        <v>17</v>
+      </c>
+      <c r="I185" t="s">
+        <v>18</v>
+      </c>
+      <c r="J185" t="s">
+        <v>179</v>
+      </c>
+      <c r="K185">
+        <v>100</v>
+      </c>
+      <c r="L185">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>26</v>
+      </c>
+      <c r="B186">
+        <v>600</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186" t="s">
+        <v>21</v>
+      </c>
+      <c r="E186" t="s">
+        <v>173</v>
+      </c>
+      <c r="F186" t="s">
+        <v>15</v>
+      </c>
+      <c r="G186" t="s">
+        <v>174</v>
+      </c>
+      <c r="H186" t="s">
+        <v>17</v>
+      </c>
+      <c r="I186" t="s">
+        <v>18</v>
+      </c>
+      <c r="K186">
+        <v>100</v>
+      </c>
+      <c r="L186">
+        <v>90.4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>12</v>
+      </c>
+      <c r="B187">
+        <v>21</v>
+      </c>
+      <c r="C187">
+        <v>24</v>
+      </c>
+      <c r="D187" t="s">
+        <v>180</v>
+      </c>
+      <c r="E187" t="s">
+        <v>181</v>
+      </c>
+      <c r="F187" t="s">
+        <v>28</v>
+      </c>
+      <c r="G187" t="s">
+        <v>174</v>
+      </c>
+      <c r="H187" t="s">
+        <v>17</v>
+      </c>
+      <c r="I187" t="s">
+        <v>18</v>
+      </c>
+      <c r="K187">
+        <v>100</v>
+      </c>
+      <c r="L187">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>20</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188" t="s">
+        <v>21</v>
+      </c>
+      <c r="E188" t="s">
+        <v>181</v>
+      </c>
+      <c r="F188" t="s">
+        <v>28</v>
+      </c>
+      <c r="G188" t="s">
+        <v>174</v>
+      </c>
+      <c r="H188" t="s">
+        <v>17</v>
+      </c>
+      <c r="I188" t="s">
+        <v>18</v>
+      </c>
+      <c r="K188">
+        <v>100</v>
+      </c>
+      <c r="L188">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>22</v>
+      </c>
+      <c r="B189">
+        <v>42</v>
+      </c>
+      <c r="C189">
+        <v>32</v>
+      </c>
+      <c r="D189" t="s">
+        <v>182</v>
+      </c>
+      <c r="E189" t="s">
+        <v>181</v>
+      </c>
+      <c r="F189" t="s">
+        <v>28</v>
+      </c>
+      <c r="G189" t="s">
+        <v>174</v>
+      </c>
+      <c r="H189" t="s">
+        <v>17</v>
+      </c>
+      <c r="I189" t="s">
+        <v>18</v>
+      </c>
+      <c r="K189">
+        <v>100</v>
+      </c>
+      <c r="L189">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>24</v>
+      </c>
+      <c r="B190">
+        <v>84</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190" t="s">
+        <v>21</v>
+      </c>
+      <c r="E190" t="s">
+        <v>181</v>
+      </c>
+      <c r="F190" t="s">
+        <v>28</v>
+      </c>
+      <c r="G190" t="s">
+        <v>174</v>
+      </c>
+      <c r="H190" t="s">
+        <v>17</v>
+      </c>
+      <c r="I190" t="s">
+        <v>18</v>
+      </c>
+      <c r="K190">
+        <v>100</v>
+      </c>
+      <c r="L190">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>26</v>
+      </c>
+      <c r="B191">
+        <v>900</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191" t="s">
+        <v>21</v>
+      </c>
+      <c r="E191" t="s">
+        <v>181</v>
+      </c>
+      <c r="F191" t="s">
+        <v>28</v>
+      </c>
+      <c r="G191" t="s">
+        <v>174</v>
+      </c>
+      <c r="H191" t="s">
+        <v>17</v>
+      </c>
+      <c r="I191" t="s">
+        <v>18</v>
+      </c>
+      <c r="K191">
+        <v>100</v>
+      </c>
+      <c r="L191">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>12</v>
+      </c>
+      <c r="B192">
+        <v>21</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192" t="s">
+        <v>21</v>
+      </c>
+      <c r="E192" t="s">
+        <v>62</v>
+      </c>
+      <c r="F192" t="s">
+        <v>63</v>
+      </c>
+      <c r="G192" t="s">
+        <v>174</v>
+      </c>
+      <c r="H192" t="s">
+        <v>17</v>
+      </c>
+      <c r="I192" t="s">
+        <v>18</v>
+      </c>
+      <c r="J192" t="s">
+        <v>183</v>
+      </c>
+      <c r="K192">
+        <v>100</v>
+      </c>
+      <c r="L192">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>20</v>
+      </c>
+      <c r="B193">
+        <v>2</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193" t="s">
+        <v>21</v>
+      </c>
+      <c r="E193" t="s">
+        <v>62</v>
+      </c>
+      <c r="F193" t="s">
+        <v>63</v>
+      </c>
+      <c r="G193" t="s">
+        <v>174</v>
+      </c>
+      <c r="H193" t="s">
+        <v>17</v>
+      </c>
+      <c r="I193" t="s">
+        <v>18</v>
+      </c>
+      <c r="K193">
+        <v>100</v>
+      </c>
+      <c r="L193">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>22</v>
+      </c>
+      <c r="B194">
+        <v>42</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194" t="s">
+        <v>21</v>
+      </c>
+      <c r="E194" t="s">
+        <v>62</v>
+      </c>
+      <c r="F194" t="s">
+        <v>63</v>
+      </c>
+      <c r="G194" t="s">
+        <v>174</v>
+      </c>
+      <c r="H194" t="s">
+        <v>17</v>
+      </c>
+      <c r="I194" t="s">
+        <v>18</v>
+      </c>
+      <c r="K194">
+        <v>100</v>
+      </c>
+      <c r="L194">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>24</v>
+      </c>
+      <c r="B195">
+        <v>84</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195" t="s">
+        <v>21</v>
+      </c>
+      <c r="E195" t="s">
+        <v>62</v>
+      </c>
+      <c r="F195" t="s">
+        <v>63</v>
+      </c>
+      <c r="G195" t="s">
+        <v>174</v>
+      </c>
+      <c r="H195" t="s">
+        <v>17</v>
+      </c>
+      <c r="I195" t="s">
+        <v>18</v>
+      </c>
+      <c r="K195">
+        <v>100</v>
+      </c>
+      <c r="L195">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>26</v>
+      </c>
+      <c r="B196">
+        <v>900</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196" t="s">
+        <v>21</v>
+      </c>
+      <c r="E196" t="s">
+        <v>62</v>
+      </c>
+      <c r="F196" t="s">
+        <v>63</v>
+      </c>
+      <c r="G196" t="s">
+        <v>174</v>
+      </c>
+      <c r="H196" t="s">
+        <v>17</v>
+      </c>
+      <c r="I196" t="s">
+        <v>18</v>
+      </c>
+      <c r="K196">
+        <v>100</v>
+      </c>
+      <c r="L196">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>12</v>
+      </c>
+      <c r="B197">
+        <v>21</v>
+      </c>
+      <c r="C197">
+        <v>2</v>
+      </c>
+      <c r="D197" t="s">
+        <v>184</v>
+      </c>
+      <c r="E197" t="s">
+        <v>69</v>
+      </c>
+      <c r="F197" t="s">
+        <v>63</v>
+      </c>
+      <c r="G197" t="s">
+        <v>174</v>
+      </c>
+      <c r="H197" t="s">
+        <v>17</v>
+      </c>
+      <c r="I197" t="s">
+        <v>18</v>
+      </c>
+      <c r="J197" t="s">
+        <v>185</v>
+      </c>
+      <c r="K197">
+        <v>100</v>
+      </c>
+      <c r="L197">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>20</v>
+      </c>
+      <c r="B198">
+        <v>2</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198" t="s">
+        <v>21</v>
+      </c>
+      <c r="E198" t="s">
+        <v>69</v>
+      </c>
+      <c r="F198" t="s">
+        <v>63</v>
+      </c>
+      <c r="G198" t="s">
+        <v>174</v>
+      </c>
+      <c r="H198" t="s">
+        <v>17</v>
+      </c>
+      <c r="I198" t="s">
+        <v>18</v>
+      </c>
+      <c r="K198">
+        <v>100</v>
+      </c>
+      <c r="L198">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>22</v>
+      </c>
+      <c r="B199">
+        <v>42</v>
+      </c>
+      <c r="C199">
+        <v>7</v>
+      </c>
+      <c r="D199" t="s">
+        <v>107</v>
+      </c>
+      <c r="E199" t="s">
+        <v>69</v>
+      </c>
+      <c r="F199" t="s">
+        <v>63</v>
+      </c>
+      <c r="G199" t="s">
+        <v>174</v>
+      </c>
+      <c r="H199" t="s">
+        <v>17</v>
+      </c>
+      <c r="I199" t="s">
+        <v>18</v>
+      </c>
+      <c r="J199" t="s">
+        <v>186</v>
+      </c>
+      <c r="K199">
+        <v>100</v>
+      </c>
+      <c r="L199">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>24</v>
+      </c>
+      <c r="B200">
+        <v>84</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200" t="s">
+        <v>21</v>
+      </c>
+      <c r="E200" t="s">
+        <v>69</v>
+      </c>
+      <c r="F200" t="s">
+        <v>63</v>
+      </c>
+      <c r="G200" t="s">
+        <v>174</v>
+      </c>
+      <c r="H200" t="s">
+        <v>17</v>
+      </c>
+      <c r="I200" t="s">
+        <v>18</v>
+      </c>
+      <c r="J200" t="s">
+        <v>187</v>
+      </c>
+      <c r="K200">
+        <v>100</v>
+      </c>
+      <c r="L200">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>26</v>
+      </c>
+      <c r="B201">
+        <v>900</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201" t="s">
+        <v>21</v>
+      </c>
+      <c r="E201" t="s">
+        <v>69</v>
+      </c>
+      <c r="F201" t="s">
+        <v>63</v>
+      </c>
+      <c r="G201" t="s">
+        <v>174</v>
+      </c>
+      <c r="H201" t="s">
+        <v>17</v>
+      </c>
+      <c r="I201" t="s">
+        <v>18</v>
+      </c>
+      <c r="K201">
+        <v>100</v>
+      </c>
+      <c r="L201">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>12</v>
+      </c>
+      <c r="B202">
+        <v>22</v>
+      </c>
+      <c r="C202">
+        <v>21</v>
+      </c>
+      <c r="D202" t="s">
+        <v>88</v>
+      </c>
+      <c r="E202" t="s">
+        <v>188</v>
+      </c>
+      <c r="F202" t="s">
+        <v>15</v>
+      </c>
+      <c r="G202" t="s">
+        <v>189</v>
+      </c>
+      <c r="H202" t="s">
+        <v>17</v>
+      </c>
+      <c r="I202" t="s">
+        <v>18</v>
+      </c>
+      <c r="K202">
+        <v>100</v>
+      </c>
+      <c r="L202">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>20</v>
+      </c>
+      <c r="B203">
+        <v>3</v>
+      </c>
+      <c r="C203">
+        <v>8</v>
+      </c>
+      <c r="D203" t="s">
+        <v>190</v>
+      </c>
+      <c r="E203" t="s">
+        <v>188</v>
+      </c>
+      <c r="F203" t="s">
+        <v>15</v>
+      </c>
+      <c r="G203" t="s">
+        <v>189</v>
+      </c>
+      <c r="H203" t="s">
+        <v>17</v>
+      </c>
+      <c r="I203" t="s">
+        <v>18</v>
+      </c>
+      <c r="K203">
+        <v>100</v>
+      </c>
+      <c r="L203">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>22</v>
+      </c>
+      <c r="B204">
+        <v>39</v>
+      </c>
+      <c r="C204">
+        <v>43</v>
+      </c>
+      <c r="D204" t="s">
+        <v>59</v>
+      </c>
+      <c r="E204" t="s">
+        <v>188</v>
+      </c>
+      <c r="F204" t="s">
+        <v>15</v>
+      </c>
+      <c r="G204" t="s">
+        <v>189</v>
+      </c>
+      <c r="H204" t="s">
+        <v>17</v>
+      </c>
+      <c r="I204" t="s">
+        <v>18</v>
+      </c>
+      <c r="K204">
+        <v>100</v>
+      </c>
+      <c r="L204">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>24</v>
+      </c>
+      <c r="B205">
+        <v>69</v>
+      </c>
+      <c r="C205">
+        <v>116</v>
+      </c>
+      <c r="D205" t="s">
+        <v>191</v>
+      </c>
+      <c r="E205" t="s">
+        <v>188</v>
+      </c>
+      <c r="F205" t="s">
+        <v>15</v>
+      </c>
+      <c r="G205" t="s">
+        <v>189</v>
+      </c>
+      <c r="H205" t="s">
+        <v>17</v>
+      </c>
+      <c r="I205" t="s">
+        <v>18</v>
+      </c>
+      <c r="K205">
+        <v>100</v>
+      </c>
+      <c r="L205">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>26</v>
+      </c>
+      <c r="B206">
+        <v>473</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206" t="s">
+        <v>21</v>
+      </c>
+      <c r="E206" t="s">
+        <v>188</v>
+      </c>
+      <c r="F206" t="s">
+        <v>15</v>
+      </c>
+      <c r="G206" t="s">
+        <v>189</v>
+      </c>
+      <c r="H206" t="s">
+        <v>17</v>
+      </c>
+      <c r="I206" t="s">
+        <v>18</v>
+      </c>
+      <c r="K206">
+        <v>100</v>
+      </c>
+      <c r="L206">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>12</v>
+      </c>
+      <c r="B207">
+        <v>15</v>
+      </c>
+      <c r="C207">
+        <v>13</v>
+      </c>
+      <c r="D207" t="s">
+        <v>81</v>
+      </c>
+      <c r="E207" t="s">
+        <v>192</v>
+      </c>
+      <c r="F207" t="s">
+        <v>28</v>
+      </c>
+      <c r="G207" t="s">
+        <v>189</v>
+      </c>
+      <c r="H207" t="s">
+        <v>17</v>
+      </c>
+      <c r="I207" t="s">
+        <v>18</v>
+      </c>
+      <c r="J207" t="s">
+        <v>193</v>
+      </c>
+      <c r="K207">
+        <v>100</v>
+      </c>
+      <c r="L207">
+        <v>109.6</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>20</v>
+      </c>
+      <c r="B208">
+        <v>2</v>
+      </c>
+      <c r="C208">
+        <v>6</v>
+      </c>
+      <c r="D208" t="s">
+        <v>194</v>
+      </c>
+      <c r="E208" t="s">
+        <v>192</v>
+      </c>
+      <c r="F208" t="s">
+        <v>28</v>
+      </c>
+      <c r="G208" t="s">
+        <v>189</v>
+      </c>
+      <c r="H208" t="s">
+        <v>17</v>
+      </c>
+      <c r="I208" t="s">
+        <v>18</v>
+      </c>
+      <c r="K208">
+        <v>100</v>
+      </c>
+      <c r="L208">
+        <v>109.6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>22</v>
+      </c>
+      <c r="B209">
+        <v>27</v>
+      </c>
+      <c r="C209">
+        <v>26</v>
+      </c>
+      <c r="D209" t="s">
+        <v>195</v>
+      </c>
+      <c r="E209" t="s">
+        <v>192</v>
+      </c>
+      <c r="F209" t="s">
+        <v>28</v>
+      </c>
+      <c r="G209" t="s">
+        <v>189</v>
+      </c>
+      <c r="H209" t="s">
+        <v>17</v>
+      </c>
+      <c r="I209" t="s">
+        <v>18</v>
+      </c>
+      <c r="K209">
+        <v>100</v>
+      </c>
+      <c r="L209">
+        <v>109.6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>24</v>
+      </c>
+      <c r="B210">
+        <v>47</v>
+      </c>
+      <c r="C210">
+        <v>47</v>
+      </c>
+      <c r="D210" t="s">
+        <v>44</v>
+      </c>
+      <c r="E210" t="s">
+        <v>192</v>
+      </c>
+      <c r="F210" t="s">
+        <v>28</v>
+      </c>
+      <c r="G210" t="s">
+        <v>189</v>
+      </c>
+      <c r="H210" t="s">
+        <v>17</v>
+      </c>
+      <c r="I210" t="s">
+        <v>18</v>
+      </c>
+      <c r="K210">
+        <v>100</v>
+      </c>
+      <c r="L210">
+        <v>109.6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>26</v>
+      </c>
+      <c r="B211">
+        <v>318</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211" t="s">
+        <v>21</v>
+      </c>
+      <c r="E211" t="s">
+        <v>192</v>
+      </c>
+      <c r="F211" t="s">
+        <v>28</v>
+      </c>
+      <c r="G211" t="s">
+        <v>189</v>
+      </c>
+      <c r="H211" t="s">
+        <v>17</v>
+      </c>
+      <c r="I211" t="s">
+        <v>18</v>
+      </c>
+      <c r="K211">
+        <v>100</v>
+      </c>
+      <c r="L211">
+        <v>109.6</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>12</v>
+      </c>
+      <c r="B212">
+        <v>33</v>
+      </c>
+      <c r="C212">
+        <v>23</v>
+      </c>
+      <c r="D212" t="s">
+        <v>196</v>
+      </c>
+      <c r="E212" t="s">
+        <v>197</v>
+      </c>
+      <c r="F212" t="s">
+        <v>28</v>
+      </c>
+      <c r="G212" t="s">
+        <v>189</v>
+      </c>
+      <c r="H212" t="s">
+        <v>17</v>
+      </c>
+      <c r="I212" t="s">
+        <v>18</v>
+      </c>
+      <c r="K212">
+        <v>100</v>
+      </c>
+      <c r="L212">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>20</v>
+      </c>
+      <c r="B213">
+        <v>5</v>
+      </c>
+      <c r="C213">
+        <v>5</v>
+      </c>
+      <c r="D213" t="s">
+        <v>44</v>
+      </c>
+      <c r="E213" t="s">
+        <v>197</v>
+      </c>
+      <c r="F213" t="s">
+        <v>28</v>
+      </c>
+      <c r="G213" t="s">
+        <v>189</v>
+      </c>
+      <c r="H213" t="s">
+        <v>17</v>
+      </c>
+      <c r="I213" t="s">
+        <v>18</v>
+      </c>
+      <c r="K213">
+        <v>100</v>
+      </c>
+      <c r="L213">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>22</v>
+      </c>
+      <c r="B214">
+        <v>59</v>
+      </c>
+      <c r="C214">
+        <v>50</v>
+      </c>
+      <c r="D214" t="s">
+        <v>56</v>
+      </c>
+      <c r="E214" t="s">
+        <v>197</v>
+      </c>
+      <c r="F214" t="s">
+        <v>28</v>
+      </c>
+      <c r="G214" t="s">
+        <v>189</v>
+      </c>
+      <c r="H214" t="s">
+        <v>17</v>
+      </c>
+      <c r="I214" t="s">
+        <v>18</v>
+      </c>
+      <c r="K214">
+        <v>100</v>
+      </c>
+      <c r="L214">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>24</v>
+      </c>
+      <c r="B215">
+        <v>104</v>
+      </c>
+      <c r="C215">
         <v>82</v>
       </c>
-      <c r="F71" t="s">
-        <v>21</v>
-      </c>
-      <c r="G71" t="s">
-        <v>75</v>
-      </c>
-      <c r="H71" t="s">
-        <v>14</v>
-      </c>
-      <c r="I71" t="s">
-        <v>15</v>
-      </c>
-      <c r="K71">
-        <v>100</v>
-      </c>
-      <c r="L71">
-        <v>78.8</v>
+      <c r="D215" t="s">
+        <v>198</v>
+      </c>
+      <c r="E215" t="s">
+        <v>197</v>
+      </c>
+      <c r="F215" t="s">
+        <v>28</v>
+      </c>
+      <c r="G215" t="s">
+        <v>189</v>
+      </c>
+      <c r="H215" t="s">
+        <v>17</v>
+      </c>
+      <c r="I215" t="s">
+        <v>18</v>
+      </c>
+      <c r="K215">
+        <v>100</v>
+      </c>
+      <c r="L215">
+        <v>74.3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>26</v>
+      </c>
+      <c r="B216">
+        <v>709</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216" t="s">
+        <v>21</v>
+      </c>
+      <c r="E216" t="s">
+        <v>197</v>
+      </c>
+      <c r="F216" t="s">
+        <v>28</v>
+      </c>
+      <c r="G216" t="s">
+        <v>189</v>
+      </c>
+      <c r="H216" t="s">
+        <v>17</v>
+      </c>
+      <c r="I216" t="s">
+        <v>18</v>
+      </c>
+      <c r="K216">
+        <v>100</v>
+      </c>
+      <c r="L216">
+        <v>74.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_77DDB655914D040E62355476585DCE3A87458B1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_77DDB655914D040E62355476585DCE3A87458B1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894CA02A-7E36-43F4-AC0C-F13CEAA9F415}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="208">
   <si>
     <t>Producto</t>
   </si>
@@ -322,9 +322,6 @@
     <t>Estelli Alejandra Ramirez Florez</t>
   </si>
   <si>
-    <t>12 días x vac meta puntos 453.9       meta post  5</t>
-  </si>
-  <si>
     <t>meta terminales 16</t>
   </si>
   <si>
@@ -547,9 +544,6 @@
     <t>TERMINAL NORTE</t>
   </si>
   <si>
-    <t xml:space="preserve">20 días x vac Meta puntos 921.7   meta postpago </t>
-  </si>
-  <si>
     <t>meta Hogar 1</t>
   </si>
   <si>
@@ -617,25 +611,52 @@
   </si>
   <si>
     <t>79%</t>
+  </si>
+  <si>
+    <t>42%</t>
+  </si>
+  <si>
+    <t>Lider Geraldin Angulo Jaramillo</t>
+  </si>
+  <si>
+    <t>YARUMAL</t>
+  </si>
+  <si>
+    <t>77%</t>
+  </si>
+  <si>
+    <t>Pendiente 4 porta pre</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>Vacaciones del 26 de junio al 13 de julio, en junio no aplica el promedio de 2 días por vacaciones</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elabora 20 días x vac  Meta puntos 921.7   meta postpago </t>
+  </si>
+  <si>
+    <t>Elabora 12 días x vac meta puntos 453.9       meta post  5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -646,7 +667,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -654,30 +675,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -980,44 +983,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L226"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3880,22 +3883,22 @@
         <v>12</v>
       </c>
       <c r="B82">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C82">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E82" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F82" t="s">
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -3907,7 +3910,7 @@
         <v>100</v>
       </c>
       <c r="L82">
-        <v>111.6</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,13 +3927,13 @@
         <v>21</v>
       </c>
       <c r="E83" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F83" t="s">
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -3942,7 +3945,7 @@
         <v>100</v>
       </c>
       <c r="L83">
-        <v>111.6</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -3950,22 +3953,22 @@
         <v>22</v>
       </c>
       <c r="B84">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C84">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E84" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F84" t="s">
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -3977,7 +3980,7 @@
         <v>100</v>
       </c>
       <c r="L84">
-        <v>111.6</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3985,22 +3988,22 @@
         <v>24</v>
       </c>
       <c r="B85">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C85">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D85" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="E85" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F85" t="s">
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -4012,7 +4015,7 @@
         <v>100</v>
       </c>
       <c r="L85">
-        <v>111.6</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4020,7 +4023,7 @@
         <v>26</v>
       </c>
       <c r="B86">
-        <v>480</v>
+        <v>750</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -4029,13 +4032,13 @@
         <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F86" t="s">
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -4047,7 +4050,7 @@
         <v>100</v>
       </c>
       <c r="L86">
-        <v>111.6</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4055,22 +4058,22 @@
         <v>12</v>
       </c>
       <c r="B87">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="E87" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F87" t="s">
         <v>28</v>
       </c>
       <c r="G87" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -4079,13 +4082,13 @@
         <v>18</v>
       </c>
       <c r="J87" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="K87">
         <v>100</v>
       </c>
       <c r="L87">
-        <v>33.700000000000003</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4102,13 +4105,13 @@
         <v>21</v>
       </c>
       <c r="E88" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F88" t="s">
         <v>28</v>
       </c>
       <c r="G88" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -4120,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="L88">
-        <v>33.700000000000003</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4128,22 +4131,22 @@
         <v>22</v>
       </c>
       <c r="B89">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C89">
         <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="E89" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F89" t="s">
         <v>28</v>
       </c>
       <c r="G89" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -4151,14 +4154,11 @@
       <c r="I89" t="s">
         <v>18</v>
       </c>
-      <c r="J89" t="s">
-        <v>101</v>
-      </c>
       <c r="K89">
         <v>100</v>
       </c>
       <c r="L89">
-        <v>33.700000000000003</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4166,7 +4166,7 @@
         <v>24</v>
       </c>
       <c r="B90">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4175,13 +4175,13 @@
         <v>21</v>
       </c>
       <c r="E90" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F90" t="s">
         <v>28</v>
       </c>
       <c r="G90" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -4189,14 +4189,11 @@
       <c r="I90" t="s">
         <v>18</v>
       </c>
-      <c r="J90" t="s">
-        <v>102</v>
-      </c>
       <c r="K90">
         <v>100</v>
       </c>
       <c r="L90">
-        <v>33.700000000000003</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4204,7 +4201,7 @@
         <v>26</v>
       </c>
       <c r="B91">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4213,13 +4210,13 @@
         <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F91" t="s">
         <v>28</v>
       </c>
       <c r="G91" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -4231,7 +4228,7 @@
         <v>100</v>
       </c>
       <c r="L91">
-        <v>33.700000000000003</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4242,31 +4239,34 @@
         <v>12</v>
       </c>
       <c r="C92">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D92" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E92" t="s">
+        <v>110</v>
+      </c>
+      <c r="F92" t="s">
+        <v>28</v>
+      </c>
+      <c r="G92" t="s">
         <v>104</v>
       </c>
-      <c r="F92" t="s">
-        <v>15</v>
-      </c>
-      <c r="G92" t="s">
-        <v>105</v>
-      </c>
       <c r="H92" t="s">
         <v>17</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
       </c>
+      <c r="J92" t="s">
+        <v>111</v>
+      </c>
       <c r="K92">
         <v>100</v>
       </c>
       <c r="L92">
-        <v>125.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4283,14 +4283,14 @@
         <v>21</v>
       </c>
       <c r="E93" t="s">
+        <v>110</v>
+      </c>
+      <c r="F93" t="s">
+        <v>28</v>
+      </c>
+      <c r="G93" t="s">
         <v>104</v>
       </c>
-      <c r="F93" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" t="s">
-        <v>105</v>
-      </c>
       <c r="H93" t="s">
         <v>17</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>100</v>
       </c>
       <c r="L93">
-        <v>125.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4312,20 +4312,20 @@
         <v>55</v>
       </c>
       <c r="C94">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="D94" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E94" t="s">
+        <v>110</v>
+      </c>
+      <c r="F94" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" t="s">
         <v>104</v>
       </c>
-      <c r="F94" t="s">
-        <v>15</v>
-      </c>
-      <c r="G94" t="s">
-        <v>105</v>
-      </c>
       <c r="H94" t="s">
         <v>17</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>100</v>
       </c>
       <c r="L94">
-        <v>125.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4353,14 +4353,14 @@
         <v>21</v>
       </c>
       <c r="E95" t="s">
+        <v>110</v>
+      </c>
+      <c r="F95" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" t="s">
         <v>104</v>
       </c>
-      <c r="F95" t="s">
-        <v>15</v>
-      </c>
-      <c r="G95" t="s">
-        <v>105</v>
-      </c>
       <c r="H95" t="s">
         <v>17</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>100</v>
       </c>
       <c r="L95">
-        <v>125.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4388,14 +4388,14 @@
         <v>21</v>
       </c>
       <c r="E96" t="s">
+        <v>110</v>
+      </c>
+      <c r="F96" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" t="s">
         <v>104</v>
       </c>
-      <c r="F96" t="s">
-        <v>15</v>
-      </c>
-      <c r="G96" t="s">
-        <v>105</v>
-      </c>
       <c r="H96" t="s">
         <v>17</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>100</v>
       </c>
       <c r="L96">
-        <v>125.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4414,22 +4414,22 @@
         <v>12</v>
       </c>
       <c r="B97">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E97" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F97" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -4437,14 +4437,11 @@
       <c r="I97" t="s">
         <v>18</v>
       </c>
-      <c r="J97" t="s">
-        <v>109</v>
-      </c>
       <c r="K97">
         <v>100</v>
       </c>
       <c r="L97">
-        <v>27.1</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4452,22 +4449,22 @@
         <v>20</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E98" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F98" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -4479,7 +4476,7 @@
         <v>100</v>
       </c>
       <c r="L98">
-        <v>27.1</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4487,22 +4484,22 @@
         <v>22</v>
       </c>
       <c r="B99">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="C99">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E99" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F99" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -4514,7 +4511,7 @@
         <v>100</v>
       </c>
       <c r="L99">
-        <v>27.1</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4522,7 +4519,7 @@
         <v>24</v>
       </c>
       <c r="B100">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -4531,13 +4528,13 @@
         <v>21</v>
       </c>
       <c r="E100" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F100" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -4549,7 +4546,7 @@
         <v>100</v>
       </c>
       <c r="L100">
-        <v>27.1</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4557,7 +4554,7 @@
         <v>26</v>
       </c>
       <c r="B101">
-        <v>750</v>
+        <v>375</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4566,13 +4563,13 @@
         <v>21</v>
       </c>
       <c r="E101" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F101" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -4584,7 +4581,7 @@
         <v>100</v>
       </c>
       <c r="L101">
-        <v>27.1</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4592,22 +4589,22 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D102" t="s">
-        <v>21</v>
+        <v>118</v>
       </c>
       <c r="E102" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
       </c>
       <c r="G102" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -4615,14 +4612,11 @@
       <c r="I102" t="s">
         <v>18</v>
       </c>
-      <c r="J102" t="s">
-        <v>112</v>
-      </c>
       <c r="K102">
         <v>100</v>
       </c>
       <c r="L102">
-        <v>43.6</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4630,22 +4624,22 @@
         <v>20</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D103" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E103" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
       </c>
       <c r="G103" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4657,7 +4651,7 @@
         <v>100</v>
       </c>
       <c r="L103">
-        <v>43.6</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4665,22 +4659,22 @@
         <v>22</v>
       </c>
       <c r="B104">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C104">
         <v>25</v>
       </c>
       <c r="D104" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E104" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
       </c>
       <c r="G104" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -4692,7 +4686,7 @@
         <v>100</v>
       </c>
       <c r="L104">
-        <v>43.6</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4700,7 +4694,7 @@
         <v>24</v>
       </c>
       <c r="B105">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -4709,13 +4703,13 @@
         <v>21</v>
       </c>
       <c r="E105" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
       </c>
       <c r="G105" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -4727,7 +4721,7 @@
         <v>100</v>
       </c>
       <c r="L105">
-        <v>43.6</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4735,7 +4729,7 @@
         <v>26</v>
       </c>
       <c r="B106">
-        <v>750</v>
+        <v>563</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4744,13 +4738,13 @@
         <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
       </c>
       <c r="G106" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -4762,7 +4756,7 @@
         <v>100</v>
       </c>
       <c r="L106">
-        <v>43.6</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4770,34 +4764,37 @@
         <v>12</v>
       </c>
       <c r="B107">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C107">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D107" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E107" t="s">
+        <v>122</v>
+      </c>
+      <c r="F107" t="s">
+        <v>28</v>
+      </c>
+      <c r="G107" t="s">
         <v>115</v>
       </c>
-      <c r="F107" t="s">
-        <v>15</v>
-      </c>
-      <c r="G107" t="s">
-        <v>116</v>
-      </c>
       <c r="H107" t="s">
         <v>17</v>
       </c>
       <c r="I107" t="s">
         <v>18</v>
       </c>
+      <c r="J107" t="s">
+        <v>123</v>
+      </c>
       <c r="K107">
         <v>100</v>
       </c>
       <c r="L107">
-        <v>107.5</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4805,23 +4802,23 @@
         <v>20</v>
       </c>
       <c r="B108">
+        <v>5</v>
+      </c>
+      <c r="C108">
         <v>3</v>
       </c>
-      <c r="C108">
-        <v>2</v>
-      </c>
       <c r="D108" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E108" t="s">
+        <v>122</v>
+      </c>
+      <c r="F108" t="s">
+        <v>28</v>
+      </c>
+      <c r="G108" t="s">
         <v>115</v>
       </c>
-      <c r="F108" t="s">
-        <v>15</v>
-      </c>
-      <c r="G108" t="s">
-        <v>116</v>
-      </c>
       <c r="H108" t="s">
         <v>17</v>
       </c>
@@ -4832,7 +4829,7 @@
         <v>100</v>
       </c>
       <c r="L108">
-        <v>107.5</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4840,23 +4837,23 @@
         <v>22</v>
       </c>
       <c r="B109">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C109">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E109" t="s">
+        <v>122</v>
+      </c>
+      <c r="F109" t="s">
+        <v>28</v>
+      </c>
+      <c r="G109" t="s">
         <v>115</v>
       </c>
-      <c r="F109" t="s">
-        <v>15</v>
-      </c>
-      <c r="G109" t="s">
-        <v>116</v>
-      </c>
       <c r="H109" t="s">
         <v>17</v>
       </c>
@@ -4867,7 +4864,7 @@
         <v>100</v>
       </c>
       <c r="L109">
-        <v>107.5</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4875,7 +4872,7 @@
         <v>24</v>
       </c>
       <c r="B110">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -4884,14 +4881,14 @@
         <v>21</v>
       </c>
       <c r="E110" t="s">
+        <v>122</v>
+      </c>
+      <c r="F110" t="s">
+        <v>28</v>
+      </c>
+      <c r="G110" t="s">
         <v>115</v>
       </c>
-      <c r="F110" t="s">
-        <v>15</v>
-      </c>
-      <c r="G110" t="s">
-        <v>116</v>
-      </c>
       <c r="H110" t="s">
         <v>17</v>
       </c>
@@ -4902,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="L110">
-        <v>107.5</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4910,7 +4907,7 @@
         <v>26</v>
       </c>
       <c r="B111">
-        <v>375</v>
+        <v>563</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4919,14 +4916,14 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
+        <v>122</v>
+      </c>
+      <c r="F111" t="s">
+        <v>28</v>
+      </c>
+      <c r="G111" t="s">
         <v>115</v>
       </c>
-      <c r="F111" t="s">
-        <v>15</v>
-      </c>
-      <c r="G111" t="s">
-        <v>116</v>
-      </c>
       <c r="H111" t="s">
         <v>17</v>
       </c>
@@ -4937,7 +4934,7 @@
         <v>100</v>
       </c>
       <c r="L111">
-        <v>107.5</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -4945,22 +4942,22 @@
         <v>12</v>
       </c>
       <c r="B112">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C112">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D112" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E112" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F112" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -4980,22 +4977,22 @@
         <v>20</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C113">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E113" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F113" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -5015,22 +5012,22 @@
         <v>22</v>
       </c>
       <c r="B114">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C114">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D114" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E114" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F114" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G114" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -5050,7 +5047,7 @@
         <v>24</v>
       </c>
       <c r="B115">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -5059,13 +5056,13 @@
         <v>21</v>
       </c>
       <c r="E115" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F115" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G115" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -5085,7 +5082,7 @@
         <v>26</v>
       </c>
       <c r="B116">
-        <v>563</v>
+        <v>375</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5094,13 +5091,13 @@
         <v>21</v>
       </c>
       <c r="E116" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F116" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G116" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -5120,22 +5117,22 @@
         <v>12</v>
       </c>
       <c r="B117">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C117">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D117" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="E117" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F117" t="s">
         <v>28</v>
       </c>
       <c r="G117" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -5144,13 +5141,13 @@
         <v>18</v>
       </c>
       <c r="J117" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K117">
         <v>100</v>
       </c>
       <c r="L117">
-        <v>100.2</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5158,22 +5155,22 @@
         <v>20</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118">
         <v>3</v>
       </c>
       <c r="D118" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="E118" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F118" t="s">
         <v>28</v>
       </c>
       <c r="G118" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -5181,11 +5178,14 @@
       <c r="I118" t="s">
         <v>18</v>
       </c>
+      <c r="J118" t="s">
+        <v>131</v>
+      </c>
       <c r="K118">
         <v>100</v>
       </c>
       <c r="L118">
-        <v>100.2</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5193,22 +5193,22 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C119">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D119" t="s">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="E119" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F119" t="s">
         <v>28</v>
       </c>
       <c r="G119" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -5220,7 +5220,7 @@
         <v>100</v>
       </c>
       <c r="L119">
-        <v>100.2</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5228,22 +5228,22 @@
         <v>24</v>
       </c>
       <c r="B120">
+        <v>36</v>
+      </c>
+      <c r="C120">
         <v>68</v>
       </c>
-      <c r="C120">
-        <v>0</v>
-      </c>
       <c r="D120" t="s">
-        <v>21</v>
+        <v>132</v>
       </c>
       <c r="E120" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F120" t="s">
         <v>28</v>
       </c>
       <c r="G120" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -5255,7 +5255,7 @@
         <v>100</v>
       </c>
       <c r="L120">
-        <v>100.2</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5272,13 +5272,13 @@
         <v>21</v>
       </c>
       <c r="E121" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F121" t="s">
         <v>28</v>
       </c>
       <c r="G121" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -5290,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="L121">
-        <v>100.2</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5298,23 +5298,23 @@
         <v>12</v>
       </c>
       <c r="B122">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C122">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D122" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E122" t="s">
+        <v>134</v>
+      </c>
+      <c r="F122" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" t="s">
         <v>127</v>
       </c>
-      <c r="F122" t="s">
-        <v>15</v>
-      </c>
-      <c r="G122" t="s">
-        <v>128</v>
-      </c>
       <c r="H122" t="s">
         <v>17</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>100</v>
       </c>
       <c r="L122">
-        <v>115.1</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5333,23 +5333,23 @@
         <v>20</v>
       </c>
       <c r="B123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D123" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E123" t="s">
+        <v>134</v>
+      </c>
+      <c r="F123" t="s">
+        <v>28</v>
+      </c>
+      <c r="G123" t="s">
         <v>127</v>
       </c>
-      <c r="F123" t="s">
-        <v>15</v>
-      </c>
-      <c r="G123" t="s">
-        <v>128</v>
-      </c>
       <c r="H123" t="s">
         <v>17</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>100</v>
       </c>
       <c r="L123">
-        <v>115.1</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5368,23 +5368,23 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C124">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D124" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E124" t="s">
+        <v>134</v>
+      </c>
+      <c r="F124" t="s">
+        <v>28</v>
+      </c>
+      <c r="G124" t="s">
         <v>127</v>
       </c>
-      <c r="F124" t="s">
-        <v>15</v>
-      </c>
-      <c r="G124" t="s">
-        <v>128</v>
-      </c>
       <c r="H124" t="s">
         <v>17</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>100</v>
       </c>
       <c r="L124">
-        <v>115.1</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5403,23 +5403,23 @@
         <v>24</v>
       </c>
       <c r="B125">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D125" t="s">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="E125" t="s">
+        <v>134</v>
+      </c>
+      <c r="F125" t="s">
+        <v>28</v>
+      </c>
+      <c r="G125" t="s">
         <v>127</v>
       </c>
-      <c r="F125" t="s">
-        <v>15</v>
-      </c>
-      <c r="G125" t="s">
-        <v>128</v>
-      </c>
       <c r="H125" t="s">
         <v>17</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>100</v>
       </c>
       <c r="L125">
-        <v>115.1</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5438,7 +5438,7 @@
         <v>26</v>
       </c>
       <c r="B126">
-        <v>375</v>
+        <v>563</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -5447,14 +5447,14 @@
         <v>21</v>
       </c>
       <c r="E126" t="s">
+        <v>134</v>
+      </c>
+      <c r="F126" t="s">
+        <v>28</v>
+      </c>
+      <c r="G126" t="s">
         <v>127</v>
       </c>
-      <c r="F126" t="s">
-        <v>15</v>
-      </c>
-      <c r="G126" t="s">
-        <v>128</v>
-      </c>
       <c r="H126" t="s">
         <v>17</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>100</v>
       </c>
       <c r="L126">
-        <v>115.1</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5473,22 +5473,22 @@
         <v>12</v>
       </c>
       <c r="B127">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C127">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D127" t="s">
         <v>44</v>
       </c>
       <c r="E127" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F127" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G127" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -5496,14 +5496,11 @@
       <c r="I127" t="s">
         <v>18</v>
       </c>
-      <c r="J127" t="s">
-        <v>131</v>
-      </c>
       <c r="K127">
         <v>100</v>
       </c>
       <c r="L127">
-        <v>106.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5511,22 +5508,22 @@
         <v>20</v>
       </c>
       <c r="B128">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="E128" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F128" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G128" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -5534,14 +5531,11 @@
       <c r="I128" t="s">
         <v>18</v>
       </c>
-      <c r="J128" t="s">
-        <v>132</v>
-      </c>
       <c r="K128">
         <v>100</v>
       </c>
       <c r="L128">
-        <v>106.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5549,22 +5543,22 @@
         <v>22</v>
       </c>
       <c r="B129">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C129">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D129" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="E129" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F129" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G129" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -5576,7 +5570,7 @@
         <v>100</v>
       </c>
       <c r="L129">
-        <v>106.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5584,22 +5578,22 @@
         <v>24</v>
       </c>
       <c r="B130">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C130">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D130" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="E130" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F130" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G130" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -5611,7 +5605,7 @@
         <v>100</v>
       </c>
       <c r="L130">
-        <v>106.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5619,7 +5613,7 @@
         <v>26</v>
       </c>
       <c r="B131">
-        <v>563</v>
+        <v>480</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -5628,13 +5622,13 @@
         <v>21</v>
       </c>
       <c r="E131" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F131" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G131" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -5646,7 +5640,7 @@
         <v>100</v>
       </c>
       <c r="L131">
-        <v>106.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5654,22 +5648,22 @@
         <v>12</v>
       </c>
       <c r="B132">
+        <v>9</v>
+      </c>
+      <c r="C132">
         <v>11</v>
       </c>
-      <c r="C132">
-        <v>15</v>
-      </c>
       <c r="D132" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="E132" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F132" t="s">
         <v>28</v>
       </c>
       <c r="G132" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -5681,7 +5675,7 @@
         <v>100</v>
       </c>
       <c r="L132">
-        <v>125.9</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5689,22 +5683,22 @@
         <v>20</v>
       </c>
       <c r="B133">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C133">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="E133" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F133" t="s">
         <v>28</v>
       </c>
       <c r="G133" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -5716,7 +5710,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>125.9</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5724,22 +5718,22 @@
         <v>22</v>
       </c>
       <c r="B134">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C134">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D134" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E134" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
       </c>
       <c r="G134" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -5751,7 +5745,7 @@
         <v>100</v>
       </c>
       <c r="L134">
-        <v>125.9</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5759,22 +5753,22 @@
         <v>24</v>
       </c>
       <c r="B135">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C135">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D135" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E135" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
       </c>
       <c r="G135" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -5786,7 +5780,7 @@
         <v>100</v>
       </c>
       <c r="L135">
-        <v>125.9</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5794,7 +5788,7 @@
         <v>26</v>
       </c>
       <c r="B136">
-        <v>563</v>
+        <v>720</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5803,13 +5797,13 @@
         <v>21</v>
       </c>
       <c r="E136" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
       </c>
       <c r="G136" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -5821,7 +5815,7 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>125.9</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5829,34 +5823,37 @@
         <v>12</v>
       </c>
       <c r="B137">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C137">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D137" t="s">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="E137" t="s">
+        <v>62</v>
+      </c>
+      <c r="F137" t="s">
+        <v>63</v>
+      </c>
+      <c r="G137" t="s">
         <v>137</v>
       </c>
-      <c r="F137" t="s">
-        <v>15</v>
-      </c>
-      <c r="G137" t="s">
-        <v>138</v>
-      </c>
       <c r="H137" t="s">
         <v>17</v>
       </c>
       <c r="I137" t="s">
         <v>18</v>
       </c>
+      <c r="J137" t="s">
+        <v>142</v>
+      </c>
       <c r="K137">
         <v>100</v>
       </c>
       <c r="L137">
-        <v>54</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -5864,23 +5861,23 @@
         <v>20</v>
       </c>
       <c r="B138">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E138" t="s">
+        <v>62</v>
+      </c>
+      <c r="F138" t="s">
+        <v>63</v>
+      </c>
+      <c r="G138" t="s">
         <v>137</v>
       </c>
-      <c r="F138" t="s">
-        <v>15</v>
-      </c>
-      <c r="G138" t="s">
-        <v>138</v>
-      </c>
       <c r="H138" t="s">
         <v>17</v>
       </c>
@@ -5891,7 +5888,7 @@
         <v>100</v>
       </c>
       <c r="L138">
-        <v>54</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -5899,34 +5896,37 @@
         <v>22</v>
       </c>
       <c r="B139">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C139">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="E139" t="s">
+        <v>62</v>
+      </c>
+      <c r="F139" t="s">
+        <v>63</v>
+      </c>
+      <c r="G139" t="s">
         <v>137</v>
       </c>
-      <c r="F139" t="s">
-        <v>15</v>
-      </c>
-      <c r="G139" t="s">
-        <v>138</v>
-      </c>
       <c r="H139" t="s">
         <v>17</v>
       </c>
       <c r="I139" t="s">
         <v>18</v>
       </c>
+      <c r="J139" t="s">
+        <v>144</v>
+      </c>
       <c r="K139">
         <v>100</v>
       </c>
       <c r="L139">
-        <v>54</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -5934,7 +5934,7 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -5943,25 +5943,28 @@
         <v>21</v>
       </c>
       <c r="E140" t="s">
+        <v>62</v>
+      </c>
+      <c r="F140" t="s">
+        <v>63</v>
+      </c>
+      <c r="G140" t="s">
         <v>137</v>
       </c>
-      <c r="F140" t="s">
-        <v>15</v>
-      </c>
-      <c r="G140" t="s">
-        <v>138</v>
-      </c>
       <c r="H140" t="s">
         <v>17</v>
       </c>
       <c r="I140" t="s">
         <v>18</v>
       </c>
+      <c r="J140" t="s">
+        <v>144</v>
+      </c>
       <c r="K140">
         <v>100</v>
       </c>
       <c r="L140">
-        <v>54</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -5969,7 +5972,7 @@
         <v>26</v>
       </c>
       <c r="B141">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5978,14 +5981,14 @@
         <v>21</v>
       </c>
       <c r="E141" t="s">
+        <v>62</v>
+      </c>
+      <c r="F141" t="s">
+        <v>63</v>
+      </c>
+      <c r="G141" t="s">
         <v>137</v>
       </c>
-      <c r="F141" t="s">
-        <v>15</v>
-      </c>
-      <c r="G141" t="s">
-        <v>138</v>
-      </c>
       <c r="H141" t="s">
         <v>17</v>
       </c>
@@ -5996,7 +5999,7 @@
         <v>100</v>
       </c>
       <c r="L141">
-        <v>54</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -6004,22 +6007,22 @@
         <v>12</v>
       </c>
       <c r="B142">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C142">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D142" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="E142" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F142" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G142" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H142" t="s">
         <v>17</v>
@@ -6027,11 +6030,14 @@
       <c r="I142" t="s">
         <v>18</v>
       </c>
+      <c r="J142" t="s">
+        <v>148</v>
+      </c>
       <c r="K142">
         <v>100</v>
       </c>
       <c r="L142">
-        <v>62.5</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -6039,22 +6045,22 @@
         <v>20</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D143" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
       <c r="E143" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F143" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G143" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
@@ -6062,11 +6068,14 @@
       <c r="I143" t="s">
         <v>18</v>
       </c>
+      <c r="J143" t="s">
+        <v>66</v>
+      </c>
       <c r="K143">
         <v>100</v>
       </c>
       <c r="L143">
-        <v>62.5</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -6074,22 +6083,22 @@
         <v>22</v>
       </c>
       <c r="B144">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C144">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D144" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E144" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F144" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G144" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H144" t="s">
         <v>17</v>
@@ -6097,11 +6106,14 @@
       <c r="I144" t="s">
         <v>18</v>
       </c>
+      <c r="J144" t="s">
+        <v>151</v>
+      </c>
       <c r="K144">
         <v>100</v>
       </c>
       <c r="L144">
-        <v>62.5</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -6109,22 +6121,22 @@
         <v>24</v>
       </c>
       <c r="B145">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C145">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="E145" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F145" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G145" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H145" t="s">
         <v>17</v>
@@ -6132,11 +6144,14 @@
       <c r="I145" t="s">
         <v>18</v>
       </c>
+      <c r="J145" t="s">
+        <v>152</v>
+      </c>
       <c r="K145">
         <v>100</v>
       </c>
       <c r="L145">
-        <v>62.5</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -6144,7 +6159,7 @@
         <v>26</v>
       </c>
       <c r="B146">
-        <v>720</v>
+        <v>600</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -6153,13 +6168,13 @@
         <v>21</v>
       </c>
       <c r="E146" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F146" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G146" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H146" t="s">
         <v>17</v>
@@ -6167,11 +6182,14 @@
       <c r="I146" t="s">
         <v>18</v>
       </c>
+      <c r="J146" t="s">
+        <v>153</v>
+      </c>
       <c r="K146">
         <v>100</v>
       </c>
       <c r="L146">
-        <v>62.5</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -6179,22 +6197,22 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D147" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="E147" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="F147" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G147" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H147" t="s">
         <v>17</v>
@@ -6202,14 +6220,11 @@
       <c r="I147" t="s">
         <v>18</v>
       </c>
-      <c r="J147" t="s">
-        <v>143</v>
-      </c>
       <c r="K147">
         <v>100</v>
       </c>
       <c r="L147">
-        <v>4.7</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -6217,22 +6232,22 @@
         <v>20</v>
       </c>
       <c r="B148">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D148" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="E148" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="F148" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G148" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -6244,7 +6259,7 @@
         <v>100</v>
       </c>
       <c r="L148">
-        <v>4.7</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -6252,22 +6267,22 @@
         <v>22</v>
       </c>
       <c r="B149">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D149" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="E149" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="F149" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G149" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H149" t="s">
         <v>17</v>
@@ -6275,14 +6290,11 @@
       <c r="I149" t="s">
         <v>18</v>
       </c>
-      <c r="J149" t="s">
-        <v>145</v>
-      </c>
       <c r="K149">
         <v>100</v>
       </c>
       <c r="L149">
-        <v>4.7</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -6290,22 +6302,22 @@
         <v>24</v>
       </c>
       <c r="B150">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="D150" t="s">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="E150" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="F150" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G150" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H150" t="s">
         <v>17</v>
@@ -6313,14 +6325,11 @@
       <c r="I150" t="s">
         <v>18</v>
       </c>
-      <c r="J150" t="s">
-        <v>145</v>
-      </c>
       <c r="K150">
         <v>100</v>
       </c>
       <c r="L150">
-        <v>4.7</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -6328,7 +6337,7 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6337,13 +6346,13 @@
         <v>21</v>
       </c>
       <c r="E151" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="F151" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G151" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -6355,7 +6364,7 @@
         <v>100</v>
       </c>
       <c r="L151">
-        <v>4.7</v>
+        <v>95.9</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6363,23 +6372,23 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C152">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D152" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E152" t="s">
+        <v>62</v>
+      </c>
+      <c r="F152" t="s">
+        <v>63</v>
+      </c>
+      <c r="G152" t="s">
         <v>147</v>
       </c>
-      <c r="F152" t="s">
-        <v>15</v>
-      </c>
-      <c r="G152" t="s">
-        <v>148</v>
-      </c>
       <c r="H152" t="s">
         <v>17</v>
       </c>
@@ -6387,13 +6396,13 @@
         <v>18</v>
       </c>
       <c r="J152" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="K152">
         <v>100</v>
       </c>
       <c r="L152">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -6401,23 +6410,23 @@
         <v>20</v>
       </c>
       <c r="B153">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="E153" t="s">
+        <v>62</v>
+      </c>
+      <c r="F153" t="s">
+        <v>63</v>
+      </c>
+      <c r="G153" t="s">
         <v>147</v>
       </c>
-      <c r="F153" t="s">
-        <v>15</v>
-      </c>
-      <c r="G153" t="s">
-        <v>148</v>
-      </c>
       <c r="H153" t="s">
         <v>17</v>
       </c>
@@ -6425,13 +6434,13 @@
         <v>18</v>
       </c>
       <c r="J153" t="s">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="K153">
         <v>100</v>
       </c>
       <c r="L153">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6439,23 +6448,23 @@
         <v>22</v>
       </c>
       <c r="B154">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C154">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D154" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E154" t="s">
+        <v>62</v>
+      </c>
+      <c r="F154" t="s">
+        <v>63</v>
+      </c>
+      <c r="G154" t="s">
         <v>147</v>
       </c>
-      <c r="F154" t="s">
-        <v>15</v>
-      </c>
-      <c r="G154" t="s">
-        <v>148</v>
-      </c>
       <c r="H154" t="s">
         <v>17</v>
       </c>
@@ -6463,13 +6472,13 @@
         <v>18</v>
       </c>
       <c r="J154" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="K154">
         <v>100</v>
       </c>
       <c r="L154">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -6477,7 +6486,7 @@
         <v>24</v>
       </c>
       <c r="B155">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -6486,14 +6495,14 @@
         <v>21</v>
       </c>
       <c r="E155" t="s">
+        <v>62</v>
+      </c>
+      <c r="F155" t="s">
+        <v>63</v>
+      </c>
+      <c r="G155" t="s">
         <v>147</v>
       </c>
-      <c r="F155" t="s">
-        <v>15</v>
-      </c>
-      <c r="G155" t="s">
-        <v>148</v>
-      </c>
       <c r="H155" t="s">
         <v>17</v>
       </c>
@@ -6501,13 +6510,13 @@
         <v>18</v>
       </c>
       <c r="J155" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K155">
         <v>100</v>
       </c>
       <c r="L155">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -6515,7 +6524,7 @@
         <v>26</v>
       </c>
       <c r="B156">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6524,14 +6533,14 @@
         <v>21</v>
       </c>
       <c r="E156" t="s">
+        <v>62</v>
+      </c>
+      <c r="F156" t="s">
+        <v>63</v>
+      </c>
+      <c r="G156" t="s">
         <v>147</v>
       </c>
-      <c r="F156" t="s">
-        <v>15</v>
-      </c>
-      <c r="G156" t="s">
-        <v>148</v>
-      </c>
       <c r="H156" t="s">
         <v>17</v>
       </c>
@@ -6539,13 +6548,13 @@
         <v>18</v>
       </c>
       <c r="J156" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="K156">
         <v>100</v>
       </c>
       <c r="L156">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -6556,19 +6565,19 @@
         <v>37</v>
       </c>
       <c r="C157">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="E157" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="F157" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G157" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H157" t="s">
         <v>17</v>
@@ -6576,11 +6585,14 @@
       <c r="I157" t="s">
         <v>18</v>
       </c>
+      <c r="J157" t="s">
+        <v>92</v>
+      </c>
       <c r="K157">
         <v>100</v>
       </c>
       <c r="L157">
-        <v>95.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -6591,19 +6603,19 @@
         <v>8</v>
       </c>
       <c r="C158">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E158" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="F158" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G158" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H158" t="s">
         <v>17</v>
@@ -6615,7 +6627,7 @@
         <v>100</v>
       </c>
       <c r="L158">
-        <v>95.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -6626,19 +6638,19 @@
         <v>36</v>
       </c>
       <c r="C159">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="D159" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E159" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="F159" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -6650,7 +6662,7 @@
         <v>100</v>
       </c>
       <c r="L159">
-        <v>95.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -6661,19 +6673,19 @@
         <v>126</v>
       </c>
       <c r="C160">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D160" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="E160" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="F160" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G160" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H160" t="s">
         <v>17</v>
@@ -6685,7 +6697,7 @@
         <v>100</v>
       </c>
       <c r="L160">
-        <v>95.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -6702,13 +6714,13 @@
         <v>21</v>
       </c>
       <c r="E161" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
       <c r="F161" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G161" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H161" t="s">
         <v>17</v>
@@ -6720,7 +6732,7 @@
         <v>100</v>
       </c>
       <c r="L161">
-        <v>95.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -6728,22 +6740,22 @@
         <v>12</v>
       </c>
       <c r="B162">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C162">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D162" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="E162" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="F162" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G162" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H162" t="s">
         <v>17</v>
@@ -6751,14 +6763,11 @@
       <c r="I162" t="s">
         <v>18</v>
       </c>
-      <c r="J162" t="s">
-        <v>160</v>
-      </c>
       <c r="K162">
         <v>100</v>
       </c>
       <c r="L162">
-        <v>23.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -6766,22 +6775,22 @@
         <v>20</v>
       </c>
       <c r="B163">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>71</v>
+        <v>149</v>
       </c>
       <c r="E163" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="F163" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G163" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
@@ -6789,14 +6798,11 @@
       <c r="I163" t="s">
         <v>18</v>
       </c>
-      <c r="J163" t="s">
-        <v>161</v>
-      </c>
       <c r="K163">
         <v>100</v>
       </c>
       <c r="L163">
-        <v>23.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -6804,22 +6810,22 @@
         <v>22</v>
       </c>
       <c r="B164">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C164">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D164" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E164" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="F164" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G164" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H164" t="s">
         <v>17</v>
@@ -6827,14 +6833,11 @@
       <c r="I164" t="s">
         <v>18</v>
       </c>
-      <c r="J164" t="s">
-        <v>163</v>
-      </c>
       <c r="K164">
         <v>100</v>
       </c>
       <c r="L164">
-        <v>23.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -6842,7 +6845,7 @@
         <v>24</v>
       </c>
       <c r="B165">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -6851,13 +6854,13 @@
         <v>21</v>
       </c>
       <c r="E165" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="F165" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G165" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H165" t="s">
         <v>17</v>
@@ -6865,14 +6868,11 @@
       <c r="I165" t="s">
         <v>18</v>
       </c>
-      <c r="J165" t="s">
-        <v>164</v>
-      </c>
       <c r="K165">
         <v>100</v>
       </c>
       <c r="L165">
-        <v>23.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -6880,7 +6880,7 @@
         <v>26</v>
       </c>
       <c r="B166">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6889,13 +6889,13 @@
         <v>21</v>
       </c>
       <c r="E166" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="F166" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G166" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H166" t="s">
         <v>17</v>
@@ -6903,14 +6903,11 @@
       <c r="I166" t="s">
         <v>18</v>
       </c>
-      <c r="J166" t="s">
-        <v>165</v>
-      </c>
       <c r="K166">
         <v>100</v>
       </c>
       <c r="L166">
-        <v>23.9</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -6918,22 +6915,22 @@
         <v>12</v>
       </c>
       <c r="B167">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>61</v>
+        <v>168</v>
       </c>
       <c r="E167" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="F167" t="s">
         <v>63</v>
       </c>
       <c r="G167" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H167" t="s">
         <v>17</v>
@@ -6942,13 +6939,13 @@
         <v>18</v>
       </c>
       <c r="J167" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="K167">
         <v>100</v>
       </c>
       <c r="L167">
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -6956,7 +6953,7 @@
         <v>20</v>
       </c>
       <c r="B168">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -6965,13 +6962,13 @@
         <v>21</v>
       </c>
       <c r="E168" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="F168" t="s">
         <v>63</v>
       </c>
       <c r="G168" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H168" t="s">
         <v>17</v>
@@ -6983,7 +6980,7 @@
         <v>100</v>
       </c>
       <c r="L168">
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -6991,22 +6988,22 @@
         <v>22</v>
       </c>
       <c r="B169">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D169" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="E169" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="F169" t="s">
         <v>63</v>
       </c>
       <c r="G169" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -7018,7 +7015,7 @@
         <v>100</v>
       </c>
       <c r="L169">
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -7026,7 +7023,7 @@
         <v>24</v>
       </c>
       <c r="B170">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -7035,13 +7032,13 @@
         <v>21</v>
       </c>
       <c r="E170" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="F170" t="s">
         <v>63</v>
       </c>
       <c r="G170" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -7053,7 +7050,7 @@
         <v>100</v>
       </c>
       <c r="L170">
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -7061,7 +7058,7 @@
         <v>26</v>
       </c>
       <c r="B171">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -7070,13 +7067,13 @@
         <v>21</v>
       </c>
       <c r="E171" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="F171" t="s">
         <v>63</v>
       </c>
       <c r="G171" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="H171" t="s">
         <v>17</v>
@@ -7088,7 +7085,7 @@
         <v>100</v>
       </c>
       <c r="L171">
-        <v>2.2000000000000002</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -7096,22 +7093,22 @@
         <v>12</v>
       </c>
       <c r="B172">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C172">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D172" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="E172" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F172" t="s">
         <v>15</v>
       </c>
       <c r="G172" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H172" t="s">
         <v>17</v>
@@ -7123,7 +7120,7 @@
         <v>100</v>
       </c>
       <c r="L172">
-        <v>58.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -7131,22 +7128,22 @@
         <v>20</v>
       </c>
       <c r="B173">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D173" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="E173" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F173" t="s">
         <v>15</v>
       </c>
       <c r="G173" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H173" t="s">
         <v>17</v>
@@ -7158,7 +7155,7 @@
         <v>100</v>
       </c>
       <c r="L173">
-        <v>58.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -7166,22 +7163,22 @@
         <v>22</v>
       </c>
       <c r="B174">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C174">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D174" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="E174" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F174" t="s">
         <v>15</v>
       </c>
       <c r="G174" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H174" t="s">
         <v>17</v>
@@ -7193,7 +7190,7 @@
         <v>100</v>
       </c>
       <c r="L174">
-        <v>58.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -7201,22 +7198,22 @@
         <v>24</v>
       </c>
       <c r="B175">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D175" t="s">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="E175" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F175" t="s">
         <v>15</v>
       </c>
       <c r="G175" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H175" t="s">
         <v>17</v>
@@ -7228,7 +7225,7 @@
         <v>100</v>
       </c>
       <c r="L175">
-        <v>58.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -7236,7 +7233,7 @@
         <v>26</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -7245,13 +7242,13 @@
         <v>21</v>
       </c>
       <c r="E176" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F176" t="s">
         <v>15</v>
       </c>
       <c r="G176" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H176" t="s">
         <v>17</v>
@@ -7263,7 +7260,7 @@
         <v>100</v>
       </c>
       <c r="L176">
-        <v>58.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -7271,22 +7268,22 @@
         <v>12</v>
       </c>
       <c r="B177">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D177" t="s">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="E177" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F177" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G177" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H177" t="s">
         <v>17</v>
@@ -7295,13 +7292,13 @@
         <v>18</v>
       </c>
       <c r="J177" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="K177">
         <v>100</v>
       </c>
       <c r="L177">
-        <v>2.6</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -7312,19 +7309,19 @@
         <v>2</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D178" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="E178" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F178" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G178" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H178" t="s">
         <v>17</v>
@@ -7336,7 +7333,7 @@
         <v>100</v>
       </c>
       <c r="L178">
-        <v>2.6</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -7344,22 +7341,22 @@
         <v>22</v>
       </c>
       <c r="B179">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D179" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="E179" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F179" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G179" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H179" t="s">
         <v>17</v>
@@ -7371,7 +7368,7 @@
         <v>100</v>
       </c>
       <c r="L179">
-        <v>2.6</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -7379,22 +7376,22 @@
         <v>24</v>
       </c>
       <c r="B180">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D180" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E180" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F180" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G180" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H180" t="s">
         <v>17</v>
@@ -7406,7 +7403,7 @@
         <v>100</v>
       </c>
       <c r="L180">
-        <v>2.6</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -7414,7 +7411,7 @@
         <v>26</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -7423,13 +7420,13 @@
         <v>21</v>
       </c>
       <c r="E181" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F181" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G181" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="H181" t="s">
         <v>17</v>
@@ -7441,7 +7438,7 @@
         <v>100</v>
       </c>
       <c r="L181">
-        <v>2.6</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -7449,22 +7446,22 @@
         <v>12</v>
       </c>
       <c r="B182">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C182">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D182" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="E182" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F182" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G182" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H182" t="s">
         <v>17</v>
@@ -7472,14 +7469,11 @@
       <c r="I182" t="s">
         <v>18</v>
       </c>
-      <c r="J182" t="s">
-        <v>175</v>
-      </c>
       <c r="K182">
         <v>100</v>
       </c>
       <c r="L182">
-        <v>90.4</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -7487,22 +7481,22 @@
         <v>20</v>
       </c>
       <c r="B183">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D183" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E183" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F183" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G183" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H183" t="s">
         <v>17</v>
@@ -7510,14 +7504,11 @@
       <c r="I183" t="s">
         <v>18</v>
       </c>
-      <c r="J183" t="s">
-        <v>176</v>
-      </c>
       <c r="K183">
         <v>100</v>
       </c>
       <c r="L183">
-        <v>90.4</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -7525,22 +7516,22 @@
         <v>22</v>
       </c>
       <c r="B184">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C184">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D184" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="E184" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F184" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G184" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H184" t="s">
         <v>17</v>
@@ -7548,14 +7539,11 @@
       <c r="I184" t="s">
         <v>18</v>
       </c>
-      <c r="J184" t="s">
-        <v>178</v>
-      </c>
       <c r="K184">
         <v>100</v>
       </c>
       <c r="L184">
-        <v>90.4</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -7563,22 +7551,22 @@
         <v>24</v>
       </c>
       <c r="B185">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="C185">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D185" t="s">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="E185" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F185" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G185" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H185" t="s">
         <v>17</v>
@@ -7586,14 +7574,11 @@
       <c r="I185" t="s">
         <v>18</v>
       </c>
-      <c r="J185" t="s">
-        <v>179</v>
-      </c>
       <c r="K185">
         <v>100</v>
       </c>
       <c r="L185">
-        <v>90.4</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -7601,7 +7586,7 @@
         <v>26</v>
       </c>
       <c r="B186">
-        <v>600</v>
+        <v>709</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7610,13 +7595,13 @@
         <v>21</v>
       </c>
       <c r="E186" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F186" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G186" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="H186" t="s">
         <v>17</v>
@@ -7628,7 +7613,7 @@
         <v>100</v>
       </c>
       <c r="L186">
-        <v>90.4</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -7636,22 +7621,22 @@
         <v>12</v>
       </c>
       <c r="B187">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C187">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D187" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="E187" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F187" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G187" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H187" t="s">
         <v>17</v>
@@ -7663,7 +7648,7 @@
         <v>100</v>
       </c>
       <c r="L187">
-        <v>54.9</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -7671,22 +7656,22 @@
         <v>20</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E188" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F188" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G188" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H188" t="s">
         <v>17</v>
@@ -7698,7 +7683,7 @@
         <v>100</v>
       </c>
       <c r="L188">
-        <v>54.9</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -7706,22 +7691,22 @@
         <v>22</v>
       </c>
       <c r="B189">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C189">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D189" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="E189" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F189" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G189" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H189" t="s">
         <v>17</v>
@@ -7733,7 +7718,7 @@
         <v>100</v>
       </c>
       <c r="L189">
-        <v>54.9</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -7741,22 +7726,22 @@
         <v>24</v>
       </c>
       <c r="B190">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D190" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="E190" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F190" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G190" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H190" t="s">
         <v>17</v>
@@ -7768,7 +7753,7 @@
         <v>100</v>
       </c>
       <c r="L190">
-        <v>54.9</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -7776,7 +7761,7 @@
         <v>26</v>
       </c>
       <c r="B191">
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -7785,13 +7770,13 @@
         <v>21</v>
       </c>
       <c r="E191" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F191" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G191" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H191" t="s">
         <v>17</v>
@@ -7803,7 +7788,7 @@
         <v>100</v>
       </c>
       <c r="L191">
-        <v>54.9</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -7811,22 +7796,22 @@
         <v>12</v>
       </c>
       <c r="B192">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D192" t="s">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="E192" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="F192" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G192" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H192" t="s">
         <v>17</v>
@@ -7835,13 +7820,13 @@
         <v>18</v>
       </c>
       <c r="J192" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="K192">
         <v>100</v>
       </c>
       <c r="L192">
-        <v>0.4</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -7849,22 +7834,22 @@
         <v>20</v>
       </c>
       <c r="B193">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D193" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="E193" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="F193" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G193" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H193" t="s">
         <v>17</v>
@@ -7876,7 +7861,7 @@
         <v>100</v>
       </c>
       <c r="L193">
-        <v>0.4</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -7884,22 +7869,22 @@
         <v>22</v>
       </c>
       <c r="B194">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D194" t="s">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="E194" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="F194" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G194" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H194" t="s">
         <v>17</v>
@@ -7911,7 +7896,7 @@
         <v>100</v>
       </c>
       <c r="L194">
-        <v>0.4</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -7919,22 +7904,22 @@
         <v>24</v>
       </c>
       <c r="B195">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C195">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D195" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E195" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="F195" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G195" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H195" t="s">
         <v>17</v>
@@ -7946,7 +7931,7 @@
         <v>100</v>
       </c>
       <c r="L195">
-        <v>0.4</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -7954,7 +7939,7 @@
         <v>26</v>
       </c>
       <c r="B196">
-        <v>900</v>
+        <v>720</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -7963,13 +7948,13 @@
         <v>21</v>
       </c>
       <c r="E196" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="F196" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G196" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="H196" t="s">
         <v>17</v>
@@ -7981,7 +7966,7 @@
         <v>100</v>
       </c>
       <c r="L196">
-        <v>0.4</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -7989,22 +7974,22 @@
         <v>12</v>
       </c>
       <c r="B197">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C197">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D197" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="E197" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="F197" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G197" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H197" t="s">
         <v>17</v>
@@ -8013,13 +7998,13 @@
         <v>18</v>
       </c>
       <c r="J197" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="K197">
         <v>100</v>
       </c>
       <c r="L197">
-        <v>12.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
@@ -8027,7 +8012,7 @@
         <v>20</v>
       </c>
       <c r="B198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -8036,25 +8021,28 @@
         <v>21</v>
       </c>
       <c r="E198" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="F198" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G198" t="s">
+        <v>173</v>
+      </c>
+      <c r="H198" t="s">
+        <v>17</v>
+      </c>
+      <c r="I198" t="s">
+        <v>18</v>
+      </c>
+      <c r="J198" t="s">
         <v>174</v>
       </c>
-      <c r="H198" t="s">
-        <v>17</v>
-      </c>
-      <c r="I198" t="s">
-        <v>18</v>
-      </c>
       <c r="K198">
         <v>100</v>
       </c>
       <c r="L198">
-        <v>12.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -8062,22 +8050,22 @@
         <v>22</v>
       </c>
       <c r="B199">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C199">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D199" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="E199" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="F199" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G199" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H199" t="s">
         <v>17</v>
@@ -8086,13 +8074,13 @@
         <v>18</v>
       </c>
       <c r="J199" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="K199">
         <v>100</v>
       </c>
       <c r="L199">
-        <v>12.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -8100,22 +8088,22 @@
         <v>24</v>
       </c>
       <c r="B200">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="C200">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D200" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="E200" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="F200" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G200" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H200" t="s">
         <v>17</v>
@@ -8124,13 +8112,13 @@
         <v>18</v>
       </c>
       <c r="J200" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="K200">
         <v>100</v>
       </c>
       <c r="L200">
-        <v>12.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
@@ -8138,7 +8126,7 @@
         <v>26</v>
       </c>
       <c r="B201">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -8147,13 +8135,13 @@
         <v>21</v>
       </c>
       <c r="E201" t="s">
-        <v>69</v>
+        <v>172</v>
       </c>
       <c r="F201" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G201" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H201" t="s">
         <v>17</v>
@@ -8165,7 +8153,7 @@
         <v>100</v>
       </c>
       <c r="L201">
-        <v>12.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -8173,22 +8161,22 @@
         <v>12</v>
       </c>
       <c r="B202">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C202">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D202" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="E202" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F202" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G202" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H202" t="s">
         <v>17</v>
@@ -8200,7 +8188,7 @@
         <v>100</v>
       </c>
       <c r="L202">
-        <v>106.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -8208,22 +8196,22 @@
         <v>20</v>
       </c>
       <c r="B203">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C203">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D203" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="E203" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F203" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G203" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H203" t="s">
         <v>17</v>
@@ -8235,7 +8223,7 @@
         <v>100</v>
       </c>
       <c r="L203">
-        <v>106.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -8243,22 +8231,22 @@
         <v>22</v>
       </c>
       <c r="B204">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C204">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D204" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="E204" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F204" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G204" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H204" t="s">
         <v>17</v>
@@ -8270,7 +8258,7 @@
         <v>100</v>
       </c>
       <c r="L204">
-        <v>106.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
@@ -8278,22 +8266,22 @@
         <v>24</v>
       </c>
       <c r="B205">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C205">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="D205" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E205" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F205" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G205" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H205" t="s">
         <v>17</v>
@@ -8305,7 +8293,7 @@
         <v>100</v>
       </c>
       <c r="L205">
-        <v>106.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -8313,7 +8301,7 @@
         <v>26</v>
       </c>
       <c r="B206">
-        <v>473</v>
+        <v>900</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -8322,13 +8310,13 @@
         <v>21</v>
       </c>
       <c r="E206" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F206" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G206" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H206" t="s">
         <v>17</v>
@@ -8340,7 +8328,7 @@
         <v>100</v>
       </c>
       <c r="L206">
-        <v>106.5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
@@ -8348,22 +8336,22 @@
         <v>12</v>
       </c>
       <c r="B207">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C207">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D207" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E207" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="F207" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G207" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H207" t="s">
         <v>17</v>
@@ -8372,13 +8360,13 @@
         <v>18</v>
       </c>
       <c r="J207" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="K207">
         <v>100</v>
       </c>
       <c r="L207">
-        <v>109.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -8389,19 +8377,19 @@
         <v>2</v>
       </c>
       <c r="C208">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D208" t="s">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="E208" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="F208" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G208" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H208" t="s">
         <v>17</v>
@@ -8413,7 +8401,7 @@
         <v>100</v>
       </c>
       <c r="L208">
-        <v>109.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -8421,22 +8409,22 @@
         <v>22</v>
       </c>
       <c r="B209">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C209">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D209" t="s">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="E209" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="F209" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G209" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H209" t="s">
         <v>17</v>
@@ -8448,7 +8436,7 @@
         <v>100</v>
       </c>
       <c r="L209">
-        <v>109.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -8456,22 +8444,22 @@
         <v>24</v>
       </c>
       <c r="B210">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C210">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D210" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="E210" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="F210" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G210" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H210" t="s">
         <v>17</v>
@@ -8483,7 +8471,7 @@
         <v>100</v>
       </c>
       <c r="L210">
-        <v>109.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -8491,7 +8479,7 @@
         <v>26</v>
       </c>
       <c r="B211">
-        <v>318</v>
+        <v>900</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -8500,13 +8488,13 @@
         <v>21</v>
       </c>
       <c r="E211" t="s">
-        <v>192</v>
+        <v>62</v>
       </c>
       <c r="F211" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G211" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H211" t="s">
         <v>17</v>
@@ -8518,7 +8506,7 @@
         <v>100</v>
       </c>
       <c r="L211">
-        <v>109.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -8526,22 +8514,22 @@
         <v>12</v>
       </c>
       <c r="B212">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C212">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D212" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E212" t="s">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="F212" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G212" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H212" t="s">
         <v>17</v>
@@ -8549,11 +8537,14 @@
       <c r="I212" t="s">
         <v>18</v>
       </c>
+      <c r="J212" t="s">
+        <v>183</v>
+      </c>
       <c r="K212">
         <v>100</v>
       </c>
       <c r="L212">
-        <v>74.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
@@ -8561,22 +8552,22 @@
         <v>20</v>
       </c>
       <c r="B213">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C213">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D213" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E213" t="s">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="F213" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G213" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H213" t="s">
         <v>17</v>
@@ -8588,7 +8579,7 @@
         <v>100</v>
       </c>
       <c r="L213">
-        <v>74.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
@@ -8596,22 +8587,22 @@
         <v>22</v>
       </c>
       <c r="B214">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C214">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="D214" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="E214" t="s">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="F214" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G214" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H214" t="s">
         <v>17</v>
@@ -8619,11 +8610,14 @@
       <c r="I214" t="s">
         <v>18</v>
       </c>
+      <c r="J214" t="s">
+        <v>184</v>
+      </c>
       <c r="K214">
         <v>100</v>
       </c>
       <c r="L214">
-        <v>74.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
@@ -8631,22 +8625,22 @@
         <v>24</v>
       </c>
       <c r="B215">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C215">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="D215" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E215" t="s">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="F215" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G215" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H215" t="s">
         <v>17</v>
@@ -8654,11 +8648,14 @@
       <c r="I215" t="s">
         <v>18</v>
       </c>
+      <c r="J215" t="s">
+        <v>185</v>
+      </c>
       <c r="K215">
         <v>100</v>
       </c>
       <c r="L215">
-        <v>74.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
@@ -8666,7 +8663,7 @@
         <v>26</v>
       </c>
       <c r="B216">
-        <v>709</v>
+        <v>900</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8675,13 +8672,13 @@
         <v>21</v>
       </c>
       <c r="E216" t="s">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="F216" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="G216" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="H216" t="s">
         <v>17</v>
@@ -8693,7 +8690,366 @@
         <v>100</v>
       </c>
       <c r="L216">
-        <v>74.3</v>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>12</v>
+      </c>
+      <c r="B217">
+        <v>6</v>
+      </c>
+      <c r="C217">
+        <v>13</v>
+      </c>
+      <c r="D217" t="s">
+        <v>94</v>
+      </c>
+      <c r="E217" t="s">
+        <v>95</v>
+      </c>
+      <c r="F217" t="s">
+        <v>15</v>
+      </c>
+      <c r="G217" t="s">
+        <v>96</v>
+      </c>
+      <c r="H217" t="s">
+        <v>17</v>
+      </c>
+      <c r="I217" t="s">
+        <v>18</v>
+      </c>
+      <c r="K217">
+        <v>100</v>
+      </c>
+      <c r="L217">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>20</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218" t="s">
+        <v>21</v>
+      </c>
+      <c r="E218" t="s">
+        <v>95</v>
+      </c>
+      <c r="F218" t="s">
+        <v>15</v>
+      </c>
+      <c r="G218" t="s">
+        <v>96</v>
+      </c>
+      <c r="H218" t="s">
+        <v>17</v>
+      </c>
+      <c r="I218" t="s">
+        <v>18</v>
+      </c>
+      <c r="K218">
+        <v>100</v>
+      </c>
+      <c r="L218">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>22</v>
+      </c>
+      <c r="B219">
+        <v>20</v>
+      </c>
+      <c r="C219">
+        <v>24</v>
+      </c>
+      <c r="D219" t="s">
+        <v>97</v>
+      </c>
+      <c r="E219" t="s">
+        <v>95</v>
+      </c>
+      <c r="F219" t="s">
+        <v>15</v>
+      </c>
+      <c r="G219" t="s">
+        <v>96</v>
+      </c>
+      <c r="H219" t="s">
+        <v>17</v>
+      </c>
+      <c r="I219" t="s">
+        <v>18</v>
+      </c>
+      <c r="K219">
+        <v>100</v>
+      </c>
+      <c r="L219">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>24</v>
+      </c>
+      <c r="B220">
+        <v>24</v>
+      </c>
+      <c r="C220">
+        <v>53</v>
+      </c>
+      <c r="D220" t="s">
+        <v>98</v>
+      </c>
+      <c r="E220" t="s">
+        <v>95</v>
+      </c>
+      <c r="F220" t="s">
+        <v>15</v>
+      </c>
+      <c r="G220" t="s">
+        <v>96</v>
+      </c>
+      <c r="H220" t="s">
+        <v>17</v>
+      </c>
+      <c r="I220" t="s">
+        <v>18</v>
+      </c>
+      <c r="K220">
+        <v>100</v>
+      </c>
+      <c r="L220">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>26</v>
+      </c>
+      <c r="B221">
+        <v>480</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221" t="s">
+        <v>21</v>
+      </c>
+      <c r="E221" t="s">
+        <v>95</v>
+      </c>
+      <c r="F221" t="s">
+        <v>15</v>
+      </c>
+      <c r="G221" t="s">
+        <v>96</v>
+      </c>
+      <c r="H221" t="s">
+        <v>17</v>
+      </c>
+      <c r="I221" t="s">
+        <v>18</v>
+      </c>
+      <c r="K221">
+        <v>100</v>
+      </c>
+      <c r="L221">
+        <v>111.6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222">
+        <v>9</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="D222" t="s">
+        <v>36</v>
+      </c>
+      <c r="E222" t="s">
+        <v>99</v>
+      </c>
+      <c r="F222" t="s">
+        <v>28</v>
+      </c>
+      <c r="G222" t="s">
+        <v>96</v>
+      </c>
+      <c r="H222" t="s">
+        <v>17</v>
+      </c>
+      <c r="I222" t="s">
+        <v>18</v>
+      </c>
+      <c r="J222" t="s">
+        <v>207</v>
+      </c>
+      <c r="K222">
+        <v>100</v>
+      </c>
+      <c r="L222">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>20</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223" t="s">
+        <v>21</v>
+      </c>
+      <c r="E223" t="s">
+        <v>99</v>
+      </c>
+      <c r="F223" t="s">
+        <v>28</v>
+      </c>
+      <c r="G223" t="s">
+        <v>96</v>
+      </c>
+      <c r="H223" t="s">
+        <v>17</v>
+      </c>
+      <c r="I223" t="s">
+        <v>18</v>
+      </c>
+      <c r="K223">
+        <v>100</v>
+      </c>
+      <c r="L223">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>22</v>
+      </c>
+      <c r="B224">
+        <v>30</v>
+      </c>
+      <c r="C224">
+        <v>13</v>
+      </c>
+      <c r="D224" t="s">
+        <v>46</v>
+      </c>
+      <c r="E224" t="s">
+        <v>99</v>
+      </c>
+      <c r="F224" t="s">
+        <v>28</v>
+      </c>
+      <c r="G224" t="s">
+        <v>96</v>
+      </c>
+      <c r="H224" t="s">
+        <v>17</v>
+      </c>
+      <c r="I224" t="s">
+        <v>18</v>
+      </c>
+      <c r="J224" t="s">
+        <v>100</v>
+      </c>
+      <c r="K224">
+        <v>100</v>
+      </c>
+      <c r="L224">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>24</v>
+      </c>
+      <c r="B225">
+        <v>36</v>
+      </c>
+      <c r="C225">
+        <v>25</v>
+      </c>
+      <c r="D225" t="s">
+        <v>201</v>
+      </c>
+      <c r="E225" t="s">
+        <v>99</v>
+      </c>
+      <c r="F225" t="s">
+        <v>28</v>
+      </c>
+      <c r="G225" t="s">
+        <v>96</v>
+      </c>
+      <c r="H225" t="s">
+        <v>17</v>
+      </c>
+      <c r="I225" t="s">
+        <v>18</v>
+      </c>
+      <c r="J225" t="s">
+        <v>101</v>
+      </c>
+      <c r="K225">
+        <v>100</v>
+      </c>
+      <c r="L225">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>26</v>
+      </c>
+      <c r="B226">
+        <v>720</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226" t="s">
+        <v>21</v>
+      </c>
+      <c r="E226" t="s">
+        <v>99</v>
+      </c>
+      <c r="F226" t="s">
+        <v>28</v>
+      </c>
+      <c r="G226" t="s">
+        <v>96</v>
+      </c>
+      <c r="H226" t="s">
+        <v>17</v>
+      </c>
+      <c r="I226" t="s">
+        <v>18</v>
+      </c>
+      <c r="K226">
+        <v>100</v>
+      </c>
+      <c r="L226">
+        <v>33.700000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_77DDB655914D040E62355476585DCE3A87458B1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894CA02A-7E36-43F4-AC0C-F13CEAA9F415}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_319573EA547B980E62355476585DCE3A87454E9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FBB29CE-28B8-4A6C-8CE6-7681DB11B053}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="208">
   <si>
     <t>Producto</t>
   </si>
@@ -115,7 +115,328 @@
     <t>41%</t>
   </si>
   <si>
-    <t>61%</t>
+    <t>113%</t>
+  </si>
+  <si>
+    <t>Lider Paula Andrea Cano Monsalve</t>
+  </si>
+  <si>
+    <t>SAN CRISTOBAL</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>87%</t>
+  </si>
+  <si>
+    <t>83%</t>
+  </si>
+  <si>
+    <t>Johan Daniel Herrera Mazo</t>
+  </si>
+  <si>
+    <t>SUPERNUMERARIO</t>
+  </si>
+  <si>
+    <t>1 día, entrega el punto</t>
+  </si>
+  <si>
+    <t>3%</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>Lider Girardota Paulina Andrea Zapata Jimenez</t>
+  </si>
+  <si>
+    <t>GIRARDOTA</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>95%</t>
+  </si>
+  <si>
+    <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>Apoyo 1 día</t>
+  </si>
+  <si>
+    <t>Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>1 día líder</t>
+  </si>
+  <si>
+    <t>117%</t>
+  </si>
+  <si>
+    <t>Lider Frontino Cely Ruiz</t>
+  </si>
+  <si>
+    <t>FRONTINO</t>
+  </si>
+  <si>
+    <t>122%</t>
+  </si>
+  <si>
+    <t>17%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Moreno Durango</t>
+  </si>
+  <si>
+    <t>Le finalizaron contraro el 11 de junio</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>Yeilisa Fernanda Higuita David</t>
+  </si>
+  <si>
+    <t>mes de gracia</t>
+  </si>
+  <si>
+    <t>45%</t>
+  </si>
+  <si>
+    <t>169%</t>
+  </si>
+  <si>
+    <t>Lider Marcela Valencia Tabares</t>
+  </si>
+  <si>
+    <t>ITAGUI</t>
+  </si>
+  <si>
+    <t>67%</t>
+  </si>
+  <si>
+    <t>105%</t>
+  </si>
+  <si>
+    <t>147%</t>
+  </si>
+  <si>
+    <t>Dailyn Del Valle Alvarez Rueda</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>142%</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Posada Galeano</t>
+  </si>
+  <si>
+    <t>Mes de gracia hasta el 15 de junio</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>133%</t>
+  </si>
+  <si>
+    <t>Evelis Mary Ojeda Baldovino</t>
+  </si>
+  <si>
+    <t>Se le tiene en cuenta los días que estuvo en Girardota, por en de el total general  no debe de contar esas cantidades para el cumplimiento general</t>
+  </si>
+  <si>
+    <t>Mes de gracia</t>
+  </si>
+  <si>
+    <t>189%</t>
+  </si>
+  <si>
+    <t>136%</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t>153%</t>
+  </si>
+  <si>
+    <t>Lider Jhon Alejandro Cardona Quintero</t>
+  </si>
+  <si>
+    <t>LA ESTRELLA</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>107%</t>
+  </si>
+  <si>
+    <t>11%</t>
+  </si>
+  <si>
+    <t>1 día lider   meta puntos 26  meta postp 1</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>meta 1</t>
+  </si>
+  <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>267%</t>
+  </si>
+  <si>
+    <t>110%</t>
+  </si>
+  <si>
+    <t>168%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t>Vacaciones del  18 al 06 de julio - se realiza reajuste de meta al CVS</t>
+  </si>
+  <si>
+    <t>300%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>70%</t>
+  </si>
+  <si>
+    <t>Maria Camila Arango VÃ©lez</t>
+  </si>
+  <si>
+    <t>85%</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>42%</t>
+  </si>
+  <si>
+    <t>Lider Geraldin Angulo Jaramillo</t>
+  </si>
+  <si>
+    <t>YARUMAL</t>
+  </si>
+  <si>
+    <t>77%</t>
+  </si>
+  <si>
+    <t>Pendiente 4 porta pre</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>Vacaciones del 26 de junio al 13 de julio, en junio no aplica el promedio de 2 días por vacaciones</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>Tatiana  Guerra Gonzalez</t>
+  </si>
+  <si>
+    <t>CAUCASIA</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>72%</t>
+  </si>
+  <si>
+    <t>12%</t>
+  </si>
+  <si>
+    <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>1 día líder  meta puntos 43 Cump 21%</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
+  </si>
+  <si>
+    <t>DABEIBA</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>221%</t>
+  </si>
+  <si>
+    <t>111%</t>
+  </si>
+  <si>
+    <t>22%</t>
+  </si>
+  <si>
+    <t>Estelli Alejandra Ramirez Florez</t>
+  </si>
+  <si>
+    <t>Elabora 12 días x vac meta puntos 453.9 cump 65%       meta post  5 cump 40%</t>
+  </si>
+  <si>
+    <t>43%</t>
+  </si>
+  <si>
+    <t>meta terminales 16 cump 81%</t>
+  </si>
+  <si>
+    <t>meta otros 19 cump 132%</t>
+  </si>
+  <si>
+    <t>74%</t>
   </si>
   <si>
     <t>Lider Don Matias Diana Ruiz</t>
@@ -124,22 +445,118 @@
     <t>DON MATIAS</t>
   </si>
   <si>
-    <t>Cubre vacaciones de cajera 7 días</t>
-  </si>
-  <si>
-    <t>250%</t>
-  </si>
-  <si>
-    <t>22%</t>
-  </si>
-  <si>
-    <t>38%</t>
+    <t>Cubre vacaciones de cajera 7 días meta puntos 432 cump 55%</t>
+  </si>
+  <si>
+    <t>18%</t>
   </si>
   <si>
     <t>Evelyn Daniela Lopera Lopera</t>
   </si>
   <si>
-    <t>37%</t>
+    <t>16%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>meta puntos 520 cump 54%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>125%</t>
+  </si>
+  <si>
+    <t>106%</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>14 días líder   meta puntos 633 cump 59%   meta postp  15  cump 87%</t>
+  </si>
+  <si>
+    <t>Meta hogar 5 cump 40%</t>
+  </si>
+  <si>
+    <t>14%</t>
+  </si>
+  <si>
+    <t>Meta terminales  15  cump 33%</t>
+  </si>
+  <si>
+    <t>Meta otros 51 cump 53%</t>
+  </si>
+  <si>
+    <t>Meta 366</t>
+  </si>
+  <si>
+    <t>157%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elabora 20 días x vac  Meta puntos 921.7  cump 104% </t>
+  </si>
+  <si>
+    <t>meta Hogar 1</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>Meta terminales  24</t>
+  </si>
+  <si>
+    <t>Meta otros 19</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>114%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
+    <t>59%</t>
+  </si>
+  <si>
+    <t>1 día asesor  meta puntos 69</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>3 días líder meta puntos 345.6  cump 58%      meta postpago  2</t>
+  </si>
+  <si>
+    <t>Meta terminales 4</t>
+  </si>
+  <si>
+    <t>Meta otros 7</t>
   </si>
   <si>
     <t>146%</t>
@@ -151,28 +568,22 @@
     <t>JUNIN</t>
   </si>
   <si>
-    <t>200%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
     <t>159%</t>
   </si>
   <si>
-    <t>43%</t>
+    <t>154%</t>
   </si>
   <si>
     <t>Diana Marcela Taborda Ruiz</t>
   </si>
   <si>
-    <t xml:space="preserve">Elabora 7 días x VAC  - meta puntos  630.7     meta post 13 </t>
-  </si>
-  <si>
-    <t>Meta hogar 2</t>
-  </si>
-  <si>
-    <t>Meta terminales 20</t>
+    <t>Elabora 7 días x VAC  - meta puntos  630.7  cump 81%    meta post 13  cump 115%</t>
+  </si>
+  <si>
+    <t>Meta hogar 2 cump 0%</t>
+  </si>
+  <si>
+    <t>Meta terminales 20 cump 70%</t>
   </si>
   <si>
     <t>Meta otros 42</t>
@@ -187,31 +598,19 @@
     <t>Jessica Catherine Gutierrez Garcia</t>
   </si>
   <si>
-    <t>115%</t>
-  </si>
-  <si>
-    <t>85%</t>
-  </si>
-  <si>
-    <t>108%</t>
+    <t>112%</t>
+  </si>
+  <si>
+    <t>84%</t>
+  </si>
+  <si>
+    <t>145%</t>
   </si>
   <si>
     <t>Sandra Milena Carmona Galeano</t>
   </si>
   <si>
-    <t>110%</t>
-  </si>
-  <si>
-    <t>93%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>Johan Daniel Herrera Mazo</t>
-  </si>
-  <si>
-    <t>SUPERNUMERARIO</t>
+    <t>92%</t>
   </si>
   <si>
     <t>1 día Líder meta puntos 591.3   meta post 1</t>
@@ -226,437 +625,44 @@
     <t>meta 5</t>
   </si>
   <si>
-    <t>57%</t>
-  </si>
-  <si>
-    <t>Sara Julieth Acevedo Gutierrez</t>
-  </si>
-  <si>
-    <t>15 días, asesora meta puntos 1.182,5   meta post 24</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>Meta Hogar  3</t>
-  </si>
-  <si>
-    <t>69%</t>
-  </si>
-  <si>
-    <t>Meta Terminales 38</t>
-  </si>
-  <si>
-    <t>46%</t>
-  </si>
-  <si>
-    <t>Meta Otros 78</t>
+    <t>15 días, asesora meta puntos 1.182,5 cump 97%  meta post 24 cump 92%</t>
+  </si>
+  <si>
+    <t>Meta Hogar  3 cump. 33%</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>Meta Terminales 38 cump 113%</t>
+  </si>
+  <si>
+    <t>48%</t>
+  </si>
+  <si>
+    <t>Meta Otros 78 cump 73%</t>
   </si>
   <si>
     <t>cvs plus 261</t>
-  </si>
-  <si>
-    <t>113%</t>
-  </si>
-  <si>
-    <t>Lider Paula Andrea Cano Monsalve</t>
-  </si>
-  <si>
-    <t>SAN CRISTOBAL</t>
-  </si>
-  <si>
-    <t>87%</t>
-  </si>
-  <si>
-    <t>83%</t>
-  </si>
-  <si>
-    <t>1 día, entrega el punto</t>
-  </si>
-  <si>
-    <t>64%</t>
-  </si>
-  <si>
-    <t>Lider Girardota Paulina Andrea Zapata Jimenez</t>
-  </si>
-  <si>
-    <t>GIRARDOTA</t>
-  </si>
-  <si>
-    <t>75%</t>
-  </si>
-  <si>
-    <t>95%</t>
-  </si>
-  <si>
-    <t>Narelig Alejandra GarcÃ­a Ramirez</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>97%</t>
-  </si>
-  <si>
-    <t>Apoyo 1 día</t>
-  </si>
-  <si>
-    <t>1 día líder</t>
-  </si>
-  <si>
-    <t>217%</t>
-  </si>
-  <si>
-    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
-  </si>
-  <si>
-    <t>DABEIBA</t>
-  </si>
-  <si>
-    <t>120%</t>
-  </si>
-  <si>
-    <t>221%</t>
-  </si>
-  <si>
-    <t>Estelli Alejandra Ramirez Florez</t>
-  </si>
-  <si>
-    <t>meta terminales 16</t>
-  </si>
-  <si>
-    <t>meta otros 19</t>
-  </si>
-  <si>
-    <t>117%</t>
-  </si>
-  <si>
-    <t>Lider Frontino Cely Ruiz</t>
-  </si>
-  <si>
-    <t>FRONTINO</t>
-  </si>
-  <si>
-    <t>122%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>Diana Marcela Moreno Durango</t>
-  </si>
-  <si>
-    <t>Le finalizaron contraro el 11 de junio</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>Yeilisa Fernanda Higuita David</t>
-  </si>
-  <si>
-    <t>mes de gracia</t>
-  </si>
-  <si>
-    <t>45%</t>
-  </si>
-  <si>
-    <t>169%</t>
-  </si>
-  <si>
-    <t>Lider Marcela Valencia Tabares</t>
-  </si>
-  <si>
-    <t>ITAGUI</t>
-  </si>
-  <si>
-    <t>67%</t>
-  </si>
-  <si>
-    <t>105%</t>
-  </si>
-  <si>
-    <t>147%</t>
-  </si>
-  <si>
-    <t>Dailyn Del Valle Alvarez Rueda</t>
-  </si>
-  <si>
-    <t>89%</t>
-  </si>
-  <si>
-    <t>142%</t>
-  </si>
-  <si>
-    <t>Maria Fernanda Posada Galeano</t>
-  </si>
-  <si>
-    <t>Mes de gracia hasta el 15 de junio</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>88%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
-  </si>
-  <si>
-    <t>BARBOSA</t>
-  </si>
-  <si>
-    <t>133%</t>
-  </si>
-  <si>
-    <t>Evelis Mary Ojeda Baldovino</t>
-  </si>
-  <si>
-    <t>Se le tiene en cuenta los días que estuvo en Girardota, por en de el total general  no debe de contar esas cantidades para el cumplimiento general</t>
-  </si>
-  <si>
-    <t>Mes de gracia</t>
-  </si>
-  <si>
-    <t>189%</t>
-  </si>
-  <si>
-    <t>136%</t>
-  </si>
-  <si>
-    <t>Sene Del Socorro Suarez Torres</t>
-  </si>
-  <si>
-    <t>153%</t>
-  </si>
-  <si>
-    <t>Lider Jhon Alejandro Cardona Quintero</t>
-  </si>
-  <si>
-    <t>LA ESTRELLA</t>
-  </si>
-  <si>
-    <t>Yessica  Restrepo Caicedo</t>
-  </si>
-  <si>
-    <t>78%</t>
-  </si>
-  <si>
-    <t>107%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>1 día lider   meta puntos 26  meta postp 1</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>meta 1</t>
-  </si>
-  <si>
-    <t>16%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Arbelaez</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>Elabora 11 días x vac -  meta puntos 497.3                    meta postp 12</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>29%</t>
-  </si>
-  <si>
-    <t>meta 11</t>
-  </si>
-  <si>
-    <t>meta 40</t>
-  </si>
-  <si>
-    <t>meta 286.9</t>
-  </si>
-  <si>
-    <t>Andrea  Arenas Hurtado</t>
-  </si>
-  <si>
-    <t>125%</t>
-  </si>
-  <si>
-    <t>106%</t>
-  </si>
-  <si>
-    <t>104%</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>14 días líder   meta puntos 633   meta postp  15</t>
-  </si>
-  <si>
-    <t>Meta hogar 5</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>Meta terminales  15</t>
-  </si>
-  <si>
-    <t>Meta otros 51</t>
-  </si>
-  <si>
-    <t>Meta 366</t>
-  </si>
-  <si>
-    <t>Tatiana  Guerra Gonzalez</t>
-  </si>
-  <si>
-    <t>CAUCASIA</t>
-  </si>
-  <si>
-    <t>72%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>Kelly Yuliana Ospina Saldarriaga</t>
-  </si>
-  <si>
-    <t>1 día líder  meta puntos 43</t>
-  </si>
-  <si>
-    <t>157%</t>
-  </si>
-  <si>
-    <t>Lider Luz Stella Serna</t>
-  </si>
-  <si>
-    <t>TERMINAL NORTE</t>
-  </si>
-  <si>
-    <t>meta Hogar 1</t>
-  </si>
-  <si>
-    <t>118%</t>
-  </si>
-  <si>
-    <t>Meta terminales  24</t>
-  </si>
-  <si>
-    <t>Meta otros 19</t>
-  </si>
-  <si>
-    <t>114%</t>
-  </si>
-  <si>
-    <t>Cristian Camilo Torres Toro</t>
-  </si>
-  <si>
-    <t>76%</t>
-  </si>
-  <si>
-    <t>1 día asesor  meta puntos 69</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>3 días líder meta puntos 345.6        meta postpago  2</t>
-  </si>
-  <si>
-    <t>Meta terminales 4</t>
-  </si>
-  <si>
-    <t>Meta otros 7</t>
-  </si>
-  <si>
-    <t>Lider Yolima Mesa Zapata</t>
-  </si>
-  <si>
-    <t>CALDAS</t>
-  </si>
-  <si>
-    <t>267%</t>
-  </si>
-  <si>
-    <t>168%</t>
-  </si>
-  <si>
-    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
-  </si>
-  <si>
-    <t>Vacaciones del  18 al 06 de julio - se realiza reajuste de meta al CVS</t>
-  </si>
-  <si>
-    <t>300%</t>
-  </si>
-  <si>
-    <t>96%</t>
-  </si>
-  <si>
-    <t>70%</t>
-  </si>
-  <si>
-    <t>Maria Camila Arango VÃ©lez</t>
-  </si>
-  <si>
-    <t>79%</t>
-  </si>
-  <si>
-    <t>42%</t>
-  </si>
-  <si>
-    <t>Lider Geraldin Angulo Jaramillo</t>
-  </si>
-  <si>
-    <t>YARUMAL</t>
-  </si>
-  <si>
-    <t>77%</t>
-  </si>
-  <si>
-    <t>Pendiente 4 porta pre</t>
-  </si>
-  <si>
-    <t>Laura Carolina Chavarria Amariles</t>
-  </si>
-  <si>
-    <t>Vacaciones del 26 de junio al 13 de julio, en junio no aplica el promedio de 2 días por vacaciones</t>
-  </si>
-  <si>
-    <t>80%</t>
-  </si>
-  <si>
-    <t>52%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elabora 20 días x vac  Meta puntos 921.7   meta postpago </t>
-  </si>
-  <si>
-    <t>Elabora 12 días x vac meta puntos 453.9       meta post  5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -667,7 +673,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -675,12 +681,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -983,44 +1007,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L226"/>
+  <dimension ref="A1:L221"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1385,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
@@ -1405,14 +1429,11 @@
       <c r="I12" t="s">
         <v>18</v>
       </c>
-      <c r="J12" t="s">
-        <v>34</v>
-      </c>
       <c r="K12">
         <v>100</v>
       </c>
       <c r="L12">
-        <v>34.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1420,13 +1441,13 @@
         <v>20</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
@@ -1447,7 +1468,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>34.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1455,13 +1476,13 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
         <v>32</v>
@@ -1482,7 +1503,7 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>34.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1490,13 +1511,13 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
         <v>32</v>
@@ -1517,7 +1538,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>34.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1525,7 +1546,7 @@
         <v>26</v>
       </c>
       <c r="B16">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1552,7 +1573,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>34.1</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1560,19 +1581,19 @@
         <v>12</v>
       </c>
       <c r="B17">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
         <v>38</v>
-      </c>
-      <c r="F17" t="s">
-        <v>28</v>
       </c>
       <c r="G17" t="s">
         <v>33</v>
@@ -1583,11 +1604,14 @@
       <c r="I17" t="s">
         <v>18</v>
       </c>
+      <c r="J17" t="s">
+        <v>39</v>
+      </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>29.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1595,7 +1619,7 @@
         <v>20</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1604,10 +1628,10 @@
         <v>21</v>
       </c>
       <c r="E18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" t="s">
         <v>38</v>
-      </c>
-      <c r="F18" t="s">
-        <v>28</v>
       </c>
       <c r="G18" t="s">
         <v>33</v>
@@ -1622,7 +1646,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>29.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1630,19 +1654,19 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" t="s">
         <v>38</v>
-      </c>
-      <c r="F19" t="s">
-        <v>28</v>
       </c>
       <c r="G19" t="s">
         <v>33</v>
@@ -1657,7 +1681,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>29.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1665,19 +1689,19 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C20">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" t="s">
         <v>38</v>
-      </c>
-      <c r="F20" t="s">
-        <v>28</v>
       </c>
       <c r="G20" t="s">
         <v>33</v>
@@ -1692,7 +1716,7 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>29.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1700,7 +1724,7 @@
         <v>26</v>
       </c>
       <c r="B21">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1709,10 +1733,10 @@
         <v>21</v>
       </c>
       <c r="E21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" t="s">
         <v>38</v>
-      </c>
-      <c r="F21" t="s">
-        <v>28</v>
       </c>
       <c r="G21" t="s">
         <v>33</v>
@@ -1727,7 +1751,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>29.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1735,22 +1759,22 @@
         <v>12</v>
       </c>
       <c r="B22">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C22">
+        <v>9</v>
+      </c>
+      <c r="D22" t="s">
         <v>41</v>
       </c>
-      <c r="D22" t="s">
-        <v>40</v>
-      </c>
       <c r="E22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1762,7 +1786,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>125.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1773,19 +1797,19 @@
         <v>3</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1797,7 +1821,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>125.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1805,22 +1829,22 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C24">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1832,7 +1856,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>125.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1840,22 +1864,22 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="C25">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1867,7 +1891,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>125.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1875,7 +1899,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1884,13 +1908,13 @@
         <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1902,7 +1926,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>125.4</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1910,22 +1934,22 @@
         <v>12</v>
       </c>
       <c r="B27">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C27">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" t="s">
         <v>46</v>
       </c>
-      <c r="E27" t="s">
-        <v>47</v>
-      </c>
       <c r="F27" t="s">
         <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1933,14 +1957,11 @@
       <c r="I27" t="s">
         <v>18</v>
       </c>
-      <c r="J27" t="s">
-        <v>48</v>
-      </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>30.4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1948,22 +1969,22 @@
         <v>20</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" t="s">
         <v>28</v>
       </c>
       <c r="G28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1971,14 +1992,11 @@
       <c r="I28" t="s">
         <v>18</v>
       </c>
-      <c r="J28" t="s">
-        <v>49</v>
-      </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>30.4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -1986,22 +2004,22 @@
         <v>22</v>
       </c>
       <c r="B29">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
         <v>28</v>
       </c>
       <c r="G29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -2009,14 +2027,11 @@
       <c r="I29" t="s">
         <v>18</v>
       </c>
-      <c r="J29" t="s">
-        <v>50</v>
-      </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>30.4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -2024,7 +2039,7 @@
         <v>24</v>
       </c>
       <c r="B30">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2033,13 +2048,13 @@
         <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
         <v>28</v>
       </c>
       <c r="G30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -2047,14 +2062,11 @@
       <c r="I30" t="s">
         <v>18</v>
       </c>
-      <c r="J30" t="s">
-        <v>51</v>
-      </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>30.4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -2062,7 +2074,7 @@
         <v>26</v>
       </c>
       <c r="B31">
-        <v>399</v>
+        <v>720</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2071,13 +2083,13 @@
         <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
         <v>28</v>
       </c>
       <c r="G31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -2085,14 +2097,11 @@
       <c r="I31" t="s">
         <v>18</v>
       </c>
-      <c r="J31" t="s">
-        <v>52</v>
-      </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>30.4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -2100,34 +2109,37 @@
         <v>12</v>
       </c>
       <c r="B32">
+        <v>21</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" t="s">
         <v>37</v>
       </c>
-      <c r="C32">
+      <c r="F32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" t="s">
         <v>43</v>
       </c>
-      <c r="D32" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" t="s">
-        <v>28</v>
-      </c>
-      <c r="G32" t="s">
-        <v>42</v>
-      </c>
       <c r="H32" t="s">
         <v>17</v>
       </c>
       <c r="I32" t="s">
         <v>18</v>
       </c>
+      <c r="J32" t="s">
+        <v>49</v>
+      </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>101.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -2135,22 +2147,22 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -2162,7 +2174,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>101.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -2170,22 +2182,22 @@
         <v>22</v>
       </c>
       <c r="B34">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C34">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -2197,7 +2209,7 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>101.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2205,22 +2217,22 @@
         <v>24</v>
       </c>
       <c r="B35">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C35">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2232,7 +2244,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>101.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2240,7 +2252,7 @@
         <v>26</v>
       </c>
       <c r="B36">
-        <v>399</v>
+        <v>720</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2249,13 +2261,13 @@
         <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2267,7 +2279,7 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>101.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2275,22 +2287,22 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C37">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2298,11 +2310,14 @@
       <c r="I37" t="s">
         <v>18</v>
       </c>
+      <c r="J37" t="s">
+        <v>51</v>
+      </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>109.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2310,22 +2325,22 @@
         <v>20</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2337,7 +2352,7 @@
         <v>100</v>
       </c>
       <c r="L38">
-        <v>109.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2345,22 +2360,22 @@
         <v>22</v>
       </c>
       <c r="B39">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C39">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2372,7 +2387,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>109.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2380,22 +2395,22 @@
         <v>24</v>
       </c>
       <c r="B40">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C40">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2407,7 +2422,7 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>109.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2415,7 +2430,7 @@
         <v>26</v>
       </c>
       <c r="B41">
-        <v>399</v>
+        <v>720</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2424,13 +2439,13 @@
         <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2442,7 +2457,7 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>109.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2450,22 +2465,22 @@
         <v>12</v>
       </c>
       <c r="B42">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E42" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F42" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2473,14 +2488,11 @@
       <c r="I42" t="s">
         <v>18</v>
       </c>
-      <c r="J42" t="s">
-        <v>64</v>
-      </c>
       <c r="K42">
         <v>100</v>
       </c>
       <c r="L42">
-        <v>1.3</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2488,7 +2500,7 @@
         <v>20</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2497,13 +2509,13 @@
         <v>21</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F43" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2515,7 +2527,7 @@
         <v>100</v>
       </c>
       <c r="L43">
-        <v>1.3</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2523,22 +2535,22 @@
         <v>22</v>
       </c>
       <c r="B44">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F44" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2546,14 +2558,11 @@
       <c r="I44" t="s">
         <v>18</v>
       </c>
-      <c r="J44" t="s">
-        <v>66</v>
-      </c>
       <c r="K44">
         <v>100</v>
       </c>
       <c r="L44">
-        <v>1.3</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2561,7 +2570,7 @@
         <v>24</v>
       </c>
       <c r="B45">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2570,13 +2579,13 @@
         <v>21</v>
       </c>
       <c r="E45" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F45" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2584,14 +2593,11 @@
       <c r="I45" t="s">
         <v>18</v>
       </c>
-      <c r="J45" t="s">
-        <v>67</v>
-      </c>
       <c r="K45">
         <v>100</v>
       </c>
       <c r="L45">
-        <v>1.3</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2599,7 +2605,7 @@
         <v>26</v>
       </c>
       <c r="B46">
-        <v>399</v>
+        <v>750</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2608,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F46" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2626,7 +2632,7 @@
         <v>100</v>
       </c>
       <c r="L46">
-        <v>1.3</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2634,22 +2640,22 @@
         <v>12</v>
       </c>
       <c r="B47">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C47">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E47" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F47" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G47" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2658,13 +2664,13 @@
         <v>18</v>
       </c>
       <c r="J47" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="K47">
         <v>100</v>
       </c>
       <c r="L47">
-        <v>61.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2672,22 +2678,22 @@
         <v>20</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="E48" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F48" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G48" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2695,14 +2701,11 @@
       <c r="I48" t="s">
         <v>18</v>
       </c>
-      <c r="J48" t="s">
-        <v>72</v>
-      </c>
       <c r="K48">
         <v>100</v>
       </c>
       <c r="L48">
-        <v>61.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2710,22 +2713,22 @@
         <v>22</v>
       </c>
       <c r="B49">
+        <v>55</v>
+      </c>
+      <c r="C49">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
         <v>59</v>
       </c>
-      <c r="C49">
-        <v>41</v>
-      </c>
-      <c r="D49" t="s">
-        <v>73</v>
-      </c>
       <c r="E49" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F49" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G49" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -2733,14 +2736,11 @@
       <c r="I49" t="s">
         <v>18</v>
       </c>
-      <c r="J49" t="s">
-        <v>74</v>
-      </c>
       <c r="K49">
         <v>100</v>
       </c>
       <c r="L49">
-        <v>61.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2748,22 +2748,22 @@
         <v>24</v>
       </c>
       <c r="B50">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="C50">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F50" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G50" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -2771,14 +2771,11 @@
       <c r="I50" t="s">
         <v>18</v>
       </c>
-      <c r="J50" t="s">
-        <v>76</v>
-      </c>
       <c r="K50">
         <v>100</v>
       </c>
       <c r="L50">
-        <v>61.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2786,7 +2783,7 @@
         <v>26</v>
       </c>
       <c r="B51">
-        <v>399</v>
+        <v>750</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2795,13 +2792,13 @@
         <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F51" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G51" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -2809,14 +2806,11 @@
       <c r="I51" t="s">
         <v>18</v>
       </c>
-      <c r="J51" t="s">
-        <v>77</v>
-      </c>
       <c r="K51">
         <v>100</v>
       </c>
       <c r="L51">
-        <v>61.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2824,22 +2818,22 @@
         <v>12</v>
       </c>
       <c r="B52">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C52">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G52" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -2847,11 +2841,14 @@
       <c r="I52" t="s">
         <v>18</v>
       </c>
+      <c r="J52" t="s">
+        <v>61</v>
+      </c>
       <c r="K52">
         <v>100</v>
       </c>
       <c r="L52">
-        <v>73.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2859,22 +2856,22 @@
         <v>20</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F53" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G53" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -2886,7 +2883,7 @@
         <v>100</v>
       </c>
       <c r="L53">
-        <v>73.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2894,22 +2891,22 @@
         <v>22</v>
       </c>
       <c r="B54">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C54">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="E54" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G54" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -2921,7 +2918,7 @@
         <v>100</v>
       </c>
       <c r="L54">
-        <v>73.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -2929,22 +2926,22 @@
         <v>24</v>
       </c>
       <c r="B55">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C55">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G55" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -2956,7 +2953,7 @@
         <v>100</v>
       </c>
       <c r="L55">
-        <v>73.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -2964,7 +2961,7 @@
         <v>26</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2973,13 +2970,13 @@
         <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G56" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -2991,7 +2988,7 @@
         <v>100</v>
       </c>
       <c r="L56">
-        <v>73.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -2999,22 +2996,22 @@
         <v>12</v>
       </c>
       <c r="B57">
+        <v>13</v>
+      </c>
+      <c r="C57">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57" t="s">
+        <v>64</v>
+      </c>
+      <c r="F57" t="s">
         <v>15</v>
       </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E57" t="s">
-        <v>62</v>
-      </c>
-      <c r="F57" t="s">
-        <v>63</v>
-      </c>
       <c r="G57" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -3022,14 +3019,11 @@
       <c r="I57" t="s">
         <v>18</v>
       </c>
-      <c r="J57" t="s">
-        <v>83</v>
-      </c>
       <c r="K57">
         <v>100</v>
       </c>
       <c r="L57">
-        <v>2.4</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -3037,22 +3031,22 @@
         <v>20</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E58" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -3064,7 +3058,7 @@
         <v>100</v>
       </c>
       <c r="L58">
-        <v>2.4</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -3072,22 +3066,22 @@
         <v>22</v>
       </c>
       <c r="B59">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E59" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F59" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -3099,7 +3093,7 @@
         <v>100</v>
       </c>
       <c r="L59">
-        <v>2.4</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -3107,7 +3101,7 @@
         <v>24</v>
       </c>
       <c r="B60">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -3116,13 +3110,13 @@
         <v>21</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -3134,7 +3128,7 @@
         <v>100</v>
       </c>
       <c r="L60">
-        <v>2.4</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -3142,7 +3136,7 @@
         <v>26</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -3151,13 +3145,13 @@
         <v>21</v>
       </c>
       <c r="E61" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F61" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -3169,7 +3163,7 @@
         <v>100</v>
       </c>
       <c r="L61">
-        <v>2.4</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -3177,22 +3171,22 @@
         <v>12</v>
       </c>
       <c r="B62">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="D62" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G62" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -3204,7 +3198,7 @@
         <v>100</v>
       </c>
       <c r="L62">
-        <v>56.4</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -3212,22 +3206,22 @@
         <v>20</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E63" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G63" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3239,7 +3233,7 @@
         <v>100</v>
       </c>
       <c r="L63">
-        <v>56.4</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3247,22 +3241,22 @@
         <v>22</v>
       </c>
       <c r="B64">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C64">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E64" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G64" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3274,7 +3268,7 @@
         <v>100</v>
       </c>
       <c r="L64">
-        <v>56.4</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3282,7 +3276,7 @@
         <v>24</v>
       </c>
       <c r="B65">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -3291,13 +3285,13 @@
         <v>21</v>
       </c>
       <c r="E65" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F65" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G65" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3309,7 +3303,7 @@
         <v>100</v>
       </c>
       <c r="L65">
-        <v>56.4</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3317,7 +3311,7 @@
         <v>26</v>
       </c>
       <c r="B66">
-        <v>480</v>
+        <v>563</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3326,13 +3320,13 @@
         <v>21</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G66" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3344,7 +3338,7 @@
         <v>100</v>
       </c>
       <c r="L66">
-        <v>56.4</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3352,22 +3346,22 @@
         <v>12</v>
       </c>
       <c r="B67">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C67">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="E67" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
       </c>
       <c r="G67" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3375,11 +3369,14 @@
       <c r="I67" t="s">
         <v>18</v>
       </c>
+      <c r="J67" t="s">
+        <v>74</v>
+      </c>
       <c r="K67">
         <v>100</v>
       </c>
       <c r="L67">
-        <v>77</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3390,19 +3387,19 @@
         <v>5</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E68" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F68" t="s">
         <v>28</v>
       </c>
       <c r="G68" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -3414,7 +3411,7 @@
         <v>100</v>
       </c>
       <c r="L68">
-        <v>77</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3422,22 +3419,22 @@
         <v>22</v>
       </c>
       <c r="B69">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C69">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E69" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F69" t="s">
         <v>28</v>
       </c>
       <c r="G69" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -3449,7 +3446,7 @@
         <v>100</v>
       </c>
       <c r="L69">
-        <v>77</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3457,7 +3454,7 @@
         <v>24</v>
       </c>
       <c r="B70">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -3466,13 +3463,13 @@
         <v>21</v>
       </c>
       <c r="E70" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F70" t="s">
         <v>28</v>
       </c>
       <c r="G70" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -3484,7 +3481,7 @@
         <v>100</v>
       </c>
       <c r="L70">
-        <v>77</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3492,7 +3489,7 @@
         <v>26</v>
       </c>
       <c r="B71">
-        <v>720</v>
+        <v>563</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3501,13 +3498,13 @@
         <v>21</v>
       </c>
       <c r="E71" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F71" t="s">
         <v>28</v>
       </c>
       <c r="G71" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -3519,7 +3516,7 @@
         <v>100</v>
       </c>
       <c r="L71">
-        <v>77</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3527,22 +3524,22 @@
         <v>12</v>
       </c>
       <c r="B72">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D72" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="E72" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F72" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -3550,14 +3547,11 @@
       <c r="I72" t="s">
         <v>18</v>
       </c>
-      <c r="J72" t="s">
-        <v>92</v>
-      </c>
       <c r="K72">
         <v>100</v>
       </c>
       <c r="L72">
-        <v>0.2</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3565,7 +3559,7 @@
         <v>20</v>
       </c>
       <c r="B73">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3574,13 +3568,13 @@
         <v>21</v>
       </c>
       <c r="E73" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F73" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -3592,7 +3586,7 @@
         <v>100</v>
       </c>
       <c r="L73">
-        <v>0.2</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3600,22 +3594,22 @@
         <v>22</v>
       </c>
       <c r="B74">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="E74" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F74" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -3627,7 +3621,7 @@
         <v>100</v>
       </c>
       <c r="L74">
-        <v>0.2</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3635,7 +3629,7 @@
         <v>24</v>
       </c>
       <c r="B75">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3644,13 +3638,13 @@
         <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F75" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -3662,7 +3656,7 @@
         <v>100</v>
       </c>
       <c r="L75">
-        <v>0.2</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3670,7 +3664,7 @@
         <v>26</v>
       </c>
       <c r="B76">
-        <v>720</v>
+        <v>375</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3679,13 +3673,13 @@
         <v>21</v>
       </c>
       <c r="E76" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="F76" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -3697,7 +3691,7 @@
         <v>100</v>
       </c>
       <c r="L76">
-        <v>0.2</v>
+        <v>115.1</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3705,22 +3699,22 @@
         <v>12</v>
       </c>
       <c r="B77">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D77" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E77" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F77" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G77" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -3729,13 +3723,13 @@
         <v>18</v>
       </c>
       <c r="J77" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K77">
         <v>100</v>
       </c>
       <c r="L77">
-        <v>0.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3743,22 +3737,22 @@
         <v>20</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E78" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F78" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G78" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -3766,11 +3760,14 @@
       <c r="I78" t="s">
         <v>18</v>
       </c>
+      <c r="J78" t="s">
+        <v>82</v>
+      </c>
       <c r="K78">
         <v>100</v>
       </c>
       <c r="L78">
-        <v>0.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -3778,22 +3775,22 @@
         <v>22</v>
       </c>
       <c r="B79">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D79" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E79" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F79" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G79" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -3805,7 +3802,7 @@
         <v>100</v>
       </c>
       <c r="L79">
-        <v>0.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3813,23 +3810,23 @@
         <v>24</v>
       </c>
       <c r="B80">
+        <v>36</v>
+      </c>
+      <c r="C80">
+        <v>68</v>
+      </c>
+      <c r="D80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80" t="s">
+        <v>80</v>
+      </c>
+      <c r="F80" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" t="s">
         <v>78</v>
       </c>
-      <c r="C80">
-        <v>0</v>
-      </c>
-      <c r="D80" t="s">
-        <v>21</v>
-      </c>
-      <c r="E80" t="s">
-        <v>69</v>
-      </c>
-      <c r="F80" t="s">
-        <v>63</v>
-      </c>
-      <c r="G80" t="s">
-        <v>86</v>
-      </c>
       <c r="H80" t="s">
         <v>17</v>
       </c>
@@ -3840,7 +3837,7 @@
         <v>100</v>
       </c>
       <c r="L80">
-        <v>0.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3848,7 +3845,7 @@
         <v>26</v>
       </c>
       <c r="B81">
-        <v>720</v>
+        <v>563</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3857,13 +3854,13 @@
         <v>21</v>
       </c>
       <c r="E81" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="F81" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G81" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -3875,7 +3872,7 @@
         <v>100</v>
       </c>
       <c r="L81">
-        <v>0.5</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3883,22 +3880,22 @@
         <v>12</v>
       </c>
       <c r="B82">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C82">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="E82" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F82" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G82" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -3910,7 +3907,7 @@
         <v>100</v>
       </c>
       <c r="L82">
-        <v>125.8</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -3918,22 +3915,22 @@
         <v>20</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E83" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F83" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G83" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -3945,7 +3942,7 @@
         <v>100</v>
       </c>
       <c r="L83">
-        <v>125.8</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -3953,22 +3950,22 @@
         <v>22</v>
       </c>
       <c r="B84">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C84">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E84" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F84" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G84" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -3980,7 +3977,7 @@
         <v>100</v>
       </c>
       <c r="L84">
-        <v>125.8</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3988,22 +3985,22 @@
         <v>24</v>
       </c>
       <c r="B85">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D85" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="E85" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F85" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G85" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -4015,7 +4012,7 @@
         <v>100</v>
       </c>
       <c r="L85">
-        <v>125.8</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -4023,7 +4020,7 @@
         <v>26</v>
       </c>
       <c r="B86">
-        <v>750</v>
+        <v>563</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -4032,13 +4029,13 @@
         <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F86" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G86" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -4050,7 +4047,7 @@
         <v>100</v>
       </c>
       <c r="L86">
-        <v>125.8</v>
+        <v>125.9</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -4058,22 +4055,22 @@
         <v>12</v>
       </c>
       <c r="B87">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="E87" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F87" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -4081,14 +4078,11 @@
       <c r="I87" t="s">
         <v>18</v>
       </c>
-      <c r="J87" t="s">
-        <v>108</v>
-      </c>
       <c r="K87">
         <v>100</v>
       </c>
       <c r="L87">
-        <v>27.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4096,22 +4090,22 @@
         <v>20</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E88" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F88" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -4123,7 +4117,7 @@
         <v>100</v>
       </c>
       <c r="L88">
-        <v>27.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4131,22 +4125,22 @@
         <v>22</v>
       </c>
       <c r="B89">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C89">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="E89" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F89" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -4158,7 +4152,7 @@
         <v>100</v>
       </c>
       <c r="L89">
-        <v>27.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4166,7 +4160,7 @@
         <v>24</v>
       </c>
       <c r="B90">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -4175,13 +4169,13 @@
         <v>21</v>
       </c>
       <c r="E90" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F90" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -4193,7 +4187,7 @@
         <v>100</v>
       </c>
       <c r="L90">
-        <v>27.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4201,7 +4195,7 @@
         <v>26</v>
       </c>
       <c r="B91">
-        <v>750</v>
+        <v>480</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4210,13 +4204,13 @@
         <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F91" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -4228,7 +4222,7 @@
         <v>100</v>
       </c>
       <c r="L91">
-        <v>27.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4236,22 +4230,22 @@
         <v>12</v>
       </c>
       <c r="B92">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E92" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
       </c>
       <c r="G92" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -4259,14 +4253,11 @@
       <c r="I92" t="s">
         <v>18</v>
       </c>
-      <c r="J92" t="s">
-        <v>111</v>
-      </c>
       <c r="K92">
         <v>100</v>
       </c>
       <c r="L92">
-        <v>43.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4274,22 +4265,22 @@
         <v>20</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="E93" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
       </c>
       <c r="G93" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -4301,7 +4292,7 @@
         <v>100</v>
       </c>
       <c r="L93">
-        <v>43.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4309,22 +4300,22 @@
         <v>22</v>
       </c>
       <c r="B94">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C94">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="E94" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
       </c>
       <c r="G94" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -4336,7 +4327,7 @@
         <v>100</v>
       </c>
       <c r="L94">
-        <v>43.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4344,22 +4335,22 @@
         <v>24</v>
       </c>
       <c r="B95">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D95" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="E95" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
       </c>
       <c r="G95" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -4371,7 +4362,7 @@
         <v>100</v>
       </c>
       <c r="L95">
-        <v>43.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4379,7 +4370,7 @@
         <v>26</v>
       </c>
       <c r="B96">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4388,13 +4379,13 @@
         <v>21</v>
       </c>
       <c r="E96" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
       </c>
       <c r="G96" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -4406,7 +4397,7 @@
         <v>100</v>
       </c>
       <c r="L96">
-        <v>43.6</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4414,22 +4405,22 @@
         <v>12</v>
       </c>
       <c r="B97">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C97">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E97" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F97" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G97" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -4437,11 +4428,14 @@
       <c r="I97" t="s">
         <v>18</v>
       </c>
+      <c r="J97" t="s">
+        <v>93</v>
+      </c>
       <c r="K97">
         <v>100</v>
       </c>
       <c r="L97">
-        <v>107.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4449,22 +4443,22 @@
         <v>20</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F98" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G98" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -4476,7 +4470,7 @@
         <v>100</v>
       </c>
       <c r="L98">
-        <v>107.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4484,22 +4478,22 @@
         <v>22</v>
       </c>
       <c r="B99">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C99">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="E99" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F99" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G99" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -4507,11 +4501,14 @@
       <c r="I99" t="s">
         <v>18</v>
       </c>
+      <c r="J99" t="s">
+        <v>95</v>
+      </c>
       <c r="K99">
         <v>100</v>
       </c>
       <c r="L99">
-        <v>107.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4519,7 +4516,7 @@
         <v>24</v>
       </c>
       <c r="B100">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -4528,13 +4525,13 @@
         <v>21</v>
       </c>
       <c r="E100" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F100" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G100" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -4542,11 +4539,14 @@
       <c r="I100" t="s">
         <v>18</v>
       </c>
+      <c r="J100" t="s">
+        <v>95</v>
+      </c>
       <c r="K100">
         <v>100</v>
       </c>
       <c r="L100">
-        <v>107.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4554,7 +4554,7 @@
         <v>26</v>
       </c>
       <c r="B101">
-        <v>375</v>
+        <v>720</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4563,13 +4563,13 @@
         <v>21</v>
       </c>
       <c r="E101" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="F101" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G101" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -4581,7 +4581,7 @@
         <v>100</v>
       </c>
       <c r="L101">
-        <v>107.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4589,22 +4589,22 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C102">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D102" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="E102" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F102" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -4616,7 +4616,7 @@
         <v>100</v>
       </c>
       <c r="L102">
-        <v>115.1</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4624,22 +4624,22 @@
         <v>20</v>
       </c>
       <c r="B103">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D103" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E103" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F103" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4651,7 +4651,7 @@
         <v>100</v>
       </c>
       <c r="L103">
-        <v>115.1</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4659,22 +4659,22 @@
         <v>22</v>
       </c>
       <c r="B104">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C104">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D104" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="E104" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F104" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -4686,7 +4686,7 @@
         <v>100</v>
       </c>
       <c r="L104">
-        <v>115.1</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4694,22 +4694,22 @@
         <v>24</v>
       </c>
       <c r="B105">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D105" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="E105" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F105" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -4721,7 +4721,7 @@
         <v>100</v>
       </c>
       <c r="L105">
-        <v>115.1</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4729,7 +4729,7 @@
         <v>26</v>
       </c>
       <c r="B106">
-        <v>563</v>
+        <v>473</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4738,13 +4738,13 @@
         <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="F106" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -4756,7 +4756,7 @@
         <v>100</v>
       </c>
       <c r="L106">
-        <v>115.1</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4764,22 +4764,22 @@
         <v>12</v>
       </c>
       <c r="B107">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C107">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D107" t="s">
-        <v>121</v>
+        <v>35</v>
       </c>
       <c r="E107" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -4788,13 +4788,13 @@
         <v>18</v>
       </c>
       <c r="J107" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="K107">
         <v>100</v>
       </c>
       <c r="L107">
-        <v>100.2</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4802,22 +4802,22 @@
         <v>20</v>
       </c>
       <c r="B108">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="E108" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -4829,7 +4829,7 @@
         <v>100</v>
       </c>
       <c r="L108">
-        <v>100.2</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4837,22 +4837,22 @@
         <v>22</v>
       </c>
       <c r="B109">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C109">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D109" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="E109" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -4864,7 +4864,7 @@
         <v>100</v>
       </c>
       <c r="L109">
-        <v>100.2</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4872,22 +4872,22 @@
         <v>24</v>
       </c>
       <c r="B110">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D110" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E110" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
       </c>
       <c r="G110" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -4899,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="L110">
-        <v>100.2</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4907,7 +4907,7 @@
         <v>26</v>
       </c>
       <c r="B111">
-        <v>563</v>
+        <v>318</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4916,13 +4916,13 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
       </c>
       <c r="G111" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -4934,7 +4934,7 @@
         <v>100</v>
       </c>
       <c r="L111">
-        <v>100.2</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -4942,22 +4942,22 @@
         <v>12</v>
       </c>
       <c r="B112">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C112">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D112" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E112" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F112" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G112" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -4969,7 +4969,7 @@
         <v>100</v>
       </c>
       <c r="L112">
-        <v>115.1</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -4977,22 +4977,22 @@
         <v>20</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E113" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F113" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G113" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -5004,7 +5004,7 @@
         <v>100</v>
       </c>
       <c r="L113">
-        <v>115.1</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -5012,22 +5012,22 @@
         <v>22</v>
       </c>
       <c r="B114">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C114">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D114" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E114" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F114" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G114" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -5039,7 +5039,7 @@
         <v>100</v>
       </c>
       <c r="L114">
-        <v>115.1</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5047,22 +5047,22 @@
         <v>24</v>
       </c>
       <c r="B115">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D115" t="s">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="E115" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F115" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G115" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -5074,7 +5074,7 @@
         <v>100</v>
       </c>
       <c r="L115">
-        <v>115.1</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5082,7 +5082,7 @@
         <v>26</v>
       </c>
       <c r="B116">
-        <v>375</v>
+        <v>709</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5091,13 +5091,13 @@
         <v>21</v>
       </c>
       <c r="E116" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F116" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G116" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -5109,7 +5109,7 @@
         <v>100</v>
       </c>
       <c r="L116">
-        <v>115.1</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -5117,22 +5117,22 @@
         <v>12</v>
       </c>
       <c r="B117">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C117">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D117" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="E117" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F117" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G117" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -5140,14 +5140,11 @@
       <c r="I117" t="s">
         <v>18</v>
       </c>
-      <c r="J117" t="s">
-        <v>130</v>
-      </c>
       <c r="K117">
         <v>100</v>
       </c>
       <c r="L117">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5155,22 +5152,22 @@
         <v>20</v>
       </c>
       <c r="B118">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="E118" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F118" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G118" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -5178,14 +5175,11 @@
       <c r="I118" t="s">
         <v>18</v>
       </c>
-      <c r="J118" t="s">
-        <v>131</v>
-      </c>
       <c r="K118">
         <v>100</v>
       </c>
       <c r="L118">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5193,22 +5187,22 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C119">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="E119" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F119" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G119" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -5220,7 +5214,7 @@
         <v>100</v>
       </c>
       <c r="L119">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5228,22 +5222,22 @@
         <v>24</v>
       </c>
       <c r="B120">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C120">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D120" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="E120" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F120" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G120" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -5255,7 +5249,7 @@
         <v>100</v>
       </c>
       <c r="L120">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5263,7 +5257,7 @@
         <v>26</v>
       </c>
       <c r="B121">
-        <v>563</v>
+        <v>480</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5272,13 +5266,13 @@
         <v>21</v>
       </c>
       <c r="E121" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="F121" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G121" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -5290,7 +5284,7 @@
         <v>100</v>
       </c>
       <c r="L121">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5298,22 +5292,22 @@
         <v>12</v>
       </c>
       <c r="B122">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C122">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="E122" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F122" t="s">
         <v>28</v>
       </c>
       <c r="G122" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -5321,11 +5315,14 @@
       <c r="I122" t="s">
         <v>18</v>
       </c>
+      <c r="J122" t="s">
+        <v>115</v>
+      </c>
       <c r="K122">
         <v>100</v>
       </c>
       <c r="L122">
-        <v>125.9</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5333,22 +5330,22 @@
         <v>20</v>
       </c>
       <c r="B123">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C123">
         <v>4</v>
       </c>
       <c r="D123" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="E123" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F123" t="s">
         <v>28</v>
       </c>
       <c r="G123" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -5360,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="L123">
-        <v>125.9</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5368,22 +5365,22 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C124">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D124" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E124" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F124" t="s">
         <v>28</v>
       </c>
       <c r="G124" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -5395,7 +5392,7 @@
         <v>100</v>
       </c>
       <c r="L124">
-        <v>125.9</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5403,22 +5400,22 @@
         <v>24</v>
       </c>
       <c r="B125">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="C125">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="D125" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E125" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F125" t="s">
         <v>28</v>
       </c>
       <c r="G125" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H125" t="s">
         <v>17</v>
@@ -5430,7 +5427,7 @@
         <v>100</v>
       </c>
       <c r="L125">
-        <v>125.9</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5438,7 +5435,7 @@
         <v>26</v>
       </c>
       <c r="B126">
-        <v>563</v>
+        <v>720</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -5447,13 +5444,13 @@
         <v>21</v>
       </c>
       <c r="E126" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="F126" t="s">
         <v>28</v>
       </c>
       <c r="G126" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -5465,7 +5462,7 @@
         <v>100</v>
       </c>
       <c r="L126">
-        <v>125.9</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5473,22 +5470,22 @@
         <v>12</v>
       </c>
       <c r="B127">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D127" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="E127" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F127" t="s">
         <v>15</v>
       </c>
       <c r="G127" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -5500,7 +5497,7 @@
         <v>100</v>
       </c>
       <c r="L127">
-        <v>54</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5508,22 +5505,22 @@
         <v>20</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C128">
         <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="E128" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F128" t="s">
         <v>15</v>
       </c>
       <c r="G128" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -5535,7 +5532,7 @@
         <v>100</v>
       </c>
       <c r="L128">
-        <v>54</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5543,22 +5540,22 @@
         <v>22</v>
       </c>
       <c r="B129">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C129">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D129" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="E129" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F129" t="s">
         <v>15</v>
       </c>
       <c r="G129" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -5570,7 +5567,7 @@
         <v>100</v>
       </c>
       <c r="L129">
-        <v>54</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5578,22 +5575,22 @@
         <v>24</v>
       </c>
       <c r="B130">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D130" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="E130" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F130" t="s">
         <v>15</v>
       </c>
       <c r="G130" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -5605,7 +5602,7 @@
         <v>100</v>
       </c>
       <c r="L130">
-        <v>54</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5613,7 +5610,7 @@
         <v>26</v>
       </c>
       <c r="B131">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -5622,13 +5619,13 @@
         <v>21</v>
       </c>
       <c r="E131" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="F131" t="s">
         <v>15</v>
       </c>
       <c r="G131" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -5640,7 +5637,7 @@
         <v>100</v>
       </c>
       <c r="L131">
-        <v>54</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5648,22 +5645,22 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C132">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D132" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E132" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F132" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G132" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -5671,11 +5668,14 @@
       <c r="I132" t="s">
         <v>18</v>
       </c>
+      <c r="J132" t="s">
+        <v>125</v>
+      </c>
       <c r="K132">
         <v>100</v>
       </c>
       <c r="L132">
-        <v>62.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5683,22 +5683,22 @@
         <v>20</v>
       </c>
       <c r="B133">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E133" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F133" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G133" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -5710,7 +5710,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>62.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5718,22 +5718,22 @@
         <v>22</v>
       </c>
       <c r="B134">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C134">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D134" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="E134" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F134" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G134" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -5745,7 +5745,7 @@
         <v>100</v>
       </c>
       <c r="L134">
-        <v>62.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5753,22 +5753,22 @@
         <v>24</v>
       </c>
       <c r="B135">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C135">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E135" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F135" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G135" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -5780,7 +5780,7 @@
         <v>100</v>
       </c>
       <c r="L135">
-        <v>62.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5788,7 +5788,7 @@
         <v>26</v>
       </c>
       <c r="B136">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>21</v>
       </c>
       <c r="E136" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F136" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G136" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -5815,7 +5815,7 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>62.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5823,22 +5823,22 @@
         <v>12</v>
       </c>
       <c r="B137">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D137" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E137" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="F137" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G137" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H137" t="s">
         <v>17</v>
@@ -5846,14 +5846,11 @@
       <c r="I137" t="s">
         <v>18</v>
       </c>
-      <c r="J137" t="s">
-        <v>142</v>
-      </c>
       <c r="K137">
         <v>100</v>
       </c>
       <c r="L137">
-        <v>4.7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -5861,7 +5858,7 @@
         <v>20</v>
       </c>
       <c r="B138">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -5870,13 +5867,13 @@
         <v>21</v>
       </c>
       <c r="E138" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="F138" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G138" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H138" t="s">
         <v>17</v>
@@ -5888,7 +5885,7 @@
         <v>100</v>
       </c>
       <c r="L138">
-        <v>4.7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -5896,22 +5893,22 @@
         <v>22</v>
       </c>
       <c r="B139">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C139">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D139" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="E139" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="F139" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G139" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H139" t="s">
         <v>17</v>
@@ -5919,14 +5916,11 @@
       <c r="I139" t="s">
         <v>18</v>
       </c>
-      <c r="J139" t="s">
-        <v>144</v>
-      </c>
       <c r="K139">
         <v>100</v>
       </c>
       <c r="L139">
-        <v>4.7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -5934,22 +5928,22 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D140" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="E140" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="F140" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G140" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H140" t="s">
         <v>17</v>
@@ -5957,14 +5951,11 @@
       <c r="I140" t="s">
         <v>18</v>
       </c>
-      <c r="J140" t="s">
-        <v>144</v>
-      </c>
       <c r="K140">
         <v>100</v>
       </c>
       <c r="L140">
-        <v>4.7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -5972,22 +5963,22 @@
         <v>26</v>
       </c>
       <c r="B141">
-        <v>720</v>
+        <v>167</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="D141" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="E141" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="F141" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G141" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H141" t="s">
         <v>17</v>
@@ -5999,7 +5990,7 @@
         <v>100</v>
       </c>
       <c r="L141">
-        <v>4.7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -6007,22 +5998,22 @@
         <v>12</v>
       </c>
       <c r="B142">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C142">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D142" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E142" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F142" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G142" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H142" t="s">
         <v>17</v>
@@ -6031,13 +6022,13 @@
         <v>18</v>
       </c>
       <c r="J142" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="K142">
         <v>100</v>
       </c>
       <c r="L142">
-        <v>28.1</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -6045,22 +6036,22 @@
         <v>20</v>
       </c>
       <c r="B143">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="E143" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F143" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G143" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
@@ -6068,14 +6059,11 @@
       <c r="I143" t="s">
         <v>18</v>
       </c>
-      <c r="J143" t="s">
-        <v>66</v>
-      </c>
       <c r="K143">
         <v>100</v>
       </c>
       <c r="L143">
-        <v>28.1</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -6083,22 +6071,22 @@
         <v>22</v>
       </c>
       <c r="B144">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E144" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F144" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G144" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H144" t="s">
         <v>17</v>
@@ -6107,13 +6095,13 @@
         <v>18</v>
       </c>
       <c r="J144" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="K144">
         <v>100</v>
       </c>
       <c r="L144">
-        <v>28.1</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -6121,22 +6109,22 @@
         <v>24</v>
       </c>
       <c r="B145">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="E145" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F145" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G145" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H145" t="s">
         <v>17</v>
@@ -6145,13 +6133,13 @@
         <v>18</v>
       </c>
       <c r="J145" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="K145">
         <v>100</v>
       </c>
       <c r="L145">
-        <v>28.1</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -6159,22 +6147,22 @@
         <v>26</v>
       </c>
       <c r="B146">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D146" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="E146" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F146" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G146" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="H146" t="s">
         <v>17</v>
@@ -6182,14 +6170,11 @@
       <c r="I146" t="s">
         <v>18</v>
       </c>
-      <c r="J146" t="s">
-        <v>153</v>
-      </c>
       <c r="K146">
         <v>100</v>
       </c>
       <c r="L146">
-        <v>28.1</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -6197,22 +6182,22 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C147">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D147" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="E147" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F147" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G147" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H147" t="s">
         <v>17</v>
@@ -6220,11 +6205,14 @@
       <c r="I147" t="s">
         <v>18</v>
       </c>
+      <c r="J147" t="s">
+        <v>141</v>
+      </c>
       <c r="K147">
         <v>100</v>
       </c>
       <c r="L147">
-        <v>95.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -6232,22 +6220,22 @@
         <v>20</v>
       </c>
       <c r="B148">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="E148" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F148" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G148" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -6259,7 +6247,7 @@
         <v>100</v>
       </c>
       <c r="L148">
-        <v>95.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -6267,22 +6255,22 @@
         <v>22</v>
       </c>
       <c r="B149">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C149">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D149" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="E149" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F149" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G149" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H149" t="s">
         <v>17</v>
@@ -6294,7 +6282,7 @@
         <v>100</v>
       </c>
       <c r="L149">
-        <v>95.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -6302,22 +6290,22 @@
         <v>24</v>
       </c>
       <c r="B150">
-        <v>126</v>
+        <v>32</v>
       </c>
       <c r="C150">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="E150" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F150" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G150" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H150" t="s">
         <v>17</v>
@@ -6329,7 +6317,7 @@
         <v>100</v>
       </c>
       <c r="L150">
-        <v>95.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -6337,22 +6325,22 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="D151" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="E151" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F151" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G151" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -6364,7 +6352,7 @@
         <v>100</v>
       </c>
       <c r="L151">
-        <v>95.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6372,22 +6360,22 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C152">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D152" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="E152" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="F152" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G152" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H152" t="s">
         <v>17</v>
@@ -6395,14 +6383,11 @@
       <c r="I152" t="s">
         <v>18</v>
       </c>
-      <c r="J152" t="s">
-        <v>159</v>
-      </c>
       <c r="K152">
         <v>100</v>
       </c>
       <c r="L152">
-        <v>23.9</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -6410,22 +6395,22 @@
         <v>20</v>
       </c>
       <c r="B153">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E153" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="F153" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G153" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H153" t="s">
         <v>17</v>
@@ -6433,14 +6418,11 @@
       <c r="I153" t="s">
         <v>18</v>
       </c>
-      <c r="J153" t="s">
-        <v>160</v>
-      </c>
       <c r="K153">
         <v>100</v>
       </c>
       <c r="L153">
-        <v>23.9</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6448,22 +6430,22 @@
         <v>22</v>
       </c>
       <c r="B154">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C154">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D154" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="E154" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="F154" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G154" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H154" t="s">
         <v>17</v>
@@ -6471,14 +6453,11 @@
       <c r="I154" t="s">
         <v>18</v>
       </c>
-      <c r="J154" t="s">
-        <v>162</v>
-      </c>
       <c r="K154">
         <v>100</v>
       </c>
       <c r="L154">
-        <v>23.9</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -6486,22 +6465,22 @@
         <v>24</v>
       </c>
       <c r="B155">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="D155" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="E155" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="F155" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G155" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H155" t="s">
         <v>17</v>
@@ -6509,14 +6488,11 @@
       <c r="I155" t="s">
         <v>18</v>
       </c>
-      <c r="J155" t="s">
-        <v>163</v>
-      </c>
       <c r="K155">
         <v>100</v>
       </c>
       <c r="L155">
-        <v>23.9</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -6524,22 +6500,22 @@
         <v>26</v>
       </c>
       <c r="B156">
-        <v>900</v>
+        <v>720</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="D156" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E156" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="F156" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G156" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H156" t="s">
         <v>17</v>
@@ -6547,14 +6523,11 @@
       <c r="I156" t="s">
         <v>18</v>
       </c>
-      <c r="J156" t="s">
-        <v>164</v>
-      </c>
       <c r="K156">
         <v>100</v>
       </c>
       <c r="L156">
-        <v>23.9</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -6562,37 +6535,37 @@
         <v>12</v>
       </c>
       <c r="B157">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D157" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="E157" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="F157" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G157" t="s">
+        <v>146</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157" t="s">
+        <v>18</v>
+      </c>
+      <c r="J157" t="s">
         <v>147</v>
       </c>
-      <c r="H157" t="s">
-        <v>17</v>
-      </c>
-      <c r="I157" t="s">
-        <v>18</v>
-      </c>
-      <c r="J157" t="s">
-        <v>92</v>
-      </c>
       <c r="K157">
         <v>100</v>
       </c>
       <c r="L157">
-        <v>2.2000000000000002</v>
+        <v>27</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -6600,22 +6573,22 @@
         <v>20</v>
       </c>
       <c r="B158">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D158" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E158" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="F158" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G158" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H158" t="s">
         <v>17</v>
@@ -6627,7 +6600,7 @@
         <v>100</v>
       </c>
       <c r="L158">
-        <v>2.2000000000000002</v>
+        <v>27</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -6635,22 +6608,22 @@
         <v>22</v>
       </c>
       <c r="B159">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C159">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D159" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E159" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="F159" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G159" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -6662,7 +6635,7 @@
         <v>100</v>
       </c>
       <c r="L159">
-        <v>2.2000000000000002</v>
+        <v>27</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -6670,22 +6643,22 @@
         <v>24</v>
       </c>
       <c r="B160">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D160" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="E160" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="F160" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G160" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H160" t="s">
         <v>17</v>
@@ -6697,7 +6670,7 @@
         <v>100</v>
       </c>
       <c r="L160">
-        <v>2.2000000000000002</v>
+        <v>27</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -6705,22 +6678,22 @@
         <v>26</v>
       </c>
       <c r="B161">
-        <v>900</v>
+        <v>365</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="D161" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E161" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="F161" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="G161" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H161" t="s">
         <v>17</v>
@@ -6732,7 +6705,7 @@
         <v>100</v>
       </c>
       <c r="L161">
-        <v>2.2000000000000002</v>
+        <v>27</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -6740,22 +6713,22 @@
         <v>12</v>
       </c>
       <c r="B162">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C162">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D162" t="s">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="E162" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="F162" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G162" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H162" t="s">
         <v>17</v>
@@ -6767,7 +6740,7 @@
         <v>100</v>
       </c>
       <c r="L162">
-        <v>58.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -6775,22 +6748,22 @@
         <v>20</v>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C163">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D163" t="s">
+        <v>150</v>
+      </c>
+      <c r="E163" t="s">
         <v>149</v>
       </c>
-      <c r="E163" t="s">
-        <v>165</v>
-      </c>
       <c r="F163" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G163" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
@@ -6802,7 +6775,7 @@
         <v>100</v>
       </c>
       <c r="L163">
-        <v>58.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -6810,22 +6783,22 @@
         <v>22</v>
       </c>
       <c r="B164">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C164">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D164" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="E164" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="F164" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G164" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H164" t="s">
         <v>17</v>
@@ -6837,7 +6810,7 @@
         <v>100</v>
       </c>
       <c r="L164">
-        <v>58.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -6845,22 +6818,22 @@
         <v>24</v>
       </c>
       <c r="B165">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="D165" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
       <c r="E165" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="F165" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G165" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H165" t="s">
         <v>17</v>
@@ -6872,7 +6845,7 @@
         <v>100</v>
       </c>
       <c r="L165">
-        <v>58.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -6880,22 +6853,22 @@
         <v>26</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="D166" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="E166" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="F166" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G166" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H166" t="s">
         <v>17</v>
@@ -6907,7 +6880,7 @@
         <v>100</v>
       </c>
       <c r="L166">
-        <v>58.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -6915,22 +6888,22 @@
         <v>12</v>
       </c>
       <c r="B167">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D167" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E167" t="s">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="F167" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G167" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H167" t="s">
         <v>17</v>
@@ -6939,13 +6912,13 @@
         <v>18</v>
       </c>
       <c r="J167" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="K167">
         <v>100</v>
       </c>
       <c r="L167">
-        <v>2.6</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -6953,22 +6926,22 @@
         <v>20</v>
       </c>
       <c r="B168">
+        <v>8</v>
+      </c>
+      <c r="C168">
         <v>2</v>
       </c>
-      <c r="C168">
-        <v>0</v>
-      </c>
       <c r="D168" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E168" t="s">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="F168" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G168" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H168" t="s">
         <v>17</v>
@@ -6976,11 +6949,14 @@
       <c r="I168" t="s">
         <v>18</v>
       </c>
+      <c r="J168" t="s">
+        <v>156</v>
+      </c>
       <c r="K168">
         <v>100</v>
       </c>
       <c r="L168">
-        <v>2.6</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -6988,22 +6964,22 @@
         <v>22</v>
       </c>
       <c r="B169">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C169">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D169" t="s">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="E169" t="s">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="F169" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G169" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -7011,11 +6987,14 @@
       <c r="I169" t="s">
         <v>18</v>
       </c>
+      <c r="J169" t="s">
+        <v>158</v>
+      </c>
       <c r="K169">
         <v>100</v>
       </c>
       <c r="L169">
-        <v>2.6</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -7023,22 +7002,22 @@
         <v>24</v>
       </c>
       <c r="B170">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D170" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="E170" t="s">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="F170" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G170" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -7046,11 +7025,14 @@
       <c r="I170" t="s">
         <v>18</v>
       </c>
+      <c r="J170" t="s">
+        <v>159</v>
+      </c>
       <c r="K170">
         <v>100</v>
       </c>
       <c r="L170">
-        <v>2.6</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -7058,7 +7040,7 @@
         <v>26</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -7067,13 +7049,13 @@
         <v>21</v>
       </c>
       <c r="E171" t="s">
-        <v>169</v>
+        <v>37</v>
       </c>
       <c r="F171" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G171" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="H171" t="s">
         <v>17</v>
@@ -7081,11 +7063,14 @@
       <c r="I171" t="s">
         <v>18</v>
       </c>
+      <c r="J171" t="s">
+        <v>160</v>
+      </c>
       <c r="K171">
         <v>100</v>
       </c>
       <c r="L171">
-        <v>2.6</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -7093,22 +7078,22 @@
         <v>12</v>
       </c>
       <c r="B172">
+        <v>14</v>
+      </c>
+      <c r="C172">
         <v>22</v>
       </c>
-      <c r="C172">
-        <v>21</v>
-      </c>
       <c r="D172" t="s">
-        <v>88</v>
+        <v>161</v>
       </c>
       <c r="E172" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F172" t="s">
         <v>15</v>
       </c>
       <c r="G172" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H172" t="s">
         <v>17</v>
@@ -7116,11 +7101,14 @@
       <c r="I172" t="s">
         <v>18</v>
       </c>
+      <c r="J172" t="s">
+        <v>164</v>
+      </c>
       <c r="K172">
         <v>100</v>
       </c>
       <c r="L172">
-        <v>106.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -7128,22 +7116,22 @@
         <v>20</v>
       </c>
       <c r="B173">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C173">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D173" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="E173" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F173" t="s">
         <v>15</v>
       </c>
       <c r="G173" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H173" t="s">
         <v>17</v>
@@ -7151,11 +7139,14 @@
       <c r="I173" t="s">
         <v>18</v>
       </c>
+      <c r="J173" t="s">
+        <v>165</v>
+      </c>
       <c r="K173">
         <v>100</v>
       </c>
       <c r="L173">
-        <v>106.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -7163,22 +7154,22 @@
         <v>22</v>
       </c>
       <c r="B174">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C174">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D174" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="E174" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F174" t="s">
         <v>15</v>
       </c>
       <c r="G174" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H174" t="s">
         <v>17</v>
@@ -7186,11 +7177,14 @@
       <c r="I174" t="s">
         <v>18</v>
       </c>
+      <c r="J174" t="s">
+        <v>167</v>
+      </c>
       <c r="K174">
         <v>100</v>
       </c>
       <c r="L174">
-        <v>106.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -7198,22 +7192,22 @@
         <v>24</v>
       </c>
       <c r="B175">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C175">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="D175" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="E175" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F175" t="s">
         <v>15</v>
       </c>
       <c r="G175" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H175" t="s">
         <v>17</v>
@@ -7221,11 +7215,14 @@
       <c r="I175" t="s">
         <v>18</v>
       </c>
+      <c r="J175" t="s">
+        <v>168</v>
+      </c>
       <c r="K175">
         <v>100</v>
       </c>
       <c r="L175">
-        <v>106.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -7233,22 +7230,22 @@
         <v>26</v>
       </c>
       <c r="B176">
-        <v>473</v>
+        <v>600</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D176" t="s">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="E176" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F176" t="s">
         <v>15</v>
       </c>
       <c r="G176" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H176" t="s">
         <v>17</v>
@@ -7260,7 +7257,7 @@
         <v>100</v>
       </c>
       <c r="L176">
-        <v>106.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -7268,22 +7265,22 @@
         <v>12</v>
       </c>
       <c r="B177">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C177">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D177" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="E177" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="F177" t="s">
         <v>28</v>
       </c>
       <c r="G177" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H177" t="s">
         <v>17</v>
@@ -7291,14 +7288,11 @@
       <c r="I177" t="s">
         <v>18</v>
       </c>
-      <c r="J177" t="s">
-        <v>191</v>
-      </c>
       <c r="K177">
         <v>100</v>
       </c>
       <c r="L177">
-        <v>109.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -7306,22 +7300,22 @@
         <v>20</v>
       </c>
       <c r="B178">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C178">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D178" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="E178" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="F178" t="s">
         <v>28</v>
       </c>
       <c r="G178" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H178" t="s">
         <v>17</v>
@@ -7333,7 +7327,7 @@
         <v>100</v>
       </c>
       <c r="L178">
-        <v>109.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -7341,22 +7335,22 @@
         <v>22</v>
       </c>
       <c r="B179">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C179">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D179" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="E179" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="F179" t="s">
         <v>28</v>
       </c>
       <c r="G179" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H179" t="s">
         <v>17</v>
@@ -7368,7 +7362,7 @@
         <v>100</v>
       </c>
       <c r="L179">
-        <v>109.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -7376,22 +7370,22 @@
         <v>24</v>
       </c>
       <c r="B180">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C180">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="D180" t="s">
-        <v>44</v>
+        <v>113</v>
       </c>
       <c r="E180" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="F180" t="s">
         <v>28</v>
       </c>
       <c r="G180" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H180" t="s">
         <v>17</v>
@@ -7403,7 +7397,7 @@
         <v>100</v>
       </c>
       <c r="L180">
-        <v>109.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -7411,22 +7405,22 @@
         <v>26</v>
       </c>
       <c r="B181">
-        <v>318</v>
+        <v>900</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="D181" t="s">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E181" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="F181" t="s">
         <v>28</v>
       </c>
       <c r="G181" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H181" t="s">
         <v>17</v>
@@ -7438,7 +7432,7 @@
         <v>100</v>
       </c>
       <c r="L181">
-        <v>109.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -7446,22 +7440,22 @@
         <v>12</v>
       </c>
       <c r="B182">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C182">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D182" t="s">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="E182" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="F182" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G182" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H182" t="s">
         <v>17</v>
@@ -7469,11 +7463,14 @@
       <c r="I182" t="s">
         <v>18</v>
       </c>
+      <c r="J182" t="s">
+        <v>174</v>
+      </c>
       <c r="K182">
         <v>100</v>
       </c>
       <c r="L182">
-        <v>74.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -7481,22 +7478,22 @@
         <v>20</v>
       </c>
       <c r="B183">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C183">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D183" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E183" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="F183" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G183" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H183" t="s">
         <v>17</v>
@@ -7508,7 +7505,7 @@
         <v>100</v>
       </c>
       <c r="L183">
-        <v>74.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -7516,22 +7513,22 @@
         <v>22</v>
       </c>
       <c r="B184">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C184">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D184" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E184" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="F184" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G184" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H184" t="s">
         <v>17</v>
@@ -7543,7 +7540,7 @@
         <v>100</v>
       </c>
       <c r="L184">
-        <v>74.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -7551,22 +7548,22 @@
         <v>24</v>
       </c>
       <c r="B185">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C185">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="D185" t="s">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="E185" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="F185" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G185" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H185" t="s">
         <v>17</v>
@@ -7578,7 +7575,7 @@
         <v>100</v>
       </c>
       <c r="L185">
-        <v>74.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -7586,7 +7583,7 @@
         <v>26</v>
       </c>
       <c r="B186">
-        <v>709</v>
+        <v>900</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7595,13 +7592,13 @@
         <v>21</v>
       </c>
       <c r="E186" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="F186" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G186" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H186" t="s">
         <v>17</v>
@@ -7613,7 +7610,7 @@
         <v>100</v>
       </c>
       <c r="L186">
-        <v>74.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -7621,22 +7618,22 @@
         <v>12</v>
       </c>
       <c r="B187">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C187">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D187" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="E187" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F187" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G187" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="H187" t="s">
         <v>17</v>
@@ -7644,11 +7641,14 @@
       <c r="I187" t="s">
         <v>18</v>
       </c>
+      <c r="J187" t="s">
+        <v>176</v>
+      </c>
       <c r="K187">
         <v>100</v>
       </c>
       <c r="L187">
-        <v>62.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -7656,22 +7656,22 @@
         <v>20</v>
       </c>
       <c r="B188">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D188" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E188" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F188" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G188" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="H188" t="s">
         <v>17</v>
@@ -7683,7 +7683,7 @@
         <v>100</v>
       </c>
       <c r="L188">
-        <v>62.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -7691,22 +7691,22 @@
         <v>22</v>
       </c>
       <c r="B189">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C189">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D189" t="s">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="E189" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F189" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G189" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="H189" t="s">
         <v>17</v>
@@ -7714,11 +7714,14 @@
       <c r="I189" t="s">
         <v>18</v>
       </c>
+      <c r="J189" t="s">
+        <v>177</v>
+      </c>
       <c r="K189">
         <v>100</v>
       </c>
       <c r="L189">
-        <v>62.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -7726,22 +7729,22 @@
         <v>24</v>
       </c>
       <c r="B190">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C190">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="D190" t="s">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="E190" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F190" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G190" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="H190" t="s">
         <v>17</v>
@@ -7749,11 +7752,14 @@
       <c r="I190" t="s">
         <v>18</v>
       </c>
+      <c r="J190" t="s">
+        <v>178</v>
+      </c>
       <c r="K190">
         <v>100</v>
       </c>
       <c r="L190">
-        <v>62.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -7761,7 +7767,7 @@
         <v>26</v>
       </c>
       <c r="B191">
-        <v>480</v>
+        <v>900</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -7770,13 +7776,13 @@
         <v>21</v>
       </c>
       <c r="E191" t="s">
-        <v>198</v>
+        <v>50</v>
       </c>
       <c r="F191" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G191" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="H191" t="s">
         <v>17</v>
@@ -7788,7 +7794,7 @@
         <v>100</v>
       </c>
       <c r="L191">
-        <v>62.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -7796,22 +7802,22 @@
         <v>12</v>
       </c>
       <c r="B192">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C192">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D192" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="E192" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F192" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G192" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="H192" t="s">
         <v>17</v>
@@ -7819,14 +7825,11 @@
       <c r="I192" t="s">
         <v>18</v>
       </c>
-      <c r="J192" t="s">
-        <v>203</v>
-      </c>
       <c r="K192">
         <v>100</v>
       </c>
       <c r="L192">
-        <v>54.6</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -7834,22 +7837,22 @@
         <v>20</v>
       </c>
       <c r="B193">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C193">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D193" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="E193" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F193" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G193" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="H193" t="s">
         <v>17</v>
@@ -7861,7 +7864,7 @@
         <v>100</v>
       </c>
       <c r="L193">
-        <v>54.6</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -7869,22 +7872,22 @@
         <v>22</v>
       </c>
       <c r="B194">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C194">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D194" t="s">
-        <v>205</v>
+        <v>70</v>
       </c>
       <c r="E194" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F194" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G194" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="H194" t="s">
         <v>17</v>
@@ -7896,7 +7899,7 @@
         <v>100</v>
       </c>
       <c r="L194">
-        <v>54.6</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -7904,22 +7907,22 @@
         <v>24</v>
       </c>
       <c r="B195">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C195">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="D195" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="E195" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F195" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G195" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="H195" t="s">
         <v>17</v>
@@ -7931,7 +7934,7 @@
         <v>100</v>
       </c>
       <c r="L195">
-        <v>54.6</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -7939,22 +7942,22 @@
         <v>26</v>
       </c>
       <c r="B196">
-        <v>720</v>
+        <v>300</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="D196" t="s">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="E196" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F196" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G196" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="H196" t="s">
         <v>17</v>
@@ -7966,7 +7969,7 @@
         <v>100</v>
       </c>
       <c r="L196">
-        <v>54.6</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -7974,22 +7977,22 @@
         <v>12</v>
       </c>
       <c r="B197">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C197">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D197" t="s">
-        <v>171</v>
+        <v>30</v>
       </c>
       <c r="E197" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F197" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G197" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H197" t="s">
         <v>17</v>
@@ -7998,13 +8001,13 @@
         <v>18</v>
       </c>
       <c r="J197" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="K197">
         <v>100</v>
       </c>
       <c r="L197">
-        <v>90.4</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
@@ -8012,7 +8015,7 @@
         <v>20</v>
       </c>
       <c r="B198">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -8021,13 +8024,13 @@
         <v>21</v>
       </c>
       <c r="E198" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F198" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G198" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H198" t="s">
         <v>17</v>
@@ -8036,13 +8039,13 @@
         <v>18</v>
       </c>
       <c r="J198" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="K198">
         <v>100</v>
       </c>
       <c r="L198">
-        <v>90.4</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -8050,22 +8053,22 @@
         <v>22</v>
       </c>
       <c r="B199">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C199">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D199" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="E199" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F199" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G199" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H199" t="s">
         <v>17</v>
@@ -8074,13 +8077,13 @@
         <v>18</v>
       </c>
       <c r="J199" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="K199">
         <v>100</v>
       </c>
       <c r="L199">
-        <v>90.4</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -8088,22 +8091,22 @@
         <v>24</v>
       </c>
       <c r="B200">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="C200">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="D200" t="s">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="E200" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F200" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G200" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H200" t="s">
         <v>17</v>
@@ -8112,13 +8115,13 @@
         <v>18</v>
       </c>
       <c r="J200" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="K200">
         <v>100</v>
       </c>
       <c r="L200">
-        <v>90.4</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
@@ -8126,22 +8129,22 @@
         <v>26</v>
       </c>
       <c r="B201">
-        <v>600</v>
+        <v>399</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="D201" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="E201" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F201" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G201" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H201" t="s">
         <v>17</v>
@@ -8149,11 +8152,14 @@
       <c r="I201" t="s">
         <v>18</v>
       </c>
+      <c r="J201" t="s">
+        <v>189</v>
+      </c>
       <c r="K201">
         <v>100</v>
       </c>
       <c r="L201">
-        <v>90.4</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -8161,22 +8167,22 @@
         <v>12</v>
       </c>
       <c r="B202">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C202">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D202" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E202" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F202" t="s">
         <v>28</v>
       </c>
       <c r="G202" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H202" t="s">
         <v>17</v>
@@ -8188,7 +8194,7 @@
         <v>100</v>
       </c>
       <c r="L202">
-        <v>54.9</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -8196,22 +8202,22 @@
         <v>20</v>
       </c>
       <c r="B203">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="E203" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F203" t="s">
         <v>28</v>
       </c>
       <c r="G203" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H203" t="s">
         <v>17</v>
@@ -8223,7 +8229,7 @@
         <v>100</v>
       </c>
       <c r="L203">
-        <v>54.9</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -8231,22 +8237,22 @@
         <v>22</v>
       </c>
       <c r="B204">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C204">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D204" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E204" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F204" t="s">
         <v>28</v>
       </c>
       <c r="G204" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H204" t="s">
         <v>17</v>
@@ -8258,7 +8264,7 @@
         <v>100</v>
       </c>
       <c r="L204">
-        <v>54.9</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
@@ -8266,22 +8272,22 @@
         <v>24</v>
       </c>
       <c r="B205">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C205">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D205" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E205" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F205" t="s">
         <v>28</v>
       </c>
       <c r="G205" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H205" t="s">
         <v>17</v>
@@ -8293,7 +8299,7 @@
         <v>100</v>
       </c>
       <c r="L205">
-        <v>54.9</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -8301,22 +8307,22 @@
         <v>26</v>
       </c>
       <c r="B206">
-        <v>900</v>
+        <v>399</v>
       </c>
       <c r="C206">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="D206" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="E206" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F206" t="s">
         <v>28</v>
       </c>
       <c r="G206" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H206" t="s">
         <v>17</v>
@@ -8328,7 +8334,7 @@
         <v>100</v>
       </c>
       <c r="L206">
-        <v>54.9</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
@@ -8336,22 +8342,22 @@
         <v>12</v>
       </c>
       <c r="B207">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C207">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D207" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="E207" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="F207" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G207" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H207" t="s">
         <v>17</v>
@@ -8359,14 +8365,11 @@
       <c r="I207" t="s">
         <v>18</v>
       </c>
-      <c r="J207" t="s">
-        <v>181</v>
-      </c>
       <c r="K207">
         <v>100</v>
       </c>
       <c r="L207">
-        <v>0.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -8374,22 +8377,22 @@
         <v>20</v>
       </c>
       <c r="B208">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D208" t="s">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="E208" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="F208" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G208" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H208" t="s">
         <v>17</v>
@@ -8401,7 +8404,7 @@
         <v>100</v>
       </c>
       <c r="L208">
-        <v>0.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -8409,22 +8412,22 @@
         <v>22</v>
       </c>
       <c r="B209">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D209" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="E209" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="F209" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G209" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H209" t="s">
         <v>17</v>
@@ -8436,7 +8439,7 @@
         <v>100</v>
       </c>
       <c r="L209">
-        <v>0.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -8444,22 +8447,22 @@
         <v>24</v>
       </c>
       <c r="B210">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C210">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="D210" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E210" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="F210" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G210" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H210" t="s">
         <v>17</v>
@@ -8471,7 +8474,7 @@
         <v>100</v>
       </c>
       <c r="L210">
-        <v>0.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -8479,22 +8482,22 @@
         <v>26</v>
       </c>
       <c r="B211">
-        <v>900</v>
+        <v>399</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="D211" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="E211" t="s">
-        <v>62</v>
+        <v>195</v>
       </c>
       <c r="F211" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G211" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H211" t="s">
         <v>17</v>
@@ -8506,7 +8509,7 @@
         <v>100</v>
       </c>
       <c r="L211">
-        <v>0.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -8514,22 +8517,22 @@
         <v>12</v>
       </c>
       <c r="B212">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>182</v>
+        <v>40</v>
       </c>
       <c r="E212" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F212" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G212" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H212" t="s">
         <v>17</v>
@@ -8538,13 +8541,13 @@
         <v>18</v>
       </c>
       <c r="J212" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="K212">
         <v>100</v>
       </c>
       <c r="L212">
-        <v>12.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
@@ -8552,7 +8555,7 @@
         <v>20</v>
       </c>
       <c r="B213">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -8561,13 +8564,13 @@
         <v>21</v>
       </c>
       <c r="E213" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F213" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G213" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H213" t="s">
         <v>17</v>
@@ -8579,7 +8582,7 @@
         <v>100</v>
       </c>
       <c r="L213">
-        <v>12.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
@@ -8587,22 +8590,22 @@
         <v>22</v>
       </c>
       <c r="B214">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C214">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="E214" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F214" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G214" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H214" t="s">
         <v>17</v>
@@ -8611,13 +8614,13 @@
         <v>18</v>
       </c>
       <c r="J214" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="K214">
         <v>100</v>
       </c>
       <c r="L214">
-        <v>12.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
@@ -8625,22 +8628,22 @@
         <v>24</v>
       </c>
       <c r="B215">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C215">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D215" t="s">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="E215" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F215" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G215" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H215" t="s">
         <v>17</v>
@@ -8649,13 +8652,13 @@
         <v>18</v>
       </c>
       <c r="J215" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="K215">
         <v>100</v>
       </c>
       <c r="L215">
-        <v>12.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
@@ -8663,7 +8666,7 @@
         <v>26</v>
       </c>
       <c r="B216">
-        <v>900</v>
+        <v>399</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8672,13 +8675,13 @@
         <v>21</v>
       </c>
       <c r="E216" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F216" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="G216" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="H216" t="s">
         <v>17</v>
@@ -8690,7 +8693,7 @@
         <v>100</v>
       </c>
       <c r="L216">
-        <v>12.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
@@ -8698,22 +8701,22 @@
         <v>12</v>
       </c>
       <c r="B217">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C217">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D217" t="s">
-        <v>94</v>
+        <v>173</v>
       </c>
       <c r="E217" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F217" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G217" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="H217" t="s">
         <v>17</v>
@@ -8721,11 +8724,14 @@
       <c r="I217" t="s">
         <v>18</v>
       </c>
+      <c r="J217" t="s">
+        <v>201</v>
+      </c>
       <c r="K217">
         <v>100</v>
       </c>
       <c r="L217">
-        <v>111.6</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
@@ -8733,22 +8739,22 @@
         <v>20</v>
       </c>
       <c r="B218">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E218" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F218" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G218" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="H218" t="s">
         <v>17</v>
@@ -8756,11 +8762,14 @@
       <c r="I218" t="s">
         <v>18</v>
       </c>
+      <c r="J218" t="s">
+        <v>202</v>
+      </c>
       <c r="K218">
         <v>100</v>
       </c>
       <c r="L218">
-        <v>111.6</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
@@ -8768,22 +8777,22 @@
         <v>22</v>
       </c>
       <c r="B219">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C219">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D219" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
       <c r="E219" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F219" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G219" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="H219" t="s">
         <v>17</v>
@@ -8791,11 +8800,14 @@
       <c r="I219" t="s">
         <v>18</v>
       </c>
+      <c r="J219" t="s">
+        <v>204</v>
+      </c>
       <c r="K219">
         <v>100</v>
       </c>
       <c r="L219">
-        <v>111.6</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
@@ -8803,22 +8815,22 @@
         <v>24</v>
       </c>
       <c r="B220">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="C220">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D220" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="E220" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F220" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G220" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="H220" t="s">
         <v>17</v>
@@ -8826,11 +8838,14 @@
       <c r="I220" t="s">
         <v>18</v>
       </c>
+      <c r="J220" t="s">
+        <v>206</v>
+      </c>
       <c r="K220">
         <v>100</v>
       </c>
       <c r="L220">
-        <v>111.6</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
@@ -8838,7 +8853,7 @@
         <v>26</v>
       </c>
       <c r="B221">
-        <v>480</v>
+        <v>399</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -8847,13 +8862,13 @@
         <v>21</v>
       </c>
       <c r="E221" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="F221" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G221" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="H221" t="s">
         <v>17</v>
@@ -8861,195 +8876,14 @@
       <c r="I221" t="s">
         <v>18</v>
       </c>
+      <c r="J221" t="s">
+        <v>207</v>
+      </c>
       <c r="K221">
         <v>100</v>
       </c>
       <c r="L221">
-        <v>111.6</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>12</v>
-      </c>
-      <c r="B222">
-        <v>9</v>
-      </c>
-      <c r="C222">
-        <v>2</v>
-      </c>
-      <c r="D222" t="s">
-        <v>36</v>
-      </c>
-      <c r="E222" t="s">
-        <v>99</v>
-      </c>
-      <c r="F222" t="s">
-        <v>28</v>
-      </c>
-      <c r="G222" t="s">
-        <v>96</v>
-      </c>
-      <c r="H222" t="s">
-        <v>17</v>
-      </c>
-      <c r="I222" t="s">
-        <v>18</v>
-      </c>
-      <c r="J222" t="s">
-        <v>207</v>
-      </c>
-      <c r="K222">
-        <v>100</v>
-      </c>
-      <c r="L222">
-        <v>33.700000000000003</v>
-      </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>20</v>
-      </c>
-      <c r="B223">
-        <v>0</v>
-      </c>
-      <c r="C223">
-        <v>0</v>
-      </c>
-      <c r="D223" t="s">
-        <v>21</v>
-      </c>
-      <c r="E223" t="s">
-        <v>99</v>
-      </c>
-      <c r="F223" t="s">
-        <v>28</v>
-      </c>
-      <c r="G223" t="s">
-        <v>96</v>
-      </c>
-      <c r="H223" t="s">
-        <v>17</v>
-      </c>
-      <c r="I223" t="s">
-        <v>18</v>
-      </c>
-      <c r="K223">
-        <v>100</v>
-      </c>
-      <c r="L223">
-        <v>33.700000000000003</v>
-      </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>22</v>
-      </c>
-      <c r="B224">
-        <v>30</v>
-      </c>
-      <c r="C224">
-        <v>13</v>
-      </c>
-      <c r="D224" t="s">
-        <v>46</v>
-      </c>
-      <c r="E224" t="s">
-        <v>99</v>
-      </c>
-      <c r="F224" t="s">
-        <v>28</v>
-      </c>
-      <c r="G224" t="s">
-        <v>96</v>
-      </c>
-      <c r="H224" t="s">
-        <v>17</v>
-      </c>
-      <c r="I224" t="s">
-        <v>18</v>
-      </c>
-      <c r="J224" t="s">
-        <v>100</v>
-      </c>
-      <c r="K224">
-        <v>100</v>
-      </c>
-      <c r="L224">
-        <v>33.700000000000003</v>
-      </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>24</v>
-      </c>
-      <c r="B225">
-        <v>36</v>
-      </c>
-      <c r="C225">
-        <v>25</v>
-      </c>
-      <c r="D225" t="s">
-        <v>201</v>
-      </c>
-      <c r="E225" t="s">
-        <v>99</v>
-      </c>
-      <c r="F225" t="s">
-        <v>28</v>
-      </c>
-      <c r="G225" t="s">
-        <v>96</v>
-      </c>
-      <c r="H225" t="s">
-        <v>17</v>
-      </c>
-      <c r="I225" t="s">
-        <v>18</v>
-      </c>
-      <c r="J225" t="s">
-        <v>101</v>
-      </c>
-      <c r="K225">
-        <v>100</v>
-      </c>
-      <c r="L225">
-        <v>33.700000000000003</v>
-      </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>26</v>
-      </c>
-      <c r="B226">
-        <v>720</v>
-      </c>
-      <c r="C226">
-        <v>0</v>
-      </c>
-      <c r="D226" t="s">
-        <v>21</v>
-      </c>
-      <c r="E226" t="s">
-        <v>99</v>
-      </c>
-      <c r="F226" t="s">
-        <v>28</v>
-      </c>
-      <c r="G226" t="s">
-        <v>96</v>
-      </c>
-      <c r="H226" t="s">
-        <v>17</v>
-      </c>
-      <c r="I226" t="s">
-        <v>18</v>
-      </c>
-      <c r="K226">
-        <v>100</v>
-      </c>
-      <c r="L226">
-        <v>33.700000000000003</v>
+        <v>63.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_319573EA547B980E62355476585DCE3A87454E9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FBB29CE-28B8-4A6C-8CE6-7681DB11B053}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_319573EA547B980E62355476585DCE3A87454E9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD8F45B6-4963-455C-9163-8786B872790E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="209">
   <si>
     <t>Producto</t>
   </si>
@@ -301,9 +301,6 @@
     <t>11%</t>
   </si>
   <si>
-    <t>1 día lider   meta puntos 26  meta postp 1</t>
-  </si>
-  <si>
     <t>6%</t>
   </si>
   <si>
@@ -544,9 +541,6 @@
     <t>59%</t>
   </si>
   <si>
-    <t>1 día asesor  meta puntos 69</t>
-  </si>
-  <si>
     <t>10%</t>
   </si>
   <si>
@@ -644,6 +638,15 @@
   </si>
   <si>
     <t>cvs plus 261</t>
+  </si>
+  <si>
+    <t>1 día lider   meta puntos 26 cump 158%   meta postp 1 cump 100%</t>
+  </si>
+  <si>
+    <t>meta 1 cump 100%</t>
+  </si>
+  <si>
+    <t>1 día asesor  meta puntos 69 cump 13%</t>
   </si>
 </sst>
 </file>
@@ -4055,22 +4058,22 @@
         <v>12</v>
       </c>
       <c r="B87">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C87">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E87" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F87" t="s">
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -4082,7 +4085,7 @@
         <v>100</v>
       </c>
       <c r="L87">
-        <v>54</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -4093,19 +4096,19 @@
         <v>3</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="E88" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F88" t="s">
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -4117,7 +4120,7 @@
         <v>100</v>
       </c>
       <c r="L88">
-        <v>54</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -4125,22 +4128,22 @@
         <v>22</v>
       </c>
       <c r="B89">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C89">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D89" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="E89" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F89" t="s">
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -4152,7 +4155,7 @@
         <v>100</v>
       </c>
       <c r="L89">
-        <v>54</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -4160,22 +4163,22 @@
         <v>24</v>
       </c>
       <c r="B90">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D90" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="E90" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F90" t="s">
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -4187,7 +4190,7 @@
         <v>100</v>
       </c>
       <c r="L90">
-        <v>54</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -4195,7 +4198,7 @@
         <v>26</v>
       </c>
       <c r="B91">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4204,13 +4207,13 @@
         <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F91" t="s">
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -4222,7 +4225,7 @@
         <v>100</v>
       </c>
       <c r="L91">
-        <v>54</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4230,22 +4233,22 @@
         <v>12</v>
       </c>
       <c r="B92">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C92">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D92" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E92" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
       </c>
       <c r="G92" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -4253,11 +4256,14 @@
       <c r="I92" t="s">
         <v>18</v>
       </c>
+      <c r="J92" t="s">
+        <v>101</v>
+      </c>
       <c r="K92">
         <v>100</v>
       </c>
       <c r="L92">
-        <v>62.5</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4265,22 +4271,22 @@
         <v>20</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="E93" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
       </c>
       <c r="G93" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -4292,7 +4298,7 @@
         <v>100</v>
       </c>
       <c r="L93">
-        <v>62.5</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4300,22 +4306,22 @@
         <v>22</v>
       </c>
       <c r="B94">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C94">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D94" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E94" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
       </c>
       <c r="G94" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -4327,7 +4333,7 @@
         <v>100</v>
       </c>
       <c r="L94">
-        <v>62.5</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4335,22 +4341,22 @@
         <v>24</v>
       </c>
       <c r="B95">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C95">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D95" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="E95" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
       </c>
       <c r="G95" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -4362,7 +4368,7 @@
         <v>100</v>
       </c>
       <c r="L95">
-        <v>62.5</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4370,7 +4376,7 @@
         <v>26</v>
       </c>
       <c r="B96">
-        <v>720</v>
+        <v>318</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4379,13 +4385,13 @@
         <v>21</v>
       </c>
       <c r="E96" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
       </c>
       <c r="G96" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -4397,7 +4403,7 @@
         <v>100</v>
       </c>
       <c r="L96">
-        <v>62.5</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4405,22 +4411,22 @@
         <v>12</v>
       </c>
       <c r="B97">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D97" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="E97" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="F97" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G97" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -4428,14 +4434,11 @@
       <c r="I97" t="s">
         <v>18</v>
       </c>
-      <c r="J97" t="s">
-        <v>93</v>
-      </c>
       <c r="K97">
         <v>100</v>
       </c>
       <c r="L97">
-        <v>4.7</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4446,19 +4449,19 @@
         <v>5</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D98" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E98" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="F98" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G98" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -4470,7 +4473,7 @@
         <v>100</v>
       </c>
       <c r="L98">
-        <v>4.7</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4478,22 +4481,22 @@
         <v>22</v>
       </c>
       <c r="B99">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E99" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="F99" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G99" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -4501,14 +4504,11 @@
       <c r="I99" t="s">
         <v>18</v>
       </c>
-      <c r="J99" t="s">
-        <v>95</v>
-      </c>
       <c r="K99">
         <v>100</v>
       </c>
       <c r="L99">
-        <v>4.7</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4516,22 +4516,22 @@
         <v>24</v>
       </c>
       <c r="B100">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D100" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E100" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="F100" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G100" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -4539,14 +4539,11 @@
       <c r="I100" t="s">
         <v>18</v>
       </c>
-      <c r="J100" t="s">
-        <v>95</v>
-      </c>
       <c r="K100">
         <v>100</v>
       </c>
       <c r="L100">
-        <v>4.7</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4554,7 +4551,7 @@
         <v>26</v>
       </c>
       <c r="B101">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4563,13 +4560,13 @@
         <v>21</v>
       </c>
       <c r="E101" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="F101" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G101" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -4581,7 +4578,7 @@
         <v>100</v>
       </c>
       <c r="L101">
-        <v>4.7</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4589,22 +4586,22 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C102">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="E102" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F102" t="s">
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -4616,7 +4613,7 @@
         <v>100</v>
       </c>
       <c r="L102">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4627,19 +4624,19 @@
         <v>3</v>
       </c>
       <c r="C103">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F103" t="s">
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4651,7 +4648,7 @@
         <v>100</v>
       </c>
       <c r="L103">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4659,22 +4656,22 @@
         <v>22</v>
       </c>
       <c r="B104">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C104">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D104" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E104" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F104" t="s">
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -4686,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="L104">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4694,22 +4691,22 @@
         <v>24</v>
       </c>
       <c r="B105">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C105">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="D105" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E105" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F105" t="s">
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -4721,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="L105">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4729,7 +4726,7 @@
         <v>26</v>
       </c>
       <c r="B106">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4738,13 +4735,13 @@
         <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F106" t="s">
         <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -4756,7 +4753,7 @@
         <v>100</v>
       </c>
       <c r="L106">
-        <v>106.5</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4764,22 +4761,22 @@
         <v>12</v>
       </c>
       <c r="B107">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C107">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="E107" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -4788,13 +4785,13 @@
         <v>18</v>
       </c>
       <c r="J107" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="K107">
         <v>100</v>
       </c>
       <c r="L107">
-        <v>109.6</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4802,22 +4799,22 @@
         <v>20</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C108">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D108" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E108" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -4829,7 +4826,7 @@
         <v>100</v>
       </c>
       <c r="L108">
-        <v>109.6</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4837,22 +4834,22 @@
         <v>22</v>
       </c>
       <c r="B109">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C109">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E109" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -4864,7 +4861,7 @@
         <v>100</v>
       </c>
       <c r="L109">
-        <v>109.6</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4872,22 +4869,22 @@
         <v>24</v>
       </c>
       <c r="B110">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="C110">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D110" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="E110" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
       </c>
       <c r="G110" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -4899,7 +4896,7 @@
         <v>100</v>
       </c>
       <c r="L110">
-        <v>109.6</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4907,7 +4904,7 @@
         <v>26</v>
       </c>
       <c r="B111">
-        <v>318</v>
+        <v>720</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4916,13 +4913,13 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
       </c>
       <c r="G111" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -4934,7 +4931,7 @@
         <v>100</v>
       </c>
       <c r="L111">
-        <v>109.6</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -4942,22 +4939,22 @@
         <v>12</v>
       </c>
       <c r="B112">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C112">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D112" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="E112" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F112" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -4969,7 +4966,7 @@
         <v>100</v>
       </c>
       <c r="L112">
-        <v>74.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -4977,22 +4974,22 @@
         <v>20</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E113" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F113" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -5004,7 +5001,7 @@
         <v>100</v>
       </c>
       <c r="L113">
-        <v>74.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -5012,22 +5009,22 @@
         <v>22</v>
       </c>
       <c r="B114">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C114">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D114" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E114" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F114" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G114" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -5039,7 +5036,7 @@
         <v>100</v>
       </c>
       <c r="L114">
-        <v>74.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5047,22 +5044,22 @@
         <v>24</v>
       </c>
       <c r="B115">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="C115">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E115" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F115" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G115" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -5074,7 +5071,7 @@
         <v>100</v>
       </c>
       <c r="L115">
-        <v>74.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5082,7 +5079,7 @@
         <v>26</v>
       </c>
       <c r="B116">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -5091,13 +5088,13 @@
         <v>21</v>
       </c>
       <c r="E116" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F116" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G116" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -5109,7 +5106,7 @@
         <v>100</v>
       </c>
       <c r="L116">
-        <v>74.3</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -5117,22 +5114,22 @@
         <v>12</v>
       </c>
       <c r="B117">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E117" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F117" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G117" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -5140,11 +5137,14 @@
       <c r="I117" t="s">
         <v>18</v>
       </c>
+      <c r="J117" t="s">
+        <v>124</v>
+      </c>
       <c r="K117">
         <v>100</v>
       </c>
       <c r="L117">
-        <v>62.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5152,22 +5152,22 @@
         <v>20</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E118" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F118" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G118" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -5179,7 +5179,7 @@
         <v>100</v>
       </c>
       <c r="L118">
-        <v>62.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5187,22 +5187,22 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C119">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="E119" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F119" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G119" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -5214,7 +5214,7 @@
         <v>100</v>
       </c>
       <c r="L119">
-        <v>62.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5222,22 +5222,22 @@
         <v>24</v>
       </c>
       <c r="B120">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="C120">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E120" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F120" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G120" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -5249,7 +5249,7 @@
         <v>100</v>
       </c>
       <c r="L120">
-        <v>62.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5257,7 +5257,7 @@
         <v>26</v>
       </c>
       <c r="B121">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5266,13 +5266,13 @@
         <v>21</v>
       </c>
       <c r="E121" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F121" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G121" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -5284,7 +5284,7 @@
         <v>100</v>
       </c>
       <c r="L121">
-        <v>62.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5292,22 +5292,22 @@
         <v>12</v>
       </c>
       <c r="B122">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C122">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D122" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="E122" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F122" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -5315,14 +5315,11 @@
       <c r="I122" t="s">
         <v>18</v>
       </c>
-      <c r="J122" t="s">
-        <v>115</v>
-      </c>
       <c r="K122">
         <v>100</v>
       </c>
       <c r="L122">
-        <v>54.6</v>
+        <v>110</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5330,22 +5327,22 @@
         <v>20</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E123" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F123" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G123" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -5357,7 +5354,7 @@
         <v>100</v>
       </c>
       <c r="L123">
-        <v>54.6</v>
+        <v>110</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5365,22 +5362,22 @@
         <v>22</v>
       </c>
       <c r="B124">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C124">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D124" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E124" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F124" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G124" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -5392,7 +5389,7 @@
         <v>100</v>
       </c>
       <c r="L124">
-        <v>54.6</v>
+        <v>110</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5400,34 +5397,34 @@
         <v>24</v>
       </c>
       <c r="B125">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C125">
+        <v>53</v>
+      </c>
+      <c r="D125" t="s">
+        <v>129</v>
+      </c>
+      <c r="E125" t="s">
+        <v>126</v>
+      </c>
+      <c r="F125" t="s">
+        <v>15</v>
+      </c>
+      <c r="G125" t="s">
+        <v>127</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125">
+        <v>100</v>
+      </c>
+      <c r="L125">
         <v>110</v>
-      </c>
-      <c r="D125" t="s">
-        <v>118</v>
-      </c>
-      <c r="E125" t="s">
-        <v>114</v>
-      </c>
-      <c r="F125" t="s">
-        <v>28</v>
-      </c>
-      <c r="G125" t="s">
-        <v>111</v>
-      </c>
-      <c r="H125" t="s">
-        <v>17</v>
-      </c>
-      <c r="I125" t="s">
-        <v>18</v>
-      </c>
-      <c r="K125">
-        <v>100</v>
-      </c>
-      <c r="L125">
-        <v>54.6</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5435,22 +5432,22 @@
         <v>26</v>
       </c>
       <c r="B126">
-        <v>720</v>
+        <v>167</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="D126" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="E126" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F126" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G126" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -5462,7 +5459,7 @@
         <v>100</v>
       </c>
       <c r="L126">
-        <v>54.6</v>
+        <v>110</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5470,22 +5467,22 @@
         <v>12</v>
       </c>
       <c r="B127">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C127">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="E127" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="F127" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G127" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -5493,11 +5490,14 @@
       <c r="I127" t="s">
         <v>18</v>
       </c>
+      <c r="J127" t="s">
+        <v>133</v>
+      </c>
       <c r="K127">
         <v>100</v>
       </c>
       <c r="L127">
-        <v>58.5</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5505,22 +5505,22 @@
         <v>20</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="E128" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="F128" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G128" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -5532,7 +5532,7 @@
         <v>100</v>
       </c>
       <c r="L128">
-        <v>58.5</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5540,22 +5540,22 @@
         <v>22</v>
       </c>
       <c r="B129">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C129">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D129" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="E129" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="F129" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G129" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -5563,11 +5563,14 @@
       <c r="I129" t="s">
         <v>18</v>
       </c>
+      <c r="J129" t="s">
+        <v>135</v>
+      </c>
       <c r="K129">
         <v>100</v>
       </c>
       <c r="L129">
-        <v>58.5</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5575,22 +5578,22 @@
         <v>24</v>
       </c>
       <c r="B130">
+        <v>36</v>
+      </c>
+      <c r="C130">
         <v>25</v>
       </c>
-      <c r="C130">
-        <v>18</v>
-      </c>
       <c r="D130" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E130" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="F130" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G130" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -5598,11 +5601,14 @@
       <c r="I130" t="s">
         <v>18</v>
       </c>
+      <c r="J130" t="s">
+        <v>136</v>
+      </c>
       <c r="K130">
         <v>100</v>
       </c>
       <c r="L130">
-        <v>58.5</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5610,22 +5616,22 @@
         <v>26</v>
       </c>
       <c r="B131">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="D131" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="E131" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="F131" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G131" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -5637,7 +5643,7 @@
         <v>100</v>
       </c>
       <c r="L131">
-        <v>58.5</v>
+        <v>34.200000000000003</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5645,22 +5651,22 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D132" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="E132" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F132" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G132" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -5669,13 +5675,13 @@
         <v>18</v>
       </c>
       <c r="J132" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="K132">
         <v>100</v>
       </c>
       <c r="L132">
-        <v>0.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5683,22 +5689,22 @@
         <v>20</v>
       </c>
       <c r="B133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" t="s">
         <v>21</v>
       </c>
       <c r="E133" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F133" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G133" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -5710,7 +5716,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>0.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5718,22 +5724,22 @@
         <v>22</v>
       </c>
       <c r="B134">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D134" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="E134" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F134" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G134" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -5745,7 +5751,7 @@
         <v>100</v>
       </c>
       <c r="L134">
-        <v>0.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5753,22 +5759,22 @@
         <v>24</v>
       </c>
       <c r="B135">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E135" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F135" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G135" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -5780,7 +5786,7 @@
         <v>100</v>
       </c>
       <c r="L135">
-        <v>0.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5788,22 +5794,22 @@
         <v>26</v>
       </c>
       <c r="B136">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="D136" t="s">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="E136" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="F136" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -5815,7 +5821,7 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>0.9</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5823,22 +5829,22 @@
         <v>12</v>
       </c>
       <c r="B137">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C137">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D137" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="E137" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F137" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G137" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="H137" t="s">
         <v>17</v>
@@ -5850,7 +5856,7 @@
         <v>100</v>
       </c>
       <c r="L137">
-        <v>110</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -5858,22 +5864,22 @@
         <v>20</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E138" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F138" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G138" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="H138" t="s">
         <v>17</v>
@@ -5885,7 +5891,7 @@
         <v>100</v>
       </c>
       <c r="L138">
-        <v>110</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -5893,22 +5899,22 @@
         <v>22</v>
       </c>
       <c r="B139">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C139">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D139" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="E139" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F139" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G139" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="H139" t="s">
         <v>17</v>
@@ -5920,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="L139">
-        <v>110</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -5928,22 +5934,22 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C140">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D140" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="E140" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F140" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G140" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="H140" t="s">
         <v>17</v>
@@ -5955,7 +5961,7 @@
         <v>100</v>
       </c>
       <c r="L140">
-        <v>110</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -5963,22 +5969,22 @@
         <v>26</v>
       </c>
       <c r="B141">
-        <v>167</v>
+        <v>720</v>
       </c>
       <c r="C141">
-        <v>186</v>
+        <v>720</v>
       </c>
       <c r="D141" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="E141" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F141" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G141" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="H141" t="s">
         <v>17</v>
@@ -5990,7 +5996,7 @@
         <v>100</v>
       </c>
       <c r="L141">
-        <v>110</v>
+        <v>93.9</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -5998,22 +6004,22 @@
         <v>12</v>
       </c>
       <c r="B142">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D142" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="E142" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F142" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G142" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H142" t="s">
         <v>17</v>
@@ -6022,13 +6028,13 @@
         <v>18</v>
       </c>
       <c r="J142" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="K142">
         <v>100</v>
       </c>
       <c r="L142">
-        <v>34.200000000000003</v>
+        <v>27</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -6036,22 +6042,22 @@
         <v>20</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D143" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E143" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F143" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G143" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
@@ -6063,7 +6069,7 @@
         <v>100</v>
       </c>
       <c r="L143">
-        <v>34.200000000000003</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -6071,22 +6077,22 @@
         <v>22</v>
       </c>
       <c r="B144">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C144">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D144" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E144" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F144" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G144" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H144" t="s">
         <v>17</v>
@@ -6094,14 +6100,11 @@
       <c r="I144" t="s">
         <v>18</v>
       </c>
-      <c r="J144" t="s">
-        <v>136</v>
-      </c>
       <c r="K144">
         <v>100</v>
       </c>
       <c r="L144">
-        <v>34.200000000000003</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -6109,22 +6112,22 @@
         <v>24</v>
       </c>
       <c r="B145">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C145">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D145" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E145" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F145" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G145" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H145" t="s">
         <v>17</v>
@@ -6132,14 +6135,11 @@
       <c r="I145" t="s">
         <v>18</v>
       </c>
-      <c r="J145" t="s">
-        <v>137</v>
-      </c>
       <c r="K145">
         <v>100</v>
       </c>
       <c r="L145">
-        <v>34.200000000000003</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -6147,22 +6147,22 @@
         <v>26</v>
       </c>
       <c r="B146">
-        <v>250</v>
+        <v>365</v>
       </c>
       <c r="C146">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="D146" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
       <c r="E146" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F146" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G146" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="H146" t="s">
         <v>17</v>
@@ -6174,7 +6174,7 @@
         <v>100</v>
       </c>
       <c r="L146">
-        <v>34.200000000000003</v>
+        <v>27</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -6182,22 +6182,22 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C147">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D147" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E147" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F147" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G147" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H147" t="s">
         <v>17</v>
@@ -6205,14 +6205,11 @@
       <c r="I147" t="s">
         <v>18</v>
       </c>
-      <c r="J147" t="s">
-        <v>141</v>
-      </c>
       <c r="K147">
         <v>100</v>
       </c>
       <c r="L147">
-        <v>39.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -6220,22 +6217,22 @@
         <v>20</v>
       </c>
       <c r="B148">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D148" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="E148" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F148" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G148" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -6247,7 +6244,7 @@
         <v>100</v>
       </c>
       <c r="L148">
-        <v>39.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -6255,22 +6252,22 @@
         <v>22</v>
       </c>
       <c r="B149">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C149">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="D149" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="E149" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F149" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G149" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H149" t="s">
         <v>17</v>
@@ -6282,7 +6279,7 @@
         <v>100</v>
       </c>
       <c r="L149">
-        <v>39.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -6290,22 +6287,22 @@
         <v>24</v>
       </c>
       <c r="B150">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="C150">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="D150" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="E150" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F150" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G150" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H150" t="s">
         <v>17</v>
@@ -6317,7 +6314,7 @@
         <v>100</v>
       </c>
       <c r="L150">
-        <v>39.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -6325,22 +6322,22 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>480</v>
+        <v>548</v>
       </c>
       <c r="C151">
-        <v>84</v>
+        <v>255</v>
       </c>
       <c r="D151" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E151" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F151" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G151" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -6352,7 +6349,7 @@
         <v>100</v>
       </c>
       <c r="L151">
-        <v>39.5</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6360,22 +6357,22 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C152">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D152" t="s">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="E152" t="s">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="F152" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G152" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H152" t="s">
         <v>17</v>
@@ -6383,11 +6380,14 @@
       <c r="I152" t="s">
         <v>18</v>
       </c>
+      <c r="J152" t="s">
+        <v>154</v>
+      </c>
       <c r="K152">
         <v>100</v>
       </c>
       <c r="L152">
-        <v>93.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -6395,22 +6395,22 @@
         <v>20</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E153" t="s">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="F153" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G153" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H153" t="s">
         <v>17</v>
@@ -6418,11 +6418,14 @@
       <c r="I153" t="s">
         <v>18</v>
       </c>
+      <c r="J153" t="s">
+        <v>155</v>
+      </c>
       <c r="K153">
         <v>100</v>
       </c>
       <c r="L153">
-        <v>93.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6430,22 +6433,22 @@
         <v>22</v>
       </c>
       <c r="B154">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C154">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D154" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="E154" t="s">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="F154" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G154" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H154" t="s">
         <v>17</v>
@@ -6453,11 +6456,14 @@
       <c r="I154" t="s">
         <v>18</v>
       </c>
+      <c r="J154" t="s">
+        <v>157</v>
+      </c>
       <c r="K154">
         <v>100</v>
       </c>
       <c r="L154">
-        <v>93.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -6465,22 +6471,22 @@
         <v>24</v>
       </c>
       <c r="B155">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="C155">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="D155" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E155" t="s">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="F155" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G155" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H155" t="s">
         <v>17</v>
@@ -6488,11 +6494,14 @@
       <c r="I155" t="s">
         <v>18</v>
       </c>
+      <c r="J155" t="s">
+        <v>158</v>
+      </c>
       <c r="K155">
         <v>100</v>
       </c>
       <c r="L155">
-        <v>93.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -6500,22 +6509,22 @@
         <v>26</v>
       </c>
       <c r="B156">
-        <v>720</v>
+        <v>548</v>
       </c>
       <c r="C156">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="E156" t="s">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="F156" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G156" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H156" t="s">
         <v>17</v>
@@ -6523,11 +6532,14 @@
       <c r="I156" t="s">
         <v>18</v>
       </c>
+      <c r="J156" t="s">
+        <v>159</v>
+      </c>
       <c r="K156">
         <v>100</v>
       </c>
       <c r="L156">
-        <v>93.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -6535,22 +6547,22 @@
         <v>12</v>
       </c>
       <c r="B157">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C157">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D157" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="E157" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="F157" t="s">
         <v>15</v>
       </c>
       <c r="G157" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H157" t="s">
         <v>17</v>
@@ -6558,14 +6570,11 @@
       <c r="I157" t="s">
         <v>18</v>
       </c>
-      <c r="J157" t="s">
-        <v>147</v>
-      </c>
       <c r="K157">
         <v>100</v>
       </c>
       <c r="L157">
-        <v>27</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -6573,22 +6582,22 @@
         <v>20</v>
       </c>
       <c r="B158">
+        <v>3</v>
+      </c>
+      <c r="C158">
         <v>6</v>
       </c>
-      <c r="C158">
-        <v>2</v>
-      </c>
       <c r="D158" t="s">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="E158" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="F158" t="s">
         <v>15</v>
       </c>
       <c r="G158" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H158" t="s">
         <v>17</v>
@@ -6600,7 +6609,7 @@
         <v>100</v>
       </c>
       <c r="L158">
-        <v>27</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -6608,22 +6617,22 @@
         <v>22</v>
       </c>
       <c r="B159">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="C159">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="D159" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="E159" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="F159" t="s">
         <v>15</v>
       </c>
       <c r="G159" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -6635,7 +6644,7 @@
         <v>100</v>
       </c>
       <c r="L159">
-        <v>27</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -6643,22 +6652,22 @@
         <v>24</v>
       </c>
       <c r="B160">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C160">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="D160" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="E160" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="F160" t="s">
         <v>15</v>
       </c>
       <c r="G160" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H160" t="s">
         <v>17</v>
@@ -6670,7 +6679,7 @@
         <v>100</v>
       </c>
       <c r="L160">
-        <v>27</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -6678,22 +6687,22 @@
         <v>26</v>
       </c>
       <c r="B161">
-        <v>365</v>
+        <v>300</v>
       </c>
       <c r="C161">
-        <v>232</v>
+        <v>462</v>
       </c>
       <c r="D161" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
       <c r="E161" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="F161" t="s">
         <v>15</v>
       </c>
       <c r="G161" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H161" t="s">
         <v>17</v>
@@ -6705,7 +6714,7 @@
         <v>100</v>
       </c>
       <c r="L161">
-        <v>27</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -6716,19 +6725,19 @@
         <v>37</v>
       </c>
       <c r="C162">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D162" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E162" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
       </c>
       <c r="G162" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H162" t="s">
         <v>17</v>
@@ -6736,11 +6745,14 @@
       <c r="I162" t="s">
         <v>18</v>
       </c>
+      <c r="J162" t="s">
+        <v>183</v>
+      </c>
       <c r="K162">
         <v>100</v>
       </c>
       <c r="L162">
-        <v>96.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -6748,22 +6760,22 @@
         <v>20</v>
       </c>
       <c r="B163">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C163">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D163" t="s">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="E163" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
       </c>
       <c r="G163" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
@@ -6771,11 +6783,14 @@
       <c r="I163" t="s">
         <v>18</v>
       </c>
+      <c r="J163" t="s">
+        <v>184</v>
+      </c>
       <c r="K163">
         <v>100</v>
       </c>
       <c r="L163">
-        <v>96.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -6783,22 +6798,22 @@
         <v>22</v>
       </c>
       <c r="B164">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C164">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D164" t="s">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="E164" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
       </c>
       <c r="G164" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H164" t="s">
         <v>17</v>
@@ -6806,11 +6821,14 @@
       <c r="I164" t="s">
         <v>18</v>
       </c>
+      <c r="J164" t="s">
+        <v>185</v>
+      </c>
       <c r="K164">
         <v>100</v>
       </c>
       <c r="L164">
-        <v>96.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -6818,22 +6836,22 @@
         <v>24</v>
       </c>
       <c r="B165">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C165">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="D165" t="s">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="E165" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
       </c>
       <c r="G165" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H165" t="s">
         <v>17</v>
@@ -6841,11 +6859,14 @@
       <c r="I165" t="s">
         <v>18</v>
       </c>
+      <c r="J165" t="s">
+        <v>186</v>
+      </c>
       <c r="K165">
         <v>100</v>
       </c>
       <c r="L165">
-        <v>96.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -6853,22 +6874,22 @@
         <v>26</v>
       </c>
       <c r="B166">
-        <v>548</v>
+        <v>399</v>
       </c>
       <c r="C166">
-        <v>255</v>
+        <v>166</v>
       </c>
       <c r="D166" t="s">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="E166" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
       </c>
       <c r="G166" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H166" t="s">
         <v>17</v>
@@ -6876,11 +6897,14 @@
       <c r="I166" t="s">
         <v>18</v>
       </c>
+      <c r="J166" t="s">
+        <v>187</v>
+      </c>
       <c r="K166">
         <v>100</v>
       </c>
       <c r="L166">
-        <v>96.9</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -6891,19 +6915,19 @@
         <v>37</v>
       </c>
       <c r="C167">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D167" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="E167" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="F167" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G167" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H167" t="s">
         <v>17</v>
@@ -6911,14 +6935,11 @@
       <c r="I167" t="s">
         <v>18</v>
       </c>
-      <c r="J167" t="s">
-        <v>155</v>
-      </c>
       <c r="K167">
         <v>100</v>
       </c>
       <c r="L167">
-        <v>24.1</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -6926,22 +6947,22 @@
         <v>20</v>
       </c>
       <c r="B168">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C168">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>34</v>
+        <v>168</v>
       </c>
       <c r="E168" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="F168" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G168" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H168" t="s">
         <v>17</v>
@@ -6949,14 +6970,11 @@
       <c r="I168" t="s">
         <v>18</v>
       </c>
-      <c r="J168" t="s">
-        <v>156</v>
-      </c>
       <c r="K168">
         <v>100</v>
       </c>
       <c r="L168">
-        <v>24.1</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -6964,22 +6982,22 @@
         <v>22</v>
       </c>
       <c r="B169">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C169">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D169" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="E169" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="F169" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G169" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -6987,14 +7005,11 @@
       <c r="I169" t="s">
         <v>18</v>
       </c>
-      <c r="J169" t="s">
-        <v>158</v>
-      </c>
       <c r="K169">
         <v>100</v>
       </c>
       <c r="L169">
-        <v>24.1</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -7002,22 +7017,22 @@
         <v>24</v>
       </c>
       <c r="B170">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C170">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D170" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="E170" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="F170" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G170" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -7025,14 +7040,11 @@
       <c r="I170" t="s">
         <v>18</v>
       </c>
-      <c r="J170" t="s">
-        <v>159</v>
-      </c>
       <c r="K170">
         <v>100</v>
       </c>
       <c r="L170">
-        <v>24.1</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -7040,22 +7052,22 @@
         <v>26</v>
       </c>
       <c r="B171">
-        <v>548</v>
+        <v>399</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="D171" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="E171" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="F171" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G171" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="H171" t="s">
         <v>17</v>
@@ -7063,14 +7075,11 @@
       <c r="I171" t="s">
         <v>18</v>
       </c>
-      <c r="J171" t="s">
-        <v>160</v>
-      </c>
       <c r="K171">
         <v>100</v>
       </c>
       <c r="L171">
-        <v>24.1</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -7078,22 +7087,22 @@
         <v>12</v>
       </c>
       <c r="B172">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C172">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D172" t="s">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="E172" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F172" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G172" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H172" t="s">
         <v>17</v>
@@ -7101,14 +7110,11 @@
       <c r="I172" t="s">
         <v>18</v>
       </c>
-      <c r="J172" t="s">
-        <v>164</v>
-      </c>
       <c r="K172">
         <v>100</v>
       </c>
       <c r="L172">
-        <v>90.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -7116,22 +7122,22 @@
         <v>20</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D173" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="E173" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F173" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G173" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H173" t="s">
         <v>17</v>
@@ -7139,14 +7145,11 @@
       <c r="I173" t="s">
         <v>18</v>
       </c>
-      <c r="J173" t="s">
-        <v>165</v>
-      </c>
       <c r="K173">
         <v>100</v>
       </c>
       <c r="L173">
-        <v>90.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -7154,22 +7157,22 @@
         <v>22</v>
       </c>
       <c r="B174">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C174">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="D174" t="s">
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="E174" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F174" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G174" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H174" t="s">
         <v>17</v>
@@ -7177,14 +7180,11 @@
       <c r="I174" t="s">
         <v>18</v>
       </c>
-      <c r="J174" t="s">
-        <v>167</v>
-      </c>
       <c r="K174">
         <v>100</v>
       </c>
       <c r="L174">
-        <v>90.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -7192,22 +7192,22 @@
         <v>24</v>
       </c>
       <c r="B175">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="C175">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="D175" t="s">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="E175" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F175" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G175" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H175" t="s">
         <v>17</v>
@@ -7215,14 +7215,11 @@
       <c r="I175" t="s">
         <v>18</v>
       </c>
-      <c r="J175" t="s">
-        <v>168</v>
-      </c>
       <c r="K175">
         <v>100</v>
       </c>
       <c r="L175">
-        <v>90.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -7230,22 +7227,22 @@
         <v>26</v>
       </c>
       <c r="B176">
-        <v>600</v>
+        <v>399</v>
       </c>
       <c r="C176">
-        <v>900</v>
+        <v>579</v>
       </c>
       <c r="D176" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="E176" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F176" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G176" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H176" t="s">
         <v>17</v>
@@ -7257,7 +7254,7 @@
         <v>100</v>
       </c>
       <c r="L176">
-        <v>90.4</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -7265,22 +7262,22 @@
         <v>12</v>
       </c>
       <c r="B177">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C177">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D177" t="s">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="E177" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="F177" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G177" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H177" t="s">
         <v>17</v>
@@ -7288,11 +7285,14 @@
       <c r="I177" t="s">
         <v>18</v>
       </c>
+      <c r="J177" t="s">
+        <v>195</v>
+      </c>
       <c r="K177">
         <v>100</v>
       </c>
       <c r="L177">
-        <v>55.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -7300,7 +7300,7 @@
         <v>20</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -7309,13 +7309,13 @@
         <v>21</v>
       </c>
       <c r="E178" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="F178" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G178" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H178" t="s">
         <v>17</v>
@@ -7327,7 +7327,7 @@
         <v>100</v>
       </c>
       <c r="L178">
-        <v>55.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -7335,22 +7335,22 @@
         <v>22</v>
       </c>
       <c r="B179">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C179">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="E179" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="F179" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G179" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H179" t="s">
         <v>17</v>
@@ -7358,11 +7358,14 @@
       <c r="I179" t="s">
         <v>18</v>
       </c>
+      <c r="J179" t="s">
+        <v>197</v>
+      </c>
       <c r="K179">
         <v>100</v>
       </c>
       <c r="L179">
-        <v>55.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -7370,22 +7373,22 @@
         <v>24</v>
       </c>
       <c r="B180">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C180">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D180" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E180" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="F180" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G180" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H180" t="s">
         <v>17</v>
@@ -7393,11 +7396,14 @@
       <c r="I180" t="s">
         <v>18</v>
       </c>
+      <c r="J180" t="s">
+        <v>198</v>
+      </c>
       <c r="K180">
         <v>100</v>
       </c>
       <c r="L180">
-        <v>55.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -7405,22 +7411,22 @@
         <v>26</v>
       </c>
       <c r="B181">
-        <v>900</v>
+        <v>399</v>
       </c>
       <c r="C181">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="D181" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E181" t="s">
-        <v>171</v>
+        <v>37</v>
       </c>
       <c r="F181" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G181" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H181" t="s">
         <v>17</v>
@@ -7432,7 +7438,7 @@
         <v>100</v>
       </c>
       <c r="L181">
-        <v>55.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -7440,22 +7446,22 @@
         <v>12</v>
       </c>
       <c r="B182">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D182" t="s">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="E182" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F182" t="s">
         <v>38</v>
       </c>
       <c r="G182" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H182" t="s">
         <v>17</v>
@@ -7464,13 +7470,13 @@
         <v>18</v>
       </c>
       <c r="J182" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="K182">
         <v>100</v>
       </c>
       <c r="L182">
-        <v>0.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -7478,22 +7484,22 @@
         <v>20</v>
       </c>
       <c r="B183">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E183" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F183" t="s">
         <v>38</v>
       </c>
       <c r="G183" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H183" t="s">
         <v>17</v>
@@ -7501,11 +7507,14 @@
       <c r="I183" t="s">
         <v>18</v>
       </c>
+      <c r="J183" t="s">
+        <v>200</v>
+      </c>
       <c r="K183">
         <v>100</v>
       </c>
       <c r="L183">
-        <v>0.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -7513,22 +7522,22 @@
         <v>22</v>
       </c>
       <c r="B184">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="C184">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D184" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="E184" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F184" t="s">
         <v>38</v>
       </c>
       <c r="G184" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H184" t="s">
         <v>17</v>
@@ -7536,11 +7545,14 @@
       <c r="I184" t="s">
         <v>18</v>
       </c>
+      <c r="J184" t="s">
+        <v>202</v>
+      </c>
       <c r="K184">
         <v>100</v>
       </c>
       <c r="L184">
-        <v>0.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -7548,22 +7560,22 @@
         <v>24</v>
       </c>
       <c r="B185">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C185">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="D185" t="s">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="E185" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F185" t="s">
         <v>38</v>
       </c>
       <c r="G185" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H185" t="s">
         <v>17</v>
@@ -7571,11 +7583,14 @@
       <c r="I185" t="s">
         <v>18</v>
       </c>
+      <c r="J185" t="s">
+        <v>204</v>
+      </c>
       <c r="K185">
         <v>100</v>
       </c>
       <c r="L185">
-        <v>0.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -7583,7 +7598,7 @@
         <v>26</v>
       </c>
       <c r="B186">
-        <v>900</v>
+        <v>399</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7592,13 +7607,13 @@
         <v>21</v>
       </c>
       <c r="E186" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F186" t="s">
         <v>38</v>
       </c>
       <c r="G186" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="H186" t="s">
         <v>17</v>
@@ -7606,11 +7621,14 @@
       <c r="I186" t="s">
         <v>18</v>
       </c>
+      <c r="J186" t="s">
+        <v>205</v>
+      </c>
       <c r="K186">
         <v>100</v>
       </c>
       <c r="L186">
-        <v>0.4</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -7618,22 +7636,22 @@
         <v>12</v>
       </c>
       <c r="B187">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C187">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D187" t="s">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="E187" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F187" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G187" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="H187" t="s">
         <v>17</v>
@@ -7641,14 +7659,11 @@
       <c r="I187" t="s">
         <v>18</v>
       </c>
-      <c r="J187" t="s">
-        <v>176</v>
-      </c>
       <c r="K187">
         <v>100</v>
       </c>
       <c r="L187">
-        <v>12.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -7656,22 +7671,22 @@
         <v>20</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E188" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F188" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G188" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="H188" t="s">
         <v>17</v>
@@ -7683,7 +7698,7 @@
         <v>100</v>
       </c>
       <c r="L188">
-        <v>12.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -7691,22 +7706,22 @@
         <v>22</v>
       </c>
       <c r="B189">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C189">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D189" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E189" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F189" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G189" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="H189" t="s">
         <v>17</v>
@@ -7714,14 +7729,11 @@
       <c r="I189" t="s">
         <v>18</v>
       </c>
-      <c r="J189" t="s">
-        <v>177</v>
-      </c>
       <c r="K189">
         <v>100</v>
       </c>
       <c r="L189">
-        <v>12.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -7729,22 +7741,22 @@
         <v>24</v>
       </c>
       <c r="B190">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="C190">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D190" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E190" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F190" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G190" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="H190" t="s">
         <v>17</v>
@@ -7752,14 +7764,11 @@
       <c r="I190" t="s">
         <v>18</v>
       </c>
-      <c r="J190" t="s">
-        <v>178</v>
-      </c>
       <c r="K190">
         <v>100</v>
       </c>
       <c r="L190">
-        <v>12.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -7767,22 +7776,22 @@
         <v>26</v>
       </c>
       <c r="B191">
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D191" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="E191" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="F191" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G191" t="s">
-        <v>163</v>
+        <v>88</v>
       </c>
       <c r="H191" t="s">
         <v>17</v>
@@ -7794,7 +7803,7 @@
         <v>100</v>
       </c>
       <c r="L191">
-        <v>12.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -7802,22 +7811,22 @@
         <v>12</v>
       </c>
       <c r="B192">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C192">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D192" t="s">
-        <v>179</v>
+        <v>55</v>
       </c>
       <c r="E192" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F192" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G192" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H192" t="s">
         <v>17</v>
@@ -7829,7 +7838,7 @@
         <v>100</v>
       </c>
       <c r="L192">
-        <v>125.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -7837,22 +7846,22 @@
         <v>20</v>
       </c>
       <c r="B193">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C193">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D193" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="E193" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F193" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G193" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H193" t="s">
         <v>17</v>
@@ -7864,7 +7873,7 @@
         <v>100</v>
       </c>
       <c r="L193">
-        <v>125.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -7872,22 +7881,22 @@
         <v>22</v>
       </c>
       <c r="B194">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C194">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D194" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="E194" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F194" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G194" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H194" t="s">
         <v>17</v>
@@ -7899,7 +7908,7 @@
         <v>100</v>
       </c>
       <c r="L194">
-        <v>125.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -7907,22 +7916,22 @@
         <v>24</v>
       </c>
       <c r="B195">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C195">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="D195" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="E195" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F195" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G195" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H195" t="s">
         <v>17</v>
@@ -7934,7 +7943,7 @@
         <v>100</v>
       </c>
       <c r="L195">
-        <v>125.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -7942,22 +7951,22 @@
         <v>26</v>
       </c>
       <c r="B196">
-        <v>300</v>
+        <v>720</v>
       </c>
       <c r="C196">
-        <v>462</v>
+        <v>602</v>
       </c>
       <c r="D196" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E196" t="s">
-        <v>180</v>
+        <v>89</v>
       </c>
       <c r="F196" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G196" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H196" t="s">
         <v>17</v>
@@ -7969,7 +7978,7 @@
         <v>100</v>
       </c>
       <c r="L196">
-        <v>125.5</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -7977,22 +7986,22 @@
         <v>12</v>
       </c>
       <c r="B197">
+        <v>9</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197" t="s">
+        <v>92</v>
+      </c>
+      <c r="E197" t="s">
         <v>37</v>
       </c>
-      <c r="C197">
-        <v>15</v>
-      </c>
-      <c r="D197" t="s">
-        <v>30</v>
-      </c>
-      <c r="E197" t="s">
-        <v>184</v>
-      </c>
       <c r="F197" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G197" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H197" t="s">
         <v>17</v>
@@ -8001,13 +8010,13 @@
         <v>18</v>
       </c>
       <c r="J197" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="K197">
         <v>100</v>
       </c>
       <c r="L197">
-        <v>28.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
@@ -8015,7 +8024,7 @@
         <v>20</v>
       </c>
       <c r="B198">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -8024,13 +8033,13 @@
         <v>21</v>
       </c>
       <c r="E198" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="F198" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G198" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H198" t="s">
         <v>17</v>
@@ -8038,14 +8047,11 @@
       <c r="I198" t="s">
         <v>18</v>
       </c>
-      <c r="J198" t="s">
-        <v>186</v>
-      </c>
       <c r="K198">
         <v>100</v>
       </c>
       <c r="L198">
-        <v>28.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -8053,22 +8059,22 @@
         <v>22</v>
       </c>
       <c r="B199">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C199">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E199" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="F199" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G199" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H199" t="s">
         <v>17</v>
@@ -8077,13 +8083,13 @@
         <v>18</v>
       </c>
       <c r="J199" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="K199">
         <v>100</v>
       </c>
       <c r="L199">
-        <v>28.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -8091,22 +8097,22 @@
         <v>24</v>
       </c>
       <c r="B200">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="C200">
+        <v>3</v>
+      </c>
+      <c r="D200" t="s">
+        <v>112</v>
+      </c>
+      <c r="E200" t="s">
+        <v>37</v>
+      </c>
+      <c r="F200" t="s">
         <v>38</v>
       </c>
-      <c r="D200" t="s">
-        <v>113</v>
-      </c>
-      <c r="E200" t="s">
-        <v>184</v>
-      </c>
-      <c r="F200" t="s">
-        <v>28</v>
-      </c>
       <c r="G200" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H200" t="s">
         <v>17</v>
@@ -8115,13 +8121,13 @@
         <v>18</v>
       </c>
       <c r="J200" t="s">
-        <v>188</v>
+        <v>94</v>
       </c>
       <c r="K200">
         <v>100</v>
       </c>
       <c r="L200">
-        <v>28.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
@@ -8129,22 +8135,22 @@
         <v>26</v>
       </c>
       <c r="B201">
-        <v>399</v>
+        <v>720</v>
       </c>
       <c r="C201">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="D201" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="E201" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="F201" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G201" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="H201" t="s">
         <v>17</v>
@@ -8152,14 +8158,11 @@
       <c r="I201" t="s">
         <v>18</v>
       </c>
-      <c r="J201" t="s">
-        <v>189</v>
-      </c>
       <c r="K201">
         <v>100</v>
       </c>
       <c r="L201">
-        <v>28.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -8167,22 +8170,22 @@
         <v>12</v>
       </c>
       <c r="B202">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C202">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D202" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="E202" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="F202" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G202" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H202" t="s">
         <v>17</v>
@@ -8190,11 +8193,14 @@
       <c r="I202" t="s">
         <v>18</v>
       </c>
+      <c r="J202" t="s">
+        <v>163</v>
+      </c>
       <c r="K202">
         <v>100</v>
       </c>
       <c r="L202">
-        <v>103.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -8202,22 +8208,22 @@
         <v>20</v>
       </c>
       <c r="B203">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C203">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D203" t="s">
-        <v>169</v>
+        <v>21</v>
       </c>
       <c r="E203" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="F203" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G203" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H203" t="s">
         <v>17</v>
@@ -8225,11 +8231,14 @@
       <c r="I203" t="s">
         <v>18</v>
       </c>
+      <c r="J203" t="s">
+        <v>164</v>
+      </c>
       <c r="K203">
         <v>100</v>
       </c>
       <c r="L203">
-        <v>103.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -8237,22 +8246,22 @@
         <v>22</v>
       </c>
       <c r="B204">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C204">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D204" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="E204" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="F204" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G204" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H204" t="s">
         <v>17</v>
@@ -8260,11 +8269,14 @@
       <c r="I204" t="s">
         <v>18</v>
       </c>
+      <c r="J204" t="s">
+        <v>166</v>
+      </c>
       <c r="K204">
         <v>100</v>
       </c>
       <c r="L204">
-        <v>103.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
@@ -8272,22 +8284,22 @@
         <v>24</v>
       </c>
       <c r="B205">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="C205">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="D205" t="s">
-        <v>193</v>
+        <v>112</v>
       </c>
       <c r="E205" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="F205" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G205" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H205" t="s">
         <v>17</v>
@@ -8295,11 +8307,14 @@
       <c r="I205" t="s">
         <v>18</v>
       </c>
+      <c r="J205" t="s">
+        <v>167</v>
+      </c>
       <c r="K205">
         <v>100</v>
       </c>
       <c r="L205">
-        <v>103.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -8307,22 +8322,22 @@
         <v>26</v>
       </c>
       <c r="B206">
-        <v>399</v>
+        <v>600</v>
       </c>
       <c r="C206">
-        <v>579</v>
+        <v>900</v>
       </c>
       <c r="D206" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="E206" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="F206" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G206" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H206" t="s">
         <v>17</v>
@@ -8334,7 +8349,7 @@
         <v>100</v>
       </c>
       <c r="L206">
-        <v>103.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
@@ -8342,22 +8357,22 @@
         <v>12</v>
       </c>
       <c r="B207">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C207">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D207" t="s">
-        <v>67</v>
+        <v>169</v>
       </c>
       <c r="E207" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F207" t="s">
         <v>28</v>
       </c>
       <c r="G207" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H207" t="s">
         <v>17</v>
@@ -8369,7 +8384,7 @@
         <v>100</v>
       </c>
       <c r="L207">
-        <v>110.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -8377,22 +8392,22 @@
         <v>20</v>
       </c>
       <c r="B208">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D208" t="s">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="E208" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F208" t="s">
         <v>28</v>
       </c>
       <c r="G208" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H208" t="s">
         <v>17</v>
@@ -8404,7 +8419,7 @@
         <v>100</v>
       </c>
       <c r="L208">
-        <v>110.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -8412,22 +8427,22 @@
         <v>22</v>
       </c>
       <c r="B209">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C209">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D209" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="E209" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F209" t="s">
         <v>28</v>
       </c>
       <c r="G209" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H209" t="s">
         <v>17</v>
@@ -8439,7 +8454,7 @@
         <v>100</v>
       </c>
       <c r="L209">
-        <v>110.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -8447,22 +8462,22 @@
         <v>24</v>
       </c>
       <c r="B210">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C210">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D210" t="s">
-        <v>196</v>
+        <v>112</v>
       </c>
       <c r="E210" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F210" t="s">
         <v>28</v>
       </c>
       <c r="G210" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H210" t="s">
         <v>17</v>
@@ -8474,7 +8489,7 @@
         <v>100</v>
       </c>
       <c r="L210">
-        <v>110.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -8482,22 +8497,22 @@
         <v>26</v>
       </c>
       <c r="B211">
-        <v>399</v>
+        <v>900</v>
       </c>
       <c r="C211">
-        <v>579</v>
+        <v>534</v>
       </c>
       <c r="D211" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="E211" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="F211" t="s">
         <v>28</v>
       </c>
       <c r="G211" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H211" t="s">
         <v>17</v>
@@ -8509,7 +8524,7 @@
         <v>100</v>
       </c>
       <c r="L211">
-        <v>110.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -8517,13 +8532,13 @@
         <v>12</v>
       </c>
       <c r="B212">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D212" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E212" t="s">
         <v>37</v>
@@ -8532,7 +8547,7 @@
         <v>38</v>
       </c>
       <c r="G212" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H212" t="s">
         <v>17</v>
@@ -8541,13 +8556,13 @@
         <v>18</v>
       </c>
       <c r="J212" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="K212">
         <v>100</v>
       </c>
       <c r="L212">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
@@ -8555,7 +8570,7 @@
         <v>20</v>
       </c>
       <c r="B213">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -8570,7 +8585,7 @@
         <v>38</v>
       </c>
       <c r="G213" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H213" t="s">
         <v>17</v>
@@ -8582,7 +8597,7 @@
         <v>100</v>
       </c>
       <c r="L213">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
@@ -8590,13 +8605,13 @@
         <v>22</v>
       </c>
       <c r="B214">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D214" t="s">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="E214" t="s">
         <v>37</v>
@@ -8605,7 +8620,7 @@
         <v>38</v>
       </c>
       <c r="G214" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H214" t="s">
         <v>17</v>
@@ -8613,14 +8628,11 @@
       <c r="I214" t="s">
         <v>18</v>
       </c>
-      <c r="J214" t="s">
-        <v>199</v>
-      </c>
       <c r="K214">
         <v>100</v>
       </c>
       <c r="L214">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
@@ -8628,13 +8640,13 @@
         <v>24</v>
       </c>
       <c r="B215">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C215">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D215" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E215" t="s">
         <v>37</v>
@@ -8643,7 +8655,7 @@
         <v>38</v>
       </c>
       <c r="G215" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H215" t="s">
         <v>17</v>
@@ -8651,14 +8663,11 @@
       <c r="I215" t="s">
         <v>18</v>
       </c>
-      <c r="J215" t="s">
-        <v>200</v>
-      </c>
       <c r="K215">
         <v>100</v>
       </c>
       <c r="L215">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
@@ -8666,7 +8675,7 @@
         <v>26</v>
       </c>
       <c r="B216">
-        <v>399</v>
+        <v>900</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8681,7 +8690,7 @@
         <v>38</v>
       </c>
       <c r="G216" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H216" t="s">
         <v>17</v>
@@ -8693,7 +8702,7 @@
         <v>100</v>
       </c>
       <c r="L216">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
@@ -8701,10 +8710,10 @@
         <v>12</v>
       </c>
       <c r="B217">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C217">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D217" t="s">
         <v>173</v>
@@ -8716,7 +8725,7 @@
         <v>38</v>
       </c>
       <c r="G217" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H217" t="s">
         <v>17</v>
@@ -8725,13 +8734,13 @@
         <v>18</v>
       </c>
       <c r="J217" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="K217">
         <v>100</v>
       </c>
       <c r="L217">
-        <v>63.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
@@ -8739,13 +8748,13 @@
         <v>20</v>
       </c>
       <c r="B218">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E218" t="s">
         <v>50</v>
@@ -8754,7 +8763,7 @@
         <v>38</v>
       </c>
       <c r="G218" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H218" t="s">
         <v>17</v>
@@ -8762,14 +8771,11 @@
       <c r="I218" t="s">
         <v>18</v>
       </c>
-      <c r="J218" t="s">
-        <v>202</v>
-      </c>
       <c r="K218">
         <v>100</v>
       </c>
       <c r="L218">
-        <v>63.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
@@ -8777,13 +8783,13 @@
         <v>22</v>
       </c>
       <c r="B219">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C219">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D219" t="s">
-        <v>203</v>
+        <v>56</v>
       </c>
       <c r="E219" t="s">
         <v>50</v>
@@ -8792,7 +8798,7 @@
         <v>38</v>
       </c>
       <c r="G219" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H219" t="s">
         <v>17</v>
@@ -8801,13 +8807,13 @@
         <v>18</v>
       </c>
       <c r="J219" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="K219">
         <v>100</v>
       </c>
       <c r="L219">
-        <v>63.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
@@ -8815,13 +8821,13 @@
         <v>24</v>
       </c>
       <c r="B220">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C220">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D220" t="s">
-        <v>205</v>
+        <v>112</v>
       </c>
       <c r="E220" t="s">
         <v>50</v>
@@ -8830,7 +8836,7 @@
         <v>38</v>
       </c>
       <c r="G220" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H220" t="s">
         <v>17</v>
@@ -8839,13 +8845,13 @@
         <v>18</v>
       </c>
       <c r="J220" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="K220">
         <v>100</v>
       </c>
       <c r="L220">
-        <v>63.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
@@ -8853,7 +8859,7 @@
         <v>26</v>
       </c>
       <c r="B221">
-        <v>399</v>
+        <v>900</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -8868,7 +8874,7 @@
         <v>38</v>
       </c>
       <c r="G221" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="H221" t="s">
         <v>17</v>
@@ -8876,14 +8882,11 @@
       <c r="I221" t="s">
         <v>18</v>
       </c>
-      <c r="J221" t="s">
-        <v>207</v>
-      </c>
       <c r="K221">
         <v>100</v>
       </c>
       <c r="L221">
-        <v>63.5</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_319573EA547B980E62355476585DCE3A87454E9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD8F45B6-4963-455C-9163-8786B872790E}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_22111D6B115E5A0F62355476585DCE3A87456A7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701A9E82-ACA3-4DAB-8184-E2478FA1CA79}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="220">
   <si>
     <t>Producto</t>
   </si>
@@ -283,370 +283,403 @@
     <t>153%</t>
   </si>
   <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>267%</t>
+  </si>
+  <si>
+    <t>110%</t>
+  </si>
+  <si>
+    <t>168%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t>Vacaciones del  18 al 06 de julio - se realiza reajuste de meta al CVS</t>
+  </si>
+  <si>
+    <t>300%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>70%</t>
+  </si>
+  <si>
+    <t>Maria Camila Arango VÃ©lez</t>
+  </si>
+  <si>
+    <t>85%</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>42%</t>
+  </si>
+  <si>
+    <t>Lider Geraldin Angulo Jaramillo</t>
+  </si>
+  <si>
+    <t>YARUMAL</t>
+  </si>
+  <si>
+    <t>77%</t>
+  </si>
+  <si>
+    <t>Pendiente 4 porta pre</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>Vacaciones del 26 de junio al 13 de julio, en junio no aplica el promedio de 2 días por vacaciones</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>52%</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>Tatiana  Guerra Gonzalez</t>
+  </si>
+  <si>
+    <t>CAUCASIA</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>72%</t>
+  </si>
+  <si>
+    <t>12%</t>
+  </si>
+  <si>
+    <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>1 día líder  meta puntos 43 Cump 21%</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
+  </si>
+  <si>
+    <t>DABEIBA</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>221%</t>
+  </si>
+  <si>
+    <t>111%</t>
+  </si>
+  <si>
+    <t>22%</t>
+  </si>
+  <si>
+    <t>Estelli Alejandra Ramirez Florez</t>
+  </si>
+  <si>
+    <t>Elabora 12 días x vac meta puntos 453.9 cump 65%       meta post  5 cump 40%</t>
+  </si>
+  <si>
+    <t>43%</t>
+  </si>
+  <si>
+    <t>meta terminales 16 cump 81%</t>
+  </si>
+  <si>
+    <t>meta otros 19 cump 132%</t>
+  </si>
+  <si>
+    <t>74%</t>
+  </si>
+  <si>
+    <t>Lider Don Matias Diana Ruiz</t>
+  </si>
+  <si>
+    <t>DON MATIAS</t>
+  </si>
+  <si>
+    <t>Cubre vacaciones de cajera 7 días meta puntos 432 cump 55%</t>
+  </si>
+  <si>
+    <t>18%</t>
+  </si>
+  <si>
+    <t>Evelyn Daniela Lopera Lopera</t>
+  </si>
+  <si>
+    <t>107%</t>
+  </si>
+  <si>
+    <t>16%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>meta puntos 520 cump 54%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>125%</t>
+  </si>
+  <si>
+    <t>106%</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>14 días líder   meta puntos 633 cump 59%   meta postp  15  cump 87%</t>
+  </si>
+  <si>
+    <t>Meta hogar 5 cump 40%</t>
+  </si>
+  <si>
+    <t>14%</t>
+  </si>
+  <si>
+    <t>Meta terminales  15  cump 33%</t>
+  </si>
+  <si>
+    <t>Meta otros 51 cump 53%</t>
+  </si>
+  <si>
+    <t>Meta 366</t>
+  </si>
+  <si>
+    <t>146%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>159%</t>
+  </si>
+  <si>
+    <t>154%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Taborda Ruiz</t>
+  </si>
+  <si>
+    <t>Elabora 7 días x VAC  - meta puntos  630.7  cump 81%    meta post 13  cump 115%</t>
+  </si>
+  <si>
+    <t>Meta hogar 2 cump 0%</t>
+  </si>
+  <si>
+    <t>Meta terminales 20 cump 70%</t>
+  </si>
+  <si>
+    <t>Meta otros 42</t>
+  </si>
+  <si>
+    <t>CVS 139</t>
+  </si>
+  <si>
+    <t>116%</t>
+  </si>
+  <si>
+    <t>Jessica Catherine Gutierrez Garcia</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>112%</t>
+  </si>
+  <si>
+    <t>84%</t>
+  </si>
+  <si>
+    <t>145%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>92%</t>
+  </si>
+  <si>
+    <t>1 día Líder meta puntos 591.3   meta post 1</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>meta 3</t>
+  </si>
+  <si>
+    <t>meta 5</t>
+  </si>
+  <si>
+    <t>59%</t>
+  </si>
+  <si>
+    <t>15 días, asesora meta puntos 1.182,5 cump 97%  meta post 24 cump 92%</t>
+  </si>
+  <si>
+    <t>Meta Hogar  3 cump. 33%</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>Meta Terminales 38 cump 113%</t>
+  </si>
+  <si>
+    <t>48%</t>
+  </si>
+  <si>
+    <t>Meta Otros 78 cump 73%</t>
+  </si>
+  <si>
+    <t>cvs plus 261</t>
+  </si>
+  <si>
+    <t>157%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elabora 20 días x vac  Meta puntos 921.7  cump 104% </t>
+  </si>
+  <si>
+    <t>meta Hogar 1</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>Meta terminales  24</t>
+  </si>
+  <si>
+    <t>Meta otros 19</t>
+  </si>
+  <si>
+    <t>114%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
+    <t>1 día asesor  meta puntos 69 cump 13%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>3 días líder meta puntos 345.6  cump 58%      meta postpago  2</t>
+  </si>
+  <si>
+    <t>Meta terminales 4</t>
+  </si>
+  <si>
+    <t>Meta otros 7</t>
+  </si>
+  <si>
+    <t>NUMERARIO</t>
+  </si>
+  <si>
+    <t>1 día en Caucasia</t>
+  </si>
+  <si>
+    <t>Junin 4%</t>
+  </si>
+  <si>
+    <t>1%</t>
+  </si>
+  <si>
+    <t>La Estrella 158%</t>
+  </si>
+  <si>
+    <t>Terminal 13%</t>
+  </si>
+  <si>
+    <t>Junín 97%</t>
+  </si>
+  <si>
+    <t>Terminal 58%</t>
+  </si>
+  <si>
     <t>Lider Jhon Alejandro Cardona Quintero</t>
   </si>
   <si>
     <t>LA ESTRELLA</t>
   </si>
   <si>
+    <t>Se realiza promedio por cubrimiento de cajera 7 días por vacaciones</t>
+  </si>
+  <si>
+    <t>173%</t>
+  </si>
+  <si>
     <t>Yessica  Restrepo Caicedo</t>
   </si>
   <si>
-    <t>78%</t>
-  </si>
-  <si>
-    <t>107%</t>
+    <t>90%</t>
   </si>
   <si>
     <t>11%</t>
   </si>
   <si>
+    <t>1 día lider   meta puntos 26 cump 158%   meta postp 1 cump 100%</t>
+  </si>
+  <si>
     <t>6%</t>
   </si>
   <si>
+    <t>meta 1 cump 100%</t>
+  </si>
+  <si>
     <t>meta 1</t>
-  </si>
-  <si>
-    <t>Lider Yolima Mesa Zapata</t>
-  </si>
-  <si>
-    <t>CALDAS</t>
-  </si>
-  <si>
-    <t>267%</t>
-  </si>
-  <si>
-    <t>110%</t>
-  </si>
-  <si>
-    <t>168%</t>
-  </si>
-  <si>
-    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
-  </si>
-  <si>
-    <t>Vacaciones del  18 al 06 de julio - se realiza reajuste de meta al CVS</t>
-  </si>
-  <si>
-    <t>300%</t>
-  </si>
-  <si>
-    <t>96%</t>
-  </si>
-  <si>
-    <t>70%</t>
-  </si>
-  <si>
-    <t>Maria Camila Arango VÃ©lez</t>
-  </si>
-  <si>
-    <t>85%</t>
-  </si>
-  <si>
-    <t>79%</t>
-  </si>
-  <si>
-    <t>42%</t>
-  </si>
-  <si>
-    <t>Lider Geraldin Angulo Jaramillo</t>
-  </si>
-  <si>
-    <t>YARUMAL</t>
-  </si>
-  <si>
-    <t>77%</t>
-  </si>
-  <si>
-    <t>Pendiente 4 porta pre</t>
-  </si>
-  <si>
-    <t>Laura Carolina Chavarria Amariles</t>
-  </si>
-  <si>
-    <t>Vacaciones del 26 de junio al 13 de julio, en junio no aplica el promedio de 2 días por vacaciones</t>
-  </si>
-  <si>
-    <t>80%</t>
-  </si>
-  <si>
-    <t>52%</t>
-  </si>
-  <si>
-    <t>115%</t>
-  </si>
-  <si>
-    <t>Tatiana  Guerra Gonzalez</t>
-  </si>
-  <si>
-    <t>CAUCASIA</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>72%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>Kelly Yuliana Ospina Saldarriaga</t>
-  </si>
-  <si>
-    <t>1 día líder  meta puntos 43 Cump 21%</t>
-  </si>
-  <si>
-    <t>200%</t>
-  </si>
-  <si>
-    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
-  </si>
-  <si>
-    <t>DABEIBA</t>
-  </si>
-  <si>
-    <t>120%</t>
-  </si>
-  <si>
-    <t>221%</t>
-  </si>
-  <si>
-    <t>111%</t>
-  </si>
-  <si>
-    <t>22%</t>
-  </si>
-  <si>
-    <t>Estelli Alejandra Ramirez Florez</t>
-  </si>
-  <si>
-    <t>Elabora 12 días x vac meta puntos 453.9 cump 65%       meta post  5 cump 40%</t>
-  </si>
-  <si>
-    <t>43%</t>
-  </si>
-  <si>
-    <t>meta terminales 16 cump 81%</t>
-  </si>
-  <si>
-    <t>meta otros 19 cump 132%</t>
-  </si>
-  <si>
-    <t>74%</t>
-  </si>
-  <si>
-    <t>Lider Don Matias Diana Ruiz</t>
-  </si>
-  <si>
-    <t>DON MATIAS</t>
-  </si>
-  <si>
-    <t>Cubre vacaciones de cajera 7 días meta puntos 432 cump 55%</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>Evelyn Daniela Lopera Lopera</t>
-  </si>
-  <si>
-    <t>16%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Arbelaez</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>meta puntos 520 cump 54%</t>
-  </si>
-  <si>
-    <t>29%</t>
-  </si>
-  <si>
-    <t>Andrea  Arenas Hurtado</t>
-  </si>
-  <si>
-    <t>125%</t>
-  </si>
-  <si>
-    <t>106%</t>
-  </si>
-  <si>
-    <t>103%</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>14 días líder   meta puntos 633 cump 59%   meta postp  15  cump 87%</t>
-  </si>
-  <si>
-    <t>Meta hogar 5 cump 40%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>Meta terminales  15  cump 33%</t>
-  </si>
-  <si>
-    <t>Meta otros 51 cump 53%</t>
-  </si>
-  <si>
-    <t>Meta 366</t>
-  </si>
-  <si>
-    <t>157%</t>
-  </si>
-  <si>
-    <t>Lider Luz Stella Serna</t>
-  </si>
-  <si>
-    <t>TERMINAL NORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elabora 20 días x vac  Meta puntos 921.7  cump 104% </t>
-  </si>
-  <si>
-    <t>meta Hogar 1</t>
-  </si>
-  <si>
-    <t>118%</t>
-  </si>
-  <si>
-    <t>Meta terminales  24</t>
-  </si>
-  <si>
-    <t>Meta otros 19</t>
-  </si>
-  <si>
-    <t>150%</t>
-  </si>
-  <si>
-    <t>114%</t>
-  </si>
-  <si>
-    <t>Cristian Camilo Torres Toro</t>
-  </si>
-  <si>
-    <t>76%</t>
-  </si>
-  <si>
-    <t>59%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>3 días líder meta puntos 345.6  cump 58%      meta postpago  2</t>
-  </si>
-  <si>
-    <t>Meta terminales 4</t>
-  </si>
-  <si>
-    <t>Meta otros 7</t>
-  </si>
-  <si>
-    <t>146%</t>
-  </si>
-  <si>
-    <t>Lider Leider  Alexander Calderon</t>
-  </si>
-  <si>
-    <t>JUNIN</t>
-  </si>
-  <si>
-    <t>159%</t>
-  </si>
-  <si>
-    <t>154%</t>
-  </si>
-  <si>
-    <t>Diana Marcela Taborda Ruiz</t>
-  </si>
-  <si>
-    <t>Elabora 7 días x VAC  - meta puntos  630.7  cump 81%    meta post 13  cump 115%</t>
-  </si>
-  <si>
-    <t>Meta hogar 2 cump 0%</t>
-  </si>
-  <si>
-    <t>Meta terminales 20 cump 70%</t>
-  </si>
-  <si>
-    <t>Meta otros 42</t>
-  </si>
-  <si>
-    <t>CVS 139</t>
-  </si>
-  <si>
-    <t>116%</t>
-  </si>
-  <si>
-    <t>Jessica Catherine Gutierrez Garcia</t>
-  </si>
-  <si>
-    <t>112%</t>
-  </si>
-  <si>
-    <t>84%</t>
-  </si>
-  <si>
-    <t>145%</t>
-  </si>
-  <si>
-    <t>Sandra Milena Carmona Galeano</t>
-  </si>
-  <si>
-    <t>92%</t>
-  </si>
-  <si>
-    <t>1 día Líder meta puntos 591.3   meta post 1</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>meta 3</t>
-  </si>
-  <si>
-    <t>meta 5</t>
-  </si>
-  <si>
-    <t>15 días, asesora meta puntos 1.182,5 cump 97%  meta post 24 cump 92%</t>
-  </si>
-  <si>
-    <t>Meta Hogar  3 cump. 33%</t>
-  </si>
-  <si>
-    <t>73%</t>
-  </si>
-  <si>
-    <t>Meta Terminales 38 cump 113%</t>
-  </si>
-  <si>
-    <t>48%</t>
-  </si>
-  <si>
-    <t>Meta Otros 78 cump 73%</t>
-  </si>
-  <si>
-    <t>cvs plus 261</t>
-  </si>
-  <si>
-    <t>1 día lider   meta puntos 26 cump 158%   meta postp 1 cump 100%</t>
-  </si>
-  <si>
-    <t>meta 1 cump 100%</t>
-  </si>
-  <si>
-    <t>1 día asesor  meta puntos 69 cump 13%</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L221"/>
+  <dimension ref="A1:L236"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4067,13 +4100,13 @@
         <v>45</v>
       </c>
       <c r="E87" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F87" t="s">
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -4099,16 +4132,16 @@
         <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E88" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F88" t="s">
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -4134,16 +4167,16 @@
         <v>43</v>
       </c>
       <c r="D89" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E89" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F89" t="s">
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -4169,16 +4202,16 @@
         <v>116</v>
       </c>
       <c r="D90" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E90" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F90" t="s">
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -4207,13 +4240,13 @@
         <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F91" t="s">
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -4242,13 +4275,13 @@
         <v>35</v>
       </c>
       <c r="E92" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F92" t="s">
         <v>28</v>
       </c>
       <c r="G92" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -4257,7 +4290,7 @@
         <v>18</v>
       </c>
       <c r="J92" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="K92">
         <v>100</v>
@@ -4277,16 +4310,16 @@
         <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E93" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F93" t="s">
         <v>28</v>
       </c>
       <c r="G93" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -4312,16 +4345,16 @@
         <v>26</v>
       </c>
       <c r="D94" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E94" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F94" t="s">
         <v>28</v>
       </c>
       <c r="G94" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -4350,13 +4383,13 @@
         <v>70</v>
       </c>
       <c r="E95" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F95" t="s">
         <v>28</v>
       </c>
       <c r="G95" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -4385,13 +4418,13 @@
         <v>21</v>
       </c>
       <c r="E96" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F96" t="s">
         <v>28</v>
       </c>
       <c r="G96" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -4417,16 +4450,16 @@
         <v>23</v>
       </c>
       <c r="D97" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E97" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F97" t="s">
         <v>28</v>
       </c>
       <c r="G97" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -4455,13 +4488,13 @@
         <v>70</v>
       </c>
       <c r="E98" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
       </c>
       <c r="G98" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -4487,16 +4520,16 @@
         <v>50</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E99" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
       </c>
       <c r="G99" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -4522,16 +4555,16 @@
         <v>82</v>
       </c>
       <c r="D100" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E100" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F100" t="s">
         <v>28</v>
       </c>
       <c r="G100" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -4560,13 +4593,13 @@
         <v>21</v>
       </c>
       <c r="E101" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
       </c>
       <c r="G101" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -4592,16 +4625,16 @@
         <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E102" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F102" t="s">
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -4630,13 +4663,13 @@
         <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F103" t="s">
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4662,16 +4695,16 @@
         <v>17</v>
       </c>
       <c r="D104" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E104" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F104" t="s">
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -4697,16 +4730,16 @@
         <v>75</v>
       </c>
       <c r="D105" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E105" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F105" t="s">
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -4735,13 +4768,13 @@
         <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F106" t="s">
         <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -4767,16 +4800,16 @@
         <v>14</v>
       </c>
       <c r="D107" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E107" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -4785,7 +4818,7 @@
         <v>18</v>
       </c>
       <c r="J107" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K107">
         <v>100</v>
@@ -4805,16 +4838,16 @@
         <v>4</v>
       </c>
       <c r="D108" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E108" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -4840,16 +4873,16 @@
         <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E109" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -4875,16 +4908,16 @@
         <v>110</v>
       </c>
       <c r="D110" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E110" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F110" t="s">
         <v>28</v>
       </c>
       <c r="G110" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -4913,13 +4946,13 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="F111" t="s">
         <v>28</v>
       </c>
       <c r="G111" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -4948,13 +4981,13 @@
         <v>76</v>
       </c>
       <c r="E112" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F112" t="s">
         <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -4980,16 +5013,16 @@
         <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E113" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F113" t="s">
         <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -5015,16 +5048,16 @@
         <v>29</v>
       </c>
       <c r="D114" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E114" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F114" t="s">
         <v>15</v>
       </c>
       <c r="G114" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -5050,16 +5083,16 @@
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E115" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F115" t="s">
         <v>15</v>
       </c>
       <c r="G115" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -5088,13 +5121,13 @@
         <v>21</v>
       </c>
       <c r="E116" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F116" t="s">
         <v>15</v>
       </c>
       <c r="G116" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -5120,16 +5153,16 @@
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E117" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F117" t="s">
         <v>38</v>
       </c>
       <c r="G117" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -5138,7 +5171,7 @@
         <v>18</v>
       </c>
       <c r="J117" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="K117">
         <v>100</v>
@@ -5161,13 +5194,13 @@
         <v>21</v>
       </c>
       <c r="E118" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F118" t="s">
         <v>38</v>
       </c>
       <c r="G118" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -5196,13 +5229,13 @@
         <v>21</v>
       </c>
       <c r="E119" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F119" t="s">
         <v>38</v>
       </c>
       <c r="G119" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -5228,16 +5261,16 @@
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E120" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F120" t="s">
         <v>38</v>
       </c>
       <c r="G120" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -5266,13 +5299,13 @@
         <v>21</v>
       </c>
       <c r="E121" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F121" t="s">
         <v>38</v>
       </c>
       <c r="G121" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -5298,16 +5331,16 @@
         <v>12</v>
       </c>
       <c r="D122" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E122" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F122" t="s">
         <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -5336,13 +5369,13 @@
         <v>21</v>
       </c>
       <c r="E123" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F123" t="s">
         <v>15</v>
       </c>
       <c r="G123" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -5368,16 +5401,16 @@
         <v>24</v>
       </c>
       <c r="D124" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E124" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F124" t="s">
         <v>15</v>
       </c>
       <c r="G124" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -5403,16 +5436,16 @@
         <v>53</v>
       </c>
       <c r="D125" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E125" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F125" t="s">
         <v>15</v>
       </c>
       <c r="G125" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H125" t="s">
         <v>17</v>
@@ -5438,16 +5471,16 @@
         <v>186</v>
       </c>
       <c r="D126" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E126" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F126" t="s">
         <v>15</v>
       </c>
       <c r="G126" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -5473,16 +5506,16 @@
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E127" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F127" t="s">
         <v>28</v>
       </c>
       <c r="G127" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -5491,7 +5524,7 @@
         <v>18</v>
       </c>
       <c r="J127" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K127">
         <v>100</v>
@@ -5514,13 +5547,13 @@
         <v>21</v>
       </c>
       <c r="E128" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F128" t="s">
         <v>28</v>
       </c>
       <c r="G128" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -5546,16 +5579,16 @@
         <v>13</v>
       </c>
       <c r="D129" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E129" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F129" t="s">
         <v>28</v>
       </c>
       <c r="G129" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -5564,7 +5597,7 @@
         <v>18</v>
       </c>
       <c r="J129" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K129">
         <v>100</v>
@@ -5584,16 +5617,16 @@
         <v>25</v>
       </c>
       <c r="D130" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E130" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F130" t="s">
         <v>28</v>
       </c>
       <c r="G130" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -5602,7 +5635,7 @@
         <v>18</v>
       </c>
       <c r="J130" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="K130">
         <v>100</v>
@@ -5622,16 +5655,16 @@
         <v>185</v>
       </c>
       <c r="D131" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E131" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F131" t="s">
         <v>28</v>
       </c>
       <c r="G131" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -5660,13 +5693,13 @@
         <v>66</v>
       </c>
       <c r="E132" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F132" t="s">
         <v>15</v>
       </c>
       <c r="G132" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -5675,7 +5708,7 @@
         <v>18</v>
       </c>
       <c r="J132" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="K132">
         <v>100</v>
@@ -5698,13 +5731,13 @@
         <v>21</v>
       </c>
       <c r="E133" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F133" t="s">
         <v>15</v>
       </c>
       <c r="G133" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -5730,16 +5763,16 @@
         <v>4</v>
       </c>
       <c r="D134" t="s">
+        <v>124</v>
+      </c>
+      <c r="E134" t="s">
         <v>131</v>
-      </c>
-      <c r="E134" t="s">
-        <v>138</v>
       </c>
       <c r="F134" t="s">
         <v>15</v>
       </c>
       <c r="G134" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -5765,16 +5798,16 @@
         <v>18</v>
       </c>
       <c r="D135" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E135" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F135" t="s">
         <v>15</v>
       </c>
       <c r="G135" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -5800,16 +5833,16 @@
         <v>84</v>
       </c>
       <c r="D136" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E136" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F136" t="s">
         <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -5838,13 +5871,13 @@
         <v>70</v>
       </c>
       <c r="E137" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
       </c>
       <c r="G137" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H137" t="s">
         <v>17</v>
@@ -5873,13 +5906,13 @@
         <v>70</v>
       </c>
       <c r="E138" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
       </c>
       <c r="G138" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H138" t="s">
         <v>17</v>
@@ -5905,16 +5938,16 @@
         <v>29</v>
       </c>
       <c r="D139" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="E139" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
       </c>
       <c r="G139" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H139" t="s">
         <v>17</v>
@@ -5940,16 +5973,16 @@
         <v>68</v>
       </c>
       <c r="D140" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E140" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
       </c>
       <c r="G140" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H140" t="s">
         <v>17</v>
@@ -5978,13 +6011,13 @@
         <v>70</v>
       </c>
       <c r="E141" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
       </c>
       <c r="G141" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H141" t="s">
         <v>17</v>
@@ -6010,16 +6043,16 @@
         <v>4</v>
       </c>
       <c r="D142" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E142" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F142" t="s">
         <v>15</v>
       </c>
       <c r="G142" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H142" t="s">
         <v>17</v>
@@ -6028,7 +6061,7 @@
         <v>18</v>
       </c>
       <c r="J142" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="K142">
         <v>100</v>
@@ -6051,13 +6084,13 @@
         <v>25</v>
       </c>
       <c r="E143" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F143" t="s">
         <v>15</v>
       </c>
       <c r="G143" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
@@ -6083,16 +6116,16 @@
         <v>7</v>
       </c>
       <c r="D144" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E144" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F144" t="s">
         <v>15</v>
       </c>
       <c r="G144" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H144" t="s">
         <v>17</v>
@@ -6118,16 +6151,16 @@
         <v>19</v>
       </c>
       <c r="D145" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E145" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F145" t="s">
         <v>15</v>
       </c>
       <c r="G145" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H145" t="s">
         <v>17</v>
@@ -6156,13 +6189,13 @@
         <v>41</v>
       </c>
       <c r="E146" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F146" t="s">
         <v>15</v>
       </c>
       <c r="G146" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H146" t="s">
         <v>17</v>
@@ -6191,13 +6224,13 @@
         <v>70</v>
       </c>
       <c r="E147" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F147" t="s">
         <v>28</v>
       </c>
       <c r="G147" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H147" t="s">
         <v>17</v>
@@ -6223,16 +6256,16 @@
         <v>10</v>
       </c>
       <c r="D148" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E148" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F148" t="s">
         <v>28</v>
       </c>
       <c r="G148" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -6258,16 +6291,16 @@
         <v>38</v>
       </c>
       <c r="D149" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E149" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F149" t="s">
         <v>28</v>
       </c>
       <c r="G149" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H149" t="s">
         <v>17</v>
@@ -6293,16 +6326,16 @@
         <v>130</v>
       </c>
       <c r="D150" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E150" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F150" t="s">
         <v>28</v>
       </c>
       <c r="G150" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H150" t="s">
         <v>17</v>
@@ -6328,16 +6361,16 @@
         <v>255</v>
       </c>
       <c r="D151" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E151" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F151" t="s">
         <v>28</v>
       </c>
       <c r="G151" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -6363,7 +6396,7 @@
         <v>13</v>
       </c>
       <c r="D152" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E152" t="s">
         <v>37</v>
@@ -6372,7 +6405,7 @@
         <v>38</v>
       </c>
       <c r="G152" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H152" t="s">
         <v>17</v>
@@ -6381,7 +6414,7 @@
         <v>18</v>
       </c>
       <c r="J152" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K152">
         <v>100</v>
@@ -6410,7 +6443,7 @@
         <v>38</v>
       </c>
       <c r="G153" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H153" t="s">
         <v>17</v>
@@ -6419,7 +6452,7 @@
         <v>18</v>
       </c>
       <c r="J153" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K153">
         <v>100</v>
@@ -6439,7 +6472,7 @@
         <v>5</v>
       </c>
       <c r="D154" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E154" t="s">
         <v>37</v>
@@ -6448,7 +6481,7 @@
         <v>38</v>
       </c>
       <c r="G154" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H154" t="s">
         <v>17</v>
@@ -6457,7 +6490,7 @@
         <v>18</v>
       </c>
       <c r="J154" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="K154">
         <v>100</v>
@@ -6477,7 +6510,7 @@
         <v>27</v>
       </c>
       <c r="D155" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E155" t="s">
         <v>37</v>
@@ -6486,7 +6519,7 @@
         <v>38</v>
       </c>
       <c r="G155" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H155" t="s">
         <v>17</v>
@@ -6495,7 +6528,7 @@
         <v>18</v>
       </c>
       <c r="J155" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="K155">
         <v>100</v>
@@ -6524,7 +6557,7 @@
         <v>38</v>
       </c>
       <c r="G156" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="H156" t="s">
         <v>17</v>
@@ -6533,7 +6566,7 @@
         <v>18</v>
       </c>
       <c r="J156" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="K156">
         <v>100</v>
@@ -6553,16 +6586,16 @@
         <v>41</v>
       </c>
       <c r="D157" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="E157" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="F157" t="s">
         <v>15</v>
       </c>
       <c r="G157" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H157" t="s">
         <v>17</v>
@@ -6588,16 +6621,16 @@
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E158" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="F158" t="s">
         <v>15</v>
       </c>
       <c r="G158" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H158" t="s">
         <v>17</v>
@@ -6626,13 +6659,13 @@
         <v>70</v>
       </c>
       <c r="E159" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="F159" t="s">
         <v>15</v>
       </c>
       <c r="G159" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -6658,16 +6691,16 @@
         <v>143</v>
       </c>
       <c r="D160" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="E160" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="F160" t="s">
         <v>15</v>
       </c>
       <c r="G160" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H160" t="s">
         <v>17</v>
@@ -6693,16 +6726,16 @@
         <v>462</v>
       </c>
       <c r="D161" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="E161" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="F161" t="s">
         <v>15</v>
       </c>
       <c r="G161" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H161" t="s">
         <v>17</v>
@@ -6731,13 +6764,13 @@
         <v>30</v>
       </c>
       <c r="E162" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
       </c>
       <c r="G162" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H162" t="s">
         <v>17</v>
@@ -6746,7 +6779,7 @@
         <v>18</v>
       </c>
       <c r="J162" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="K162">
         <v>100</v>
@@ -6769,13 +6802,13 @@
         <v>21</v>
       </c>
       <c r="E163" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
       </c>
       <c r="G163" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
@@ -6784,7 +6817,7 @@
         <v>18</v>
       </c>
       <c r="J163" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="K163">
         <v>100</v>
@@ -6807,13 +6840,13 @@
         <v>59</v>
       </c>
       <c r="E164" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
       </c>
       <c r="G164" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H164" t="s">
         <v>17</v>
@@ -6822,7 +6855,7 @@
         <v>18</v>
       </c>
       <c r="J164" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="K164">
         <v>100</v>
@@ -6842,16 +6875,16 @@
         <v>38</v>
       </c>
       <c r="D165" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E165" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
       </c>
       <c r="G165" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H165" t="s">
         <v>17</v>
@@ -6860,7 +6893,7 @@
         <v>18</v>
       </c>
       <c r="J165" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="K165">
         <v>100</v>
@@ -6880,16 +6913,16 @@
         <v>166</v>
       </c>
       <c r="D166" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E166" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
       </c>
       <c r="G166" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H166" t="s">
         <v>17</v>
@@ -6898,7 +6931,7 @@
         <v>18</v>
       </c>
       <c r="J166" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="K166">
         <v>100</v>
@@ -6918,16 +6951,16 @@
         <v>43</v>
       </c>
       <c r="D167" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E167" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="F167" t="s">
         <v>28</v>
       </c>
       <c r="G167" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H167" t="s">
         <v>17</v>
@@ -6953,16 +6986,16 @@
         <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E168" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="F168" t="s">
         <v>28</v>
       </c>
       <c r="G168" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H168" t="s">
         <v>17</v>
@@ -6988,16 +7021,16 @@
         <v>66</v>
       </c>
       <c r="D169" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="E169" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="F169" t="s">
         <v>28</v>
       </c>
       <c r="G169" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -7023,16 +7056,16 @@
         <v>101</v>
       </c>
       <c r="D170" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="E170" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="F170" t="s">
         <v>28</v>
       </c>
       <c r="G170" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -7058,16 +7091,16 @@
         <v>579</v>
       </c>
       <c r="D171" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="E171" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="F171" t="s">
         <v>28</v>
       </c>
       <c r="G171" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H171" t="s">
         <v>17</v>
@@ -7096,13 +7129,13 @@
         <v>67</v>
       </c>
       <c r="E172" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="F172" t="s">
         <v>28</v>
       </c>
       <c r="G172" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H172" t="s">
         <v>17</v>
@@ -7128,16 +7161,16 @@
         <v>5</v>
       </c>
       <c r="D173" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E173" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="F173" t="s">
         <v>28</v>
       </c>
       <c r="G173" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H173" t="s">
         <v>17</v>
@@ -7163,16 +7196,16 @@
         <v>65</v>
       </c>
       <c r="D174" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E174" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="F174" t="s">
         <v>28</v>
       </c>
       <c r="G174" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H174" t="s">
         <v>17</v>
@@ -7198,16 +7231,16 @@
         <v>111</v>
       </c>
       <c r="D175" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="E175" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="F175" t="s">
         <v>28</v>
       </c>
       <c r="G175" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H175" t="s">
         <v>17</v>
@@ -7233,16 +7266,16 @@
         <v>579</v>
       </c>
       <c r="D176" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="E176" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="F176" t="s">
         <v>28</v>
       </c>
       <c r="G176" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H176" t="s">
         <v>17</v>
@@ -7277,7 +7310,7 @@
         <v>38</v>
       </c>
       <c r="G177" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H177" t="s">
         <v>17</v>
@@ -7286,7 +7319,7 @@
         <v>18</v>
       </c>
       <c r="J177" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="K177">
         <v>100</v>
@@ -7315,7 +7348,7 @@
         <v>38</v>
       </c>
       <c r="G178" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H178" t="s">
         <v>17</v>
@@ -7341,7 +7374,7 @@
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="E179" t="s">
         <v>37</v>
@@ -7350,7 +7383,7 @@
         <v>38</v>
       </c>
       <c r="G179" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H179" t="s">
         <v>17</v>
@@ -7359,7 +7392,7 @@
         <v>18</v>
       </c>
       <c r="J179" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="K179">
         <v>100</v>
@@ -7379,7 +7412,7 @@
         <v>2</v>
       </c>
       <c r="D180" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E180" t="s">
         <v>37</v>
@@ -7388,7 +7421,7 @@
         <v>38</v>
       </c>
       <c r="G180" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H180" t="s">
         <v>17</v>
@@ -7397,7 +7430,7 @@
         <v>18</v>
       </c>
       <c r="J180" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="K180">
         <v>100</v>
@@ -7426,7 +7459,7 @@
         <v>38</v>
       </c>
       <c r="G181" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H181" t="s">
         <v>17</v>
@@ -7452,7 +7485,7 @@
         <v>22</v>
       </c>
       <c r="D182" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E182" t="s">
         <v>50</v>
@@ -7461,7 +7494,7 @@
         <v>38</v>
       </c>
       <c r="G182" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H182" t="s">
         <v>17</v>
@@ -7470,7 +7503,7 @@
         <v>18</v>
       </c>
       <c r="J182" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="K182">
         <v>100</v>
@@ -7499,16 +7532,16 @@
         <v>38</v>
       </c>
       <c r="G183" t="s">
+        <v>156</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183" t="s">
+        <v>18</v>
+      </c>
+      <c r="J183" t="s">
         <v>179</v>
-      </c>
-      <c r="H183" t="s">
-        <v>17</v>
-      </c>
-      <c r="I183" t="s">
-        <v>18</v>
-      </c>
-      <c r="J183" t="s">
-        <v>200</v>
       </c>
       <c r="K183">
         <v>100</v>
@@ -7528,7 +7561,7 @@
         <v>43</v>
       </c>
       <c r="D184" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="E184" t="s">
         <v>50</v>
@@ -7537,7 +7570,7 @@
         <v>38</v>
       </c>
       <c r="G184" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H184" t="s">
         <v>17</v>
@@ -7546,7 +7579,7 @@
         <v>18</v>
       </c>
       <c r="J184" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="K184">
         <v>100</v>
@@ -7566,7 +7599,7 @@
         <v>57</v>
       </c>
       <c r="D185" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="E185" t="s">
         <v>50</v>
@@ -7575,7 +7608,7 @@
         <v>38</v>
       </c>
       <c r="G185" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H185" t="s">
         <v>17</v>
@@ -7584,7 +7617,7 @@
         <v>18</v>
       </c>
       <c r="J185" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="K185">
         <v>100</v>
@@ -7613,7 +7646,7 @@
         <v>38</v>
       </c>
       <c r="G186" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="H186" t="s">
         <v>17</v>
@@ -7622,7 +7655,7 @@
         <v>18</v>
       </c>
       <c r="J186" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="K186">
         <v>100</v>
@@ -7636,22 +7669,22 @@
         <v>12</v>
       </c>
       <c r="B187">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C187">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D187" t="s">
-        <v>70</v>
+        <v>185</v>
       </c>
       <c r="E187" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="F187" t="s">
         <v>15</v>
       </c>
       <c r="G187" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H187" t="s">
         <v>17</v>
@@ -7659,11 +7692,14 @@
       <c r="I187" t="s">
         <v>18</v>
       </c>
+      <c r="J187" t="s">
+        <v>188</v>
+      </c>
       <c r="K187">
         <v>100</v>
       </c>
       <c r="L187">
-        <v>54.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -7671,22 +7707,22 @@
         <v>20</v>
       </c>
       <c r="B188">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D188" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E188" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="F188" t="s">
         <v>15</v>
       </c>
       <c r="G188" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H188" t="s">
         <v>17</v>
@@ -7694,11 +7730,14 @@
       <c r="I188" t="s">
         <v>18</v>
       </c>
+      <c r="J188" t="s">
+        <v>189</v>
+      </c>
       <c r="K188">
         <v>100</v>
       </c>
       <c r="L188">
-        <v>54.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -7706,22 +7745,22 @@
         <v>22</v>
       </c>
       <c r="B189">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C189">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D189" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="E189" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="F189" t="s">
         <v>15</v>
       </c>
       <c r="G189" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H189" t="s">
         <v>17</v>
@@ -7729,11 +7768,14 @@
       <c r="I189" t="s">
         <v>18</v>
       </c>
+      <c r="J189" t="s">
+        <v>191</v>
+      </c>
       <c r="K189">
         <v>100</v>
       </c>
       <c r="L189">
-        <v>54.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -7741,22 +7783,22 @@
         <v>24</v>
       </c>
       <c r="B190">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C190">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="D190" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E190" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="F190" t="s">
         <v>15</v>
       </c>
       <c r="G190" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H190" t="s">
         <v>17</v>
@@ -7764,11 +7806,14 @@
       <c r="I190" t="s">
         <v>18</v>
       </c>
+      <c r="J190" t="s">
+        <v>192</v>
+      </c>
       <c r="K190">
         <v>100</v>
       </c>
       <c r="L190">
-        <v>54.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -7776,22 +7821,22 @@
         <v>26</v>
       </c>
       <c r="B191">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="C191">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="D191" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E191" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="F191" t="s">
         <v>15</v>
       </c>
       <c r="G191" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H191" t="s">
         <v>17</v>
@@ -7803,7 +7848,7 @@
         <v>100</v>
       </c>
       <c r="L191">
-        <v>54.5</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -7811,22 +7856,22 @@
         <v>12</v>
       </c>
       <c r="B192">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C192">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D192" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="E192" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="F192" t="s">
         <v>28</v>
       </c>
       <c r="G192" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H192" t="s">
         <v>17</v>
@@ -7838,7 +7883,7 @@
         <v>100</v>
       </c>
       <c r="L192">
-        <v>62.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -7846,22 +7891,22 @@
         <v>20</v>
       </c>
       <c r="B193">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C193">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D193" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E193" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="F193" t="s">
         <v>28</v>
       </c>
       <c r="G193" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H193" t="s">
         <v>17</v>
@@ -7873,7 +7918,7 @@
         <v>100</v>
       </c>
       <c r="L193">
-        <v>62.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -7881,22 +7926,22 @@
         <v>22</v>
       </c>
       <c r="B194">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C194">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D194" t="s">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="E194" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="F194" t="s">
         <v>28</v>
       </c>
       <c r="G194" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H194" t="s">
         <v>17</v>
@@ -7908,7 +7953,7 @@
         <v>100</v>
       </c>
       <c r="L194">
-        <v>62.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -7916,22 +7961,22 @@
         <v>24</v>
       </c>
       <c r="B195">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C195">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D195" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E195" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="F195" t="s">
         <v>28</v>
       </c>
       <c r="G195" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H195" t="s">
         <v>17</v>
@@ -7943,7 +7988,7 @@
         <v>100</v>
       </c>
       <c r="L195">
-        <v>62.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -7951,22 +7996,22 @@
         <v>26</v>
       </c>
       <c r="B196">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="C196">
-        <v>602</v>
+        <v>534</v>
       </c>
       <c r="D196" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E196" t="s">
-        <v>89</v>
+        <v>194</v>
       </c>
       <c r="F196" t="s">
         <v>28</v>
       </c>
       <c r="G196" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H196" t="s">
         <v>17</v>
@@ -7978,7 +8023,7 @@
         <v>100</v>
       </c>
       <c r="L196">
-        <v>62.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -7986,13 +8031,13 @@
         <v>12</v>
       </c>
       <c r="B197">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D197" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="E197" t="s">
         <v>37</v>
@@ -8001,7 +8046,7 @@
         <v>38</v>
       </c>
       <c r="G197" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H197" t="s">
         <v>17</v>
@@ -8010,13 +8055,13 @@
         <v>18</v>
       </c>
       <c r="J197" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="K197">
         <v>100</v>
       </c>
       <c r="L197">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
@@ -8024,7 +8069,7 @@
         <v>20</v>
       </c>
       <c r="B198">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -8039,7 +8084,7 @@
         <v>38</v>
       </c>
       <c r="G198" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H198" t="s">
         <v>17</v>
@@ -8051,7 +8096,7 @@
         <v>100</v>
       </c>
       <c r="L198">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -8059,13 +8104,13 @@
         <v>22</v>
       </c>
       <c r="B199">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D199" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="E199" t="s">
         <v>37</v>
@@ -8074,7 +8119,7 @@
         <v>38</v>
       </c>
       <c r="G199" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H199" t="s">
         <v>17</v>
@@ -8082,14 +8127,11 @@
       <c r="I199" t="s">
         <v>18</v>
       </c>
-      <c r="J199" t="s">
-        <v>207</v>
-      </c>
       <c r="K199">
         <v>100</v>
       </c>
       <c r="L199">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -8097,13 +8139,13 @@
         <v>24</v>
       </c>
       <c r="B200">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C200">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D200" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E200" t="s">
         <v>37</v>
@@ -8112,7 +8154,7 @@
         <v>38</v>
       </c>
       <c r="G200" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H200" t="s">
         <v>17</v>
@@ -8120,14 +8162,11 @@
       <c r="I200" t="s">
         <v>18</v>
       </c>
-      <c r="J200" t="s">
-        <v>94</v>
-      </c>
       <c r="K200">
         <v>100</v>
       </c>
       <c r="L200">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
@@ -8135,7 +8174,7 @@
         <v>26</v>
       </c>
       <c r="B201">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -8150,7 +8189,7 @@
         <v>38</v>
       </c>
       <c r="G201" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="H201" t="s">
         <v>17</v>
@@ -8162,7 +8201,7 @@
         <v>100</v>
       </c>
       <c r="L201">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -8170,22 +8209,22 @@
         <v>12</v>
       </c>
       <c r="B202">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C202">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D202" t="s">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="E202" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="F202" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G202" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="H202" t="s">
         <v>17</v>
@@ -8194,13 +8233,13 @@
         <v>18</v>
       </c>
       <c r="J202" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="K202">
         <v>100</v>
       </c>
       <c r="L202">
-        <v>90.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -8217,13 +8256,13 @@
         <v>21</v>
       </c>
       <c r="E203" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="F203" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G203" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="H203" t="s">
         <v>17</v>
@@ -8231,14 +8270,11 @@
       <c r="I203" t="s">
         <v>18</v>
       </c>
-      <c r="J203" t="s">
-        <v>164</v>
-      </c>
       <c r="K203">
         <v>100</v>
       </c>
       <c r="L203">
-        <v>90.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -8246,22 +8282,22 @@
         <v>22</v>
       </c>
       <c r="B204">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C204">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="D204" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="E204" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="F204" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G204" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="H204" t="s">
         <v>17</v>
@@ -8270,13 +8306,13 @@
         <v>18</v>
       </c>
       <c r="J204" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="K204">
         <v>100</v>
       </c>
       <c r="L204">
-        <v>90.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
@@ -8284,22 +8320,22 @@
         <v>24</v>
       </c>
       <c r="B205">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C205">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="D205" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E205" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="F205" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G205" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="H205" t="s">
         <v>17</v>
@@ -8308,13 +8344,13 @@
         <v>18</v>
       </c>
       <c r="J205" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="K205">
         <v>100</v>
       </c>
       <c r="L205">
-        <v>90.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -8322,22 +8358,22 @@
         <v>26</v>
       </c>
       <c r="B206">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="C206">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="D206" t="s">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="E206" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="F206" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G206" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="H206" t="s">
         <v>17</v>
@@ -8349,7 +8385,7 @@
         <v>100</v>
       </c>
       <c r="L206">
-        <v>90.4</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
@@ -8357,22 +8393,22 @@
         <v>12</v>
       </c>
       <c r="B207">
+        <v>930</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+      <c r="D207" t="s">
         <v>21</v>
       </c>
-      <c r="C207">
-        <v>24</v>
-      </c>
-      <c r="D207" t="s">
-        <v>169</v>
-      </c>
       <c r="E207" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="F207" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G207" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H207" t="s">
         <v>17</v>
@@ -8380,11 +8416,14 @@
       <c r="I207" t="s">
         <v>18</v>
       </c>
+      <c r="J207" t="s">
+        <v>202</v>
+      </c>
       <c r="K207">
         <v>100</v>
       </c>
       <c r="L207">
-        <v>55.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -8392,7 +8431,7 @@
         <v>20</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -8401,13 +8440,13 @@
         <v>21</v>
       </c>
       <c r="E208" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="F208" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G208" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H208" t="s">
         <v>17</v>
@@ -8419,7 +8458,7 @@
         <v>100</v>
       </c>
       <c r="L208">
-        <v>55.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -8427,22 +8466,22 @@
         <v>22</v>
       </c>
       <c r="B209">
-        <v>42</v>
+        <v>1712</v>
       </c>
       <c r="C209">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D209" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="E209" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="F209" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G209" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H209" t="s">
         <v>17</v>
@@ -8454,7 +8493,7 @@
         <v>100</v>
       </c>
       <c r="L209">
-        <v>55.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -8462,22 +8501,22 @@
         <v>24</v>
       </c>
       <c r="B210">
-        <v>84</v>
+        <v>3255</v>
       </c>
       <c r="C210">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D210" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E210" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="F210" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G210" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H210" t="s">
         <v>17</v>
@@ -8489,7 +8528,7 @@
         <v>100</v>
       </c>
       <c r="L210">
-        <v>55.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -8497,22 +8536,22 @@
         <v>26</v>
       </c>
       <c r="B211">
-        <v>900</v>
+        <v>25304</v>
       </c>
       <c r="C211">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="D211" t="s">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="E211" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="F211" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G211" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H211" t="s">
         <v>17</v>
@@ -8524,7 +8563,7 @@
         <v>100</v>
       </c>
       <c r="L211">
-        <v>55.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -8532,13 +8571,13 @@
         <v>12</v>
       </c>
       <c r="B212">
-        <v>21</v>
+        <v>930</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D212" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="E212" t="s">
         <v>37</v>
@@ -8547,7 +8586,7 @@
         <v>38</v>
       </c>
       <c r="G212" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H212" t="s">
         <v>17</v>
@@ -8556,13 +8595,13 @@
         <v>18</v>
       </c>
       <c r="J212" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K212">
         <v>100</v>
       </c>
       <c r="L212">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
@@ -8570,13 +8609,13 @@
         <v>20</v>
       </c>
       <c r="B213">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D213" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="E213" t="s">
         <v>37</v>
@@ -8585,7 +8624,7 @@
         <v>38</v>
       </c>
       <c r="G213" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H213" t="s">
         <v>17</v>
@@ -8593,11 +8632,14 @@
       <c r="I213" t="s">
         <v>18</v>
       </c>
+      <c r="J213" t="s">
+        <v>205</v>
+      </c>
       <c r="K213">
         <v>100</v>
       </c>
       <c r="L213">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
@@ -8605,10 +8647,10 @@
         <v>22</v>
       </c>
       <c r="B214">
-        <v>42</v>
+        <v>1712</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D214" t="s">
         <v>21</v>
@@ -8620,7 +8662,7 @@
         <v>38</v>
       </c>
       <c r="G214" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H214" t="s">
         <v>17</v>
@@ -8628,11 +8670,14 @@
       <c r="I214" t="s">
         <v>18</v>
       </c>
+      <c r="J214" t="s">
+        <v>206</v>
+      </c>
       <c r="K214">
         <v>100</v>
       </c>
       <c r="L214">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
@@ -8640,13 +8685,13 @@
         <v>24</v>
       </c>
       <c r="B215">
-        <v>84</v>
+        <v>3255</v>
       </c>
       <c r="C215">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D215" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E215" t="s">
         <v>37</v>
@@ -8655,7 +8700,7 @@
         <v>38</v>
       </c>
       <c r="G215" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H215" t="s">
         <v>17</v>
@@ -8667,7 +8712,7 @@
         <v>100</v>
       </c>
       <c r="L215">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
@@ -8675,7 +8720,7 @@
         <v>26</v>
       </c>
       <c r="B216">
-        <v>900</v>
+        <v>25304</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8690,7 +8735,7 @@
         <v>38</v>
       </c>
       <c r="G216" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H216" t="s">
         <v>17</v>
@@ -8702,7 +8747,7 @@
         <v>100</v>
       </c>
       <c r="L216">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
@@ -8710,13 +8755,13 @@
         <v>12</v>
       </c>
       <c r="B217">
-        <v>21</v>
+        <v>930</v>
       </c>
       <c r="C217">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D217" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E217" t="s">
         <v>50</v>
@@ -8725,7 +8770,7 @@
         <v>38</v>
       </c>
       <c r="G217" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H217" t="s">
         <v>17</v>
@@ -8734,13 +8779,13 @@
         <v>18</v>
       </c>
       <c r="J217" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="K217">
         <v>100</v>
       </c>
       <c r="L217">
-        <v>12.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
@@ -8748,13 +8793,13 @@
         <v>20</v>
       </c>
       <c r="B218">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="E218" t="s">
         <v>50</v>
@@ -8763,7 +8808,7 @@
         <v>38</v>
       </c>
       <c r="G218" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H218" t="s">
         <v>17</v>
@@ -8771,11 +8816,14 @@
       <c r="I218" t="s">
         <v>18</v>
       </c>
+      <c r="J218" t="s">
+        <v>208</v>
+      </c>
       <c r="K218">
         <v>100</v>
       </c>
       <c r="L218">
-        <v>12.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
@@ -8783,13 +8831,13 @@
         <v>22</v>
       </c>
       <c r="B219">
-        <v>42</v>
+        <v>1712</v>
       </c>
       <c r="C219">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D219" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E219" t="s">
         <v>50</v>
@@ -8798,7 +8846,7 @@
         <v>38</v>
       </c>
       <c r="G219" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H219" t="s">
         <v>17</v>
@@ -8806,14 +8854,11 @@
       <c r="I219" t="s">
         <v>18</v>
       </c>
-      <c r="J219" t="s">
-        <v>175</v>
-      </c>
       <c r="K219">
         <v>100</v>
       </c>
       <c r="L219">
-        <v>12.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
@@ -8821,13 +8866,13 @@
         <v>24</v>
       </c>
       <c r="B220">
-        <v>84</v>
+        <v>3255</v>
       </c>
       <c r="C220">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D220" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E220" t="s">
         <v>50</v>
@@ -8836,7 +8881,7 @@
         <v>38</v>
       </c>
       <c r="G220" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H220" t="s">
         <v>17</v>
@@ -8844,14 +8889,11 @@
       <c r="I220" t="s">
         <v>18</v>
       </c>
-      <c r="J220" t="s">
-        <v>176</v>
-      </c>
       <c r="K220">
         <v>100</v>
       </c>
       <c r="L220">
-        <v>12.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
@@ -8859,7 +8901,7 @@
         <v>26</v>
       </c>
       <c r="B221">
-        <v>900</v>
+        <v>25304</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -8874,7 +8916,7 @@
         <v>38</v>
       </c>
       <c r="G221" t="s">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="H221" t="s">
         <v>17</v>
@@ -8886,7 +8928,544 @@
         <v>100</v>
       </c>
       <c r="L221">
-        <v>12.5</v>
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222">
+        <v>4</v>
+      </c>
+      <c r="C222">
+        <v>6</v>
+      </c>
+      <c r="D222" t="s">
+        <v>167</v>
+      </c>
+      <c r="E222" t="s">
+        <v>209</v>
+      </c>
+      <c r="F222" t="s">
+        <v>15</v>
+      </c>
+      <c r="G222" t="s">
+        <v>210</v>
+      </c>
+      <c r="H222" t="s">
+        <v>17</v>
+      </c>
+      <c r="I222" t="s">
+        <v>18</v>
+      </c>
+      <c r="J222" t="s">
+        <v>211</v>
+      </c>
+      <c r="K222">
+        <v>100</v>
+      </c>
+      <c r="L222">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>20</v>
+      </c>
+      <c r="B223">
+        <v>2</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223" t="s">
+        <v>113</v>
+      </c>
+      <c r="E223" t="s">
+        <v>209</v>
+      </c>
+      <c r="F223" t="s">
+        <v>15</v>
+      </c>
+      <c r="G223" t="s">
+        <v>210</v>
+      </c>
+      <c r="H223" t="s">
+        <v>17</v>
+      </c>
+      <c r="I223" t="s">
+        <v>18</v>
+      </c>
+      <c r="K223">
+        <v>100</v>
+      </c>
+      <c r="L223">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>22</v>
+      </c>
+      <c r="B224">
+        <v>9</v>
+      </c>
+      <c r="C224">
+        <v>9</v>
+      </c>
+      <c r="D224" t="s">
+        <v>70</v>
+      </c>
+      <c r="E224" t="s">
+        <v>209</v>
+      </c>
+      <c r="F224" t="s">
+        <v>15</v>
+      </c>
+      <c r="G224" t="s">
+        <v>210</v>
+      </c>
+      <c r="H224" t="s">
+        <v>17</v>
+      </c>
+      <c r="I224" t="s">
+        <v>18</v>
+      </c>
+      <c r="K224">
+        <v>100</v>
+      </c>
+      <c r="L224">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>24</v>
+      </c>
+      <c r="B225">
+        <v>20</v>
+      </c>
+      <c r="C225">
+        <v>23</v>
+      </c>
+      <c r="D225" t="s">
+        <v>104</v>
+      </c>
+      <c r="E225" t="s">
+        <v>209</v>
+      </c>
+      <c r="F225" t="s">
+        <v>15</v>
+      </c>
+      <c r="G225" t="s">
+        <v>210</v>
+      </c>
+      <c r="H225" t="s">
+        <v>17</v>
+      </c>
+      <c r="I225" t="s">
+        <v>18</v>
+      </c>
+      <c r="K225">
+        <v>100</v>
+      </c>
+      <c r="L225">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>26</v>
+      </c>
+      <c r="B226">
+        <v>346</v>
+      </c>
+      <c r="C226">
+        <v>600</v>
+      </c>
+      <c r="D226" t="s">
+        <v>212</v>
+      </c>
+      <c r="E226" t="s">
+        <v>209</v>
+      </c>
+      <c r="F226" t="s">
+        <v>15</v>
+      </c>
+      <c r="G226" t="s">
+        <v>210</v>
+      </c>
+      <c r="H226" t="s">
+        <v>17</v>
+      </c>
+      <c r="I226" t="s">
+        <v>18</v>
+      </c>
+      <c r="K226">
+        <v>100</v>
+      </c>
+      <c r="L226">
+        <v>75.599999999999994</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227">
+        <v>11</v>
+      </c>
+      <c r="C227">
+        <v>11</v>
+      </c>
+      <c r="D227" t="s">
+        <v>70</v>
+      </c>
+      <c r="E227" t="s">
+        <v>213</v>
+      </c>
+      <c r="F227" t="s">
+        <v>28</v>
+      </c>
+      <c r="G227" t="s">
+        <v>210</v>
+      </c>
+      <c r="H227" t="s">
+        <v>17</v>
+      </c>
+      <c r="I227" t="s">
+        <v>18</v>
+      </c>
+      <c r="K227">
+        <v>100</v>
+      </c>
+      <c r="L227">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>20</v>
+      </c>
+      <c r="B228">
+        <v>6</v>
+      </c>
+      <c r="C228">
+        <v>2</v>
+      </c>
+      <c r="D228" t="s">
+        <v>25</v>
+      </c>
+      <c r="E228" t="s">
+        <v>213</v>
+      </c>
+      <c r="F228" t="s">
+        <v>28</v>
+      </c>
+      <c r="G228" t="s">
+        <v>210</v>
+      </c>
+      <c r="H228" t="s">
+        <v>17</v>
+      </c>
+      <c r="I228" t="s">
+        <v>18</v>
+      </c>
+      <c r="K228">
+        <v>100</v>
+      </c>
+      <c r="L228">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>22</v>
+      </c>
+      <c r="B229">
+        <v>21</v>
+      </c>
+      <c r="C229">
+        <v>14</v>
+      </c>
+      <c r="D229" t="s">
+        <v>66</v>
+      </c>
+      <c r="E229" t="s">
+        <v>213</v>
+      </c>
+      <c r="F229" t="s">
+        <v>28</v>
+      </c>
+      <c r="G229" t="s">
+        <v>210</v>
+      </c>
+      <c r="H229" t="s">
+        <v>17</v>
+      </c>
+      <c r="I229" t="s">
+        <v>18</v>
+      </c>
+      <c r="K229">
+        <v>100</v>
+      </c>
+      <c r="L229">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>24</v>
+      </c>
+      <c r="B230">
+        <v>50</v>
+      </c>
+      <c r="C230">
+        <v>45</v>
+      </c>
+      <c r="D230" t="s">
+        <v>214</v>
+      </c>
+      <c r="E230" t="s">
+        <v>213</v>
+      </c>
+      <c r="F230" t="s">
+        <v>28</v>
+      </c>
+      <c r="G230" t="s">
+        <v>210</v>
+      </c>
+      <c r="H230" t="s">
+        <v>17</v>
+      </c>
+      <c r="I230" t="s">
+        <v>18</v>
+      </c>
+      <c r="K230">
+        <v>100</v>
+      </c>
+      <c r="L230">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>26</v>
+      </c>
+      <c r="B231">
+        <v>854</v>
+      </c>
+      <c r="C231">
+        <v>602</v>
+      </c>
+      <c r="D231" t="s">
+        <v>96</v>
+      </c>
+      <c r="E231" t="s">
+        <v>213</v>
+      </c>
+      <c r="F231" t="s">
+        <v>28</v>
+      </c>
+      <c r="G231" t="s">
+        <v>210</v>
+      </c>
+      <c r="H231" t="s">
+        <v>17</v>
+      </c>
+      <c r="I231" t="s">
+        <v>18</v>
+      </c>
+      <c r="K231">
+        <v>100</v>
+      </c>
+      <c r="L231">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>12</v>
+      </c>
+      <c r="B232">
+        <v>9</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232" t="s">
+        <v>215</v>
+      </c>
+      <c r="E232" t="s">
+        <v>37</v>
+      </c>
+      <c r="F232" t="s">
+        <v>38</v>
+      </c>
+      <c r="G232" t="s">
+        <v>210</v>
+      </c>
+      <c r="H232" t="s">
+        <v>17</v>
+      </c>
+      <c r="I232" t="s">
+        <v>18</v>
+      </c>
+      <c r="J232" t="s">
+        <v>216</v>
+      </c>
+      <c r="K232">
+        <v>100</v>
+      </c>
+      <c r="L232">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>20</v>
+      </c>
+      <c r="B233">
+        <v>5</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233" t="s">
+        <v>21</v>
+      </c>
+      <c r="E233" t="s">
+        <v>37</v>
+      </c>
+      <c r="F233" t="s">
+        <v>38</v>
+      </c>
+      <c r="G233" t="s">
+        <v>210</v>
+      </c>
+      <c r="H233" t="s">
+        <v>17</v>
+      </c>
+      <c r="I233" t="s">
+        <v>18</v>
+      </c>
+      <c r="K233">
+        <v>100</v>
+      </c>
+      <c r="L233">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>22</v>
+      </c>
+      <c r="B234">
+        <v>18</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234" t="s">
+        <v>217</v>
+      </c>
+      <c r="E234" t="s">
+        <v>37</v>
+      </c>
+      <c r="F234" t="s">
+        <v>38</v>
+      </c>
+      <c r="G234" t="s">
+        <v>210</v>
+      </c>
+      <c r="H234" t="s">
+        <v>17</v>
+      </c>
+      <c r="I234" t="s">
+        <v>18</v>
+      </c>
+      <c r="J234" t="s">
+        <v>218</v>
+      </c>
+      <c r="K234">
+        <v>100</v>
+      </c>
+      <c r="L234">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>24</v>
+      </c>
+      <c r="B235">
+        <v>42</v>
+      </c>
+      <c r="C235">
+        <v>3</v>
+      </c>
+      <c r="D235" t="s">
+        <v>104</v>
+      </c>
+      <c r="E235" t="s">
+        <v>37</v>
+      </c>
+      <c r="F235" t="s">
+        <v>38</v>
+      </c>
+      <c r="G235" t="s">
+        <v>210</v>
+      </c>
+      <c r="H235" t="s">
+        <v>17</v>
+      </c>
+      <c r="I235" t="s">
+        <v>18</v>
+      </c>
+      <c r="J235" t="s">
+        <v>219</v>
+      </c>
+      <c r="K235">
+        <v>100</v>
+      </c>
+      <c r="L235">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>26</v>
+      </c>
+      <c r="B236">
+        <v>720</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236" t="s">
+        <v>21</v>
+      </c>
+      <c r="E236" t="s">
+        <v>37</v>
+      </c>
+      <c r="F236" t="s">
+        <v>38</v>
+      </c>
+      <c r="G236" t="s">
+        <v>210</v>
+      </c>
+      <c r="H236" t="s">
+        <v>17</v>
+      </c>
+      <c r="I236" t="s">
+        <v>18</v>
+      </c>
+      <c r="K236">
+        <v>100</v>
+      </c>
+      <c r="L236">
+        <v>4.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_22111D6B115E5A0F62355476585DCE3A87456A7D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{701A9E82-ACA3-4DAB-8184-E2478FA1CA79}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_7C198C749052620F62355476585DCE3A87450AED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49BD6DDE-A297-4346-837F-4DAE309CB6B1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -415,271 +415,271 @@
     <t>74%</t>
   </si>
   <si>
+    <t>16%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>meta puntos 520 cump 54%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>125%</t>
+  </si>
+  <si>
+    <t>106%</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>14 días líder   meta puntos 633 cump 59%   meta postp  15  cump 87%</t>
+  </si>
+  <si>
+    <t>Meta hogar 5 cump 40%</t>
+  </si>
+  <si>
+    <t>14%</t>
+  </si>
+  <si>
+    <t>Meta terminales  15  cump 33%</t>
+  </si>
+  <si>
+    <t>Meta otros 51 cump 53%</t>
+  </si>
+  <si>
+    <t>Meta 366</t>
+  </si>
+  <si>
+    <t>146%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>159%</t>
+  </si>
+  <si>
+    <t>154%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Taborda Ruiz</t>
+  </si>
+  <si>
+    <t>Elabora 7 días x VAC  - meta puntos  630.7  cump 81%    meta post 13  cump 115%</t>
+  </si>
+  <si>
+    <t>Meta hogar 2 cump 0%</t>
+  </si>
+  <si>
+    <t>Meta terminales 20 cump 70%</t>
+  </si>
+  <si>
+    <t>Meta otros 42</t>
+  </si>
+  <si>
+    <t>CVS 139</t>
+  </si>
+  <si>
+    <t>116%</t>
+  </si>
+  <si>
+    <t>Jessica Catherine Gutierrez Garcia</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>112%</t>
+  </si>
+  <si>
+    <t>84%</t>
+  </si>
+  <si>
+    <t>145%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>92%</t>
+  </si>
+  <si>
+    <t>1 día Líder meta puntos 591.3   meta post 1</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>meta 3</t>
+  </si>
+  <si>
+    <t>meta 5</t>
+  </si>
+  <si>
+    <t>59%</t>
+  </si>
+  <si>
+    <t>15 días, asesora meta puntos 1.182,5 cump 97%  meta post 24 cump 92%</t>
+  </si>
+  <si>
+    <t>Meta Hogar  3 cump. 33%</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>Meta Terminales 38 cump 113%</t>
+  </si>
+  <si>
+    <t>48%</t>
+  </si>
+  <si>
+    <t>Meta Otros 78 cump 73%</t>
+  </si>
+  <si>
+    <t>cvs plus 261</t>
+  </si>
+  <si>
+    <t>157%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elabora 20 días x vac  Meta puntos 921.7  cump 104% </t>
+  </si>
+  <si>
+    <t>meta Hogar 1</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>Meta terminales  24</t>
+  </si>
+  <si>
+    <t>Meta otros 19</t>
+  </si>
+  <si>
+    <t>114%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
+    <t>1 día asesor  meta puntos 69 cump 13%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>3 días líder meta puntos 345.6  cump 58%      meta postpago  2</t>
+  </si>
+  <si>
+    <t>Meta terminales 4</t>
+  </si>
+  <si>
+    <t>Meta otros 7</t>
+  </si>
+  <si>
+    <t>NUMERARIO</t>
+  </si>
+  <si>
+    <t>1 día en Caucasia</t>
+  </si>
+  <si>
+    <t>Junin 4%</t>
+  </si>
+  <si>
+    <t>1%</t>
+  </si>
+  <si>
+    <t>La Estrella 158%</t>
+  </si>
+  <si>
+    <t>Terminal 13%</t>
+  </si>
+  <si>
+    <t>Junín 97%</t>
+  </si>
+  <si>
+    <t>Terminal 58%</t>
+  </si>
+  <si>
+    <t>Lider Jhon Alejandro Cardona Quintero</t>
+  </si>
+  <si>
+    <t>LA ESTRELLA</t>
+  </si>
+  <si>
+    <t>Se realiza promedio por cubrimiento de cajera 7 días por vacaciones</t>
+  </si>
+  <si>
+    <t>173%</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>11%</t>
+  </si>
+  <si>
+    <t>1 día lider   meta puntos 26 cump 158%   meta postp 1 cump 100%</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>meta 1 cump 100%</t>
+  </si>
+  <si>
+    <t>meta 1</t>
+  </si>
+  <si>
+    <t>167%</t>
+  </si>
+  <si>
     <t>Lider Don Matias Diana Ruiz</t>
   </si>
   <si>
     <t>DON MATIAS</t>
   </si>
   <si>
-    <t>Cubre vacaciones de cajera 7 días meta puntos 432 cump 55%</t>
-  </si>
-  <si>
-    <t>18%</t>
+    <t>Cubre vac de cajera 7 días y sale a vac 6 días</t>
+  </si>
+  <si>
+    <t>71%</t>
   </si>
   <si>
     <t>Evelyn Daniela Lopera Lopera</t>
-  </si>
-  <si>
-    <t>107%</t>
-  </si>
-  <si>
-    <t>16%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Arbelaez</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>meta puntos 520 cump 54%</t>
-  </si>
-  <si>
-    <t>29%</t>
-  </si>
-  <si>
-    <t>Andrea  Arenas Hurtado</t>
-  </si>
-  <si>
-    <t>125%</t>
-  </si>
-  <si>
-    <t>106%</t>
-  </si>
-  <si>
-    <t>103%</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>14 días líder   meta puntos 633 cump 59%   meta postp  15  cump 87%</t>
-  </si>
-  <si>
-    <t>Meta hogar 5 cump 40%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>Meta terminales  15  cump 33%</t>
-  </si>
-  <si>
-    <t>Meta otros 51 cump 53%</t>
-  </si>
-  <si>
-    <t>Meta 366</t>
-  </si>
-  <si>
-    <t>146%</t>
-  </si>
-  <si>
-    <t>Lider Leider  Alexander Calderon</t>
-  </si>
-  <si>
-    <t>JUNIN</t>
-  </si>
-  <si>
-    <t>159%</t>
-  </si>
-  <si>
-    <t>154%</t>
-  </si>
-  <si>
-    <t>Diana Marcela Taborda Ruiz</t>
-  </si>
-  <si>
-    <t>Elabora 7 días x VAC  - meta puntos  630.7  cump 81%    meta post 13  cump 115%</t>
-  </si>
-  <si>
-    <t>Meta hogar 2 cump 0%</t>
-  </si>
-  <si>
-    <t>Meta terminales 20 cump 70%</t>
-  </si>
-  <si>
-    <t>Meta otros 42</t>
-  </si>
-  <si>
-    <t>CVS 139</t>
-  </si>
-  <si>
-    <t>116%</t>
-  </si>
-  <si>
-    <t>Jessica Catherine Gutierrez Garcia</t>
-  </si>
-  <si>
-    <t>150%</t>
-  </si>
-  <si>
-    <t>112%</t>
-  </si>
-  <si>
-    <t>84%</t>
-  </si>
-  <si>
-    <t>145%</t>
-  </si>
-  <si>
-    <t>Sandra Milena Carmona Galeano</t>
-  </si>
-  <si>
-    <t>92%</t>
-  </si>
-  <si>
-    <t>1 día Líder meta puntos 591.3   meta post 1</t>
-  </si>
-  <si>
-    <t>2%</t>
-  </si>
-  <si>
-    <t>meta 3</t>
-  </si>
-  <si>
-    <t>meta 5</t>
-  </si>
-  <si>
-    <t>59%</t>
-  </si>
-  <si>
-    <t>15 días, asesora meta puntos 1.182,5 cump 97%  meta post 24 cump 92%</t>
-  </si>
-  <si>
-    <t>Meta Hogar  3 cump. 33%</t>
-  </si>
-  <si>
-    <t>73%</t>
-  </si>
-  <si>
-    <t>Meta Terminales 38 cump 113%</t>
-  </si>
-  <si>
-    <t>48%</t>
-  </si>
-  <si>
-    <t>Meta Otros 78 cump 73%</t>
-  </si>
-  <si>
-    <t>cvs plus 261</t>
-  </si>
-  <si>
-    <t>157%</t>
-  </si>
-  <si>
-    <t>Lider Luz Stella Serna</t>
-  </si>
-  <si>
-    <t>TERMINAL NORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elabora 20 días x vac  Meta puntos 921.7  cump 104% </t>
-  </si>
-  <si>
-    <t>meta Hogar 1</t>
-  </si>
-  <si>
-    <t>118%</t>
-  </si>
-  <si>
-    <t>Meta terminales  24</t>
-  </si>
-  <si>
-    <t>Meta otros 19</t>
-  </si>
-  <si>
-    <t>114%</t>
-  </si>
-  <si>
-    <t>Cristian Camilo Torres Toro</t>
-  </si>
-  <si>
-    <t>76%</t>
-  </si>
-  <si>
-    <t>1 día asesor  meta puntos 69 cump 13%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>3 días líder meta puntos 345.6  cump 58%      meta postpago  2</t>
-  </si>
-  <si>
-    <t>Meta terminales 4</t>
-  </si>
-  <si>
-    <t>Meta otros 7</t>
-  </si>
-  <si>
-    <t>NUMERARIO</t>
-  </si>
-  <si>
-    <t>1 día en Caucasia</t>
-  </si>
-  <si>
-    <t>Junin 4%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>La Estrella 158%</t>
-  </si>
-  <si>
-    <t>Terminal 13%</t>
-  </si>
-  <si>
-    <t>Junín 97%</t>
-  </si>
-  <si>
-    <t>Terminal 58%</t>
-  </si>
-  <si>
-    <t>Lider Jhon Alejandro Cardona Quintero</t>
-  </si>
-  <si>
-    <t>LA ESTRELLA</t>
-  </si>
-  <si>
-    <t>Se realiza promedio por cubrimiento de cajera 7 días por vacaciones</t>
-  </si>
-  <si>
-    <t>173%</t>
-  </si>
-  <si>
-    <t>Yessica  Restrepo Caicedo</t>
-  </si>
-  <si>
-    <t>90%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>1 día lider   meta puntos 26 cump 158%   meta postp 1 cump 100%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>meta 1 cump 100%</t>
-  </si>
-  <si>
-    <t>meta 1</t>
   </si>
 </sst>
 </file>
@@ -698,7 +698,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5684,22 +5683,22 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C132">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D132" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="E132" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F132" t="s">
         <v>15</v>
       </c>
       <c r="G132" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -5708,13 +5707,13 @@
         <v>18</v>
       </c>
       <c r="J132" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K132">
         <v>100</v>
       </c>
       <c r="L132">
-        <v>39.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5722,22 +5721,22 @@
         <v>20</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E133" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F133" t="s">
         <v>15</v>
       </c>
       <c r="G133" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -5749,7 +5748,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>39.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5757,22 +5756,22 @@
         <v>22</v>
       </c>
       <c r="B134">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C134">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D134" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E134" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F134" t="s">
         <v>15</v>
       </c>
       <c r="G134" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -5784,7 +5783,7 @@
         <v>100</v>
       </c>
       <c r="L134">
-        <v>39.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5792,22 +5791,22 @@
         <v>24</v>
       </c>
       <c r="B135">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C135">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D135" t="s">
         <v>104</v>
       </c>
       <c r="E135" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F135" t="s">
         <v>15</v>
       </c>
       <c r="G135" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -5819,7 +5818,7 @@
         <v>100</v>
       </c>
       <c r="L135">
-        <v>39.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5827,22 +5826,22 @@
         <v>26</v>
       </c>
       <c r="B136">
-        <v>480</v>
+        <v>365</v>
       </c>
       <c r="C136">
-        <v>84</v>
+        <v>232</v>
       </c>
       <c r="D136" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="E136" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F136" t="s">
         <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -5854,7 +5853,7 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>39.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5862,22 +5861,22 @@
         <v>12</v>
       </c>
       <c r="B137">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C137">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D137" t="s">
         <v>70</v>
       </c>
       <c r="E137" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
       </c>
       <c r="G137" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H137" t="s">
         <v>17</v>
@@ -5889,7 +5888,7 @@
         <v>100</v>
       </c>
       <c r="L137">
-        <v>93.9</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -5897,22 +5896,22 @@
         <v>20</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D138" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="E138" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
       </c>
       <c r="G138" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H138" t="s">
         <v>17</v>
@@ -5924,7 +5923,7 @@
         <v>100</v>
       </c>
       <c r="L138">
-        <v>93.9</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -5932,22 +5931,22 @@
         <v>22</v>
       </c>
       <c r="B139">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C139">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D139" t="s">
+        <v>138</v>
+      </c>
+      <c r="E139" t="s">
         <v>136</v>
       </c>
-      <c r="E139" t="s">
-        <v>135</v>
-      </c>
       <c r="F139" t="s">
         <v>28</v>
       </c>
       <c r="G139" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H139" t="s">
         <v>17</v>
@@ -5959,7 +5958,7 @@
         <v>100</v>
       </c>
       <c r="L139">
-        <v>93.9</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -5967,22 +5966,22 @@
         <v>24</v>
       </c>
       <c r="B140">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="C140">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="D140" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="E140" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F140" t="s">
         <v>28</v>
       </c>
       <c r="G140" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H140" t="s">
         <v>17</v>
@@ -5994,7 +5993,7 @@
         <v>100</v>
       </c>
       <c r="L140">
-        <v>93.9</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -6002,22 +6001,22 @@
         <v>26</v>
       </c>
       <c r="B141">
-        <v>720</v>
+        <v>548</v>
       </c>
       <c r="C141">
-        <v>720</v>
+        <v>255</v>
       </c>
       <c r="D141" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="E141" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F141" t="s">
         <v>28</v>
       </c>
       <c r="G141" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H141" t="s">
         <v>17</v>
@@ -6029,7 +6028,7 @@
         <v>100</v>
       </c>
       <c r="L141">
-        <v>93.9</v>
+        <v>96.9</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -6037,22 +6036,22 @@
         <v>12</v>
       </c>
       <c r="B142">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C142">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D142" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E142" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="F142" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G142" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H142" t="s">
         <v>17</v>
@@ -6061,13 +6060,13 @@
         <v>18</v>
       </c>
       <c r="J142" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K142">
         <v>100</v>
       </c>
       <c r="L142">
-        <v>27</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -6075,22 +6074,22 @@
         <v>20</v>
       </c>
       <c r="B143">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C143">
         <v>2</v>
       </c>
       <c r="D143" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E143" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="F143" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G143" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
@@ -6098,11 +6097,14 @@
       <c r="I143" t="s">
         <v>18</v>
       </c>
+      <c r="J143" t="s">
+        <v>143</v>
+      </c>
       <c r="K143">
         <v>100</v>
       </c>
       <c r="L143">
-        <v>27</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -6110,22 +6112,22 @@
         <v>22</v>
       </c>
       <c r="B144">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C144">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D144" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E144" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="F144" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G144" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H144" t="s">
         <v>17</v>
@@ -6133,11 +6135,14 @@
       <c r="I144" t="s">
         <v>18</v>
       </c>
+      <c r="J144" t="s">
+        <v>145</v>
+      </c>
       <c r="K144">
         <v>100</v>
       </c>
       <c r="L144">
-        <v>27</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -6145,22 +6150,22 @@
         <v>24</v>
       </c>
       <c r="B145">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C145">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D145" t="s">
         <v>104</v>
       </c>
       <c r="E145" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="F145" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G145" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H145" t="s">
         <v>17</v>
@@ -6168,11 +6173,14 @@
       <c r="I145" t="s">
         <v>18</v>
       </c>
+      <c r="J145" t="s">
+        <v>146</v>
+      </c>
       <c r="K145">
         <v>100</v>
       </c>
       <c r="L145">
-        <v>27</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -6180,22 +6188,22 @@
         <v>26</v>
       </c>
       <c r="B146">
-        <v>365</v>
+        <v>548</v>
       </c>
       <c r="C146">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="E146" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="F146" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G146" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="H146" t="s">
         <v>17</v>
@@ -6203,11 +6211,14 @@
       <c r="I146" t="s">
         <v>18</v>
       </c>
+      <c r="J146" t="s">
+        <v>147</v>
+      </c>
       <c r="K146">
         <v>100</v>
       </c>
       <c r="L146">
-        <v>27</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -6215,22 +6226,22 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C147">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D147" t="s">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="E147" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F147" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G147" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H147" t="s">
         <v>17</v>
@@ -6242,7 +6253,7 @@
         <v>100</v>
       </c>
       <c r="L147">
-        <v>96.9</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -6250,22 +6261,22 @@
         <v>20</v>
       </c>
       <c r="B148">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C148">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E148" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F148" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G148" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -6277,7 +6288,7 @@
         <v>100</v>
       </c>
       <c r="L148">
-        <v>96.9</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -6285,22 +6296,22 @@
         <v>22</v>
       </c>
       <c r="B149">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C149">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D149" t="s">
-        <v>144</v>
+        <v>70</v>
       </c>
       <c r="E149" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F149" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G149" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H149" t="s">
         <v>17</v>
@@ -6312,7 +6323,7 @@
         <v>100</v>
       </c>
       <c r="L149">
-        <v>96.9</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -6320,22 +6331,22 @@
         <v>24</v>
       </c>
       <c r="B150">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C150">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D150" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E150" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F150" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G150" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H150" t="s">
         <v>17</v>
@@ -6347,7 +6358,7 @@
         <v>100</v>
       </c>
       <c r="L150">
-        <v>96.9</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -6355,22 +6366,22 @@
         <v>26</v>
       </c>
       <c r="B151">
-        <v>548</v>
+        <v>300</v>
       </c>
       <c r="C151">
-        <v>255</v>
+        <v>462</v>
       </c>
       <c r="D151" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E151" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="F151" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G151" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -6382,7 +6393,7 @@
         <v>100</v>
       </c>
       <c r="L151">
-        <v>96.9</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6393,19 +6404,19 @@
         <v>37</v>
       </c>
       <c r="C152">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>147</v>
+        <v>30</v>
       </c>
       <c r="E152" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="F152" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G152" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H152" t="s">
         <v>17</v>
@@ -6414,13 +6425,13 @@
         <v>18</v>
       </c>
       <c r="J152" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K152">
         <v>100</v>
       </c>
       <c r="L152">
-        <v>24.1</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -6428,22 +6439,22 @@
         <v>20</v>
       </c>
       <c r="B153">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E153" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="F153" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G153" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H153" t="s">
         <v>17</v>
@@ -6452,13 +6463,13 @@
         <v>18</v>
       </c>
       <c r="J153" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K153">
         <v>100</v>
       </c>
       <c r="L153">
-        <v>24.1</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6466,23 +6477,23 @@
         <v>22</v>
       </c>
       <c r="B154">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C154">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D154" t="s">
+        <v>59</v>
+      </c>
+      <c r="E154" t="s">
+        <v>153</v>
+      </c>
+      <c r="F154" t="s">
+        <v>28</v>
+      </c>
+      <c r="G154" t="s">
         <v>150</v>
       </c>
-      <c r="E154" t="s">
-        <v>37</v>
-      </c>
-      <c r="F154" t="s">
-        <v>38</v>
-      </c>
-      <c r="G154" t="s">
-        <v>139</v>
-      </c>
       <c r="H154" t="s">
         <v>17</v>
       </c>
@@ -6490,13 +6501,13 @@
         <v>18</v>
       </c>
       <c r="J154" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K154">
         <v>100</v>
       </c>
       <c r="L154">
-        <v>24.1</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -6504,22 +6515,22 @@
         <v>24</v>
       </c>
       <c r="B155">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C155">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D155" t="s">
         <v>104</v>
       </c>
       <c r="E155" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="F155" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G155" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H155" t="s">
         <v>17</v>
@@ -6528,13 +6539,13 @@
         <v>18</v>
       </c>
       <c r="J155" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="K155">
         <v>100</v>
       </c>
       <c r="L155">
-        <v>24.1</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -6542,22 +6553,22 @@
         <v>26</v>
       </c>
       <c r="B156">
-        <v>548</v>
+        <v>399</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="D156" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="E156" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="F156" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G156" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="H156" t="s">
         <v>17</v>
@@ -6566,13 +6577,13 @@
         <v>18</v>
       </c>
       <c r="J156" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K156">
         <v>100</v>
       </c>
       <c r="L156">
-        <v>24.1</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -6580,22 +6591,22 @@
         <v>12</v>
       </c>
       <c r="B157">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C157">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D157" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E157" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F157" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G157" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H157" t="s">
         <v>17</v>
@@ -6607,7 +6618,7 @@
         <v>100</v>
       </c>
       <c r="L157">
-        <v>125.5</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -6615,22 +6626,22 @@
         <v>20</v>
       </c>
       <c r="B158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C158">
         <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="E158" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F158" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G158" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H158" t="s">
         <v>17</v>
@@ -6642,7 +6653,7 @@
         <v>100</v>
       </c>
       <c r="L158">
-        <v>125.5</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -6650,22 +6661,22 @@
         <v>22</v>
       </c>
       <c r="B159">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C159">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D159" t="s">
-        <v>70</v>
+        <v>162</v>
       </c>
       <c r="E159" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F159" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G159" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -6677,7 +6688,7 @@
         <v>100</v>
       </c>
       <c r="L159">
-        <v>125.5</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -6685,22 +6696,22 @@
         <v>24</v>
       </c>
       <c r="B160">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C160">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="D160" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E160" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F160" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G160" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H160" t="s">
         <v>17</v>
@@ -6712,7 +6723,7 @@
         <v>100</v>
       </c>
       <c r="L160">
-        <v>125.5</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -6720,22 +6731,22 @@
         <v>26</v>
       </c>
       <c r="B161">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="C161">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="D161" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E161" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F161" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G161" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H161" t="s">
         <v>17</v>
@@ -6747,7 +6758,7 @@
         <v>100</v>
       </c>
       <c r="L161">
-        <v>125.5</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -6758,19 +6769,19 @@
         <v>37</v>
       </c>
       <c r="C162">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="D162" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="E162" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F162" t="s">
         <v>28</v>
       </c>
       <c r="G162" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H162" t="s">
         <v>17</v>
@@ -6778,14 +6789,11 @@
       <c r="I162" t="s">
         <v>18</v>
       </c>
-      <c r="J162" t="s">
-        <v>160</v>
-      </c>
       <c r="K162">
         <v>100</v>
       </c>
       <c r="L162">
-        <v>28.2</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -6796,19 +6804,19 @@
         <v>4</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D163" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="E163" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F163" t="s">
         <v>28</v>
       </c>
       <c r="G163" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
@@ -6816,14 +6824,11 @@
       <c r="I163" t="s">
         <v>18</v>
       </c>
-      <c r="J163" t="s">
-        <v>161</v>
-      </c>
       <c r="K163">
         <v>100</v>
       </c>
       <c r="L163">
-        <v>28.2</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -6834,19 +6839,19 @@
         <v>59</v>
       </c>
       <c r="C164">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D164" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="E164" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F164" t="s">
         <v>28</v>
       </c>
       <c r="G164" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H164" t="s">
         <v>17</v>
@@ -6854,14 +6859,11 @@
       <c r="I164" t="s">
         <v>18</v>
       </c>
-      <c r="J164" t="s">
-        <v>162</v>
-      </c>
       <c r="K164">
         <v>100</v>
       </c>
       <c r="L164">
-        <v>28.2</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -6872,19 +6874,19 @@
         <v>120</v>
       </c>
       <c r="C165">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="D165" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="E165" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F165" t="s">
         <v>28</v>
       </c>
       <c r="G165" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H165" t="s">
         <v>17</v>
@@ -6892,14 +6894,11 @@
       <c r="I165" t="s">
         <v>18</v>
       </c>
-      <c r="J165" t="s">
-        <v>163</v>
-      </c>
       <c r="K165">
         <v>100</v>
       </c>
       <c r="L165">
-        <v>28.2</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -6910,19 +6909,19 @@
         <v>399</v>
       </c>
       <c r="C166">
-        <v>166</v>
+        <v>579</v>
       </c>
       <c r="D166" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="E166" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="F166" t="s">
         <v>28</v>
       </c>
       <c r="G166" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H166" t="s">
         <v>17</v>
@@ -6930,14 +6929,11 @@
       <c r="I166" t="s">
         <v>18</v>
       </c>
-      <c r="J166" t="s">
-        <v>164</v>
-      </c>
       <c r="K166">
         <v>100</v>
       </c>
       <c r="L166">
-        <v>28.2</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -6948,19 +6944,19 @@
         <v>37</v>
       </c>
       <c r="C167">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="E167" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="F167" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G167" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H167" t="s">
         <v>17</v>
@@ -6968,11 +6964,14 @@
       <c r="I167" t="s">
         <v>18</v>
       </c>
+      <c r="J167" t="s">
+        <v>167</v>
+      </c>
       <c r="K167">
         <v>100</v>
       </c>
       <c r="L167">
-        <v>103.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -6983,19 +6982,19 @@
         <v>4</v>
       </c>
       <c r="C168">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="E168" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="F168" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G168" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H168" t="s">
         <v>17</v>
@@ -7007,7 +7006,7 @@
         <v>100</v>
       </c>
       <c r="L168">
-        <v>103.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -7018,19 +7017,19 @@
         <v>59</v>
       </c>
       <c r="C169">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="D169" t="s">
         <v>168</v>
       </c>
       <c r="E169" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="F169" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G169" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -7038,11 +7037,14 @@
       <c r="I169" t="s">
         <v>18</v>
       </c>
+      <c r="J169" t="s">
+        <v>169</v>
+      </c>
       <c r="K169">
         <v>100</v>
       </c>
       <c r="L169">
-        <v>103.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -7053,19 +7055,19 @@
         <v>120</v>
       </c>
       <c r="C170">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="D170" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="E170" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="F170" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G170" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -7073,11 +7075,14 @@
       <c r="I170" t="s">
         <v>18</v>
       </c>
+      <c r="J170" t="s">
+        <v>170</v>
+      </c>
       <c r="K170">
         <v>100</v>
       </c>
       <c r="L170">
-        <v>103.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -7088,19 +7093,19 @@
         <v>399</v>
       </c>
       <c r="C171">
-        <v>579</v>
+        <v>0</v>
       </c>
       <c r="D171" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="E171" t="s">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="F171" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G171" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H171" t="s">
         <v>17</v>
@@ -7112,7 +7117,7 @@
         <v>100</v>
       </c>
       <c r="L171">
-        <v>103.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -7123,19 +7128,19 @@
         <v>37</v>
       </c>
       <c r="C172">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D172" t="s">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="E172" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F172" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G172" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H172" t="s">
         <v>17</v>
@@ -7143,11 +7148,14 @@
       <c r="I172" t="s">
         <v>18</v>
       </c>
+      <c r="J172" t="s">
+        <v>172</v>
+      </c>
       <c r="K172">
         <v>100</v>
       </c>
       <c r="L172">
-        <v>110.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -7158,19 +7166,19 @@
         <v>4</v>
       </c>
       <c r="C173">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="E173" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F173" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G173" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H173" t="s">
         <v>17</v>
@@ -7178,11 +7186,14 @@
       <c r="I173" t="s">
         <v>18</v>
       </c>
+      <c r="J173" t="s">
+        <v>173</v>
+      </c>
       <c r="K173">
         <v>100</v>
       </c>
       <c r="L173">
-        <v>110.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -7193,19 +7204,19 @@
         <v>59</v>
       </c>
       <c r="C174">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D174" t="s">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="E174" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F174" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G174" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H174" t="s">
         <v>17</v>
@@ -7213,11 +7224,14 @@
       <c r="I174" t="s">
         <v>18</v>
       </c>
+      <c r="J174" t="s">
+        <v>175</v>
+      </c>
       <c r="K174">
         <v>100</v>
       </c>
       <c r="L174">
-        <v>110.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -7228,19 +7242,19 @@
         <v>120</v>
       </c>
       <c r="C175">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="D175" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E175" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F175" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G175" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H175" t="s">
         <v>17</v>
@@ -7248,11 +7262,14 @@
       <c r="I175" t="s">
         <v>18</v>
       </c>
+      <c r="J175" t="s">
+        <v>177</v>
+      </c>
       <c r="K175">
         <v>100</v>
       </c>
       <c r="L175">
-        <v>110.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -7263,19 +7280,19 @@
         <v>399</v>
       </c>
       <c r="C176">
-        <v>579</v>
+        <v>0</v>
       </c>
       <c r="D176" t="s">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="E176" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F176" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G176" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H176" t="s">
         <v>17</v>
@@ -7283,11 +7300,14 @@
       <c r="I176" t="s">
         <v>18</v>
       </c>
+      <c r="J176" t="s">
+        <v>178</v>
+      </c>
       <c r="K176">
         <v>100</v>
       </c>
       <c r="L176">
-        <v>110.5</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -7295,22 +7315,22 @@
         <v>12</v>
       </c>
       <c r="B177">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D177" t="s">
-        <v>40</v>
+        <v>179</v>
       </c>
       <c r="E177" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="F177" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G177" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H177" t="s">
         <v>17</v>
@@ -7319,13 +7339,13 @@
         <v>18</v>
       </c>
       <c r="J177" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="K177">
         <v>100</v>
       </c>
       <c r="L177">
-        <v>1.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -7333,7 +7353,7 @@
         <v>20</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -7342,13 +7362,13 @@
         <v>21</v>
       </c>
       <c r="E178" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="F178" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G178" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H178" t="s">
         <v>17</v>
@@ -7356,11 +7376,14 @@
       <c r="I178" t="s">
         <v>18</v>
       </c>
+      <c r="J178" t="s">
+        <v>183</v>
+      </c>
       <c r="K178">
         <v>100</v>
       </c>
       <c r="L178">
-        <v>1.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -7368,22 +7391,22 @@
         <v>22</v>
       </c>
       <c r="B179">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D179" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E179" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="F179" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G179" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H179" t="s">
         <v>17</v>
@@ -7392,13 +7415,13 @@
         <v>18</v>
       </c>
       <c r="J179" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K179">
         <v>100</v>
       </c>
       <c r="L179">
-        <v>1.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -7406,22 +7429,22 @@
         <v>24</v>
       </c>
       <c r="B180">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="C180">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="D180" t="s">
         <v>104</v>
       </c>
       <c r="E180" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="F180" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G180" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H180" t="s">
         <v>17</v>
@@ -7430,13 +7453,13 @@
         <v>18</v>
       </c>
       <c r="J180" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="K180">
         <v>100</v>
       </c>
       <c r="L180">
-        <v>1.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -7444,22 +7467,22 @@
         <v>26</v>
       </c>
       <c r="B181">
-        <v>399</v>
+        <v>600</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="D181" t="s">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="E181" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
       <c r="F181" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G181" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H181" t="s">
         <v>17</v>
@@ -7471,7 +7494,7 @@
         <v>100</v>
       </c>
       <c r="L181">
-        <v>1.3</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -7479,22 +7502,22 @@
         <v>12</v>
       </c>
       <c r="B182">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C182">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D182" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E182" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="F182" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G182" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H182" t="s">
         <v>17</v>
@@ -7502,14 +7525,11 @@
       <c r="I182" t="s">
         <v>18</v>
       </c>
-      <c r="J182" t="s">
-        <v>178</v>
-      </c>
       <c r="K182">
         <v>100</v>
       </c>
       <c r="L182">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -7517,22 +7537,22 @@
         <v>20</v>
       </c>
       <c r="B183">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D183" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E183" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="F183" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G183" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H183" t="s">
         <v>17</v>
@@ -7540,14 +7560,11 @@
       <c r="I183" t="s">
         <v>18</v>
       </c>
-      <c r="J183" t="s">
-        <v>179</v>
-      </c>
       <c r="K183">
         <v>100</v>
       </c>
       <c r="L183">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -7555,22 +7572,22 @@
         <v>22</v>
       </c>
       <c r="B184">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C184">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D184" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E184" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="F184" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G184" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H184" t="s">
         <v>17</v>
@@ -7578,14 +7595,11 @@
       <c r="I184" t="s">
         <v>18</v>
       </c>
-      <c r="J184" t="s">
-        <v>181</v>
-      </c>
       <c r="K184">
         <v>100</v>
       </c>
       <c r="L184">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -7593,22 +7607,22 @@
         <v>24</v>
       </c>
       <c r="B185">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="C185">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D185" t="s">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="E185" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="F185" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G185" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H185" t="s">
         <v>17</v>
@@ -7616,14 +7630,11 @@
       <c r="I185" t="s">
         <v>18</v>
       </c>
-      <c r="J185" t="s">
-        <v>183</v>
-      </c>
       <c r="K185">
         <v>100</v>
       </c>
       <c r="L185">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -7631,22 +7642,22 @@
         <v>26</v>
       </c>
       <c r="B186">
-        <v>399</v>
+        <v>900</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>534</v>
       </c>
       <c r="D186" t="s">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="E186" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="F186" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G186" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="H186" t="s">
         <v>17</v>
@@ -7654,14 +7665,11 @@
       <c r="I186" t="s">
         <v>18</v>
       </c>
-      <c r="J186" t="s">
-        <v>184</v>
-      </c>
       <c r="K186">
         <v>100</v>
       </c>
       <c r="L186">
-        <v>63.5</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -7669,22 +7677,22 @@
         <v>12</v>
       </c>
       <c r="B187">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C187">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D187" t="s">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="E187" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="F187" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G187" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H187" t="s">
         <v>17</v>
@@ -7693,13 +7701,13 @@
         <v>18</v>
       </c>
       <c r="J187" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K187">
         <v>100</v>
       </c>
       <c r="L187">
-        <v>90.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -7716,13 +7724,13 @@
         <v>21</v>
       </c>
       <c r="E188" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="F188" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G188" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H188" t="s">
         <v>17</v>
@@ -7730,14 +7738,11 @@
       <c r="I188" t="s">
         <v>18</v>
       </c>
-      <c r="J188" t="s">
-        <v>189</v>
-      </c>
       <c r="K188">
         <v>100</v>
       </c>
       <c r="L188">
-        <v>90.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -7745,22 +7750,22 @@
         <v>22</v>
       </c>
       <c r="B189">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C189">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D189" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="E189" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="F189" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G189" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H189" t="s">
         <v>17</v>
@@ -7768,14 +7773,11 @@
       <c r="I189" t="s">
         <v>18</v>
       </c>
-      <c r="J189" t="s">
-        <v>191</v>
-      </c>
       <c r="K189">
         <v>100</v>
       </c>
       <c r="L189">
-        <v>90.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -7783,22 +7785,22 @@
         <v>24</v>
       </c>
       <c r="B190">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C190">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="D190" t="s">
         <v>104</v>
       </c>
       <c r="E190" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="F190" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G190" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H190" t="s">
         <v>17</v>
@@ -7806,14 +7808,11 @@
       <c r="I190" t="s">
         <v>18</v>
       </c>
-      <c r="J190" t="s">
-        <v>192</v>
-      </c>
       <c r="K190">
         <v>100</v>
       </c>
       <c r="L190">
-        <v>90.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -7821,22 +7820,22 @@
         <v>26</v>
       </c>
       <c r="B191">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="C191">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="D191" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="E191" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="F191" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G191" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H191" t="s">
         <v>17</v>
@@ -7848,7 +7847,7 @@
         <v>100</v>
       </c>
       <c r="L191">
-        <v>90.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -7859,19 +7858,19 @@
         <v>21</v>
       </c>
       <c r="C192">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D192" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E192" t="s">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="F192" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G192" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H192" t="s">
         <v>17</v>
@@ -7879,11 +7878,14 @@
       <c r="I192" t="s">
         <v>18</v>
       </c>
+      <c r="J192" t="s">
+        <v>192</v>
+      </c>
       <c r="K192">
         <v>100</v>
       </c>
       <c r="L192">
-        <v>55.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -7900,13 +7902,13 @@
         <v>21</v>
       </c>
       <c r="E193" t="s">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="F193" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G193" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H193" t="s">
         <v>17</v>
@@ -7918,7 +7920,7 @@
         <v>100</v>
       </c>
       <c r="L193">
-        <v>55.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -7929,19 +7931,19 @@
         <v>42</v>
       </c>
       <c r="C194">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D194" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="E194" t="s">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="F194" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G194" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H194" t="s">
         <v>17</v>
@@ -7949,11 +7951,14 @@
       <c r="I194" t="s">
         <v>18</v>
       </c>
+      <c r="J194" t="s">
+        <v>193</v>
+      </c>
       <c r="K194">
         <v>100</v>
       </c>
       <c r="L194">
-        <v>55.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -7964,31 +7969,34 @@
         <v>84</v>
       </c>
       <c r="C195">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="D195" t="s">
         <v>104</v>
       </c>
       <c r="E195" t="s">
+        <v>50</v>
+      </c>
+      <c r="F195" t="s">
+        <v>38</v>
+      </c>
+      <c r="G195" t="s">
+        <v>181</v>
+      </c>
+      <c r="H195" t="s">
+        <v>17</v>
+      </c>
+      <c r="I195" t="s">
+        <v>18</v>
+      </c>
+      <c r="J195" t="s">
         <v>194</v>
       </c>
-      <c r="F195" t="s">
-        <v>28</v>
-      </c>
-      <c r="G195" t="s">
-        <v>187</v>
-      </c>
-      <c r="H195" t="s">
-        <v>17</v>
-      </c>
-      <c r="I195" t="s">
-        <v>18</v>
-      </c>
       <c r="K195">
         <v>100</v>
       </c>
       <c r="L195">
-        <v>55.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -7999,19 +8007,19 @@
         <v>900</v>
       </c>
       <c r="C196">
-        <v>534</v>
+        <v>0</v>
       </c>
       <c r="D196" t="s">
-        <v>177</v>
+        <v>21</v>
       </c>
       <c r="E196" t="s">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="F196" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G196" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H196" t="s">
         <v>17</v>
@@ -8023,7 +8031,7 @@
         <v>100</v>
       </c>
       <c r="L196">
-        <v>55.2</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -8031,22 +8039,22 @@
         <v>12</v>
       </c>
       <c r="B197">
-        <v>21</v>
+        <v>930</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D197" t="s">
         <v>21</v>
       </c>
       <c r="E197" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="F197" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G197" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H197" t="s">
         <v>17</v>
@@ -8061,7 +8069,7 @@
         <v>100</v>
       </c>
       <c r="L197">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
@@ -8069,7 +8077,7 @@
         <v>20</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -8078,13 +8086,13 @@
         <v>21</v>
       </c>
       <c r="E198" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="F198" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G198" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H198" t="s">
         <v>17</v>
@@ -8096,7 +8104,7 @@
         <v>100</v>
       </c>
       <c r="L198">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -8104,7 +8112,7 @@
         <v>22</v>
       </c>
       <c r="B199">
-        <v>42</v>
+        <v>1712</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -8113,13 +8121,13 @@
         <v>21</v>
       </c>
       <c r="E199" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="F199" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G199" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H199" t="s">
         <v>17</v>
@@ -8131,7 +8139,7 @@
         <v>100</v>
       </c>
       <c r="L199">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -8139,22 +8147,22 @@
         <v>24</v>
       </c>
       <c r="B200">
-        <v>84</v>
+        <v>3255</v>
       </c>
       <c r="C200">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D200" t="s">
         <v>104</v>
       </c>
       <c r="E200" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="F200" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G200" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H200" t="s">
         <v>17</v>
@@ -8166,7 +8174,7 @@
         <v>100</v>
       </c>
       <c r="L200">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
@@ -8174,7 +8182,7 @@
         <v>26</v>
       </c>
       <c r="B201">
-        <v>900</v>
+        <v>25304</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -8183,13 +8191,13 @@
         <v>21</v>
       </c>
       <c r="E201" t="s">
-        <v>37</v>
+        <v>116</v>
       </c>
       <c r="F201" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G201" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H201" t="s">
         <v>17</v>
@@ -8201,7 +8209,7 @@
         <v>100</v>
       </c>
       <c r="L201">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -8209,22 +8217,22 @@
         <v>12</v>
       </c>
       <c r="B202">
-        <v>21</v>
+        <v>930</v>
       </c>
       <c r="C202">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D202" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="E202" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F202" t="s">
         <v>38</v>
       </c>
       <c r="G202" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H202" t="s">
         <v>17</v>
@@ -8233,13 +8241,13 @@
         <v>18</v>
       </c>
       <c r="J202" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K202">
         <v>100</v>
       </c>
       <c r="L202">
-        <v>12.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -8247,22 +8255,22 @@
         <v>20</v>
       </c>
       <c r="B203">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D203" t="s">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="E203" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F203" t="s">
         <v>38</v>
       </c>
       <c r="G203" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H203" t="s">
         <v>17</v>
@@ -8270,11 +8278,14 @@
       <c r="I203" t="s">
         <v>18</v>
       </c>
+      <c r="J203" t="s">
+        <v>199</v>
+      </c>
       <c r="K203">
         <v>100</v>
       </c>
       <c r="L203">
-        <v>12.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -8282,22 +8293,22 @@
         <v>22</v>
       </c>
       <c r="B204">
-        <v>42</v>
+        <v>1712</v>
       </c>
       <c r="C204">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D204" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E204" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F204" t="s">
         <v>38</v>
       </c>
       <c r="G204" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H204" t="s">
         <v>17</v>
@@ -8306,13 +8317,13 @@
         <v>18</v>
       </c>
       <c r="J204" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K204">
         <v>100</v>
       </c>
       <c r="L204">
-        <v>12.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
@@ -8320,22 +8331,22 @@
         <v>24</v>
       </c>
       <c r="B205">
-        <v>84</v>
+        <v>3255</v>
       </c>
       <c r="C205">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D205" t="s">
         <v>104</v>
       </c>
       <c r="E205" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F205" t="s">
         <v>38</v>
       </c>
       <c r="G205" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H205" t="s">
         <v>17</v>
@@ -8343,14 +8354,11 @@
       <c r="I205" t="s">
         <v>18</v>
       </c>
-      <c r="J205" t="s">
-        <v>200</v>
-      </c>
       <c r="K205">
         <v>100</v>
       </c>
       <c r="L205">
-        <v>12.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -8358,7 +8366,7 @@
         <v>26</v>
       </c>
       <c r="B206">
-        <v>900</v>
+        <v>25304</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -8367,13 +8375,13 @@
         <v>21</v>
       </c>
       <c r="E206" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F206" t="s">
         <v>38</v>
       </c>
       <c r="G206" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H206" t="s">
         <v>17</v>
@@ -8385,7 +8393,7 @@
         <v>100</v>
       </c>
       <c r="L206">
-        <v>12.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
@@ -8396,34 +8404,34 @@
         <v>930</v>
       </c>
       <c r="C207">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D207" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="E207" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F207" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G207" t="s">
+        <v>195</v>
+      </c>
+      <c r="H207" t="s">
+        <v>17</v>
+      </c>
+      <c r="I207" t="s">
+        <v>18</v>
+      </c>
+      <c r="J207" t="s">
         <v>201</v>
       </c>
-      <c r="H207" t="s">
-        <v>17</v>
-      </c>
-      <c r="I207" t="s">
-        <v>18</v>
-      </c>
-      <c r="J207" t="s">
-        <v>202</v>
-      </c>
       <c r="K207">
         <v>100</v>
       </c>
       <c r="L207">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -8434,19 +8442,19 @@
         <v>153</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="E208" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F208" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G208" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H208" t="s">
         <v>17</v>
@@ -8454,11 +8462,14 @@
       <c r="I208" t="s">
         <v>18</v>
       </c>
+      <c r="J208" t="s">
+        <v>202</v>
+      </c>
       <c r="K208">
         <v>100</v>
       </c>
       <c r="L208">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -8469,19 +8480,19 @@
         <v>1712</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D209" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E209" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F209" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G209" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H209" t="s">
         <v>17</v>
@@ -8493,7 +8504,7 @@
         <v>100</v>
       </c>
       <c r="L209">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -8504,19 +8515,19 @@
         <v>3255</v>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D210" t="s">
         <v>104</v>
       </c>
       <c r="E210" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F210" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G210" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H210" t="s">
         <v>17</v>
@@ -8528,7 +8539,7 @@
         <v>100</v>
       </c>
       <c r="L210">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -8545,13 +8556,13 @@
         <v>21</v>
       </c>
       <c r="E211" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="F211" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G211" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H211" t="s">
         <v>17</v>
@@ -8563,7 +8574,7 @@
         <v>100</v>
       </c>
       <c r="L211">
-        <v>0</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -8571,22 +8582,22 @@
         <v>12</v>
       </c>
       <c r="B212">
-        <v>930</v>
+        <v>4</v>
       </c>
       <c r="C212">
+        <v>6</v>
+      </c>
+      <c r="D212" t="s">
+        <v>161</v>
+      </c>
+      <c r="E212" t="s">
+        <v>203</v>
+      </c>
+      <c r="F212" t="s">
         <v>15</v>
       </c>
-      <c r="D212" t="s">
-        <v>174</v>
-      </c>
-      <c r="E212" t="s">
-        <v>37</v>
-      </c>
-      <c r="F212" t="s">
-        <v>38</v>
-      </c>
       <c r="G212" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H212" t="s">
         <v>17</v>
@@ -8595,13 +8606,13 @@
         <v>18</v>
       </c>
       <c r="J212" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K212">
         <v>100</v>
       </c>
       <c r="L212">
-        <v>0.9</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
@@ -8609,37 +8620,34 @@
         <v>20</v>
       </c>
       <c r="B213">
-        <v>153</v>
+        <v>2</v>
       </c>
       <c r="C213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D213" t="s">
+        <v>113</v>
+      </c>
+      <c r="E213" t="s">
+        <v>203</v>
+      </c>
+      <c r="F213" t="s">
+        <v>15</v>
+      </c>
+      <c r="G213" t="s">
         <v>204</v>
       </c>
-      <c r="E213" t="s">
-        <v>37</v>
-      </c>
-      <c r="F213" t="s">
-        <v>38</v>
-      </c>
-      <c r="G213" t="s">
-        <v>201</v>
-      </c>
       <c r="H213" t="s">
         <v>17</v>
       </c>
       <c r="I213" t="s">
         <v>18</v>
       </c>
-      <c r="J213" t="s">
-        <v>205</v>
-      </c>
       <c r="K213">
         <v>100</v>
       </c>
       <c r="L213">
-        <v>0.9</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
@@ -8647,22 +8655,22 @@
         <v>22</v>
       </c>
       <c r="B214">
-        <v>1712</v>
+        <v>9</v>
       </c>
       <c r="C214">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D214" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E214" t="s">
-        <v>37</v>
+        <v>203</v>
       </c>
       <c r="F214" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G214" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H214" t="s">
         <v>17</v>
@@ -8670,14 +8678,11 @@
       <c r="I214" t="s">
         <v>18</v>
       </c>
-      <c r="J214" t="s">
-        <v>206</v>
-      </c>
       <c r="K214">
         <v>100</v>
       </c>
       <c r="L214">
-        <v>0.9</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
@@ -8685,22 +8690,22 @@
         <v>24</v>
       </c>
       <c r="B215">
-        <v>3255</v>
+        <v>20</v>
       </c>
       <c r="C215">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D215" t="s">
         <v>104</v>
       </c>
       <c r="E215" t="s">
-        <v>37</v>
+        <v>203</v>
       </c>
       <c r="F215" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G215" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H215" t="s">
         <v>17</v>
@@ -8712,7 +8717,7 @@
         <v>100</v>
       </c>
       <c r="L215">
-        <v>0.9</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
@@ -8720,22 +8725,22 @@
         <v>26</v>
       </c>
       <c r="B216">
-        <v>25304</v>
+        <v>346</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D216" t="s">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="E216" t="s">
-        <v>37</v>
+        <v>203</v>
       </c>
       <c r="F216" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G216" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H216" t="s">
         <v>17</v>
@@ -8747,7 +8752,7 @@
         <v>100</v>
       </c>
       <c r="L216">
-        <v>0.9</v>
+        <v>75.599999999999994</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
@@ -8755,22 +8760,22 @@
         <v>12</v>
       </c>
       <c r="B217">
-        <v>930</v>
+        <v>11</v>
       </c>
       <c r="C217">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="E217" t="s">
-        <v>50</v>
+        <v>207</v>
       </c>
       <c r="F217" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G217" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H217" t="s">
         <v>17</v>
@@ -8778,14 +8783,11 @@
       <c r="I217" t="s">
         <v>18</v>
       </c>
-      <c r="J217" t="s">
-        <v>207</v>
-      </c>
       <c r="K217">
         <v>100</v>
       </c>
       <c r="L217">
-        <v>2.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
@@ -8793,37 +8795,34 @@
         <v>20</v>
       </c>
       <c r="B218">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D218" t="s">
+        <v>25</v>
+      </c>
+      <c r="E218" t="s">
+        <v>207</v>
+      </c>
+      <c r="F218" t="s">
+        <v>28</v>
+      </c>
+      <c r="G218" t="s">
         <v>204</v>
       </c>
-      <c r="E218" t="s">
-        <v>50</v>
-      </c>
-      <c r="F218" t="s">
-        <v>38</v>
-      </c>
-      <c r="G218" t="s">
-        <v>201</v>
-      </c>
       <c r="H218" t="s">
         <v>17</v>
       </c>
       <c r="I218" t="s">
         <v>18</v>
       </c>
-      <c r="J218" t="s">
-        <v>208</v>
-      </c>
       <c r="K218">
         <v>100</v>
       </c>
       <c r="L218">
-        <v>2.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
@@ -8831,22 +8830,22 @@
         <v>22</v>
       </c>
       <c r="B219">
-        <v>1712</v>
+        <v>21</v>
       </c>
       <c r="C219">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D219" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E219" t="s">
-        <v>50</v>
+        <v>207</v>
       </c>
       <c r="F219" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G219" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H219" t="s">
         <v>17</v>
@@ -8858,7 +8857,7 @@
         <v>100</v>
       </c>
       <c r="L219">
-        <v>2.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
@@ -8866,22 +8865,22 @@
         <v>24</v>
       </c>
       <c r="B220">
-        <v>3255</v>
+        <v>50</v>
       </c>
       <c r="C220">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="D220" t="s">
-        <v>104</v>
+        <v>208</v>
       </c>
       <c r="E220" t="s">
-        <v>50</v>
+        <v>207</v>
       </c>
       <c r="F220" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G220" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H220" t="s">
         <v>17</v>
@@ -8893,7 +8892,7 @@
         <v>100</v>
       </c>
       <c r="L220">
-        <v>2.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
@@ -8901,22 +8900,22 @@
         <v>26</v>
       </c>
       <c r="B221">
-        <v>25304</v>
+        <v>854</v>
       </c>
       <c r="C221">
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="D221" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="E221" t="s">
-        <v>50</v>
+        <v>207</v>
       </c>
       <c r="F221" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G221" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H221" t="s">
         <v>17</v>
@@ -8928,7 +8927,7 @@
         <v>100</v>
       </c>
       <c r="L221">
-        <v>2.4</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
@@ -8936,37 +8935,37 @@
         <v>12</v>
       </c>
       <c r="B222">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C222">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="E222" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="F222" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G222" t="s">
+        <v>204</v>
+      </c>
+      <c r="H222" t="s">
+        <v>17</v>
+      </c>
+      <c r="I222" t="s">
+        <v>18</v>
+      </c>
+      <c r="J222" t="s">
         <v>210</v>
       </c>
-      <c r="H222" t="s">
-        <v>17</v>
-      </c>
-      <c r="I222" t="s">
-        <v>18</v>
-      </c>
-      <c r="J222" t="s">
-        <v>211</v>
-      </c>
       <c r="K222">
         <v>100</v>
       </c>
       <c r="L222">
-        <v>75.599999999999994</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
@@ -8974,22 +8973,22 @@
         <v>20</v>
       </c>
       <c r="B223">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D223" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="E223" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="F223" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G223" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H223" t="s">
         <v>17</v>
@@ -9001,7 +9000,7 @@
         <v>100</v>
       </c>
       <c r="L223">
-        <v>75.599999999999994</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
@@ -9009,22 +9008,22 @@
         <v>22</v>
       </c>
       <c r="B224">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C224">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="E224" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="F224" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G224" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H224" t="s">
         <v>17</v>
@@ -9032,11 +9031,14 @@
       <c r="I224" t="s">
         <v>18</v>
       </c>
+      <c r="J224" t="s">
+        <v>212</v>
+      </c>
       <c r="K224">
         <v>100</v>
       </c>
       <c r="L224">
-        <v>75.599999999999994</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
@@ -9044,22 +9046,22 @@
         <v>24</v>
       </c>
       <c r="B225">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C225">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D225" t="s">
         <v>104</v>
       </c>
       <c r="E225" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="F225" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G225" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H225" t="s">
         <v>17</v>
@@ -9067,11 +9069,14 @@
       <c r="I225" t="s">
         <v>18</v>
       </c>
+      <c r="J225" t="s">
+        <v>213</v>
+      </c>
       <c r="K225">
         <v>100</v>
       </c>
       <c r="L225">
-        <v>75.599999999999994</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
@@ -9079,22 +9084,22 @@
         <v>26</v>
       </c>
       <c r="B226">
-        <v>346</v>
+        <v>720</v>
       </c>
       <c r="C226">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="D226" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="E226" t="s">
-        <v>209</v>
+        <v>37</v>
       </c>
       <c r="F226" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G226" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="H226" t="s">
         <v>17</v>
@@ -9106,7 +9111,7 @@
         <v>100</v>
       </c>
       <c r="L226">
-        <v>75.599999999999994</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
@@ -9114,22 +9119,22 @@
         <v>12</v>
       </c>
       <c r="B227">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C227">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D227" t="s">
-        <v>70</v>
+        <v>214</v>
       </c>
       <c r="E227" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F227" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G227" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H227" t="s">
         <v>17</v>
@@ -9137,11 +9142,14 @@
       <c r="I227" t="s">
         <v>18</v>
       </c>
+      <c r="J227" t="s">
+        <v>217</v>
+      </c>
       <c r="K227">
         <v>100</v>
       </c>
       <c r="L227">
-        <v>52.8</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
@@ -9149,22 +9157,22 @@
         <v>20</v>
       </c>
       <c r="B228">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E228" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F228" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G228" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H228" t="s">
         <v>17</v>
@@ -9176,7 +9184,7 @@
         <v>100</v>
       </c>
       <c r="L228">
-        <v>52.8</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
@@ -9184,22 +9192,22 @@
         <v>22</v>
       </c>
       <c r="B229">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C229">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D229" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="E229" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F229" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G229" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H229" t="s">
         <v>17</v>
@@ -9211,7 +9219,7 @@
         <v>100</v>
       </c>
       <c r="L229">
-        <v>52.8</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
@@ -9219,22 +9227,22 @@
         <v>24</v>
       </c>
       <c r="B230">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C230">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D230" t="s">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="E230" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F230" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G230" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H230" t="s">
         <v>17</v>
@@ -9246,7 +9254,7 @@
         <v>100</v>
       </c>
       <c r="L230">
-        <v>52.8</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
@@ -9254,22 +9262,22 @@
         <v>26</v>
       </c>
       <c r="B231">
-        <v>854</v>
+        <v>209</v>
       </c>
       <c r="C231">
-        <v>602</v>
+        <v>84</v>
       </c>
       <c r="D231" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="E231" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F231" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G231" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H231" t="s">
         <v>17</v>
@@ -9281,7 +9289,7 @@
         <v>100</v>
       </c>
       <c r="L231">
-        <v>52.8</v>
+        <v>90.9</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
@@ -9289,22 +9297,22 @@
         <v>12</v>
       </c>
       <c r="B232">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C232">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D232" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E232" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="F232" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G232" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H232" t="s">
         <v>17</v>
@@ -9312,14 +9320,11 @@
       <c r="I232" t="s">
         <v>18</v>
       </c>
-      <c r="J232" t="s">
-        <v>216</v>
-      </c>
       <c r="K232">
         <v>100</v>
       </c>
       <c r="L232">
-        <v>4.7</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
@@ -9327,22 +9332,22 @@
         <v>20</v>
       </c>
       <c r="B233">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="E233" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="F233" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G233" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H233" t="s">
         <v>17</v>
@@ -9354,7 +9359,7 @@
         <v>100</v>
       </c>
       <c r="L233">
-        <v>4.7</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
@@ -9362,22 +9367,22 @@
         <v>22</v>
       </c>
       <c r="B234">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D234" t="s">
-        <v>217</v>
+        <v>105</v>
       </c>
       <c r="E234" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="F234" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G234" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H234" t="s">
         <v>17</v>
@@ -9385,14 +9390,11 @@
       <c r="I234" t="s">
         <v>18</v>
       </c>
-      <c r="J234" t="s">
-        <v>218</v>
-      </c>
       <c r="K234">
         <v>100</v>
       </c>
       <c r="L234">
-        <v>4.7</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
@@ -9400,22 +9402,22 @@
         <v>24</v>
       </c>
       <c r="B235">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C235">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="D235" t="s">
         <v>104</v>
       </c>
       <c r="E235" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="F235" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G235" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H235" t="s">
         <v>17</v>
@@ -9423,14 +9425,11 @@
       <c r="I235" t="s">
         <v>18</v>
       </c>
-      <c r="J235" t="s">
-        <v>219</v>
-      </c>
       <c r="K235">
         <v>100</v>
       </c>
       <c r="L235">
-        <v>4.7</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
@@ -9438,22 +9437,22 @@
         <v>26</v>
       </c>
       <c r="B236">
+        <v>991</v>
+      </c>
+      <c r="C236">
         <v>720</v>
       </c>
-      <c r="C236">
-        <v>0</v>
-      </c>
       <c r="D236" t="s">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="E236" t="s">
-        <v>37</v>
+        <v>219</v>
       </c>
       <c r="F236" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G236" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="H236" t="s">
         <v>17</v>
@@ -9465,7 +9464,7 @@
         <v>100</v>
       </c>
       <c r="L236">
-        <v>4.7</v>
+        <v>68.2</v>
       </c>
     </row>
   </sheetData>
